--- a/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
+++ b/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R6254ba9883ae44fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="R50f6f97b775c44e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="Ra1cf1594e9b14def"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="Rdefb00047cb74d33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R62a1d3664c26424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="Rc35ffce7be104722"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="R42b7c8c70d074d73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="Ra8e39f07cc504b65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R149a1f881fff4665"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R96ccad1547524a67"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
+++ b/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="Rc35ffce7be104722"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="R42b7c8c70d074d73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="Ra8e39f07cc504b65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R149a1f881fff4665"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R96ccad1547524a67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="Rc679f67b560e4ffa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="Rb2d627211118405c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R4063fa3306954475"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R05e3b438968246d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R7533fcaaffe34f81"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
+++ b/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="Rc679f67b560e4ffa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="Rb2d627211118405c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R4063fa3306954475"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R05e3b438968246d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R7533fcaaffe34f81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R5a2e3f56cee145ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="R58e5f50aa2454e62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="Rc2496c2bf8cc49a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R54b2e9fcfad945f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="Re8dbaa1ba799499c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
+++ b/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R5a2e3f56cee145ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="R58e5f50aa2454e62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="Rc2496c2bf8cc49a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R54b2e9fcfad945f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="Re8dbaa1ba799499c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="Rf7670484217e432d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="Rd20e8f95313042f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R420068a996c9489c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="Rf10aa64b72534c5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R2a1d920d79294623"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
+++ b/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="Rf7670484217e432d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="Rd20e8f95313042f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R420068a996c9489c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="Rf10aa64b72534c5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R2a1d920d79294623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R8968d7db937943ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="Ra819a76505d24971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R75b437eeff1b4e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R4125d5cfc4984ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="Rc20790101dbe4c57"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -248,7 +248,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="3" t="str">
-        <x:v>招生主体数</x:v>
+        <x:v>公办招生主体数</x:v>
       </x:c>
       <x:c r="B2" s="3" t="n">
         <x:v>42</x:v>
@@ -259,7 +259,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="3" t="str">
-        <x:v>拆分园区/分园数</x:v>
+        <x:v>公办园区/分园点位数</x:v>
       </x:c>
       <x:c r="B3" s="3" t="n">
         <x:v>81</x:v>
@@ -270,45 +270,67 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="3" t="str">
-        <x:v>小班计划合计</x:v>
+        <x:v>民办/私立点位数</x:v>
       </x:c>
       <x:c r="B4" s="3" t="n">
-        <x:v>149</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C4" s="3" t="str">
-        <x:v>PDF计划班级数合计。</x:v>
+        <x:v>来自徐汇区民办幼儿园名单公开资料；招生条件、收费和名额需电话确认。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="str">
-        <x:v>托班明确班级数合计</x:v>
+        <x:v>全部园区/点位数</x:v>
       </x:c>
       <x:c r="B5" s="3" t="n">
-        <x:v>71</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C5" s="3" t="str">
-        <x:v>不含混龄式招生。</x:v>
+        <x:v>公办园区点位 + 民办/私立点位。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="str">
-        <x:v>混龄式招生主体数</x:v>
+        <x:v>小班计划合计</x:v>
       </x:c>
       <x:c r="B6" s="3" t="n">
-        <x:v>4</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C6" s="3" t="str">
-        <x:v>混龄式招生不直接等同托班班级数。</x:v>
+        <x:v>PDF计划班级数合计。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="str">
+        <x:v>托班明确班级数合计</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>不含混龄式招生。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="3" t="str">
+        <x:v>混龄式招生主体数</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>混龄式招生不直接等同托班班级数。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="3" t="str">
         <x:v>重点核验</x:v>
       </x:c>
-      <x:c r="B7" s="3" t="str">
+      <x:c r="B9" s="3" t="str">
         <x:v>汇星北园、复旦大学附属徐汇实验幼儿园</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="str">
+      <x:c r="C9" s="3" t="str">
         <x:v>公开资料出现地址/合并后的园部安排差异，择园前应电话确认。</x:v>
       </x:c>
     </x:row>
@@ -1538,17 +1560,21 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="6.010000228881836" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22.700000762939453" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="17.790000915527344" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17.790000915527344" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="43.560001373291016" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10.180000305175781" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="10.180000305175781" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="63.189998626708984" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="7.980000019073486" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="43.560001373291016" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="43.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.199999809265137" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.199999809265137" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22.700000762939453" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17.790000915527344" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17.790000915527344" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="43.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="10.180000305175781" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.180000305175781" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="63.189998626708984" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="43.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="43.560001373291016" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1556,42 +1582,50 @@
         <x:v>编号</x:v>
       </x:c>
       <x:c r="B1" s="2" t="str">
+        <x:v>性质</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="str">
+        <x:v>级别</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="str">
         <x:v>幼儿园</x:v>
       </x:c>
-      <x:c r="C1" s="2" t="str">
+      <x:c r="E1" s="2" t="str">
         <x:v>片区</x:v>
       </x:c>
-      <x:c r="D1" s="2" t="str">
+      <x:c r="F1" s="2" t="str">
         <x:v>园区/分园</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="str">
+      <x:c r="G1" s="2" t="str">
         <x:v>地址</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="str">
+      <x:c r="H1" s="2" t="str">
         <x:v>高德搜索链接</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="str">
+      <x:c r="I1" s="2" t="str">
+        <x:v>联系电话</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="str">
         <x:v>托班计划</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="str">
+      <x:c r="K1" s="2" t="str">
         <x:v>小班计划</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="str">
+      <x:c r="L1" s="2" t="str">
         <x:v>对口居委/招生范围</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="str">
+      <x:c r="M1" s="2" t="str">
+        <x:v>招生类型</x:v>
+      </x:c>
+      <x:c r="N1" s="2" t="str">
         <x:v>置信度</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="str">
+      <x:c r="O1" s="2" t="str">
         <x:v>备注</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="str">
+      <x:c r="P1" s="2" t="str">
         <x:v>主要来源</x:v>
       </x:c>
-      <x:c r="M1" s="2"/>
-      <x:c r="N1" s="2"/>
-      <x:c r="O1" s="2"/>
-      <x:c r="P1" s="2"/>
       <x:c r="Q1" s="2"/>
       <x:c r="R1" s="2"/>
       <x:c r="S1" s="2"/>
@@ -1608,34 +1642,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D2" s="3" t="str">
         <x:v>襄阳南路第一幼儿园</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="E2" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="F2" s="3" t="str">
         <x:v>复中园</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="G2" s="3" t="str">
         <x:v>复兴中路1260弄2号</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="H2" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A4%8D%E4%B8%AD%E5%9B%AD%20%E5%A4%8D%E5%85%B4%E4%B8%AD%E8%B7%AF1260%E5%BC%842%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="I2" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="n">
+      <x:c r="K2" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="str">
+      <x:c r="L2" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K2" s="3" t="str"/>
-      <x:c r="L2" s="3" t="str">
+      <x:c r="M2" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N2" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O2" s="3" t="str"/>
+      <x:c r="P2" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1644,34 +1690,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="str">
         <x:v>襄阳南路第一幼儿园</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="str">
+      <x:c r="E3" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="F3" s="3" t="str">
         <x:v>南园</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="G3" s="3" t="str">
         <x:v>襄阳南路317号</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="str">
+      <x:c r="H3" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF317%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="str">
+      <x:c r="I3" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="n">
+      <x:c r="K3" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I3" s="3" t="str">
+      <x:c r="L3" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="J3" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="str"/>
-      <x:c r="L3" s="3" t="str">
+      <x:c r="M3" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N3" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O3" s="3" t="str"/>
+      <x:c r="P3" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1680,34 +1738,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D4" s="3" t="str">
         <x:v>襄阳南路第一幼儿园</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="E4" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="F4" s="3" t="str">
         <x:v>陕南园</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="G4" s="3" t="str">
         <x:v>陕西南路540号</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="str">
+      <x:c r="H4" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%99%95%E5%8D%97%E5%9B%AD%20%E9%99%95%E8%A5%BF%E5%8D%97%E8%B7%AF540%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="str">
+      <x:c r="I4" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J4" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H4" s="3" t="n">
+      <x:c r="K4" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I4" s="3" t="str">
+      <x:c r="L4" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="J4" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K4" s="3" t="str"/>
-      <x:c r="L4" s="3" t="str">
+      <x:c r="M4" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N4" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O4" s="3" t="str"/>
+      <x:c r="P4" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1716,34 +1786,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="str">
         <x:v>襄阳南路第一幼儿园</x:v>
       </x:c>
-      <x:c r="C5" s="3" t="str">
+      <x:c r="E5" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="D5" s="3" t="str">
+      <x:c r="F5" s="3" t="str">
         <x:v>北园</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="str">
+      <x:c r="G5" s="3" t="str">
         <x:v>襄阳南路207号</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="str">
+      <x:c r="H5" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF207%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="str">
+      <x:c r="I5" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J5" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H5" s="3" t="n">
+      <x:c r="K5" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I5" s="3" t="str">
+      <x:c r="L5" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="J5" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K5" s="3" t="str"/>
-      <x:c r="L5" s="3" t="str">
+      <x:c r="M5" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N5" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O5" s="3" t="str"/>
+      <x:c r="P5" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1752,34 +1834,46 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D6" s="3" t="str">
         <x:v>五原路幼儿园</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="str">
+      <x:c r="E6" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="str">
+      <x:c r="F6" s="3" t="str">
         <x:v>永嘉园</x:v>
       </x:c>
-      <x:c r="E6" s="3" t="str">
+      <x:c r="G6" s="3" t="str">
         <x:v>永嘉路420号</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="str">
+      <x:c r="H6" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BA%94%E5%8E%9F%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%B0%B8%E5%98%89%E5%9B%AD%20%E6%B0%B8%E5%98%89%E8%B7%AF420%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="str">
+      <x:c r="I6" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J6" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H6" s="3" t="n">
+      <x:c r="K6" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I6" s="3" t="str">
+      <x:c r="L6" s="3" t="str">
         <x:v>上海新村、东湖、金波、延庆、陕新、新乐、复襄、淮海、安福、春华、淮中、建岳、太原、永太、永嘉新村、复永、兴武、华康、武康</x:v>
       </x:c>
-      <x:c r="J6" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K6" s="3" t="str"/>
-      <x:c r="L6" s="3" t="str">
+      <x:c r="M6" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N6" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O6" s="3" t="str"/>
+      <x:c r="P6" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1788,34 +1882,46 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D7" s="3" t="str">
         <x:v>五原路幼儿园</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="str">
+      <x:c r="E7" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="D7" s="3" t="str">
+      <x:c r="F7" s="3" t="str">
         <x:v>武康园</x:v>
       </x:c>
-      <x:c r="E7" s="3" t="str">
+      <x:c r="G7" s="3" t="str">
         <x:v>五原路400号</x:v>
       </x:c>
-      <x:c r="F7" s="3" t="str">
+      <x:c r="H7" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BA%94%E5%8E%9F%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%AD%A6%E5%BA%B7%E5%9B%AD%20%E4%BA%94%E5%8E%9F%E8%B7%AF400%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="str">
+      <x:c r="I7" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J7" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H7" s="3" t="n">
+      <x:c r="K7" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I7" s="3" t="str">
+      <x:c r="L7" s="3" t="str">
         <x:v>上海新村、东湖、金波、延庆、陕新、新乐、复襄、淮海、安福、春华、淮中、建岳、太原、永太、永嘉新村、复永、兴武、华康、武康</x:v>
       </x:c>
-      <x:c r="J7" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K7" s="3" t="str"/>
-      <x:c r="L7" s="3" t="str">
+      <x:c r="M7" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N7" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O7" s="3" t="str"/>
+      <x:c r="P7" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1824,34 +1930,46 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D8" s="3" t="str">
         <x:v>五原路幼儿园</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="str">
+      <x:c r="E8" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="D8" s="3" t="str">
+      <x:c r="F8" s="3" t="str">
         <x:v>兴国园</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="str">
+      <x:c r="G8" s="3" t="str">
         <x:v>武康路280弄24号</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="str">
+      <x:c r="H8" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BA%94%E5%8E%9F%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%85%B4%E5%9B%BD%E5%9B%AD%20%E6%AD%A6%E5%BA%B7%E8%B7%AF280%E5%BC%8424%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="str">
+      <x:c r="I8" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J8" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="n">
+      <x:c r="K8" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="str">
+      <x:c r="L8" s="3" t="str">
         <x:v>上海新村、东湖、金波、延庆、陕新、新乐、复襄、淮海、安福、春华、淮中、建岳、太原、永太、永嘉新村、复永、兴武、华康、武康</x:v>
       </x:c>
-      <x:c r="J8" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K8" s="3" t="str"/>
-      <x:c r="L8" s="3" t="str">
+      <x:c r="M8" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N8" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O8" s="3" t="str"/>
+      <x:c r="P8" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1860,34 +1978,46 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D9" s="3" t="str">
         <x:v>汇星幼儿园</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="str">
+      <x:c r="E9" s="3" t="str">
         <x:v>徐家汇/天平</x:v>
       </x:c>
-      <x:c r="D9" s="3" t="str">
+      <x:c r="F9" s="3" t="str">
         <x:v>南园</x:v>
       </x:c>
-      <x:c r="E9" s="3" t="str">
+      <x:c r="G9" s="3" t="str">
         <x:v>宛平南路19弄3号</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="str">
+      <x:c r="H9" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E6%98%9F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E5%AE%9B%E5%B9%B3%E5%8D%97%E8%B7%AF19%E5%BC%843%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="3" t="n">
+      <x:c r="I9" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I9" s="3" t="str">
+      <x:c r="L9" s="3" t="str">
         <x:v>天平、高安、康平、吴兴、宛平、余庆、广元、安亭、徐汇新村、张家浜肇谨、零陵、科汇、启明、沈马、王家堂、南赵巷、殷家角、汇翠、名园、德昌</x:v>
       </x:c>
-      <x:c r="J9" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K9" s="3" t="str"/>
-      <x:c r="L9" s="3" t="str">
+      <x:c r="M9" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N9" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O9" s="3" t="str"/>
+      <x:c r="P9" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1896,36 +2026,48 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D10" s="3" t="str">
         <x:v>汇星幼儿园</x:v>
       </x:c>
-      <x:c r="C10" s="3" t="str">
+      <x:c r="E10" s="3" t="str">
         <x:v>徐家汇/天平</x:v>
       </x:c>
-      <x:c r="D10" s="3" t="str">
+      <x:c r="F10" s="3" t="str">
         <x:v>北园</x:v>
       </x:c>
-      <x:c r="E10" s="3" t="str">
+      <x:c r="G10" s="3" t="str">
         <x:v>康平路200号</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="str">
+      <x:c r="H10" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E6%98%9F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E5%BA%B7%E5%B9%B3%E8%B7%AF200%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="3" t="n">
+      <x:c r="I10" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K10" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I10" s="3" t="str">
+      <x:c r="L10" s="3" t="str">
         <x:v>天平、高安、康平、吴兴、宛平、余庆、广元、安亭、徐汇新村、张家浜肇谨、零陵、科汇、启明、沈马、王家堂、南赵巷、殷家角、汇翠、名园、德昌</x:v>
       </x:c>
-      <x:c r="J10" s="3" t="str">
+      <x:c r="M10" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N10" s="3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="K10" s="3" t="str">
+      <x:c r="O10" s="3" t="str">
         <x:v>2024公办名单写康平路200号；2024招生简章/部分旧资料写华山路1815号，建议电话确认当前小班实际园区。</x:v>
       </x:c>
-      <x:c r="L10" s="3" t="str">
+      <x:c r="P10" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1934,34 +2076,46 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B11" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D11" s="3" t="str">
         <x:v>乐山幼儿园</x:v>
       </x:c>
-      <x:c r="C11" s="3" t="str">
+      <x:c r="E11" s="3" t="str">
         <x:v>徐家汇/交大</x:v>
       </x:c>
-      <x:c r="D11" s="3" t="str">
+      <x:c r="F11" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E11" s="3" t="str">
+      <x:c r="G11" s="3" t="str">
         <x:v>乐山路18号</x:v>
       </x:c>
-      <x:c r="F11" s="3" t="str">
+      <x:c r="H11" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%90%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B9%90%E5%B1%B1%E8%B7%AF18%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G11" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="3" t="n">
+      <x:c r="I11" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I11" s="3" t="str">
+      <x:c r="L11" s="3" t="str">
         <x:v>乐山一村、乐山二三村、乐山四五村、乐山六七村、乐山八九村、文定、汇站、交大、豪庭</x:v>
       </x:c>
-      <x:c r="J11" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K11" s="3" t="str"/>
-      <x:c r="L11" s="3" t="str">
+      <x:c r="M11" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N11" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O11" s="3" t="str"/>
+      <x:c r="P11" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1970,34 +2124,46 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B12" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
         <x:v>汇家幼儿园</x:v>
       </x:c>
-      <x:c r="C12" s="3" t="str">
+      <x:c r="E12" s="3" t="str">
         <x:v>徐家汇/虹桥路</x:v>
       </x:c>
-      <x:c r="D12" s="3" t="str">
+      <x:c r="F12" s="3" t="str">
         <x:v>北园</x:v>
       </x:c>
-      <x:c r="E12" s="3" t="str">
+      <x:c r="G12" s="3" t="str">
         <x:v>番禺路800弄24号</x:v>
       </x:c>
-      <x:c r="F12" s="3" t="str">
+      <x:c r="H12" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%AE%B6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E7%95%AA%E7%A6%BA%E8%B7%AF800%E5%BC%8424%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G12" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="3" t="n">
+      <x:c r="I12" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I12" s="3" t="str">
+      <x:c r="L12" s="3" t="str">
         <x:v>番禺、南丹、柿子湾、潘家宅、陈家宅、虹二、虹交、西塘、东塘</x:v>
       </x:c>
-      <x:c r="J12" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K12" s="3" t="str"/>
-      <x:c r="L12" s="3" t="str">
+      <x:c r="M12" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N12" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O12" s="3" t="str"/>
+      <x:c r="P12" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2006,34 +2172,46 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
         <x:v>汇家幼儿园</x:v>
       </x:c>
-      <x:c r="C13" s="3" t="str">
+      <x:c r="E13" s="3" t="str">
         <x:v>徐家汇/虹桥路</x:v>
       </x:c>
-      <x:c r="D13" s="3" t="str">
+      <x:c r="F13" s="3" t="str">
         <x:v>南园</x:v>
       </x:c>
-      <x:c r="E13" s="3" t="str">
+      <x:c r="G13" s="3" t="str">
         <x:v>番禺路1188号</x:v>
       </x:c>
-      <x:c r="F13" s="3" t="str">
+      <x:c r="H13" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%AE%B6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E7%95%AA%E7%A6%BA%E8%B7%AF1188%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G13" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="3" t="n">
+      <x:c r="I13" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K13" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I13" s="3" t="str">
+      <x:c r="L13" s="3" t="str">
         <x:v>番禺、南丹、柿子湾、潘家宅、陈家宅、虹二、虹交、西塘、东塘</x:v>
       </x:c>
-      <x:c r="J13" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K13" s="3" t="str"/>
-      <x:c r="L13" s="3" t="str">
+      <x:c r="M13" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N13" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O13" s="3" t="str"/>
+      <x:c r="P13" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2042,34 +2220,46 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B14" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
         <x:v>枫林幼儿园</x:v>
       </x:c>
-      <x:c r="C14" s="3" t="str">
+      <x:c r="E14" s="3" t="str">
         <x:v>枫林/斜土</x:v>
       </x:c>
-      <x:c r="D14" s="3" t="str">
+      <x:c r="F14" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E14" s="3" t="str">
+      <x:c r="G14" s="3" t="str">
         <x:v>小木桥路440弄30号</x:v>
       </x:c>
-      <x:c r="F14" s="3" t="str">
+      <x:c r="H14" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%AB%E6%9E%97%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%B0%8F%E6%9C%A8%E6%A1%A5%E8%B7%AF440%E5%BC%8430%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G14" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I14" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K14" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L14" s="3" t="str">
         <x:v>日新、日二、日五、日六第一、日六第二、大三、大四、康巨、茶陵、景泰、恒益、西木南、西木北、江南</x:v>
       </x:c>
-      <x:c r="J14" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K14" s="3" t="str"/>
-      <x:c r="L14" s="3" t="str">
+      <x:c r="M14" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O14" s="3" t="str"/>
+      <x:c r="P14" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2078,36 +2268,48 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="str">
         <x:v>复旦大学附属徐汇实验幼儿园</x:v>
       </x:c>
-      <x:c r="C15" s="3" t="str">
+      <x:c r="E15" s="3" t="str">
         <x:v>枫林/斜土</x:v>
       </x:c>
-      <x:c r="D15" s="3" t="str">
+      <x:c r="F15" s="3" t="str">
         <x:v>托小班部</x:v>
       </x:c>
-      <x:c r="E15" s="3" t="str">
+      <x:c r="G15" s="3" t="str">
         <x:v>平江路17号</x:v>
       </x:c>
-      <x:c r="F15" s="3" t="str">
+      <x:c r="H15" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%A4%8D%E6%97%A6%E5%A4%A7%E5%AD%A6%E9%99%84%E5%B1%9E%E5%BE%90%E6%B1%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%89%98%E5%B0%8F%E7%8F%AD%E9%83%A8%20%E5%B9%B3%E6%B1%9F%E8%B7%AF17%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G15" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="3" t="n">
+      <x:c r="I15" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J15" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K15" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I15" s="3" t="str">
+      <x:c r="L15" s="3" t="str">
         <x:v>平江、肇一、上影、日七、大五、医清、四季园、肇清、医学院</x:v>
       </x:c>
-      <x:c r="J15" s="3" t="str">
+      <x:c r="M15" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N15" s="3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="K15" s="3" t="str">
+      <x:c r="O15" s="3" t="str">
         <x:v>2024年7月由原平江路幼儿园与原复旦大学医学院幼儿园合并组建；2025/公开资料显示新小班启用平江路32号，需确认2026实际安排。</x:v>
       </x:c>
-      <x:c r="L15" s="3" t="str">
+      <x:c r="P15" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；复旦附属徐汇实验幼儿园公开资料/上哪学/021school；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2116,36 +2318,48 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D16" s="3" t="str">
         <x:v>复旦大学附属徐汇实验幼儿园</x:v>
       </x:c>
-      <x:c r="C16" s="3" t="str">
+      <x:c r="E16" s="3" t="str">
         <x:v>枫林/斜土</x:v>
       </x:c>
-      <x:c r="D16" s="3" t="str">
+      <x:c r="F16" s="3" t="str">
         <x:v>中大班部/新小班候选</x:v>
       </x:c>
-      <x:c r="E16" s="3" t="str">
+      <x:c r="G16" s="3" t="str">
         <x:v>平江路32号</x:v>
       </x:c>
-      <x:c r="F16" s="3" t="str">
+      <x:c r="H16" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%A4%8D%E6%97%A6%E5%A4%A7%E5%AD%A6%E9%99%84%E5%B1%9E%E5%BE%90%E6%B1%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%AD%E5%A4%A7%E7%8F%AD%E9%83%A8%2F%E6%96%B0%E5%B0%8F%E7%8F%AD%E5%80%99%E9%80%89%20%E5%B9%B3%E6%B1%9F%E8%B7%AF32%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G16" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="3" t="n">
+      <x:c r="I16" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K16" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I16" s="3" t="str">
+      <x:c r="L16" s="3" t="str">
         <x:v>平江、肇一、上影、日七、大五、医清、四季园、肇清、医学院</x:v>
       </x:c>
-      <x:c r="J16" s="3" t="str">
+      <x:c r="M16" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N16" s="3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="K16" s="3" t="str">
+      <x:c r="O16" s="3" t="str">
         <x:v>公开资料显示办学地址为平江路32号、17号；原复旦医学院幼儿园东安路50弄10号为历史/合并相关地址。</x:v>
       </x:c>
-      <x:c r="L16" s="3" t="str">
+      <x:c r="P16" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；复旦附属徐汇实验幼儿园公开资料/上哪学/021school；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2154,34 +2368,46 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C17" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D17" s="3" t="str">
         <x:v>东安一村幼儿园</x:v>
       </x:c>
-      <x:c r="C17" s="3" t="str">
+      <x:c r="E17" s="3" t="str">
         <x:v>枫林/斜土</x:v>
       </x:c>
-      <x:c r="D17" s="3" t="str">
+      <x:c r="F17" s="3" t="str">
         <x:v>零陵园</x:v>
       </x:c>
-      <x:c r="E17" s="3" t="str">
+      <x:c r="G17" s="3" t="str">
         <x:v>零陵路250弄33号</x:v>
       </x:c>
-      <x:c r="F17" s="3" t="str">
+      <x:c r="H17" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%9C%E5%AE%89%E4%B8%80%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%9B%B6%E9%99%B5%E5%9B%AD%20%E9%9B%B6%E9%99%B5%E8%B7%AF250%E5%BC%8433%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G17" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I17" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J17" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K17" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L17" s="3" t="str">
         <x:v>东安一村北、东安一村南、安康、振兴、张东、爱华、汇园、东安二村、沈家里、东安四村、谨斜、东安苑、枫林新村、南康</x:v>
       </x:c>
-      <x:c r="J17" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K17" s="3" t="str"/>
-      <x:c r="L17" s="3" t="str">
+      <x:c r="M17" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N17" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O17" s="3" t="str"/>
+      <x:c r="P17" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2190,36 +2416,48 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D18" s="3" t="str">
         <x:v>东安一村幼儿园</x:v>
       </x:c>
-      <x:c r="C18" s="3" t="str">
+      <x:c r="E18" s="3" t="str">
         <x:v>枫林/斜土</x:v>
       </x:c>
-      <x:c r="D18" s="3" t="str">
+      <x:c r="F18" s="3" t="str">
         <x:v>东安园</x:v>
       </x:c>
-      <x:c r="E18" s="3" t="str">
+      <x:c r="G18" s="3" t="str">
         <x:v>东安一村39号</x:v>
       </x:c>
-      <x:c r="F18" s="3" t="str">
+      <x:c r="H18" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%9C%E5%AE%89%E4%B8%80%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%9C%E5%AE%89%E5%9B%AD%20%E4%B8%9C%E5%AE%89%E4%B8%80%E6%9D%9139%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G18" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I18" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J18" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K18" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L18" s="3" t="str">
         <x:v>东安一村北、东安一村南、安康、振兴、张东、爱华、汇园、东安二村、沈家里、东安四村、谨斜、东安苑、枫林新村、南康</x:v>
       </x:c>
-      <x:c r="J18" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K18" s="3" t="str">
+      <x:c r="M18" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N18" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O18" s="3" t="str">
         <x:v>公办名单列出东安一村39号及零陵路250弄33号。</x:v>
       </x:c>
-      <x:c r="L18" s="3" t="str">
+      <x:c r="P18" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2228,34 +2466,46 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B19" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D19" s="3" t="str">
         <x:v>龙山幼儿园</x:v>
       </x:c>
-      <x:c r="C19" s="3" t="str">
+      <x:c r="E19" s="3" t="str">
         <x:v>枫林/宛南</x:v>
       </x:c>
-      <x:c r="D19" s="3" t="str">
+      <x:c r="F19" s="3" t="str">
         <x:v>一分园</x:v>
       </x:c>
-      <x:c r="E19" s="3" t="str">
+      <x:c r="G19" s="3" t="str">
         <x:v>宛南四村16号</x:v>
       </x:c>
-      <x:c r="F19" s="3" t="str">
+      <x:c r="H19" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%80%E5%88%86%E5%9B%AD%20%E5%AE%9B%E5%8D%97%E5%9B%9B%E6%9D%9116%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G19" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="3" t="n">
+      <x:c r="I19" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J19" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K19" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I19" s="3" t="str">
+      <x:c r="L19" s="3" t="str">
         <x:v>天一二、天三、天四、宛南一二、宛三、宛四、宛五、宛六、庄家宅、黄家宅、华容、龙山一、龙山二、徐汇苑</x:v>
       </x:c>
-      <x:c r="J19" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K19" s="3" t="str"/>
-      <x:c r="L19" s="3" t="str">
+      <x:c r="M19" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N19" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O19" s="3" t="str"/>
+      <x:c r="P19" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2264,34 +2514,46 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B20" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C20" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D20" s="3" t="str">
         <x:v>龙山幼儿园</x:v>
       </x:c>
-      <x:c r="C20" s="3" t="str">
+      <x:c r="E20" s="3" t="str">
         <x:v>枫林/宛南</x:v>
       </x:c>
-      <x:c r="D20" s="3" t="str">
+      <x:c r="F20" s="3" t="str">
         <x:v>二分园</x:v>
       </x:c>
-      <x:c r="E20" s="3" t="str">
+      <x:c r="G20" s="3" t="str">
         <x:v>中山南二路999弄5号</x:v>
       </x:c>
-      <x:c r="F20" s="3" t="str">
+      <x:c r="H20" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%BA%8C%E5%88%86%E5%9B%AD%20%E4%B8%AD%E5%B1%B1%E5%8D%97%E4%BA%8C%E8%B7%AF999%E5%BC%845%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G20" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="3" t="n">
+      <x:c r="I20" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J20" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K20" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I20" s="3" t="str">
+      <x:c r="L20" s="3" t="str">
         <x:v>天一二、天三、天四、宛南一二、宛三、宛四、宛五、宛六、庄家宅、黄家宅、华容、龙山一、龙山二、徐汇苑</x:v>
       </x:c>
-      <x:c r="J20" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K20" s="3" t="str"/>
-      <x:c r="L20" s="3" t="str">
+      <x:c r="M20" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N20" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O20" s="3" t="str"/>
+      <x:c r="P20" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2300,34 +2562,46 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B21" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C21" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D21" s="3" t="str">
         <x:v>龙山幼儿园</x:v>
       </x:c>
-      <x:c r="C21" s="3" t="str">
+      <x:c r="E21" s="3" t="str">
         <x:v>枫林/宛南</x:v>
       </x:c>
-      <x:c r="D21" s="3" t="str">
+      <x:c r="F21" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E21" s="3" t="str">
+      <x:c r="G21" s="3" t="str">
         <x:v>天钥新村90号</x:v>
       </x:c>
-      <x:c r="F21" s="3" t="str">
+      <x:c r="H21" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%A9%E9%92%A5%E6%96%B0%E6%9D%9190%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G21" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="3" t="n">
+      <x:c r="I21" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J21" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K21" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I21" s="3" t="str">
+      <x:c r="L21" s="3" t="str">
         <x:v>天一二、天三、天四、宛南一二、宛三、宛四、宛五、宛六、庄家宅、黄家宅、华容、龙山一、龙山二、徐汇苑</x:v>
       </x:c>
-      <x:c r="J21" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K21" s="3" t="str"/>
-      <x:c r="L21" s="3" t="str">
+      <x:c r="M21" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N21" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O21" s="3" t="str"/>
+      <x:c r="P21" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2336,34 +2610,46 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B22" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C22" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D22" s="3" t="str">
         <x:v>龙华幼儿园</x:v>
       </x:c>
-      <x:c r="C22" s="3" t="str">
+      <x:c r="E22" s="3" t="str">
         <x:v>龙华/西岸</x:v>
       </x:c>
-      <x:c r="D22" s="3" t="str">
+      <x:c r="F22" s="3" t="str">
         <x:v>丰谷园</x:v>
       </x:c>
-      <x:c r="E22" s="3" t="str">
+      <x:c r="G22" s="3" t="str">
         <x:v>丰谷路205弄34号</x:v>
       </x:c>
-      <x:c r="F22" s="3" t="str">
+      <x:c r="H22" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%B0%E8%B0%B7%E5%9B%AD%20%E4%B8%B0%E8%B0%B7%E8%B7%AF205%E5%BC%8434%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G22" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H22" s="3" t="n">
+      <x:c r="I22" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J22" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K22" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I22" s="3" t="str">
+      <x:c r="L22" s="3" t="str">
         <x:v>上缝、强生、东蔡、狮城、佳友、华富、宏润花园、漕溪四村单号、丰谷、云锦、机场、尚海湾、盛大、民苑、丰谷三、俞一、俞二、俞三、龙华新村、周家湾、汇龙、红馨、百汇园</x:v>
       </x:c>
-      <x:c r="J22" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K22" s="3" t="str"/>
-      <x:c r="L22" s="3" t="str">
+      <x:c r="M22" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O22" s="3" t="str"/>
+      <x:c r="P22" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2372,34 +2658,46 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B23" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C23" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D23" s="3" t="str">
         <x:v>龙华幼儿园</x:v>
       </x:c>
-      <x:c r="C23" s="3" t="str">
+      <x:c r="E23" s="3" t="str">
         <x:v>龙华/西岸</x:v>
       </x:c>
-      <x:c r="D23" s="3" t="str">
+      <x:c r="F23" s="3" t="str">
         <x:v>龙恒园</x:v>
       </x:c>
-      <x:c r="E23" s="3" t="str">
+      <x:c r="G23" s="3" t="str">
         <x:v>龙华西路31弄15号</x:v>
       </x:c>
-      <x:c r="F23" s="3" t="str">
+      <x:c r="H23" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%BE%99%E6%81%92%E5%9B%AD%20%E9%BE%99%E5%8D%8E%E8%A5%BF%E8%B7%AF31%E5%BC%8415%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G23" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H23" s="3" t="n">
+      <x:c r="I23" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J23" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K23" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I23" s="3" t="str">
+      <x:c r="L23" s="3" t="str">
         <x:v>上缝、强生、东蔡、狮城、佳友、华富、宏润花园、漕溪四村单号、丰谷、云锦、机场、尚海湾、盛大、民苑、丰谷三、俞一、俞二、俞三、龙华新村、周家湾、汇龙、红馨、百汇园</x:v>
       </x:c>
-      <x:c r="J23" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K23" s="3" t="str"/>
-      <x:c r="L23" s="3" t="str">
+      <x:c r="M23" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N23" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O23" s="3" t="str"/>
+      <x:c r="P23" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2408,34 +2706,46 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B24" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C24" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D24" s="3" t="str">
         <x:v>龙华幼儿园</x:v>
       </x:c>
-      <x:c r="C24" s="3" t="str">
+      <x:c r="E24" s="3" t="str">
         <x:v>龙华/西岸</x:v>
       </x:c>
-      <x:c r="D24" s="3" t="str">
+      <x:c r="F24" s="3" t="str">
         <x:v>龙华园</x:v>
       </x:c>
-      <x:c r="E24" s="3" t="str">
+      <x:c r="G24" s="3" t="str">
         <x:v>龙华西路285弄14号</x:v>
       </x:c>
-      <x:c r="F24" s="3" t="str">
+      <x:c r="H24" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%BE%99%E5%8D%8E%E5%9B%AD%20%E9%BE%99%E5%8D%8E%E8%A5%BF%E8%B7%AF285%E5%BC%8414%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G24" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H24" s="3" t="n">
+      <x:c r="I24" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J24" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K24" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I24" s="3" t="str">
+      <x:c r="L24" s="3" t="str">
         <x:v>上缝、强生、东蔡、狮城、佳友、华富、宏润花园、漕溪四村单号、丰谷、云锦、机场、尚海湾、盛大、民苑、丰谷三、俞一、俞二、俞三、龙华新村、周家湾、汇龙、红馨、百汇园</x:v>
       </x:c>
-      <x:c r="J24" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K24" s="3" t="str"/>
-      <x:c r="L24" s="3" t="str">
+      <x:c r="M24" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N24" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O24" s="3" t="str"/>
+      <x:c r="P24" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2444,34 +2754,46 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B25" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C25" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D25" s="3" t="str">
         <x:v>汇霖幼儿园</x:v>
       </x:c>
-      <x:c r="C25" s="3" t="str">
+      <x:c r="E25" s="3" t="str">
         <x:v>田林/虹桥</x:v>
       </x:c>
-      <x:c r="D25" s="3" t="str">
+      <x:c r="F25" s="3" t="str">
         <x:v>吴中园</x:v>
       </x:c>
-      <x:c r="E25" s="3" t="str">
+      <x:c r="G25" s="3" t="str">
         <x:v>吴中东路500弄67号</x:v>
       </x:c>
-      <x:c r="F25" s="3" t="str">
+      <x:c r="H25" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E9%9C%96%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%90%B4%E4%B8%AD%E5%9B%AD%20%E5%90%B4%E4%B8%AD%E4%B8%9C%E8%B7%AF500%E5%BC%8467%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G25" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="3" t="n">
+      <x:c r="I25" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J25" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K25" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I25" s="3" t="str">
+      <x:c r="L25" s="3" t="str">
         <x:v>古宜、长春、吴中、桂林苑、虹南、虹星、怡桂苑、钦北、华悦家园、鑫耀</x:v>
       </x:c>
-      <x:c r="J25" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K25" s="3" t="str"/>
-      <x:c r="L25" s="3" t="str">
+      <x:c r="M25" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N25" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O25" s="3" t="str"/>
+      <x:c r="P25" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2480,34 +2802,46 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B26" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C26" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D26" s="3" t="str">
         <x:v>汇霖幼儿园</x:v>
       </x:c>
-      <x:c r="C26" s="3" t="str">
+      <x:c r="E26" s="3" t="str">
         <x:v>田林/虹桥</x:v>
       </x:c>
-      <x:c r="D26" s="3" t="str">
+      <x:c r="F26" s="3" t="str">
         <x:v>钦州园</x:v>
       </x:c>
-      <x:c r="E26" s="3" t="str">
+      <x:c r="G26" s="3" t="str">
         <x:v>钦州北路898号</x:v>
       </x:c>
-      <x:c r="F26" s="3" t="str">
+      <x:c r="H26" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E9%9C%96%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%92%A6%E5%B7%9E%E5%9B%AD%20%E9%92%A6%E5%B7%9E%E5%8C%97%E8%B7%AF898%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G26" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H26" s="3" t="n">
+      <x:c r="I26" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K26" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I26" s="3" t="str">
+      <x:c r="L26" s="3" t="str">
         <x:v>古宜、长春、吴中、桂林苑、虹南、虹星、怡桂苑、钦北、华悦家园、鑫耀</x:v>
       </x:c>
-      <x:c r="J26" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K26" s="3" t="str"/>
-      <x:c r="L26" s="3" t="str">
+      <x:c r="M26" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N26" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O26" s="3" t="str"/>
+      <x:c r="P26" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2516,34 +2850,46 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B27" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C27" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D27" s="3" t="str">
         <x:v>阳光幼儿园</x:v>
       </x:c>
-      <x:c r="C27" s="3" t="str">
+      <x:c r="E27" s="3" t="str">
         <x:v>龙华/滨江</x:v>
       </x:c>
-      <x:c r="D27" s="3" t="str">
+      <x:c r="F27" s="3" t="str">
         <x:v>中大班部</x:v>
       </x:c>
-      <x:c r="E27" s="3" t="str">
+      <x:c r="G27" s="3" t="str">
         <x:v>天钥桥南路1249弄11号</x:v>
       </x:c>
-      <x:c r="F27" s="3" t="str">
+      <x:c r="H27" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%98%B3%E5%85%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%AD%E5%A4%A7%E7%8F%AD%E9%83%A8%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E5%8D%97%E8%B7%AF1249%E5%BC%8411%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G27" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="3" t="n">
+      <x:c r="I27" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K27" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I27" s="3" t="str">
+      <x:c r="L27" s="3" t="str">
         <x:v>龙南三四、龙南五、龙南六、龙南七、滨江、樟树苑、东泉、张家园</x:v>
       </x:c>
-      <x:c r="J27" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K27" s="3" t="str"/>
-      <x:c r="L27" s="3" t="str">
+      <x:c r="M27" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N27" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O27" s="3" t="str"/>
+      <x:c r="P27" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2552,34 +2898,46 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B28" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C28" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D28" s="3" t="str">
         <x:v>阳光幼儿园</x:v>
       </x:c>
-      <x:c r="C28" s="3" t="str">
+      <x:c r="E28" s="3" t="str">
         <x:v>龙华/滨江</x:v>
       </x:c>
-      <x:c r="D28" s="3" t="str">
+      <x:c r="F28" s="3" t="str">
         <x:v>小班部</x:v>
       </x:c>
-      <x:c r="E28" s="3" t="str">
+      <x:c r="G28" s="3" t="str">
         <x:v>龙水南路龙南三村7号</x:v>
       </x:c>
-      <x:c r="F28" s="3" t="str">
+      <x:c r="H28" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%98%B3%E5%85%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%B0%8F%E7%8F%AD%E9%83%A8%20%E9%BE%99%E6%B0%B4%E5%8D%97%E8%B7%AF%E9%BE%99%E5%8D%97%E4%B8%89%E6%9D%917%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G28" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H28" s="3" t="n">
+      <x:c r="I28" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K28" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I28" s="3" t="str">
+      <x:c r="L28" s="3" t="str">
         <x:v>龙南三四、龙南五、龙南六、龙南七、滨江、樟树苑、东泉、张家园</x:v>
       </x:c>
-      <x:c r="J28" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K28" s="3" t="str"/>
-      <x:c r="L28" s="3" t="str">
+      <x:c r="M28" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N28" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O28" s="3" t="str"/>
+      <x:c r="P28" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2588,34 +2946,46 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B29" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C29" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D29" s="3" t="str">
         <x:v>漕溪新村幼儿园</x:v>
       </x:c>
-      <x:c r="C29" s="3" t="str">
+      <x:c r="E29" s="3" t="str">
         <x:v>漕溪/龙漕</x:v>
       </x:c>
-      <x:c r="D29" s="3" t="str">
+      <x:c r="F29" s="3" t="str">
         <x:v>中大班部</x:v>
       </x:c>
-      <x:c r="E29" s="3" t="str">
+      <x:c r="G29" s="3" t="str">
         <x:v>龙漕路139号</x:v>
       </x:c>
-      <x:c r="F29" s="3" t="str">
+      <x:c r="H29" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BC%95%E6%BA%AA%E6%96%B0%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%AD%E5%A4%A7%E7%8F%AD%E9%83%A8%20%E9%BE%99%E6%BC%95%E8%B7%AF139%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G29" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H29" s="3" t="n">
+      <x:c r="I29" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J29" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K29" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I29" s="3" t="str">
+      <x:c r="L29" s="3" t="str">
         <x:v>金谷园、南一村一、南一村二、漕溪四村双号、凯翔、龙漕、嘉萱苑、漕东</x:v>
       </x:c>
-      <x:c r="J29" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K29" s="3" t="str"/>
-      <x:c r="L29" s="3" t="str">
+      <x:c r="M29" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N29" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O29" s="3" t="str"/>
+      <x:c r="P29" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2624,34 +2994,46 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B30" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C30" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D30" s="3" t="str">
         <x:v>漕溪新村幼儿园</x:v>
       </x:c>
-      <x:c r="C30" s="3" t="str">
+      <x:c r="E30" s="3" t="str">
         <x:v>漕溪/龙漕</x:v>
       </x:c>
-      <x:c r="D30" s="3" t="str">
+      <x:c r="F30" s="3" t="str">
         <x:v>小班部</x:v>
       </x:c>
-      <x:c r="E30" s="3" t="str">
+      <x:c r="G30" s="3" t="str">
         <x:v>漕东路193号</x:v>
       </x:c>
-      <x:c r="F30" s="3" t="str">
+      <x:c r="H30" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BC%95%E6%BA%AA%E6%96%B0%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%B0%8F%E7%8F%AD%E9%83%A8%20%E6%BC%95%E4%B8%9C%E8%B7%AF193%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G30" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H30" s="3" t="n">
+      <x:c r="I30" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J30" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I30" s="3" t="str">
+      <x:c r="L30" s="3" t="str">
         <x:v>金谷园、南一村一、南一村二、漕溪四村双号、凯翔、龙漕、嘉萱苑、漕东</x:v>
       </x:c>
-      <x:c r="J30" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K30" s="3" t="str"/>
-      <x:c r="L30" s="3" t="str">
+      <x:c r="M30" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N30" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O30" s="3" t="str"/>
+      <x:c r="P30" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2660,34 +3042,46 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C31" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D31" s="3" t="str">
         <x:v>望德幼儿园</x:v>
       </x:c>
-      <x:c r="C31" s="3" t="str">
+      <x:c r="E31" s="3" t="str">
         <x:v>康健/南站</x:v>
       </x:c>
-      <x:c r="D31" s="3" t="str">
+      <x:c r="F31" s="3" t="str">
         <x:v>冠生园</x:v>
       </x:c>
-      <x:c r="E31" s="3" t="str">
+      <x:c r="G31" s="3" t="str">
         <x:v>冠生园路28号</x:v>
       </x:c>
-      <x:c r="F31" s="3" t="str">
+      <x:c r="H31" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%9B%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%86%A0%E7%94%9F%E5%9B%AD%20%E5%86%A0%E7%94%9F%E5%9B%AD%E8%B7%AF28%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G31" s="3" t="str">
+      <x:c r="I31" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J31" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H31" s="3" t="n">
+      <x:c r="K31" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I31" s="3" t="str">
+      <x:c r="L31" s="3" t="str">
         <x:v>康健路、习勤、薛家宅、科苑、九弄、中海、梓树园、月河、宾阳、馨汇南苑、公园道</x:v>
       </x:c>
-      <x:c r="J31" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K31" s="3" t="str"/>
-      <x:c r="L31" s="3" t="str">
+      <x:c r="M31" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N31" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O31" s="3" t="str"/>
+      <x:c r="P31" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2696,34 +3090,46 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C32" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D32" s="3" t="str">
         <x:v>望德幼儿园</x:v>
       </x:c>
-      <x:c r="C32" s="3" t="str">
+      <x:c r="E32" s="3" t="str">
         <x:v>康健/南站</x:v>
       </x:c>
-      <x:c r="D32" s="3" t="str">
+      <x:c r="F32" s="3" t="str">
         <x:v>南宁园</x:v>
       </x:c>
-      <x:c r="E32" s="3" t="str">
+      <x:c r="G32" s="3" t="str">
         <x:v>南宁路636号</x:v>
       </x:c>
-      <x:c r="F32" s="3" t="str">
+      <x:c r="H32" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%9B%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%AE%81%E5%9B%AD%20%E5%8D%97%E5%AE%81%E8%B7%AF636%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G32" s="3" t="str">
+      <x:c r="I32" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J32" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H32" s="3" t="n">
+      <x:c r="K32" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I32" s="3" t="str">
+      <x:c r="L32" s="3" t="str">
         <x:v>康健路、习勤、薛家宅、科苑、九弄、中海、梓树园、月河、宾阳、馨汇南苑、公园道</x:v>
       </x:c>
-      <x:c r="J32" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K32" s="3" t="str"/>
-      <x:c r="L32" s="3" t="str">
+      <x:c r="M32" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N32" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O32" s="3" t="str"/>
+      <x:c r="P32" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2732,34 +3138,46 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B33" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C33" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D33" s="3" t="str">
         <x:v>瑞德幼儿园</x:v>
       </x:c>
-      <x:c r="C33" s="3" t="str">
+      <x:c r="E33" s="3" t="str">
         <x:v>长桥/汇成</x:v>
       </x:c>
-      <x:c r="D33" s="3" t="str">
+      <x:c r="F33" s="3" t="str">
         <x:v>楼园园</x:v>
       </x:c>
-      <x:c r="E33" s="3" t="str">
+      <x:c r="G33" s="3" t="str">
         <x:v>老沪闵路706弄37号</x:v>
       </x:c>
-      <x:c r="F33" s="3" t="str">
+      <x:c r="H33" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%91%9E%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%A5%BC%E5%9B%AD%E5%9B%AD%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF706%E5%BC%8437%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G33" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H33" s="3" t="n">
+      <x:c r="I33" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J33" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K33" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I33" s="3" t="str">
+      <x:c r="L33" s="3" t="str">
         <x:v>汇成一村、汇成二村、汇成三村、汇成四村、华东二、楼园、金牛、挹翠苑、罗城、光华、汇澜苑、金塘</x:v>
       </x:c>
-      <x:c r="J33" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K33" s="3" t="str"/>
-      <x:c r="L33" s="3" t="str">
+      <x:c r="M33" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N33" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O33" s="3" t="str"/>
+      <x:c r="P33" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2768,34 +3186,46 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B34" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C34" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D34" s="3" t="str">
         <x:v>瑞德幼儿园</x:v>
       </x:c>
-      <x:c r="C34" s="3" t="str">
+      <x:c r="E34" s="3" t="str">
         <x:v>长桥/汇成</x:v>
       </x:c>
-      <x:c r="D34" s="3" t="str">
+      <x:c r="F34" s="3" t="str">
         <x:v>金塘园</x:v>
       </x:c>
-      <x:c r="E34" s="3" t="str">
+      <x:c r="G34" s="3" t="str">
         <x:v>老沪闵路333弄70号</x:v>
       </x:c>
-      <x:c r="F34" s="3" t="str">
+      <x:c r="H34" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%91%9E%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%87%91%E5%A1%98%E5%9B%AD%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF333%E5%BC%8470%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G34" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H34" s="3" t="n">
+      <x:c r="I34" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J34" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K34" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I34" s="3" t="str">
+      <x:c r="L34" s="3" t="str">
         <x:v>汇成一村、汇成二村、汇成三村、汇成四村、华东二、楼园、金牛、挹翠苑、罗城、光华、汇澜苑、金塘</x:v>
       </x:c>
-      <x:c r="J34" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K34" s="3" t="str"/>
-      <x:c r="L34" s="3" t="str">
+      <x:c r="M34" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N34" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O34" s="3" t="str"/>
+      <x:c r="P34" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2804,34 +3234,46 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B35" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C35" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D35" s="3" t="str">
         <x:v>益思幼儿园</x:v>
       </x:c>
-      <x:c r="C35" s="3" t="str">
+      <x:c r="E35" s="3" t="str">
         <x:v>田林/漕河泾</x:v>
       </x:c>
-      <x:c r="D35" s="3" t="str">
+      <x:c r="F35" s="3" t="str">
         <x:v>东园</x:v>
       </x:c>
-      <x:c r="E35" s="3" t="str">
+      <x:c r="G35" s="3" t="str">
         <x:v>田林九村6号</x:v>
       </x:c>
-      <x:c r="F35" s="3" t="str">
+      <x:c r="H35" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%9B%8A%E6%80%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%9C%E5%9B%AD%20%E7%94%B0%E6%9E%97%E4%B9%9D%E6%9D%916%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G35" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H35" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I35" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J35" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K35" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L35" s="3" t="str">
         <x:v>田林一二村、田林五六七村、田林八九十村、田林十三村、田林十一村、千鹤三、爱建园、万科华尔兹、新苑一二、新苑三四、新苑五六七、田林十四村第一、田林十四村第二</x:v>
       </x:c>
-      <x:c r="J35" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K35" s="3" t="str"/>
-      <x:c r="L35" s="3" t="str">
+      <x:c r="M35" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N35" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O35" s="3" t="str"/>
+      <x:c r="P35" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2840,34 +3282,46 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B36" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C36" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D36" s="3" t="str">
         <x:v>益思幼儿园</x:v>
       </x:c>
-      <x:c r="C36" s="3" t="str">
+      <x:c r="E36" s="3" t="str">
         <x:v>田林/漕河泾</x:v>
       </x:c>
-      <x:c r="D36" s="3" t="str">
+      <x:c r="F36" s="3" t="str">
         <x:v>西园</x:v>
       </x:c>
-      <x:c r="E36" s="3" t="str">
+      <x:c r="G36" s="3" t="str">
         <x:v>宜山路701弄53号</x:v>
       </x:c>
-      <x:c r="F36" s="3" t="str">
+      <x:c r="H36" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%9B%8A%E6%80%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E8%A5%BF%E5%9B%AD%20%E5%AE%9C%E5%B1%B1%E8%B7%AF701%E5%BC%8453%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G36" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H36" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I36" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J36" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K36" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L36" s="3" t="str">
         <x:v>田林一二村、田林五六七村、田林八九十村、田林十三村、田林十一村、千鹤三、爱建园、万科华尔兹、新苑一二、新苑三四、新苑五六七、田林十四村第一、田林十四村第二</x:v>
       </x:c>
-      <x:c r="J36" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K36" s="3" t="str"/>
-      <x:c r="L36" s="3" t="str">
+      <x:c r="M36" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N36" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O36" s="3" t="str"/>
+      <x:c r="P36" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2876,34 +3330,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B37" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C37" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D37" s="3" t="str">
         <x:v>樱花园幼儿园</x:v>
       </x:c>
-      <x:c r="C37" s="3" t="str">
+      <x:c r="E37" s="3" t="str">
         <x:v>康健/桂林</x:v>
       </x:c>
-      <x:c r="D37" s="3" t="str">
+      <x:c r="F37" s="3" t="str">
         <x:v>南园</x:v>
       </x:c>
-      <x:c r="E37" s="3" t="str">
+      <x:c r="G37" s="3" t="str">
         <x:v>百花街398号</x:v>
       </x:c>
-      <x:c r="F37" s="3" t="str">
+      <x:c r="H37" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A8%B1%E8%8A%B1%E5%9B%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E7%99%BE%E8%8A%B1%E8%A1%97398%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G37" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H37" s="3" t="n">
+      <x:c r="I37" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J37" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K37" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I37" s="3" t="str">
+      <x:c r="L37" s="3" t="str">
         <x:v>月季百藤、樱花园、茶花桂花、丁香迎春、玉兰园、寿益坊（海上华庭）、紫鹃园、紫薇园（牡丹园、玫瑰园）、金桂苑、紫荆党校</x:v>
       </x:c>
-      <x:c r="J37" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K37" s="3" t="str"/>
-      <x:c r="L37" s="3" t="str">
+      <x:c r="M37" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N37" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O37" s="3" t="str"/>
+      <x:c r="P37" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2912,34 +3378,46 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B38" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C38" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D38" s="3" t="str">
         <x:v>樱花园幼儿园</x:v>
       </x:c>
-      <x:c r="C38" s="3" t="str">
+      <x:c r="E38" s="3" t="str">
         <x:v>康健/桂林</x:v>
       </x:c>
-      <x:c r="D38" s="3" t="str">
+      <x:c r="F38" s="3" t="str">
         <x:v>北园</x:v>
       </x:c>
-      <x:c r="E38" s="3" t="str">
+      <x:c r="G38" s="3" t="str">
         <x:v>虹漕南路杨家桥88号</x:v>
       </x:c>
-      <x:c r="F38" s="3" t="str">
+      <x:c r="H38" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A8%B1%E8%8A%B1%E5%9B%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E8%99%B9%E6%BC%95%E5%8D%97%E8%B7%AF%E6%9D%A8%E5%AE%B6%E6%A1%A588%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G38" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H38" s="3" t="n">
+      <x:c r="I38" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J38" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K38" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I38" s="3" t="str">
+      <x:c r="L38" s="3" t="str">
         <x:v>月季百藤、樱花园、茶花桂花、丁香迎春、玉兰园、寿益坊（海上华庭）、紫鹃园、紫薇园（牡丹园、玫瑰园）、金桂苑、紫荆党校</x:v>
       </x:c>
-      <x:c r="J38" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K38" s="3" t="str"/>
-      <x:c r="L38" s="3" t="str">
+      <x:c r="M38" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N38" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O38" s="3" t="str"/>
+      <x:c r="P38" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2948,34 +3426,46 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C39" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D39" s="3" t="str">
         <x:v>长海幼儿园</x:v>
       </x:c>
-      <x:c r="C39" s="3" t="str">
+      <x:c r="E39" s="3" t="str">
         <x:v>康健/桂林</x:v>
       </x:c>
-      <x:c r="D39" s="3" t="str">
+      <x:c r="F39" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E39" s="3" t="str">
+      <x:c r="G39" s="3" t="str">
         <x:v>桂林西街15弄2号</x:v>
       </x:c>
-      <x:c r="F39" s="3" t="str">
+      <x:c r="H39" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E6%9E%97%E8%A5%BF%E8%A1%9715%E5%BC%842%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G39" s="3" t="str">
+      <x:c r="I39" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J39" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="H39" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I39" s="3" t="str">
+      <x:c r="K39" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L39" s="3" t="str">
         <x:v>长顺海、长虹坊、长青坊、长丰坊、长兴坊、师大新村、桂康</x:v>
       </x:c>
-      <x:c r="J39" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K39" s="3" t="str"/>
-      <x:c r="L39" s="3" t="str">
+      <x:c r="M39" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N39" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O39" s="3" t="str"/>
+      <x:c r="P39" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2984,34 +3474,46 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B40" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C40" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D40" s="3" t="str">
         <x:v>康沁幼儿园</x:v>
       </x:c>
-      <x:c r="C40" s="3" t="str">
+      <x:c r="E40" s="3" t="str">
         <x:v>康健/桂林</x:v>
       </x:c>
-      <x:c r="D40" s="3" t="str">
+      <x:c r="F40" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E40" s="3" t="str">
+      <x:c r="G40" s="3" t="str">
         <x:v>桂林西街151弄20号甲</x:v>
       </x:c>
-      <x:c r="F40" s="3" t="str">
+      <x:c r="H40" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%BA%B7%E6%B2%81%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E6%9E%97%E8%A5%BF%E8%A1%97151%E5%BC%8420%E5%8F%B7%E7%94%B2</x:v>
       </x:c>
-      <x:c r="G40" s="3" t="str">
+      <x:c r="I40" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J40" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="H40" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I40" s="3" t="str">
+      <x:c r="K40" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L40" s="3" t="str">
         <x:v>寿昌山、寿祥坊、寿益坊（寿益坊、桂林西街101弄）、康乐、桂二、冠生园、康宁馨、康强海（康强坊）</x:v>
       </x:c>
-      <x:c r="J40" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K40" s="3" t="str"/>
-      <x:c r="L40" s="3" t="str">
+      <x:c r="M40" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N40" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O40" s="3" t="str"/>
+      <x:c r="P40" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3020,34 +3522,46 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B41" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C41" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D41" s="3" t="str">
         <x:v>长桥第一幼儿园</x:v>
       </x:c>
-      <x:c r="C41" s="3" t="str">
+      <x:c r="E41" s="3" t="str">
         <x:v>长桥</x:v>
       </x:c>
-      <x:c r="D41" s="3" t="str">
+      <x:c r="F41" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E41" s="3" t="str">
+      <x:c r="G41" s="3" t="str">
         <x:v>长桥一村56号</x:v>
       </x:c>
-      <x:c r="F41" s="3" t="str">
+      <x:c r="H41" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%95%BF%E6%A1%A5%E4%B8%80%E6%9D%9156%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G41" s="3" t="str">
+      <x:c r="I41" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J41" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="H41" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I41" s="3" t="str">
+      <x:c r="K41" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L41" s="3" t="str">
         <x:v>长桥一村、长桥五村（书香逸居、长桥五村）、闵朱、舒城</x:v>
       </x:c>
-      <x:c r="J41" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K41" s="3" t="str"/>
-      <x:c r="L41" s="3" t="str">
+      <x:c r="M41" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N41" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O41" s="3" t="str"/>
+      <x:c r="P41" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3056,34 +3570,46 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B42" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C42" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D42" s="3" t="str">
         <x:v>长桥第二幼儿园</x:v>
       </x:c>
-      <x:c r="C42" s="3" t="str">
+      <x:c r="E42" s="3" t="str">
         <x:v>长桥/凌云</x:v>
       </x:c>
-      <x:c r="D42" s="3" t="str">
+      <x:c r="F42" s="3" t="str">
         <x:v>凌云园</x:v>
       </x:c>
-      <x:c r="E42" s="3" t="str">
+      <x:c r="G42" s="3" t="str">
         <x:v>梅陇十一村97号</x:v>
       </x:c>
-      <x:c r="F42" s="3" t="str">
+      <x:c r="H42" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%BA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%87%8C%E4%BA%91%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%8D%81%E4%B8%80%E6%9D%9197%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G42" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H42" s="3" t="n">
+      <x:c r="I42" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J42" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K42" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I42" s="3" t="str">
+      <x:c r="L42" s="3" t="str">
         <x:v>长桥新村一、长桥新二村、长桥七村、兴荣苑、和平、龙州、梅陇十一第一、梅陇十一第二、陇南、闵秀</x:v>
       </x:c>
-      <x:c r="J42" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K42" s="3" t="str"/>
-      <x:c r="L42" s="3" t="str">
+      <x:c r="M42" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N42" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O42" s="3" t="str"/>
+      <x:c r="P42" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3092,34 +3618,46 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B43" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C43" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D43" s="3" t="str">
         <x:v>长桥第二幼儿园</x:v>
       </x:c>
-      <x:c r="C43" s="3" t="str">
+      <x:c r="E43" s="3" t="str">
         <x:v>长桥/凌云</x:v>
       </x:c>
-      <x:c r="D43" s="3" t="str">
+      <x:c r="F43" s="3" t="str">
         <x:v>长桥园</x:v>
       </x:c>
-      <x:c r="E43" s="3" t="str">
+      <x:c r="G43" s="3" t="str">
         <x:v>长桥二村34号</x:v>
       </x:c>
-      <x:c r="F43" s="3" t="str">
+      <x:c r="H43" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%BA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E4%BA%8C%E6%9D%9134%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G43" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H43" s="3" t="n">
+      <x:c r="I43" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J43" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K43" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I43" s="3" t="str">
+      <x:c r="L43" s="3" t="str">
         <x:v>长桥新村一、长桥新二村、长桥七村、兴荣苑、和平、龙州、梅陇十一第一、梅陇十一第二、陇南、闵秀</x:v>
       </x:c>
-      <x:c r="J43" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K43" s="3" t="str"/>
-      <x:c r="L43" s="3" t="str">
+      <x:c r="M43" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N43" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O43" s="3" t="str"/>
+      <x:c r="P43" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3128,34 +3666,46 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B44" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C44" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D44" s="3" t="str">
         <x:v>长桥第三幼儿园</x:v>
       </x:c>
-      <x:c r="C44" s="3" t="str">
+      <x:c r="E44" s="3" t="str">
         <x:v>长桥</x:v>
       </x:c>
-      <x:c r="D44" s="3" t="str">
+      <x:c r="F44" s="3" t="str">
         <x:v>长桥园</x:v>
       </x:c>
-      <x:c r="E44" s="3" t="str">
+      <x:c r="G44" s="3" t="str">
         <x:v>长桥三村124号</x:v>
       </x:c>
-      <x:c r="F44" s="3" t="str">
+      <x:c r="H44" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%B8%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E4%B8%89%E6%9D%91124%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G44" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H44" s="3" t="n">
+      <x:c r="I44" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J44" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K44" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I44" s="3" t="str">
+      <x:c r="L44" s="3" t="str">
         <x:v>长桥三村一、长桥三村二（长桥三村东区）、长桥八村、平福、长桥四村</x:v>
       </x:c>
-      <x:c r="J44" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K44" s="3" t="str"/>
-      <x:c r="L44" s="3" t="str">
+      <x:c r="M44" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N44" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O44" s="3" t="str"/>
+      <x:c r="P44" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3164,34 +3714,46 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B45" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C45" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D45" s="3" t="str">
         <x:v>长桥第三幼儿园</x:v>
       </x:c>
-      <x:c r="C45" s="3" t="str">
+      <x:c r="E45" s="3" t="str">
         <x:v>长桥</x:v>
       </x:c>
-      <x:c r="D45" s="3" t="str">
+      <x:c r="F45" s="3" t="str">
         <x:v>平福园</x:v>
       </x:c>
-      <x:c r="E45" s="3" t="str">
+      <x:c r="G45" s="3" t="str">
         <x:v>上中路483弄32号</x:v>
       </x:c>
-      <x:c r="F45" s="3" t="str">
+      <x:c r="H45" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%B8%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%B9%B3%E7%A6%8F%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E8%B7%AF483%E5%BC%8432%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G45" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H45" s="3" t="n">
+      <x:c r="I45" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J45" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K45" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I45" s="3" t="str">
+      <x:c r="L45" s="3" t="str">
         <x:v>长桥三村一、长桥三村二（长桥三村东区）、长桥八村、平福、长桥四村</x:v>
       </x:c>
-      <x:c r="J45" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K45" s="3" t="str"/>
-      <x:c r="L45" s="3" t="str">
+      <x:c r="M45" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N45" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O45" s="3" t="str"/>
+      <x:c r="P45" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3200,34 +3762,46 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B46" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C46" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D46" s="3" t="str">
         <x:v>园南幼儿园</x:v>
       </x:c>
-      <x:c r="C46" s="3" t="str">
+      <x:c r="E46" s="3" t="str">
         <x:v>长桥/园南</x:v>
       </x:c>
-      <x:c r="D46" s="3" t="str">
+      <x:c r="F46" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E46" s="3" t="str">
+      <x:c r="G46" s="3" t="str">
         <x:v>龙川北路园南一村27号</x:v>
       </x:c>
-      <x:c r="F46" s="3" t="str">
+      <x:c r="H46" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9B%AD%E5%8D%97%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%B7%9D%E5%8C%97%E8%B7%AF%E5%9B%AD%E5%8D%97%E4%B8%80%E6%9D%9127%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G46" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H46" s="3" t="n">
+      <x:c r="I46" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J46" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K46" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I46" s="3" t="str">
+      <x:c r="L46" s="3" t="str">
         <x:v>园南一村、园南二村、园南三村、汇成五村、华东一</x:v>
       </x:c>
-      <x:c r="J46" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K46" s="3" t="str"/>
-      <x:c r="L46" s="3" t="str">
+      <x:c r="M46" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N46" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O46" s="3" t="str"/>
+      <x:c r="P46" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3236,34 +3810,46 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B47" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C47" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D47" s="3" t="str">
         <x:v>梅陇幼儿园</x:v>
       </x:c>
-      <x:c r="C47" s="3" t="str">
+      <x:c r="E47" s="3" t="str">
         <x:v>凌云/梅陇</x:v>
       </x:c>
-      <x:c r="D47" s="3" t="str">
+      <x:c r="F47" s="3" t="str">
         <x:v>嘉川园</x:v>
       </x:c>
-      <x:c r="E47" s="3" t="str">
+      <x:c r="G47" s="3" t="str">
         <x:v>梅陇四村56号甲</x:v>
       </x:c>
-      <x:c r="F47" s="3" t="str">
+      <x:c r="H47" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A2%85%E9%99%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%98%89%E5%B7%9D%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%9B%9B%E6%9D%9156%E5%8F%B7%E7%94%B2</x:v>
       </x:c>
-      <x:c r="G47" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H47" s="3" t="n">
+      <x:c r="I47" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J47" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K47" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I47" s="3" t="str">
+      <x:c r="L47" s="3" t="str">
         <x:v>梅三、梅六、梅苑一、梅苑二、凌云、梅四、理工一、理工二、华理苑、书香苑、家乐苑、阳光（阳光新景）</x:v>
       </x:c>
-      <x:c r="J47" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K47" s="3" t="str"/>
-      <x:c r="L47" s="3" t="str">
+      <x:c r="M47" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N47" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O47" s="3" t="str"/>
+      <x:c r="P47" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3272,34 +3858,46 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B48" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C48" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D48" s="3" t="str">
         <x:v>梅陇幼儿园</x:v>
       </x:c>
-      <x:c r="C48" s="3" t="str">
+      <x:c r="E48" s="3" t="str">
         <x:v>凌云/梅陇</x:v>
       </x:c>
-      <x:c r="D48" s="3" t="str">
+      <x:c r="F48" s="3" t="str">
         <x:v>梅陇园</x:v>
       </x:c>
-      <x:c r="E48" s="3" t="str">
+      <x:c r="G48" s="3" t="str">
         <x:v>梅陇六村65号</x:v>
       </x:c>
-      <x:c r="F48" s="3" t="str">
+      <x:c r="H48" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A2%85%E9%99%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%85%AD%E6%9D%9165%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G48" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H48" s="3" t="n">
+      <x:c r="I48" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J48" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K48" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I48" s="3" t="str">
+      <x:c r="L48" s="3" t="str">
         <x:v>梅三、梅六、梅苑一、梅苑二、凌云、梅四、理工一、理工二、华理苑、书香苑、家乐苑、阳光（阳光新景）</x:v>
       </x:c>
-      <x:c r="J48" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K48" s="3" t="str"/>
-      <x:c r="L48" s="3" t="str">
+      <x:c r="M48" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N48" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O48" s="3" t="str"/>
+      <x:c r="P48" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3308,34 +3906,46 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B49" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C49" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D49" s="3" t="str">
         <x:v>梅陇第二幼儿园</x:v>
       </x:c>
-      <x:c r="C49" s="3" t="str">
+      <x:c r="E49" s="3" t="str">
         <x:v>凌云/梅陇</x:v>
       </x:c>
-      <x:c r="D49" s="3" t="str">
+      <x:c r="F49" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E49" s="3" t="str">
+      <x:c r="G49" s="3" t="str">
         <x:v>梅陇五村54号</x:v>
       </x:c>
-      <x:c r="F49" s="3" t="str">
+      <x:c r="H49" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A2%85%E9%99%87%E7%AC%AC%E4%BA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E4%BA%94%E6%9D%9154%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G49" s="3" t="str">
+      <x:c r="I49" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J49" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="H49" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I49" s="3" t="str">
+      <x:c r="K49" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L49" s="3" t="str">
         <x:v>梅陇五村、梅陇七村、梅陇八村、梅陇十村、梅陇九村、阳光（阳光绿园）、长陇苑</x:v>
       </x:c>
-      <x:c r="J49" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K49" s="3" t="str"/>
-      <x:c r="L49" s="3" t="str">
+      <x:c r="M49" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N49" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O49" s="3" t="str"/>
+      <x:c r="P49" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3344,34 +3954,46 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B50" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C50" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D50" s="3" t="str">
         <x:v>华建幼儿园</x:v>
       </x:c>
-      <x:c r="C50" s="3" t="str">
+      <x:c r="E50" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="D50" s="3" t="str">
+      <x:c r="F50" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E50" s="3" t="str">
+      <x:c r="G50" s="3" t="str">
         <x:v>老沪闵路1300号</x:v>
       </x:c>
-      <x:c r="F50" s="3" t="str">
+      <x:c r="H50" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%8D%8E%E5%BB%BA%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF1300%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G50" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H50" s="3" t="n">
+      <x:c r="I50" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J50" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K50" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I50" s="3" t="str">
+      <x:c r="L50" s="3" t="str">
         <x:v>华建、建华村、北杨村</x:v>
       </x:c>
-      <x:c r="J50" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K50" s="3" t="str"/>
-      <x:c r="L50" s="3" t="str">
+      <x:c r="M50" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N50" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O50" s="3" t="str"/>
+      <x:c r="P50" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3380,34 +4002,46 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B51" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C51" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D51" s="3" t="str">
         <x:v>位育幼儿园</x:v>
       </x:c>
-      <x:c r="C51" s="3" t="str">
+      <x:c r="E51" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="D51" s="3" t="str">
+      <x:c r="F51" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E51" s="3" t="str">
+      <x:c r="G51" s="3" t="str">
         <x:v>建华路102号</x:v>
       </x:c>
-      <x:c r="F51" s="3" t="str">
+      <x:c r="H51" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BD%8D%E8%82%B2%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%BB%BA%E5%8D%8E%E8%B7%AF102%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G51" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H51" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I51" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J51" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K51" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L51" s="3" t="str">
         <x:v>华泾四村、华泾五村、漓江山水、联合居委</x:v>
       </x:c>
-      <x:c r="J51" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K51" s="3" t="str"/>
-      <x:c r="L51" s="3" t="str">
+      <x:c r="M51" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N51" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O51" s="3" t="str"/>
+      <x:c r="P51" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3416,34 +4050,46 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B52" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C52" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D52" s="3" t="str">
         <x:v>果果幼儿园</x:v>
       </x:c>
-      <x:c r="C52" s="3" t="str">
+      <x:c r="E52" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="D52" s="3" t="str">
+      <x:c r="F52" s="3" t="str">
         <x:v>华欣园</x:v>
       </x:c>
-      <x:c r="E52" s="3" t="str">
+      <x:c r="G52" s="3" t="str">
         <x:v>龙吴路2422号</x:v>
       </x:c>
-      <x:c r="F52" s="3" t="str">
+      <x:c r="H52" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%9C%E6%9E%9C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%8E%E6%AC%A3%E5%9B%AD%20%E9%BE%99%E5%90%B4%E8%B7%AF2422%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G52" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H52" s="3" t="n">
+      <x:c r="I52" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J52" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K52" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I52" s="3" t="str">
+      <x:c r="L52" s="3" t="str">
         <x:v>华欣家园、华发、馨宁、大桥、明丰新纪苑、名苑、华臻</x:v>
       </x:c>
-      <x:c r="J52" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K52" s="3" t="str"/>
-      <x:c r="L52" s="3" t="str">
+      <x:c r="M52" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N52" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O52" s="3" t="str"/>
+      <x:c r="P52" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3452,34 +4098,46 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B53" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C53" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D53" s="3" t="str">
         <x:v>果果幼儿园</x:v>
       </x:c>
-      <x:c r="C53" s="3" t="str">
+      <x:c r="E53" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="D53" s="3" t="str">
+      <x:c r="F53" s="3" t="str">
         <x:v>华发园</x:v>
       </x:c>
-      <x:c r="E53" s="3" t="str">
+      <x:c r="G53" s="3" t="str">
         <x:v>华发路100弄22号</x:v>
       </x:c>
-      <x:c r="F53" s="3" t="str">
+      <x:c r="H53" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%9C%E6%9E%9C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%8E%E5%8F%91%E5%9B%AD%20%E5%8D%8E%E5%8F%91%E8%B7%AF100%E5%BC%8422%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G53" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H53" s="3" t="n">
+      <x:c r="I53" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J53" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K53" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I53" s="3" t="str">
+      <x:c r="L53" s="3" t="str">
         <x:v>华欣家园、华发、馨宁、大桥、明丰新纪苑、名苑、华臻</x:v>
       </x:c>
-      <x:c r="J53" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K53" s="3" t="str"/>
-      <x:c r="L53" s="3" t="str">
+      <x:c r="M53" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N53" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O53" s="3" t="str"/>
+      <x:c r="P53" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3488,34 +4146,46 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B54" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C54" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D54" s="3" t="str">
         <x:v>星辰幼儿园</x:v>
       </x:c>
-      <x:c r="C54" s="3" t="str">
+      <x:c r="E54" s="3" t="str">
         <x:v>华泾/罗秀</x:v>
       </x:c>
-      <x:c r="D54" s="3" t="str">
+      <x:c r="F54" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E54" s="3" t="str">
+      <x:c r="G54" s="3" t="str">
         <x:v>罗秀路11号</x:v>
       </x:c>
-      <x:c r="F54" s="3" t="str">
+      <x:c r="H54" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%98%9F%E8%BE%B0%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%BD%97%E7%A7%80%E8%B7%AF11%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G54" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H54" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I54" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J54" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K54" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L54" s="3" t="str">
         <x:v>徐汇新城、罗秀三村、华滨家园、华沁家园、罗秀、罗秀二村</x:v>
       </x:c>
-      <x:c r="J54" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K54" s="3" t="str"/>
-      <x:c r="L54" s="3" t="str">
+      <x:c r="M54" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N54" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O54" s="3" t="str"/>
+      <x:c r="P54" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3524,34 +4194,46 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B55" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C55" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D55" s="3" t="str">
         <x:v>徐汇实验幼儿园</x:v>
       </x:c>
-      <x:c r="C55" s="3" t="str">
+      <x:c r="E55" s="3" t="str">
         <x:v>华泾/罗秀</x:v>
       </x:c>
-      <x:c r="D55" s="3" t="str">
+      <x:c r="F55" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E55" s="3" t="str">
+      <x:c r="G55" s="3" t="str">
         <x:v>龙瑞路135号</x:v>
       </x:c>
-      <x:c r="F55" s="3" t="str">
+      <x:c r="H55" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%BE%90%E6%B1%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E7%91%9E%E8%B7%AF135%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G55" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H55" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I55" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J55" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K55" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L55" s="3" t="str">
         <x:v>中海瀛台、百龙、港口</x:v>
       </x:c>
-      <x:c r="J55" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K55" s="3" t="str"/>
-      <x:c r="L55" s="3" t="str">
+      <x:c r="M55" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N55" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O55" s="3" t="str"/>
+      <x:c r="P55" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3560,34 +4242,46 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B56" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C56" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D56" s="3" t="str">
         <x:v>印象幼儿园</x:v>
       </x:c>
-      <x:c r="C56" s="3" t="str">
+      <x:c r="E56" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="D56" s="3" t="str">
+      <x:c r="F56" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E56" s="3" t="str">
+      <x:c r="G56" s="3" t="str">
         <x:v>望月路882号</x:v>
       </x:c>
-      <x:c r="F56" s="3" t="str">
+      <x:c r="H56" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%8D%B0%E8%B1%A1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%9C%9B%E6%9C%88%E8%B7%AF882%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G56" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H56" s="3" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I56" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J56" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K56" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L56" s="3" t="str">
         <x:v>印象、华阳、沙家浜</x:v>
       </x:c>
-      <x:c r="J56" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K56" s="3" t="str"/>
-      <x:c r="L56" s="3" t="str">
+      <x:c r="M56" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N56" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O56" s="3" t="str"/>
+      <x:c r="P56" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3596,34 +4290,46 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B57" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C57" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D57" s="3" t="str">
         <x:v>科技逸夫幼儿园</x:v>
       </x:c>
-      <x:c r="C57" s="3" t="str">
+      <x:c r="E57" s="3" t="str">
         <x:v>南站/石龙</x:v>
       </x:c>
-      <x:c r="D57" s="3" t="str">
+      <x:c r="F57" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E57" s="3" t="str">
+      <x:c r="G57" s="3" t="str">
         <x:v>石龙路818弄8号</x:v>
       </x:c>
-      <x:c r="F57" s="3" t="str">
+      <x:c r="H57" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E9%80%B8%E5%A4%AB%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%9F%B3%E9%BE%99%E8%B7%AF818%E5%BC%848%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G57" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H57" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="I57" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J57" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K57" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L57" s="3" t="str">
         <x:v>正南、东荡、南站居委（临）</x:v>
       </x:c>
-      <x:c r="J57" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K57" s="3" t="str"/>
-      <x:c r="L57" s="3" t="str">
+      <x:c r="M57" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N57" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O57" s="3" t="str"/>
+      <x:c r="P57" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3632,34 +4338,46 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B58" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C58" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D58" s="3" t="str">
         <x:v>盛华幼儿园</x:v>
       </x:c>
-      <x:c r="C58" s="3" t="str">
+      <x:c r="E58" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="D58" s="3" t="str">
+      <x:c r="F58" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E58" s="3" t="str">
+      <x:c r="G58" s="3" t="str">
         <x:v>望月路401号</x:v>
       </x:c>
-      <x:c r="F58" s="3" t="str">
+      <x:c r="H58" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%9B%9B%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%9C%9B%E6%9C%88%E8%B7%AF401%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G58" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H58" s="3" t="n">
+      <x:c r="I58" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J58" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K58" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I58" s="3" t="str">
+      <x:c r="L58" s="3" t="str">
         <x:v>盛华、华泾绿苑、光华绿苑</x:v>
       </x:c>
-      <x:c r="J58" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K58" s="3" t="str"/>
-      <x:c r="L58" s="3" t="str">
+      <x:c r="M58" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N58" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O58" s="3" t="str"/>
+      <x:c r="P58" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3668,34 +4386,46 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B59" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C59" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D59" s="3" t="str">
         <x:v>艺树幼儿园</x:v>
       </x:c>
-      <x:c r="C59" s="3" t="str">
+      <x:c r="E59" s="3" t="str">
         <x:v>徐家汇/田林</x:v>
       </x:c>
-      <x:c r="D59" s="3" t="str">
+      <x:c r="F59" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E59" s="3" t="str">
+      <x:c r="G59" s="3" t="str">
         <x:v>古井路160号</x:v>
       </x:c>
-      <x:c r="F59" s="3" t="str">
+      <x:c r="H59" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%89%BA%E6%A0%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E4%BA%95%E8%B7%AF160%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G59" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H59" s="3" t="n">
+      <x:c r="I59" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J59" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K59" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I59" s="3" t="str">
+      <x:c r="L59" s="3" t="str">
         <x:v>锦馨苑、千鹤第六、小安桥、华鼎广场、千鹤五、尚汇豪庭、千鹤一、千鹤二；另向徐家汇街道、田林街道扩招</x:v>
       </x:c>
-      <x:c r="J59" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K59" s="3" t="str"/>
-      <x:c r="L59" s="3" t="str">
+      <x:c r="M59" s="3" t="str">
+        <x:v>扩招</x:v>
+      </x:c>
+      <x:c r="N59" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O59" s="3" t="str"/>
+      <x:c r="P59" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3704,34 +4434,46 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B60" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C60" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D60" s="3" t="str">
         <x:v>桂平幼儿园</x:v>
       </x:c>
-      <x:c r="C60" s="3" t="str">
+      <x:c r="E60" s="3" t="str">
         <x:v>漕河泾/虹梅</x:v>
       </x:c>
-      <x:c r="D60" s="3" t="str">
+      <x:c r="F60" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E60" s="3" t="str">
+      <x:c r="G60" s="3" t="str">
         <x:v>桂平路260弄14号</x:v>
       </x:c>
-      <x:c r="F60" s="3" t="str">
+      <x:c r="H60" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A1%82%E5%B9%B3%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E5%B9%B3%E8%B7%AF260%E5%BC%8414%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G60" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H60" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="I60" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J60" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K60" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L60" s="3" t="str">
         <x:v>联莘、欣园</x:v>
       </x:c>
-      <x:c r="J60" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K60" s="3" t="str"/>
-      <x:c r="L60" s="3" t="str">
+      <x:c r="M60" s="3" t="str">
+        <x:v>固定对口</x:v>
+      </x:c>
+      <x:c r="N60" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O60" s="3" t="str"/>
+      <x:c r="P60" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3740,34 +4482,46 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B61" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C61" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D61" s="3" t="str">
         <x:v>田林第六幼儿园</x:v>
       </x:c>
-      <x:c r="C61" s="3" t="str">
+      <x:c r="E61" s="3" t="str">
         <x:v>田林/虹梅</x:v>
       </x:c>
-      <x:c r="D61" s="3" t="str">
+      <x:c r="F61" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E61" s="3" t="str">
+      <x:c r="G61" s="3" t="str">
         <x:v>田林十二村40号</x:v>
       </x:c>
-      <x:c r="F61" s="3" t="str">
+      <x:c r="H61" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E7%AC%AC%E5%85%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%8D%81%E4%BA%8C%E6%9D%9140%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G61" s="3" t="str">
+      <x:c r="I61" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J61" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H61" s="3" t="n">
+      <x:c r="K61" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I61" s="3" t="str">
+      <x:c r="L61" s="3" t="str">
         <x:v>田林十二村、田林三四村、古一、古二、古三、古四、东兰、航天新苑、永兆、漕河泾开发园区（临）；另向田林街道、虹梅路街道扩招</x:v>
       </x:c>
-      <x:c r="J61" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K61" s="3" t="str"/>
-      <x:c r="L61" s="3" t="str">
+      <x:c r="M61" s="3" t="str">
+        <x:v>扩招</x:v>
+      </x:c>
+      <x:c r="N61" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O61" s="3" t="str"/>
+      <x:c r="P61" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3776,34 +4530,46 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B62" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C62" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D62" s="3" t="str">
         <x:v>田林第六幼儿园</x:v>
       </x:c>
-      <x:c r="C62" s="3" t="str">
+      <x:c r="E62" s="3" t="str">
         <x:v>田林/虹梅</x:v>
       </x:c>
-      <x:c r="D62" s="3" t="str">
+      <x:c r="F62" s="3" t="str">
         <x:v>贝贝分园</x:v>
       </x:c>
-      <x:c r="E62" s="3" t="str">
+      <x:c r="G62" s="3" t="str">
         <x:v>田林四村18号</x:v>
       </x:c>
-      <x:c r="F62" s="3" t="str">
+      <x:c r="H62" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E7%AC%AC%E5%85%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E8%B4%9D%E8%B4%9D%E5%88%86%E5%9B%AD%20%E7%94%B0%E6%9E%97%E5%9B%9B%E6%9D%9118%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G62" s="3" t="str">
+      <x:c r="I62" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J62" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H62" s="3" t="n">
+      <x:c r="K62" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I62" s="3" t="str">
+      <x:c r="L62" s="3" t="str">
         <x:v>田林十二村、田林三四村、古一、古二、古三、古四、东兰、航天新苑、永兆、漕河泾开发园区（临）；另向田林街道、虹梅路街道扩招</x:v>
       </x:c>
-      <x:c r="J62" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K62" s="3" t="str"/>
-      <x:c r="L62" s="3" t="str">
+      <x:c r="M62" s="3" t="str">
+        <x:v>扩招</x:v>
+      </x:c>
+      <x:c r="N62" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O62" s="3" t="str"/>
+      <x:c r="P62" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3812,34 +4578,46 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B63" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C63" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D63" s="3" t="str">
         <x:v>田林第六幼儿园</x:v>
       </x:c>
-      <x:c r="C63" s="3" t="str">
+      <x:c r="E63" s="3" t="str">
         <x:v>田林/虹梅</x:v>
       </x:c>
-      <x:c r="D63" s="3" t="str">
+      <x:c r="F63" s="3" t="str">
         <x:v>东兰分园</x:v>
       </x:c>
-      <x:c r="E63" s="3" t="str">
+      <x:c r="G63" s="3" t="str">
         <x:v>古美路1107弄65号</x:v>
       </x:c>
-      <x:c r="F63" s="3" t="str">
+      <x:c r="H63" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E7%AC%AC%E5%85%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%9C%E5%85%B0%E5%88%86%E5%9B%AD%20%E5%8F%A4%E7%BE%8E%E8%B7%AF1107%E5%BC%8465%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G63" s="3" t="str">
+      <x:c r="I63" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J63" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H63" s="3" t="n">
+      <x:c r="K63" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I63" s="3" t="str">
+      <x:c r="L63" s="3" t="str">
         <x:v>田林十二村、田林三四村、古一、古二、古三、古四、东兰、航天新苑、永兆、漕河泾开发园区（临）；另向田林街道、虹梅路街道扩招</x:v>
       </x:c>
-      <x:c r="J63" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K63" s="3" t="str"/>
-      <x:c r="L63" s="3" t="str">
+      <x:c r="M63" s="3" t="str">
+        <x:v>扩招</x:v>
+      </x:c>
+      <x:c r="N63" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O63" s="3" t="str"/>
+      <x:c r="P63" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3848,34 +4626,46 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B64" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C64" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D64" s="3" t="str">
         <x:v>紫薇实验幼儿园</x:v>
       </x:c>
-      <x:c r="C64" s="3" t="str">
+      <x:c r="E64" s="3" t="str">
         <x:v>康健/漕河泾</x:v>
       </x:c>
-      <x:c r="D64" s="3" t="str">
+      <x:c r="F64" s="3" t="str">
         <x:v>桂平园</x:v>
       </x:c>
-      <x:c r="E64" s="3" t="str">
+      <x:c r="G64" s="3" t="str">
         <x:v>桂平路123弄23号</x:v>
       </x:c>
-      <x:c r="F64" s="3" t="str">
+      <x:c r="H64" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%B4%AB%E8%96%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%A1%82%E5%B9%B3%E5%9B%AD%20%E6%A1%82%E5%B9%B3%E8%B7%AF123%E5%BC%8423%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G64" s="3" t="str">
+      <x:c r="I64" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J64" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H64" s="3" t="n">
+      <x:c r="K64" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I64" s="3" t="str">
+      <x:c r="L64" s="3" t="str">
         <x:v>紫薇园（桂平路123弄）、康强海（海上名邸）；区域内自主招生</x:v>
       </x:c>
-      <x:c r="J64" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K64" s="3" t="str"/>
-      <x:c r="L64" s="3" t="str">
+      <x:c r="M64" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N64" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O64" s="3" t="str"/>
+      <x:c r="P64" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3884,34 +4674,46 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B65" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C65" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D65" s="3" t="str">
         <x:v>紫薇实验幼儿园</x:v>
       </x:c>
-      <x:c r="C65" s="3" t="str">
+      <x:c r="E65" s="3" t="str">
         <x:v>康健/漕河泾</x:v>
       </x:c>
-      <x:c r="D65" s="3" t="str">
+      <x:c r="F65" s="3" t="str">
         <x:v>浦北园</x:v>
       </x:c>
-      <x:c r="E65" s="3" t="str">
+      <x:c r="G65" s="3" t="str">
         <x:v>浦北路173号</x:v>
       </x:c>
-      <x:c r="F65" s="3" t="str">
+      <x:c r="H65" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%B4%AB%E8%96%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%B5%A6%E5%8C%97%E5%9B%AD%20%E6%B5%A6%E5%8C%97%E8%B7%AF173%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G65" s="3" t="str">
+      <x:c r="I65" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J65" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H65" s="3" t="n">
+      <x:c r="K65" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I65" s="3" t="str">
+      <x:c r="L65" s="3" t="str">
         <x:v>紫薇园（桂平路123弄）、康强海（海上名邸）；区域内自主招生</x:v>
       </x:c>
-      <x:c r="J65" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K65" s="3" t="str"/>
-      <x:c r="L65" s="3" t="str">
+      <x:c r="M65" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N65" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O65" s="3" t="str"/>
+      <x:c r="P65" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3920,34 +4722,46 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B66" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C66" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D66" s="3" t="str">
         <x:v>紫薇实验幼儿园</x:v>
       </x:c>
-      <x:c r="C66" s="3" t="str">
+      <x:c r="E66" s="3" t="str">
         <x:v>康健/漕河泾</x:v>
       </x:c>
-      <x:c r="D66" s="3" t="str">
+      <x:c r="F66" s="3" t="str">
         <x:v>全州园</x:v>
       </x:c>
-      <x:c r="E66" s="3" t="str">
+      <x:c r="G66" s="3" t="str">
         <x:v>宜州路26号</x:v>
       </x:c>
-      <x:c r="F66" s="3" t="str">
+      <x:c r="H66" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%B4%AB%E8%96%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%85%A8%E5%B7%9E%E5%9B%AD%20%E5%AE%9C%E5%B7%9E%E8%B7%AF26%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G66" s="3" t="str">
+      <x:c r="I66" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J66" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H66" s="3" t="n">
+      <x:c r="K66" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I66" s="3" t="str">
+      <x:c r="L66" s="3" t="str">
         <x:v>紫薇园（桂平路123弄）、康强海（海上名邸）；区域内自主招生</x:v>
       </x:c>
-      <x:c r="J66" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K66" s="3" t="str"/>
-      <x:c r="L66" s="3" t="str">
+      <x:c r="M66" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N66" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O66" s="3" t="str"/>
+      <x:c r="P66" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3956,34 +4770,46 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B67" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C67" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D67" s="3" t="str">
         <x:v>上海幼儿园</x:v>
       </x:c>
-      <x:c r="C67" s="3" t="str">
+      <x:c r="E67" s="3" t="str">
         <x:v>长桥/凌云</x:v>
       </x:c>
-      <x:c r="D67" s="3" t="str">
+      <x:c r="F67" s="3" t="str">
         <x:v>凌云园</x:v>
       </x:c>
-      <x:c r="E67" s="3" t="str">
+      <x:c r="G67" s="3" t="str">
         <x:v>上中西路378号</x:v>
       </x:c>
-      <x:c r="F67" s="3" t="str">
+      <x:c r="H67" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%8A%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%87%8C%E4%BA%91%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E8%A5%BF%E8%B7%AF378%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G67" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H67" s="3" t="n">
+      <x:c r="I67" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J67" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K67" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I67" s="3" t="str">
+      <x:c r="L67" s="3" t="str">
         <x:v>体育花苑、长桥五村（上中路100弄）、长桥三村二（尚海悦庭）；另向凌云路街道、长桥街道、华泾镇扩招</x:v>
       </x:c>
-      <x:c r="J67" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K67" s="3" t="str"/>
-      <x:c r="L67" s="3" t="str">
+      <x:c r="M67" s="3" t="str">
+        <x:v>扩招</x:v>
+      </x:c>
+      <x:c r="N67" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O67" s="3" t="str"/>
+      <x:c r="P67" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3992,34 +4818,46 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B68" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C68" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D68" s="3" t="str">
         <x:v>上海幼儿园</x:v>
       </x:c>
-      <x:c r="C68" s="3" t="str">
+      <x:c r="E68" s="3" t="str">
         <x:v>长桥/凌云</x:v>
       </x:c>
-      <x:c r="D68" s="3" t="str">
+      <x:c r="F68" s="3" t="str">
         <x:v>冠军园</x:v>
       </x:c>
-      <x:c r="E68" s="3" t="str">
+      <x:c r="G68" s="3" t="str">
         <x:v>老沪闵路729弄41号乙</x:v>
       </x:c>
-      <x:c r="F68" s="3" t="str">
+      <x:c r="H68" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%8A%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%86%A0%E5%86%9B%E5%9B%AD%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF729%E5%BC%8441%E5%8F%B7%E4%B9%99</x:v>
       </x:c>
-      <x:c r="G68" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H68" s="3" t="n">
+      <x:c r="I68" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J68" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K68" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I68" s="3" t="str">
+      <x:c r="L68" s="3" t="str">
         <x:v>体育花苑、长桥五村（上中路100弄）、长桥三村二（尚海悦庭）；另向凌云路街道、长桥街道、华泾镇扩招</x:v>
       </x:c>
-      <x:c r="J68" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K68" s="3" t="str"/>
-      <x:c r="L68" s="3" t="str">
+      <x:c r="M68" s="3" t="str">
+        <x:v>扩招</x:v>
+      </x:c>
+      <x:c r="N68" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O68" s="3" t="str"/>
+      <x:c r="P68" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4028,34 +4866,46 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B69" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C69" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D69" s="3" t="str">
         <x:v>上海幼儿园</x:v>
       </x:c>
-      <x:c r="C69" s="3" t="str">
+      <x:c r="E69" s="3" t="str">
         <x:v>长桥/凌云</x:v>
       </x:c>
-      <x:c r="D69" s="3" t="str">
+      <x:c r="F69" s="3" t="str">
         <x:v>上中园</x:v>
       </x:c>
-      <x:c r="E69" s="3" t="str">
+      <x:c r="G69" s="3" t="str">
         <x:v>上中路402号</x:v>
       </x:c>
-      <x:c r="F69" s="3" t="str">
+      <x:c r="H69" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%8A%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E8%B7%AF402%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G69" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H69" s="3" t="n">
+      <x:c r="I69" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J69" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K69" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I69" s="3" t="str">
+      <x:c r="L69" s="3" t="str">
         <x:v>体育花苑、长桥五村（上中路100弄）、长桥三村二（尚海悦庭）；另向凌云路街道、长桥街道、华泾镇扩招</x:v>
       </x:c>
-      <x:c r="J69" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K69" s="3" t="str"/>
-      <x:c r="L69" s="3" t="str">
+      <x:c r="M69" s="3" t="str">
+        <x:v>扩招</x:v>
+      </x:c>
+      <x:c r="N69" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O69" s="3" t="str"/>
+      <x:c r="P69" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4064,34 +4914,46 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B70" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C70" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D70" s="3" t="str">
         <x:v>乌鲁木齐南路幼儿园</x:v>
       </x:c>
-      <x:c r="C70" s="3" t="str">
+      <x:c r="E70" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="D70" s="3" t="str">
+      <x:c r="F70" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="E70" s="3" t="str">
+      <x:c r="G70" s="3" t="str">
         <x:v>乌鲁木齐南路14号</x:v>
       </x:c>
-      <x:c r="F70" s="3" t="str">
+      <x:c r="H70" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF14%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G70" s="3" t="str">
+      <x:c r="I70" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J70" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H70" s="3" t="n">
+      <x:c r="K70" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I70" s="3" t="str">
+      <x:c r="L70" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J70" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K70" s="3" t="str"/>
-      <x:c r="L70" s="3" t="str">
+      <x:c r="M70" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N70" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O70" s="3" t="str"/>
+      <x:c r="P70" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4100,34 +4962,46 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B71" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C71" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D71" s="3" t="str">
         <x:v>乌鲁木齐南路幼儿园</x:v>
       </x:c>
-      <x:c r="C71" s="3" t="str">
+      <x:c r="E71" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="D71" s="3" t="str">
+      <x:c r="F71" s="3" t="str">
         <x:v>境内部</x:v>
       </x:c>
-      <x:c r="E71" s="3" t="str">
+      <x:c r="G71" s="3" t="str">
         <x:v>淮海路1788号</x:v>
       </x:c>
-      <x:c r="F71" s="3" t="str">
+      <x:c r="H71" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A2%83%E5%86%85%E9%83%A8%20%E6%B7%AE%E6%B5%B7%E8%B7%AF1788%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G71" s="3" t="str">
+      <x:c r="I71" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J71" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H71" s="3" t="n">
+      <x:c r="K71" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I71" s="3" t="str">
+      <x:c r="L71" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J71" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K71" s="3" t="str"/>
-      <x:c r="L71" s="3" t="str">
+      <x:c r="M71" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N71" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O71" s="3" t="str"/>
+      <x:c r="P71" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4136,34 +5010,46 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B72" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C72" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D72" s="3" t="str">
         <x:v>乌鲁木齐南路幼儿园</x:v>
       </x:c>
-      <x:c r="C72" s="3" t="str">
+      <x:c r="E72" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="D72" s="3" t="str">
+      <x:c r="F72" s="3" t="str">
         <x:v>境外部</x:v>
       </x:c>
-      <x:c r="E72" s="3" t="str">
+      <x:c r="G72" s="3" t="str">
         <x:v>淮海中路1480号</x:v>
       </x:c>
-      <x:c r="F72" s="3" t="str">
+      <x:c r="H72" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A2%83%E5%A4%96%E9%83%A8%20%E6%B7%AE%E6%B5%B7%E4%B8%AD%E8%B7%AF1480%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G72" s="3" t="str">
+      <x:c r="I72" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J72" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H72" s="3" t="n">
+      <x:c r="K72" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I72" s="3" t="str">
+      <x:c r="L72" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J72" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K72" s="3" t="str"/>
-      <x:c r="L72" s="3" t="str">
+      <x:c r="M72" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N72" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O72" s="3" t="str"/>
+      <x:c r="P72" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4172,34 +5058,46 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B73" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C73" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D73" s="3" t="str">
         <x:v>科技幼儿园</x:v>
       </x:c>
-      <x:c r="C73" s="3" t="str">
+      <x:c r="E73" s="3" t="str">
         <x:v>徐家汇/田林</x:v>
       </x:c>
-      <x:c r="D73" s="3" t="str">
+      <x:c r="F73" s="3" t="str">
         <x:v>宜山园1部</x:v>
       </x:c>
-      <x:c r="E73" s="3" t="str">
+      <x:c r="G73" s="3" t="str">
         <x:v>宜山路655弄1号</x:v>
       </x:c>
-      <x:c r="F73" s="3" t="str">
+      <x:c r="H73" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%AE%9C%E5%B1%B1%E5%9B%AD1%E9%83%A8%20%E5%AE%9C%E5%B1%B1%E8%B7%AF655%E5%BC%841%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G73" s="3" t="str">
+      <x:c r="I73" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J73" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H73" s="3" t="n">
+      <x:c r="K73" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I73" s="3" t="str">
+      <x:c r="L73" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J73" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K73" s="3" t="str"/>
-      <x:c r="L73" s="3" t="str">
+      <x:c r="M73" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N73" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O73" s="3" t="str"/>
+      <x:c r="P73" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4208,34 +5106,46 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B74" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C74" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D74" s="3" t="str">
         <x:v>科技幼儿园</x:v>
       </x:c>
-      <x:c r="C74" s="3" t="str">
+      <x:c r="E74" s="3" t="str">
         <x:v>徐家汇/田林</x:v>
       </x:c>
-      <x:c r="D74" s="3" t="str">
+      <x:c r="F74" s="3" t="str">
         <x:v>嘉陵园</x:v>
       </x:c>
-      <x:c r="E74" s="3" t="str">
+      <x:c r="G74" s="3" t="str">
         <x:v>嘉陵路28号</x:v>
       </x:c>
-      <x:c r="F74" s="3" t="str">
+      <x:c r="H74" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%98%89%E9%99%B5%E5%9B%AD%20%E5%98%89%E9%99%B5%E8%B7%AF28%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G74" s="3" t="str">
+      <x:c r="I74" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J74" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H74" s="3" t="n">
+      <x:c r="K74" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I74" s="3" t="str">
+      <x:c r="L74" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J74" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K74" s="3" t="str"/>
-      <x:c r="L74" s="3" t="str">
+      <x:c r="M74" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N74" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O74" s="3" t="str"/>
+      <x:c r="P74" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4244,34 +5154,46 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B75" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C75" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D75" s="3" t="str">
         <x:v>科技幼儿园</x:v>
       </x:c>
-      <x:c r="C75" s="3" t="str">
+      <x:c r="E75" s="3" t="str">
         <x:v>徐家汇/田林</x:v>
       </x:c>
-      <x:c r="D75" s="3" t="str">
+      <x:c r="F75" s="3" t="str">
         <x:v>文定园</x:v>
       </x:c>
-      <x:c r="E75" s="3" t="str">
+      <x:c r="G75" s="3" t="str">
         <x:v>文定路476号</x:v>
       </x:c>
-      <x:c r="F75" s="3" t="str">
+      <x:c r="H75" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%96%87%E5%AE%9A%E5%9B%AD%20%E6%96%87%E5%AE%9A%E8%B7%AF476%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G75" s="3" t="str">
+      <x:c r="I75" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J75" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H75" s="3" t="n">
+      <x:c r="K75" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I75" s="3" t="str">
+      <x:c r="L75" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J75" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K75" s="3" t="str"/>
-      <x:c r="L75" s="3" t="str">
+      <x:c r="M75" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N75" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O75" s="3" t="str"/>
+      <x:c r="P75" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4280,34 +5202,46 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B76" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C76" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D76" s="3" t="str">
         <x:v>科技幼儿园</x:v>
       </x:c>
-      <x:c r="C76" s="3" t="str">
+      <x:c r="E76" s="3" t="str">
         <x:v>徐家汇/田林</x:v>
       </x:c>
-      <x:c r="D76" s="3" t="str">
+      <x:c r="F76" s="3" t="str">
         <x:v>宜山园10部</x:v>
       </x:c>
-      <x:c r="E76" s="3" t="str">
+      <x:c r="G76" s="3" t="str">
         <x:v>宜山路655弄10号</x:v>
       </x:c>
-      <x:c r="F76" s="3" t="str">
+      <x:c r="H76" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%AE%9C%E5%B1%B1%E5%9B%AD10%E9%83%A8%20%E5%AE%9C%E5%B1%B1%E8%B7%AF655%E5%BC%8410%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G76" s="3" t="str">
+      <x:c r="I76" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J76" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H76" s="3" t="n">
+      <x:c r="K76" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="I76" s="3" t="str">
+      <x:c r="L76" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J76" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K76" s="3" t="str"/>
-      <x:c r="L76" s="3" t="str">
+      <x:c r="M76" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N76" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O76" s="3" t="str"/>
+      <x:c r="P76" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4316,34 +5250,46 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B77" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C77" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D77" s="3" t="str">
         <x:v>宛南实验幼儿园</x:v>
       </x:c>
-      <x:c r="C77" s="3" t="str">
+      <x:c r="E77" s="3" t="str">
         <x:v>龙华/滨江</x:v>
       </x:c>
-      <x:c r="D77" s="3" t="str">
+      <x:c r="F77" s="3" t="str">
         <x:v>瑞宁部</x:v>
       </x:c>
-      <x:c r="E77" s="3" t="str">
+      <x:c r="G77" s="3" t="str">
         <x:v>瑞宁路816号</x:v>
       </x:c>
-      <x:c r="F77" s="3" t="str">
+      <x:c r="H77" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%9B%E5%8D%97%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E7%91%9E%E5%AE%81%E9%83%A8%20%E7%91%9E%E5%AE%81%E8%B7%AF816%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G77" s="3" t="str">
+      <x:c r="I77" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J77" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H77" s="3" t="n">
+      <x:c r="K77" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I77" s="3" t="str">
+      <x:c r="L77" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J77" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K77" s="3" t="str"/>
-      <x:c r="L77" s="3" t="str">
+      <x:c r="M77" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N77" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O77" s="3" t="str"/>
+      <x:c r="P77" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4352,34 +5298,46 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B78" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C78" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D78" s="3" t="str">
         <x:v>宛南实验幼儿园</x:v>
       </x:c>
-      <x:c r="C78" s="3" t="str">
+      <x:c r="E78" s="3" t="str">
         <x:v>龙华/滨江</x:v>
       </x:c>
-      <x:c r="D78" s="3" t="str">
+      <x:c r="F78" s="3" t="str">
         <x:v>滨江部</x:v>
       </x:c>
-      <x:c r="E78" s="3" t="str">
+      <x:c r="G78" s="3" t="str">
         <x:v>瑞宁路851号</x:v>
       </x:c>
-      <x:c r="F78" s="3" t="str">
+      <x:c r="H78" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%9B%E5%8D%97%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%BB%A8%E6%B1%9F%E9%83%A8%20%E7%91%9E%E5%AE%81%E8%B7%AF851%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G78" s="3" t="str">
+      <x:c r="I78" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J78" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H78" s="3" t="n">
+      <x:c r="K78" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I78" s="3" t="str">
+      <x:c r="L78" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J78" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K78" s="3" t="str"/>
-      <x:c r="L78" s="3" t="str">
+      <x:c r="M78" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N78" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O78" s="3" t="str"/>
+      <x:c r="P78" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4388,34 +5346,46 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B79" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C79" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D79" s="3" t="str">
         <x:v>宛南实验幼儿园</x:v>
       </x:c>
-      <x:c r="C79" s="3" t="str">
+      <x:c r="E79" s="3" t="str">
         <x:v>龙华/滨江</x:v>
       </x:c>
-      <x:c r="D79" s="3" t="str">
+      <x:c r="F79" s="3" t="str">
         <x:v>大木桥部</x:v>
       </x:c>
-      <x:c r="E79" s="3" t="str">
+      <x:c r="G79" s="3" t="str">
         <x:v>大木桥路323号</x:v>
       </x:c>
-      <x:c r="F79" s="3" t="str">
+      <x:c r="H79" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%9B%E5%8D%97%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A4%A7%E6%9C%A8%E6%A1%A5%E9%83%A8%20%E5%A4%A7%E6%9C%A8%E6%A1%A5%E8%B7%AF323%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G79" s="3" t="str">
+      <x:c r="I79" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J79" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H79" s="3" t="n">
+      <x:c r="K79" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I79" s="3" t="str">
+      <x:c r="L79" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J79" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K79" s="3" t="str"/>
-      <x:c r="L79" s="3" t="str">
+      <x:c r="M79" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N79" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O79" s="3" t="str"/>
+      <x:c r="P79" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4424,34 +5394,46 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B80" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C80" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D80" s="3" t="str">
         <x:v>机关建国幼儿园</x:v>
       </x:c>
-      <x:c r="C80" s="3" t="str">
+      <x:c r="E80" s="3" t="str">
         <x:v>衡复/湖南/滨江</x:v>
       </x:c>
-      <x:c r="D80" s="3" t="str">
+      <x:c r="F80" s="3" t="str">
         <x:v>建国园</x:v>
       </x:c>
-      <x:c r="E80" s="3" t="str">
+      <x:c r="G80" s="3" t="str">
         <x:v>建国西路570号</x:v>
       </x:c>
-      <x:c r="F80" s="3" t="str">
+      <x:c r="H80" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%BA%E5%85%B3%E5%BB%BA%E5%9B%BD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%BB%BA%E5%9B%BD%E5%9B%AD%20%E5%BB%BA%E5%9B%BD%E8%A5%BF%E8%B7%AF570%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G80" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H80" s="3" t="n">
+      <x:c r="I80" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J80" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K80" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I80" s="3" t="str">
+      <x:c r="L80" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J80" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K80" s="3" t="str"/>
-      <x:c r="L80" s="3" t="str">
+      <x:c r="M80" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N80" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O80" s="3" t="str"/>
+      <x:c r="P80" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4460,34 +5442,46 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B81" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C81" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D81" s="3" t="str">
         <x:v>机关建国幼儿园</x:v>
       </x:c>
-      <x:c r="C81" s="3" t="str">
+      <x:c r="E81" s="3" t="str">
         <x:v>衡复/湖南/滨江</x:v>
       </x:c>
-      <x:c r="D81" s="3" t="str">
+      <x:c r="F81" s="3" t="str">
         <x:v>安亭园</x:v>
       </x:c>
-      <x:c r="E81" s="3" t="str">
+      <x:c r="G81" s="3" t="str">
         <x:v>安亭路112号</x:v>
       </x:c>
-      <x:c r="F81" s="3" t="str">
+      <x:c r="H81" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%BA%E5%85%B3%E5%BB%BA%E5%9B%BD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%AE%89%E4%BA%AD%E5%9B%AD%20%E5%AE%89%E4%BA%AD%E8%B7%AF112%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G81" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H81" s="3" t="n">
+      <x:c r="I81" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J81" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K81" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I81" s="3" t="str">
+      <x:c r="L81" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J81" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K81" s="3" t="str"/>
-      <x:c r="L81" s="3" t="str">
+      <x:c r="M81" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N81" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O81" s="3" t="str"/>
+      <x:c r="P81" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4496,35 +5490,2197 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B82" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="C82" s="3" t="str">
+        <x:v>公办</x:v>
+      </x:c>
+      <x:c r="D82" s="3" t="str">
         <x:v>机关建国幼儿园</x:v>
       </x:c>
-      <x:c r="C82" s="3" t="str">
+      <x:c r="E82" s="3" t="str">
         <x:v>衡复/湖南/滨江</x:v>
       </x:c>
-      <x:c r="D82" s="3" t="str">
+      <x:c r="F82" s="3" t="str">
         <x:v>滨江园</x:v>
       </x:c>
-      <x:c r="E82" s="3" t="str">
+      <x:c r="G82" s="3" t="str">
         <x:v>云锦路183弄30号</x:v>
       </x:c>
-      <x:c r="F82" s="3" t="str">
+      <x:c r="H82" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%BA%E5%85%B3%E5%BB%BA%E5%9B%BD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%BB%A8%E6%B1%9F%E5%9B%AD%20%E4%BA%91%E9%94%A6%E8%B7%AF183%E5%BC%8430%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="G82" s="3" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H82" s="3" t="n">
+      <x:c r="I82" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="J82" s="3" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K82" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I82" s="3" t="str">
+      <x:c r="L82" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="J82" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="K82" s="3" t="str"/>
-      <x:c r="L82" s="3" t="str">
+      <x:c r="M82" s="3" t="str">
+        <x:v>区域自主</x:v>
+      </x:c>
+      <x:c r="N82" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O82" s="3" t="str"/>
+      <x:c r="P82" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="3" t="str">
+        <x:v>M1</x:v>
+      </x:c>
+      <x:c r="B83" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C83" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D83" s="3" t="str">
+        <x:v>维亚幼儿园</x:v>
+      </x:c>
+      <x:c r="E83" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="F83" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G83" s="3" t="str">
+        <x:v>华亭路71弄1号</x:v>
+      </x:c>
+      <x:c r="H83" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%BB%B4%E4%BA%9A%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8D%8E%E4%BA%AD%E8%B7%AF71%E5%BC%841%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I83" s="3" t="str">
+        <x:v>54036901</x:v>
+      </x:c>
+      <x:c r="J83" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K83" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L83" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M83" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N83" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O83" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P83" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="3" t="str">
+        <x:v>M2</x:v>
+      </x:c>
+      <x:c r="B84" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C84" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D84" s="3" t="str">
+        <x:v>四季方馨幼儿园</x:v>
+      </x:c>
+      <x:c r="E84" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="F84" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G84" s="3" t="str">
+        <x:v>五原路112号</x:v>
+      </x:c>
+      <x:c r="H84" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9B%9B%E5%AD%A3%E6%96%B9%E9%A6%A8%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%BA%94%E5%8E%9F%E8%B7%AF112%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I84" s="3" t="str">
+        <x:v>021-54036603</x:v>
+      </x:c>
+      <x:c r="J84" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K84" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L84" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M84" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N84" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O84" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P84" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="3" t="str">
+        <x:v>M3</x:v>
+      </x:c>
+      <x:c r="B85" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C85" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D85" s="3" t="str">
+        <x:v>滨江幼儿园</x:v>
+      </x:c>
+      <x:c r="E85" s="3" t="str">
+        <x:v>龙华/滨江</x:v>
+      </x:c>
+      <x:c r="F85" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G85" s="3" t="str">
+        <x:v>云锦路80弄10号</x:v>
+      </x:c>
+      <x:c r="H85" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BB%A8%E6%B1%9F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%BA%91%E9%94%A6%E8%B7%AF80%E5%BC%8410%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I85" s="3" t="str">
+        <x:v>64380700</x:v>
+      </x:c>
+      <x:c r="J85" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K85" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L85" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M85" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N85" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O85" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P85" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="3" t="str">
+        <x:v>M4</x:v>
+      </x:c>
+      <x:c r="B86" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C86" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D86" s="3" t="str">
+        <x:v>汇宝幼儿园</x:v>
+      </x:c>
+      <x:c r="E86" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="F86" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G86" s="3" t="str">
+        <x:v>宛平南路592号</x:v>
+      </x:c>
+      <x:c r="H86" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9B%E5%B9%B3%E5%8D%97%E8%B7%AF592%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I86" s="3" t="str">
+        <x:v>64690445</x:v>
+      </x:c>
+      <x:c r="J86" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K86" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L86" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M86" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N86" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O86" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P86" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="3" t="str">
+        <x:v>M5</x:v>
+      </x:c>
+      <x:c r="B87" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C87" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D87" s="3" t="str">
+        <x:v>蒙世学堂幼儿园</x:v>
+      </x:c>
+      <x:c r="E87" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="F87" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G87" s="3" t="str">
+        <x:v>斜土路2421号</x:v>
+      </x:c>
+      <x:c r="H87" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%92%99%E4%B8%96%E5%AD%A6%E5%A0%82%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%96%9C%E5%9C%9F%E8%B7%AF2421%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I87" s="3" t="str">
+        <x:v>021-64686261*8103</x:v>
+      </x:c>
+      <x:c r="J87" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K87" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L87" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M87" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N87" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O87" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P87" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="3" t="str">
+        <x:v>M6</x:v>
+      </x:c>
+      <x:c r="B88" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C88" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D88" s="3" t="str">
+        <x:v>樱花园幼稚园</x:v>
+      </x:c>
+      <x:c r="E88" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="F88" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G88" s="3" t="str">
+        <x:v>百花街380号</x:v>
+      </x:c>
+      <x:c r="H88" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A8%B1%E8%8A%B1%E5%9B%AD%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%99%BE%E8%8A%B1%E8%A1%97380%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I88" s="3" t="str">
+        <x:v>54185106</x:v>
+      </x:c>
+      <x:c r="J88" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K88" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L88" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M88" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N88" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O88" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P88" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="3" t="str">
+        <x:v>M7</x:v>
+      </x:c>
+      <x:c r="B89" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C89" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D89" s="3" t="str">
+        <x:v>新宜幼稚园</x:v>
+      </x:c>
+      <x:c r="E89" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="F89" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G89" s="3" t="str">
+        <x:v>古宜路170弄7号</x:v>
+      </x:c>
+      <x:c r="H89" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%96%B0%E5%AE%9C%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E5%AE%9C%E8%B7%AF170%E5%BC%847%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I89" s="3" t="str">
+        <x:v>64684874</x:v>
+      </x:c>
+      <x:c r="J89" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K89" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L89" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M89" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N89" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O89" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P89" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="3" t="str">
+        <x:v>M8</x:v>
+      </x:c>
+      <x:c r="B90" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C90" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D90" s="3" t="str">
+        <x:v>蓓蕾幼稚园</x:v>
+      </x:c>
+      <x:c r="E90" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="F90" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G90" s="3" t="str">
+        <x:v>蒲江塘路50号玉兰花苑6幢</x:v>
+      </x:c>
+      <x:c r="H90" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%93%93%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%92%B2%E6%B1%9F%E5%A1%98%E8%B7%AF50%E5%8F%B7%E7%8E%89%E5%85%B0%E8%8A%B1%E8%8B%916%E5%B9%A2</x:v>
+      </x:c>
+      <x:c r="I90" s="3" t="str">
+        <x:v>64647491</x:v>
+      </x:c>
+      <x:c r="J90" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K90" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L90" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M90" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N90" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O90" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P90" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="3" t="str">
+        <x:v>M9</x:v>
+      </x:c>
+      <x:c r="B91" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C91" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D91" s="3" t="str">
+        <x:v>蓓蕾幼稚园</x:v>
+      </x:c>
+      <x:c r="E91" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="F91" s="3" t="str">
+        <x:v>分园</x:v>
+      </x:c>
+      <x:c r="G91" s="3" t="str">
+        <x:v>天钥桥路380弄11号</x:v>
+      </x:c>
+      <x:c r="H91" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%93%93%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E8%B7%AF380%E5%BC%8411%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I91" s="3" t="str">
+        <x:v>64647491</x:v>
+      </x:c>
+      <x:c r="J91" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K91" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L91" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M91" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N91" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O91" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P91" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="3" t="str">
+        <x:v>M10</x:v>
+      </x:c>
+      <x:c r="B92" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C92" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D92" s="3" t="str">
+        <x:v>淇莲幼儿园</x:v>
+      </x:c>
+      <x:c r="E92" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="F92" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G92" s="3" t="str">
+        <x:v>浦北路50号</x:v>
+      </x:c>
+      <x:c r="H92" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B7%87%E8%8E%B2%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B5%A6%E5%8C%97%E8%B7%AF50%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I92" s="3" t="str">
+        <x:v>54669909</x:v>
+      </x:c>
+      <x:c r="J92" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K92" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L92" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M92" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N92" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O92" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P92" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="3" t="str">
+        <x:v>M11</x:v>
+      </x:c>
+      <x:c r="B93" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C93" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D93" s="3" t="str">
+        <x:v>田林街道中心幼儿园</x:v>
+      </x:c>
+      <x:c r="E93" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="F93" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G93" s="3" t="str">
+        <x:v>田林六村10号</x:v>
+      </x:c>
+      <x:c r="H93" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E8%A1%97%E9%81%93%E4%B8%AD%E5%BF%83%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%85%AD%E6%9D%9110%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I93" s="3" t="str">
+        <x:v>64705223</x:v>
+      </x:c>
+      <x:c r="J93" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K93" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L93" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M93" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N93" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O93" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P93" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="3" t="str">
+        <x:v>M12</x:v>
+      </x:c>
+      <x:c r="B94" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C94" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D94" s="3" t="str">
+        <x:v>胡姬港湾新汇幼儿园</x:v>
+      </x:c>
+      <x:c r="E94" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="F94" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G94" s="3" t="str">
+        <x:v>浦北路21弄42号</x:v>
+      </x:c>
+      <x:c r="H94" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%83%A1%E5%A7%AC%E6%B8%AF%E6%B9%BE%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B5%A6%E5%8C%97%E8%B7%AF21%E5%BC%8442%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I94" s="3" t="str">
+        <x:v>54669810</x:v>
+      </x:c>
+      <x:c r="J94" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K94" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L94" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M94" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N94" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O94" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P94" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="3" t="str">
+        <x:v>M13</x:v>
+      </x:c>
+      <x:c r="B95" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C95" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D95" s="3" t="str">
+        <x:v>小神童幼儿园</x:v>
+      </x:c>
+      <x:c r="E95" s="3" t="str">
+        <x:v>华泾/龙吴</x:v>
+      </x:c>
+      <x:c r="F95" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G95" s="3" t="str">
+        <x:v>龙吴路988弄25号</x:v>
+      </x:c>
+      <x:c r="H95" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%B0%8F%E7%A5%9E%E7%AB%A5%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%90%B4%E8%B7%AF988%E5%BC%8425%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I95" s="3" t="str">
+        <x:v>021-54360296</x:v>
+      </x:c>
+      <x:c r="J95" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K95" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L95" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M95" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N95" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O95" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P95" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="3" t="str">
+        <x:v>M14</x:v>
+      </x:c>
+      <x:c r="B96" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C96" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D96" s="3" t="str">
+        <x:v>安琪曈幼稚园</x:v>
+      </x:c>
+      <x:c r="E96" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="F96" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G96" s="3" t="str">
+        <x:v>衡山路9弄2号</x:v>
+      </x:c>
+      <x:c r="H96" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%89%E7%90%AA%E6%9B%88%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%A1%A1%E5%B1%B1%E8%B7%AF9%E5%BC%842%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I96" s="3" t="str">
+        <x:v>64665309</x:v>
+      </x:c>
+      <x:c r="J96" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K96" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L96" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M96" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N96" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O96" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P96" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="3" t="str">
+        <x:v>M15</x:v>
+      </x:c>
+      <x:c r="B97" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C97" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D97" s="3" t="str">
+        <x:v>鲁浦幼儿园</x:v>
+      </x:c>
+      <x:c r="E97" s="3" t="str">
+        <x:v>龙华/滨江</x:v>
+      </x:c>
+      <x:c r="F97" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G97" s="3" t="str">
+        <x:v>宛南一村23号</x:v>
+      </x:c>
+      <x:c r="H97" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%B2%81%E6%B5%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9B%E5%8D%97%E4%B8%80%E6%9D%9123%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I97" s="3" t="str">
+        <x:v>64384206</x:v>
+      </x:c>
+      <x:c r="J97" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K97" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L97" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M97" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N97" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O97" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P97" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="3" t="str">
+        <x:v>M16</x:v>
+      </x:c>
+      <x:c r="B98" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C98" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D98" s="3" t="str">
+        <x:v>鲁浦幼儿园</x:v>
+      </x:c>
+      <x:c r="E98" s="3" t="str">
+        <x:v>龙华/滨江</x:v>
+      </x:c>
+      <x:c r="F98" s="3" t="str">
+        <x:v>分园</x:v>
+      </x:c>
+      <x:c r="G98" s="3" t="str">
+        <x:v>宛南五村1号</x:v>
+      </x:c>
+      <x:c r="H98" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%B2%81%E6%B5%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E5%AE%9B%E5%8D%97%E4%BA%94%E6%9D%911%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I98" s="3" t="str">
+        <x:v>64384206</x:v>
+      </x:c>
+      <x:c r="J98" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K98" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L98" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M98" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N98" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O98" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P98" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="3" t="str">
+        <x:v>M17</x:v>
+      </x:c>
+      <x:c r="B99" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C99" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D99" s="3" t="str">
+        <x:v>康文云锦幼儿园</x:v>
+      </x:c>
+      <x:c r="E99" s="3" t="str">
+        <x:v>龙华/滨江</x:v>
+      </x:c>
+      <x:c r="F99" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G99" s="3" t="str">
+        <x:v>龙兰路398号</x:v>
+      </x:c>
+      <x:c r="H99" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%BA%B7%E6%96%87%E4%BA%91%E9%94%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%85%B0%E8%B7%AF398%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I99" s="3" t="str">
+        <x:v>64282682</x:v>
+      </x:c>
+      <x:c r="J99" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K99" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L99" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M99" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N99" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O99" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P99" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="3" t="str">
+        <x:v>M18</x:v>
+      </x:c>
+      <x:c r="B100" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C100" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D100" s="3" t="str">
+        <x:v>爱文幼儿园</x:v>
+      </x:c>
+      <x:c r="E100" s="3" t="str">
+        <x:v>徐家汇/虹桥</x:v>
+      </x:c>
+      <x:c r="F100" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G100" s="3" t="str">
+        <x:v>古羊路160号1幢</x:v>
+      </x:c>
+      <x:c r="H100" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E6%96%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E7%BE%8A%E8%B7%AF160%E5%8F%B71%E5%B9%A2</x:v>
+      </x:c>
+      <x:c r="I100" s="3" t="str">
+        <x:v>021-62090135</x:v>
+      </x:c>
+      <x:c r="J100" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K100" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L100" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M100" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N100" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O100" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P100" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="3" t="str">
+        <x:v>M19</x:v>
+      </x:c>
+      <x:c r="B101" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C101" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D101" s="3" t="str">
+        <x:v>童稻幼儿园</x:v>
+      </x:c>
+      <x:c r="E101" s="3" t="str">
+        <x:v>徐家汇/虹桥</x:v>
+      </x:c>
+      <x:c r="F101" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G101" s="3" t="str">
+        <x:v>淮海西路365弄2号楼、3号楼</x:v>
+      </x:c>
+      <x:c r="H101" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%AB%A5%E7%A8%BB%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B7%AE%E6%B5%B7%E8%A5%BF%E8%B7%AF365%E5%BC%842%E5%8F%B7%E6%A5%BC%E3%80%813%E5%8F%B7%E6%A5%BC</x:v>
+      </x:c>
+      <x:c r="I101" s="3" t="str">
+        <x:v>52668270</x:v>
+      </x:c>
+      <x:c r="J101" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K101" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L101" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M101" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N101" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O101" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P101" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="3" t="str">
+        <x:v>M20</x:v>
+      </x:c>
+      <x:c r="B102" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C102" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D102" s="3" t="str">
+        <x:v>嘉宝幼儿园</x:v>
+      </x:c>
+      <x:c r="E102" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="F102" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G102" s="3" t="str">
+        <x:v>吴兴路75号</x:v>
+      </x:c>
+      <x:c r="H102" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%98%89%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%90%B4%E5%85%B4%E8%B7%AF75%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I102" s="3" t="str">
+        <x:v>64373773</x:v>
+      </x:c>
+      <x:c r="J102" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K102" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L102" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M102" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N102" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O102" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P102" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="3" t="str">
+        <x:v>M21</x:v>
+      </x:c>
+      <x:c r="B103" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C103" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D103" s="3" t="str">
+        <x:v>金贝贝幼儿园</x:v>
+      </x:c>
+      <x:c r="E103" s="3" t="str">
+        <x:v>华泾/龙吴</x:v>
+      </x:c>
+      <x:c r="F103" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G103" s="3" t="str">
+        <x:v>龙吟路300号</x:v>
+      </x:c>
+      <x:c r="H103" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%87%91%E8%B4%9D%E8%B4%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%90%9F%E8%B7%AF300%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I103" s="3" t="str">
+        <x:v>54820000</x:v>
+      </x:c>
+      <x:c r="J103" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K103" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L103" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M103" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N103" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O103" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P103" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="3" t="str">
+        <x:v>M22</x:v>
+      </x:c>
+      <x:c r="B104" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C104" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D104" s="3" t="str">
+        <x:v>世纪昂立幼儿园</x:v>
+      </x:c>
+      <x:c r="E104" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="F104" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G104" s="3" t="str">
+        <x:v>龙山新村115号（近零陵路）</x:v>
+      </x:c>
+      <x:c r="H104" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%96%E7%BA%AA%E6%98%82%E7%AB%8B%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%B1%B1%E6%96%B0%E6%9D%91115%E5%8F%B7%EF%BC%88%E8%BF%91%E9%9B%B6%E9%99%B5%E8%B7%AF%EF%BC%89</x:v>
+      </x:c>
+      <x:c r="I104" s="3" t="str">
+        <x:v>54890979 / 64382277</x:v>
+      </x:c>
+      <x:c r="J104" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K104" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L104" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M104" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N104" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O104" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P104" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="3" t="str">
+        <x:v>M23</x:v>
+      </x:c>
+      <x:c r="B105" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C105" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D105" s="3" t="str">
+        <x:v>爱菊幼儿园</x:v>
+      </x:c>
+      <x:c r="E105" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="F105" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G105" s="3" t="str">
+        <x:v>复兴西路70号</x:v>
+      </x:c>
+      <x:c r="H105" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E8%8F%8A%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%8D%E5%85%B4%E8%A5%BF%E8%B7%AF70%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I105" s="3" t="str">
+        <x:v>64043162</x:v>
+      </x:c>
+      <x:c r="J105" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K105" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L105" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M105" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N105" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O105" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P105" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="3" t="str">
+        <x:v>M24</x:v>
+      </x:c>
+      <x:c r="B106" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C106" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D106" s="3" t="str">
+        <x:v>培蕾幼稚园</x:v>
+      </x:c>
+      <x:c r="E106" s="3" t="str">
+        <x:v>长桥/梅陇</x:v>
+      </x:c>
+      <x:c r="F106" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G106" s="3" t="str">
+        <x:v>梅陇三村49号</x:v>
+      </x:c>
+      <x:c r="H106" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9F%B9%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E4%B8%89%E6%9D%9149%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I106" s="3" t="str">
+        <x:v>64768480</x:v>
+      </x:c>
+      <x:c r="J106" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K106" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L106" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M106" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N106" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O106" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P106" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="3" t="str">
+        <x:v>M25</x:v>
+      </x:c>
+      <x:c r="B107" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C107" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D107" s="3" t="str">
+        <x:v>培蕾幼稚园</x:v>
+      </x:c>
+      <x:c r="E107" s="3" t="str">
+        <x:v>长桥/梅陇</x:v>
+      </x:c>
+      <x:c r="F107" s="3" t="str">
+        <x:v>分园</x:v>
+      </x:c>
+      <x:c r="G107" s="3" t="str">
+        <x:v>梅陇六村41号</x:v>
+      </x:c>
+      <x:c r="H107" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9F%B9%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%85%AD%E6%9D%9141%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I107" s="3" t="str">
+        <x:v>64767077</x:v>
+      </x:c>
+      <x:c r="J107" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K107" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L107" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M107" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N107" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O107" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P107" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="3" t="str">
+        <x:v>M26</x:v>
+      </x:c>
+      <x:c r="B108" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C108" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D108" s="3" t="str">
+        <x:v>枫叶交响幼儿园</x:v>
+      </x:c>
+      <x:c r="E108" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="F108" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G108" s="3" t="str">
+        <x:v>太原路87号</x:v>
+      </x:c>
+      <x:c r="H108" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%AB%E5%8F%B6%E4%BA%A4%E5%93%8D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%AA%E5%8E%9F%E8%B7%AF87%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I108" s="3" t="str">
+        <x:v>64730053</x:v>
+      </x:c>
+      <x:c r="J108" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K108" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L108" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M108" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N108" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O108" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P108" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="3" t="str">
+        <x:v>M27</x:v>
+      </x:c>
+      <x:c r="B109" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C109" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D109" s="3" t="str">
+        <x:v>泰宁田林幼儿园</x:v>
+      </x:c>
+      <x:c r="E109" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="F109" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G109" s="3" t="str">
+        <x:v>田林十一村36号</x:v>
+      </x:c>
+      <x:c r="H109" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B3%B0%E5%AE%81%E7%94%B0%E6%9E%97%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%8D%81%E4%B8%80%E6%9D%9136%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I109" s="3" t="str">
+        <x:v>64755118-804</x:v>
+      </x:c>
+      <x:c r="J109" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K109" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L109" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M109" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N109" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O109" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P109" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="3" t="str">
+        <x:v>M28</x:v>
+      </x:c>
+      <x:c r="B110" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C110" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D110" s="3" t="str">
+        <x:v>田林东方幼儿园</x:v>
+      </x:c>
+      <x:c r="E110" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="F110" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G110" s="3" t="str">
+        <x:v>宜山路田林十四村27号</x:v>
+      </x:c>
+      <x:c r="H110" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E4%B8%9C%E6%96%B9%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9C%E5%B1%B1%E8%B7%AF%E7%94%B0%E6%9E%97%E5%8D%81%E5%9B%9B%E6%9D%9127%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I110" s="3" t="str">
+        <x:v>021-64085912</x:v>
+      </x:c>
+      <x:c r="J110" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K110" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L110" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M110" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N110" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O110" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P110" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="3" t="str">
+        <x:v>M29</x:v>
+      </x:c>
+      <x:c r="B111" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C111" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D111" s="3" t="str">
+        <x:v>澳宝幼儿园</x:v>
+      </x:c>
+      <x:c r="E111" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="F111" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G111" s="3" t="str">
+        <x:v>永嘉路356弄31号</x:v>
+      </x:c>
+      <x:c r="H111" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BE%B3%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B0%B8%E5%98%89%E8%B7%AF356%E5%BC%8431%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I111" s="3" t="str">
+        <x:v>64720200</x:v>
+      </x:c>
+      <x:c r="J111" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K111" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L111" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M111" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N111" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O111" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P111" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="3" t="str">
+        <x:v>M30</x:v>
+      </x:c>
+      <x:c r="B112" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C112" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D112" s="3" t="str">
+        <x:v>吉的堡小蜻蜓幼儿园</x:v>
+      </x:c>
+      <x:c r="E112" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="F112" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G112" s="3" t="str">
+        <x:v>虹梅路1035弄30号</x:v>
+      </x:c>
+      <x:c r="H112" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E5%B0%8F%E8%9C%BB%E8%9C%93%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%99%B9%E6%A2%85%E8%B7%AF1035%E5%BC%8430%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I112" s="3" t="str">
+        <x:v>64368108</x:v>
+      </x:c>
+      <x:c r="J112" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K112" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L112" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M112" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N112" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O112" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P112" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="3" t="str">
+        <x:v>M31</x:v>
+      </x:c>
+      <x:c r="B113" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C113" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D113" s="3" t="str">
+        <x:v>东泉大地幼儿园</x:v>
+      </x:c>
+      <x:c r="E113" s="3" t="str">
+        <x:v>龙华/滨江</x:v>
+      </x:c>
+      <x:c r="F113" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G113" s="3" t="str">
+        <x:v>东泉路65弄9号</x:v>
+      </x:c>
+      <x:c r="H113" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%9C%E6%B3%89%E5%A4%A7%E5%9C%B0%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B8%9C%E6%B3%89%E8%B7%AF65%E5%BC%849%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I113" s="3" t="str">
+        <x:v>54084130</x:v>
+      </x:c>
+      <x:c r="J113" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K113" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L113" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M113" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N113" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O113" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P113" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="3" t="str">
+        <x:v>M32</x:v>
+      </x:c>
+      <x:c r="B114" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C114" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D114" s="3" t="str">
+        <x:v>吉的堡新徐汇幼儿园</x:v>
+      </x:c>
+      <x:c r="E114" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="F114" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G114" s="3" t="str">
+        <x:v>小木桥路101弄20号</x:v>
+      </x:c>
+      <x:c r="H114" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E6%96%B0%E5%BE%90%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%B0%8F%E6%9C%A8%E6%A1%A5%E8%B7%AF101%E5%BC%8420%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I114" s="3" t="str">
+        <x:v>021-54245100</x:v>
+      </x:c>
+      <x:c r="J114" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K114" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L114" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M114" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N114" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O114" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P114" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="3" t="str">
+        <x:v>M33</x:v>
+      </x:c>
+      <x:c r="B115" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C115" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D115" s="3" t="str">
+        <x:v>爱悠小红花幼儿园</x:v>
+      </x:c>
+      <x:c r="E115" s="3" t="str">
+        <x:v>长桥/梅陇</x:v>
+      </x:c>
+      <x:c r="F115" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G115" s="3" t="str">
+        <x:v>梅陇路130号1幢、2幢</x:v>
+      </x:c>
+      <x:c r="H115" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E6%82%A0%E5%B0%8F%E7%BA%A2%E8%8A%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E8%B7%AF130%E5%8F%B71%E5%B9%A2%E3%80%812%E5%B9%A2</x:v>
+      </x:c>
+      <x:c r="I115" s="3" t="str">
+        <x:v>021-54333289</x:v>
+      </x:c>
+      <x:c r="J115" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K115" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L115" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M115" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N115" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O115" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P115" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="3" t="str">
+        <x:v>M34</x:v>
+      </x:c>
+      <x:c r="B116" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C116" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D116" s="3" t="str">
+        <x:v>中山幼儿园</x:v>
+      </x:c>
+      <x:c r="E116" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="F116" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G116" s="3" t="str">
+        <x:v>桃江路42号</x:v>
+      </x:c>
+      <x:c r="H116" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%AD%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%83%E6%B1%9F%E8%B7%AF42%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I116" s="3" t="str">
+        <x:v>021-33565515</x:v>
+      </x:c>
+      <x:c r="J116" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K116" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L116" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M116" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N116" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O116" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P116" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="3" t="str">
+        <x:v>M35</x:v>
+      </x:c>
+      <x:c r="B117" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C117" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D117" s="3" t="str">
+        <x:v>创意幼儿园</x:v>
+      </x:c>
+      <x:c r="E117" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="F117" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G117" s="3" t="str">
+        <x:v>柳州路田林十村6号</x:v>
+      </x:c>
+      <x:c r="H117" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%88%9B%E6%84%8F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%9F%B3%E5%B7%9E%E8%B7%AF%E7%94%B0%E6%9E%97%E5%8D%81%E6%9D%916%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I117" s="3" t="str">
+        <x:v>64828813 / 64820881</x:v>
+      </x:c>
+      <x:c r="J117" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K117" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L117" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M117" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N117" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O117" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P117" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="3" t="str">
+        <x:v>M36</x:v>
+      </x:c>
+      <x:c r="B118" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C118" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D118" s="3" t="str">
+        <x:v>牛牛幼稚园</x:v>
+      </x:c>
+      <x:c r="E118" s="3" t="str">
+        <x:v>长桥/梅陇</x:v>
+      </x:c>
+      <x:c r="F118" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G118" s="3" t="str">
+        <x:v>罗城路700弄95号</x:v>
+      </x:c>
+      <x:c r="H118" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%89%9B%E7%89%9B%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%BD%97%E5%9F%8E%E8%B7%AF700%E5%BC%8495%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I118" s="3" t="str">
+        <x:v>54115988</x:v>
+      </x:c>
+      <x:c r="J118" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K118" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L118" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M118" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N118" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O118" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P118" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="3" t="str">
+        <x:v>M37</x:v>
+      </x:c>
+      <x:c r="B119" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C119" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D119" s="3" t="str">
+        <x:v>领幼幼儿园</x:v>
+      </x:c>
+      <x:c r="E119" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="F119" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G119" s="3" t="str">
+        <x:v>天钥桥路1057弄3号</x:v>
+      </x:c>
+      <x:c r="H119" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%A2%86%E5%B9%BC%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E8%B7%AF1057%E5%BC%843%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I119" s="3" t="str">
+        <x:v>64458520</x:v>
+      </x:c>
+      <x:c r="J119" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K119" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L119" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M119" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N119" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O119" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P119" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="3" t="str">
+        <x:v>M38</x:v>
+      </x:c>
+      <x:c r="B120" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C120" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D120" s="3" t="str">
+        <x:v>漕河泾新汇幼儿园</x:v>
+      </x:c>
+      <x:c r="E120" s="3" t="str">
+        <x:v>漕溪/龙漕</x:v>
+      </x:c>
+      <x:c r="F120" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G120" s="3" t="str">
+        <x:v>漕泾一村30号</x:v>
+      </x:c>
+      <x:c r="H120" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BC%95%E6%B2%B3%E6%B3%BE%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%BC%95%E6%B3%BE%E4%B8%80%E6%9D%9130%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I120" s="3" t="str">
+        <x:v>64364348</x:v>
+      </x:c>
+      <x:c r="J120" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K120" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L120" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M120" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N120" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O120" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P120" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="3" t="str">
+        <x:v>M39</x:v>
+      </x:c>
+      <x:c r="B121" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C121" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D121" s="3" t="str">
+        <x:v>凯琴数码幼儿园</x:v>
+      </x:c>
+      <x:c r="E121" s="3" t="str">
+        <x:v>华泾/龙吴</x:v>
+      </x:c>
+      <x:c r="F121" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G121" s="3" t="str">
+        <x:v>华泾路995号</x:v>
+      </x:c>
+      <x:c r="H121" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%87%AF%E7%90%B4%E6%95%B0%E7%A0%81%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8D%8E%E6%B3%BE%E8%B7%AF995%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I121" s="3" t="str">
+        <x:v>54822626</x:v>
+      </x:c>
+      <x:c r="J121" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K121" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L121" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M121" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N121" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O121" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P121" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="3" t="str">
+        <x:v>M40</x:v>
+      </x:c>
+      <x:c r="B122" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C122" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D122" s="3" t="str">
+        <x:v>陇龙幼稚园</x:v>
+      </x:c>
+      <x:c r="E122" s="3" t="str">
+        <x:v>长桥/梅陇</x:v>
+      </x:c>
+      <x:c r="F122" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G122" s="3" t="str">
+        <x:v>梅陇十一村96号</x:v>
+      </x:c>
+      <x:c r="H122" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%99%87%E9%BE%99%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E5%8D%81%E4%B8%80%E6%9D%9196%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I122" s="3" t="str">
+        <x:v>64549910</x:v>
+      </x:c>
+      <x:c r="J122" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K122" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L122" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M122" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N122" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O122" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P122" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="3" t="str">
+        <x:v>M41</x:v>
+      </x:c>
+      <x:c r="B123" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C123" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D123" s="3" t="str">
+        <x:v>世蒙幼儿园</x:v>
+      </x:c>
+      <x:c r="E123" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="F123" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G123" s="3" t="str">
+        <x:v>东湖路21号</x:v>
+      </x:c>
+      <x:c r="H123" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%96%E8%92%99%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B8%9C%E6%B9%96%E8%B7%AF21%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I123" s="3" t="str">
+        <x:v>021-54038979</x:v>
+      </x:c>
+      <x:c r="J123" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K123" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L123" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M123" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N123" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O123" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P123" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="3" t="str">
+        <x:v>M42</x:v>
+      </x:c>
+      <x:c r="B124" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C124" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D124" s="3" t="str">
+        <x:v>蒂伊幼稚园</x:v>
+      </x:c>
+      <x:c r="E124" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="F124" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G124" s="3" t="str">
+        <x:v>永嘉路383号</x:v>
+      </x:c>
+      <x:c r="H124" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%92%82%E4%BC%8A%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B0%B8%E5%98%89%E8%B7%AF383%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I124" s="3" t="str">
+        <x:v>64749388</x:v>
+      </x:c>
+      <x:c r="J124" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K124" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L124" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M124" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N124" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O124" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P124" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="3" t="str">
+        <x:v>M43</x:v>
+      </x:c>
+      <x:c r="B125" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C125" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="D125" s="3" t="str">
+        <x:v>吉的堡新汇幼儿园</x:v>
+      </x:c>
+      <x:c r="E125" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="F125" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="G125" s="3" t="str">
+        <x:v>康健小区虹漕南路百花街18号、6号</x:v>
+      </x:c>
+      <x:c r="H125" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%BA%B7%E5%81%A5%E5%B0%8F%E5%8C%BA%E8%99%B9%E6%BC%95%E5%8D%97%E8%B7%AF%E7%99%BE%E8%8A%B1%E8%A1%9718%E5%8F%B7%E3%80%816%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="I125" s="3" t="str">
+        <x:v>54183331</x:v>
+      </x:c>
+      <x:c r="J125" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="K125" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="L125" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="M125" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="N125" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="O125" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="P125" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5167,7 +8323,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="3" t="str">
-        <x:v>园部地址主来源</x:v>
+        <x:v>公办园部地址主来源</x:v>
       </x:c>
       <x:c r="B4" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
@@ -5175,42 +8331,50 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="str">
-        <x:v>高德检索口径</x:v>
+        <x:v>民办/私立地址与电话来源</x:v>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>表格中的高德链接使用“上海市徐汇区 + 幼儿园名 + 园区名 + 地址”生成，用于逐点打开核验。</x:v>
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="str">
-        <x:v>A级</x:v>
+        <x:v>高德检索口径</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
-        <x:v>园部地址在公办园地址清单中明确列出，且无明显冲突。</x:v>
+        <x:v>表格中的高德链接使用“上海市徐汇区 + 幼儿园名 + 园区名 + 地址”生成，用于逐点打开核验。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="str">
-        <x:v>B级</x:v>
+        <x:v>A级</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
-        <x:v>公开资料有变更、合并或地址冲突，位置大体可定位，但实际入读园区需电话确认。</x:v>
+        <x:v>园部地址在公办园地址清单中明确列出，且无明显冲突。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="str">
-        <x:v>C级</x:v>
+        <x:v>B级</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
-        <x:v>仅有第三方或地图信息，缺少官方交叉验证。本表目前未使用C级作为主确认。</x:v>
+        <x:v>公开资料有变更、合并或地址冲突，位置大体可定位，但实际入读园区需电话确认。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="str">
+        <x:v>C级</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="str">
+        <x:v>仅有第三方或地图信息，缺少官方交叉验证。本表目前未使用C级作为主确认。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="3" t="str">
         <x:v>电话确认重点</x:v>
       </x:c>
-      <x:c r="B9" s="3" t="str">
-        <x:v>汇星幼儿园北园；复旦大学附属徐汇实验幼儿园；区域内自主招生及扩招园。</x:v>
+      <x:c r="B10" s="3" t="str">
+        <x:v>汇星幼儿园北园；复旦大学附属徐汇实验幼儿园；区域内自主招生、扩招园、民办/私立园。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
+++ b/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R8968d7db937943ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="Ra819a76505d24971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R75b437eeff1b4e34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R4125d5cfc4984ef1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="Rc20790101dbe4c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="Rc804914f18b54af6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="R609c636306114181"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R08cc0d7c87cb41ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="Re02d65294e944d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="Ra4a66fcb8bde4813"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -273,7 +273,7 @@
         <x:v>民办/私立点位数</x:v>
       </x:c>
       <x:c r="B4" s="3" t="n">
-        <x:v>43</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C4" s="3" t="str">
         <x:v>来自徐汇区民办幼儿园名单公开资料；招生条件、收费和名额需电话确认。</x:v>
@@ -284,7 +284,7 @@
         <x:v>全部园区/点位数</x:v>
       </x:c>
       <x:c r="B5" s="3" t="n">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C5" s="3" t="str">
         <x:v>公办园区点位 + 民办/私立点位。</x:v>
@@ -292,45 +292,56 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="str">
-        <x:v>小班计划合计</x:v>
-      </x:c>
-      <x:c r="B6" s="3" t="n">
-        <x:v>149</x:v>
+        <x:v>高德增强字段</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="str">
+        <x:v>待接入</x:v>
       </x:c>
       <x:c r="C6" s="3" t="str">
-        <x:v>PDF计划班级数合计。</x:v>
+        <x:v>高德MCP需要AMAP_MAPS_API_KEY；接入后补POI名称、经纬度和到西岸网易距离。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="str">
-        <x:v>托班明确班级数合计</x:v>
+        <x:v>小班计划合计</x:v>
       </x:c>
       <x:c r="B7" s="3" t="n">
-        <x:v>71</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C7" s="3" t="str">
-        <x:v>不含混龄式招生。</x:v>
+        <x:v>PDF计划班级数合计。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="str">
-        <x:v>混龄式招生主体数</x:v>
+        <x:v>托班明确班级数合计</x:v>
       </x:c>
       <x:c r="B8" s="3" t="n">
-        <x:v>4</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C8" s="3" t="str">
-        <x:v>混龄式招生不直接等同托班班级数。</x:v>
+        <x:v>不含混龄式招生。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="str">
+        <x:v>混龄式招生主体数</x:v>
+      </x:c>
+      <x:c r="B9" s="3" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="str">
+        <x:v>混龄式招生不直接等同托班班级数。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="3" t="str">
         <x:v>重点核验</x:v>
       </x:c>
-      <x:c r="B9" s="3" t="str">
+      <x:c r="B10" s="3" t="str">
         <x:v>汇星北园、复旦大学附属徐汇实验幼儿园</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="str">
+      <x:c r="C10" s="3" t="str">
         <x:v>公开资料出现地址/合并后的园部安排差异，择园前应电话确认。</x:v>
       </x:c>
     </x:row>
@@ -1560,21 +1571,25 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="6.010000228881836" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="9.199999809265137" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.199999809265137" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22.700000762939453" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17.790000915527344" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22.700000762939453" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="17.790000915527344" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="43.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17.790000915527344" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="14.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="10.180000305175781" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="10.180000305175781" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="63.189998626708984" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="43.560001373291016" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="43.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="43.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10.180000305175781" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10.180000305175781" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="63.189998626708984" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="43.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="43.560001373291016" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1585,51 +1600,59 @@
         <x:v>性质</x:v>
       </x:c>
       <x:c r="C1" s="2" t="str">
-        <x:v>级别</x:v>
+        <x:v>办园类型</x:v>
       </x:c>
       <x:c r="D1" s="2" t="str">
+        <x:v>办园等级</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="str">
         <x:v>幼儿园</x:v>
       </x:c>
-      <x:c r="E1" s="2" t="str">
+      <x:c r="F1" s="2" t="str">
         <x:v>片区</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="str">
+      <x:c r="G1" s="2" t="str">
         <x:v>园区/分园</x:v>
       </x:c>
-      <x:c r="G1" s="2" t="str">
+      <x:c r="H1" s="2" t="str">
         <x:v>地址</x:v>
       </x:c>
-      <x:c r="H1" s="2" t="str">
+      <x:c r="I1" s="2" t="str">
+        <x:v>高德POI名称</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="str">
+        <x:v>高德经纬度</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="str">
+        <x:v>距西岸网易研发中心</x:v>
+      </x:c>
+      <x:c r="L1" s="2" t="str">
         <x:v>高德搜索链接</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="str">
+      <x:c r="M1" s="2" t="str">
         <x:v>联系电话</x:v>
       </x:c>
-      <x:c r="J1" s="2" t="str">
+      <x:c r="N1" s="2" t="str">
         <x:v>托班计划</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="str">
+      <x:c r="O1" s="2" t="str">
         <x:v>小班计划</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="str">
+      <x:c r="P1" s="2" t="str">
         <x:v>对口居委/招生范围</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="str">
+      <x:c r="Q1" s="2" t="str">
         <x:v>招生类型</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="str">
+      <x:c r="R1" s="2" t="str">
         <x:v>置信度</x:v>
       </x:c>
-      <x:c r="O1" s="2" t="str">
+      <x:c r="S1" s="2" t="str">
         <x:v>备注</x:v>
       </x:c>
-      <x:c r="P1" s="2" t="str">
+      <x:c r="T1" s="2" t="str">
         <x:v>主要来源</x:v>
       </x:c>
-      <x:c r="Q1" s="2"/>
-      <x:c r="R1" s="2"/>
-      <x:c r="S1" s="2"/>
-      <x:c r="T1" s="2"/>
       <x:c r="U1" s="2"/>
       <x:c r="V1" s="2"/>
       <x:c r="W1" s="2"/>
@@ -1648,40 +1671,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="str">
         <x:v>襄阳南路第一幼儿园</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="F2" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="G2" s="3" t="str">
         <x:v>复中园</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="H2" s="3" t="str">
         <x:v>复兴中路1260弄2号</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="str">
+      <x:c r="I2" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J2" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K2" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L2" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A4%8D%E4%B8%AD%E5%9B%AD%20%E5%A4%8D%E5%85%B4%E4%B8%AD%E8%B7%AF1260%E5%BC%842%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J2" s="3" t="str">
+      <x:c r="M2" s="3" t="str">
+        <x:v>021-64335881</x:v>
+      </x:c>
+      <x:c r="N2" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K2" s="3" t="n">
+      <x:c r="O2" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L2" s="3" t="str">
+      <x:c r="P2" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="M2" s="3" t="str">
+      <x:c r="Q2" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N2" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O2" s="3" t="str"/>
-      <x:c r="P2" s="3" t="str">
+      <x:c r="R2" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S2" s="3" t="str"/>
+      <x:c r="T2" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1696,40 +1731,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D3" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="str">
         <x:v>襄阳南路第一幼儿园</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="F3" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="str">
+      <x:c r="G3" s="3" t="str">
         <x:v>南园</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="str">
+      <x:c r="H3" s="3" t="str">
         <x:v>襄阳南路317号</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="str">
+      <x:c r="I3" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J3" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K3" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L3" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF317%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I3" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J3" s="3" t="str">
+      <x:c r="M3" s="3" t="str">
+        <x:v>021-64335881</x:v>
+      </x:c>
+      <x:c r="N3" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K3" s="3" t="n">
+      <x:c r="O3" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L3" s="3" t="str">
+      <x:c r="P3" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="M3" s="3" t="str">
+      <x:c r="Q3" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N3" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O3" s="3" t="str"/>
-      <x:c r="P3" s="3" t="str">
+      <x:c r="R3" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S3" s="3" t="str"/>
+      <x:c r="T3" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1744,40 +1791,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D4" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E4" s="3" t="str">
         <x:v>襄阳南路第一幼儿园</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
+      <x:c r="F4" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F4" s="3" t="str">
+      <x:c r="G4" s="3" t="str">
         <x:v>陕南园</x:v>
       </x:c>
-      <x:c r="G4" s="3" t="str">
+      <x:c r="H4" s="3" t="str">
         <x:v>陕西南路540号</x:v>
       </x:c>
-      <x:c r="H4" s="3" t="str">
+      <x:c r="I4" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J4" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K4" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L4" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%99%95%E5%8D%97%E5%9B%AD%20%E9%99%95%E8%A5%BF%E5%8D%97%E8%B7%AF540%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I4" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J4" s="3" t="str">
+      <x:c r="M4" s="3" t="str">
+        <x:v>021-64335881</x:v>
+      </x:c>
+      <x:c r="N4" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K4" s="3" t="n">
+      <x:c r="O4" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L4" s="3" t="str">
+      <x:c r="P4" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="M4" s="3" t="str">
+      <x:c r="Q4" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N4" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O4" s="3" t="str"/>
-      <x:c r="P4" s="3" t="str">
+      <x:c r="R4" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S4" s="3" t="str"/>
+      <x:c r="T4" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1792,40 +1851,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D5" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="str">
         <x:v>襄阳南路第一幼儿园</x:v>
       </x:c>
-      <x:c r="E5" s="3" t="str">
+      <x:c r="F5" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F5" s="3" t="str">
+      <x:c r="G5" s="3" t="str">
         <x:v>北园</x:v>
       </x:c>
-      <x:c r="G5" s="3" t="str">
+      <x:c r="H5" s="3" t="str">
         <x:v>襄阳南路207号</x:v>
       </x:c>
-      <x:c r="H5" s="3" t="str">
+      <x:c r="I5" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J5" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K5" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L5" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF207%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I5" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J5" s="3" t="str">
+      <x:c r="M5" s="3" t="str">
+        <x:v>64335881</x:v>
+      </x:c>
+      <x:c r="N5" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K5" s="3" t="n">
+      <x:c r="O5" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L5" s="3" t="str">
+      <x:c r="P5" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="M5" s="3" t="str">
+      <x:c r="Q5" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O5" s="3" t="str"/>
-      <x:c r="P5" s="3" t="str">
+      <x:c r="R5" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S5" s="3" t="str"/>
+      <x:c r="T5" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1840,40 +1911,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D6" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E6" s="3" t="str">
         <x:v>五原路幼儿园</x:v>
       </x:c>
-      <x:c r="E6" s="3" t="str">
+      <x:c r="F6" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="str">
+      <x:c r="G6" s="3" t="str">
         <x:v>永嘉园</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="str">
+      <x:c r="H6" s="3" t="str">
         <x:v>永嘉路420号</x:v>
       </x:c>
-      <x:c r="H6" s="3" t="str">
+      <x:c r="I6" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J6" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K6" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L6" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BA%94%E5%8E%9F%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%B0%B8%E5%98%89%E5%9B%AD%20%E6%B0%B8%E5%98%89%E8%B7%AF420%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I6" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J6" s="3" t="str">
+      <x:c r="M6" s="3" t="str">
+        <x:v>64759122</x:v>
+      </x:c>
+      <x:c r="N6" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K6" s="3" t="n">
+      <x:c r="O6" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L6" s="3" t="str">
+      <x:c r="P6" s="3" t="str">
         <x:v>上海新村、东湖、金波、延庆、陕新、新乐、复襄、淮海、安福、春华、淮中、建岳、太原、永太、永嘉新村、复永、兴武、华康、武康</x:v>
       </x:c>
-      <x:c r="M6" s="3" t="str">
+      <x:c r="Q6" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N6" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O6" s="3" t="str"/>
-      <x:c r="P6" s="3" t="str">
+      <x:c r="R6" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S6" s="3" t="str"/>
+      <x:c r="T6" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1888,40 +1971,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D7" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="str">
         <x:v>五原路幼儿园</x:v>
       </x:c>
-      <x:c r="E7" s="3" t="str">
+      <x:c r="F7" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F7" s="3" t="str">
+      <x:c r="G7" s="3" t="str">
         <x:v>武康园</x:v>
       </x:c>
-      <x:c r="G7" s="3" t="str">
+      <x:c r="H7" s="3" t="str">
         <x:v>五原路400号</x:v>
       </x:c>
-      <x:c r="H7" s="3" t="str">
+      <x:c r="I7" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J7" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K7" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L7" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BA%94%E5%8E%9F%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%AD%A6%E5%BA%B7%E5%9B%AD%20%E4%BA%94%E5%8E%9F%E8%B7%AF400%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I7" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J7" s="3" t="str">
+      <x:c r="M7" s="3" t="str">
+        <x:v>54035366</x:v>
+      </x:c>
+      <x:c r="N7" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K7" s="3" t="n">
+      <x:c r="O7" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L7" s="3" t="str">
+      <x:c r="P7" s="3" t="str">
         <x:v>上海新村、东湖、金波、延庆、陕新、新乐、复襄、淮海、安福、春华、淮中、建岳、太原、永太、永嘉新村、复永、兴武、华康、武康</x:v>
       </x:c>
-      <x:c r="M7" s="3" t="str">
+      <x:c r="Q7" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N7" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O7" s="3" t="str"/>
-      <x:c r="P7" s="3" t="str">
+      <x:c r="R7" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S7" s="3" t="str"/>
+      <x:c r="T7" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1936,40 +2031,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D8" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="str">
         <x:v>五原路幼儿园</x:v>
       </x:c>
-      <x:c r="E8" s="3" t="str">
+      <x:c r="F8" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F8" s="3" t="str">
+      <x:c r="G8" s="3" t="str">
         <x:v>兴国园</x:v>
       </x:c>
-      <x:c r="G8" s="3" t="str">
+      <x:c r="H8" s="3" t="str">
         <x:v>武康路280弄24号</x:v>
       </x:c>
-      <x:c r="H8" s="3" t="str">
+      <x:c r="I8" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J8" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K8" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L8" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BA%94%E5%8E%9F%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%85%B4%E5%9B%BD%E5%9B%AD%20%E6%AD%A6%E5%BA%B7%E8%B7%AF280%E5%BC%8424%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I8" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J8" s="3" t="str">
+      <x:c r="M8" s="3" t="str">
+        <x:v>64360627</x:v>
+      </x:c>
+      <x:c r="N8" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K8" s="3" t="n">
+      <x:c r="O8" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L8" s="3" t="str">
+      <x:c r="P8" s="3" t="str">
         <x:v>上海新村、东湖、金波、延庆、陕新、新乐、复襄、淮海、安福、春华、淮中、建岳、太原、永太、永嘉新村、复永、兴武、华康、武康</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="str">
+      <x:c r="Q8" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O8" s="3" t="str"/>
-      <x:c r="P8" s="3" t="str">
+      <x:c r="R8" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S8" s="3" t="str"/>
+      <x:c r="T8" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1984,40 +2091,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D9" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="str">
         <x:v>汇星幼儿园</x:v>
       </x:c>
-      <x:c r="E9" s="3" t="str">
+      <x:c r="F9" s="3" t="str">
         <x:v>徐家汇/天平</x:v>
       </x:c>
-      <x:c r="F9" s="3" t="str">
+      <x:c r="G9" s="3" t="str">
         <x:v>南园</x:v>
       </x:c>
-      <x:c r="G9" s="3" t="str">
+      <x:c r="H9" s="3" t="str">
         <x:v>宛平南路19弄3号</x:v>
       </x:c>
-      <x:c r="H9" s="3" t="str">
+      <x:c r="I9" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J9" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K9" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L9" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E6%98%9F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E5%AE%9B%E5%B9%B3%E5%8D%97%E8%B7%AF19%E5%BC%843%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I9" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J9" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K9" s="3" t="n">
+      <x:c r="M9" s="3" t="str">
+        <x:v>021-64689142</x:v>
+      </x:c>
+      <x:c r="N9" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O9" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L9" s="3" t="str">
+      <x:c r="P9" s="3" t="str">
         <x:v>天平、高安、康平、吴兴、宛平、余庆、广元、安亭、徐汇新村、张家浜肇谨、零陵、科汇、启明、沈马、王家堂、南赵巷、殷家角、汇翠、名园、德昌</x:v>
       </x:c>
-      <x:c r="M9" s="3" t="str">
+      <x:c r="Q9" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N9" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O9" s="3" t="str"/>
-      <x:c r="P9" s="3" t="str">
+      <x:c r="R9" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S9" s="3" t="str"/>
+      <x:c r="T9" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2032,42 +2151,54 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D10" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="str">
         <x:v>汇星幼儿园</x:v>
       </x:c>
-      <x:c r="E10" s="3" t="str">
+      <x:c r="F10" s="3" t="str">
         <x:v>徐家汇/天平</x:v>
       </x:c>
-      <x:c r="F10" s="3" t="str">
+      <x:c r="G10" s="3" t="str">
         <x:v>北园</x:v>
       </x:c>
-      <x:c r="G10" s="3" t="str">
+      <x:c r="H10" s="3" t="str">
         <x:v>康平路200号</x:v>
       </x:c>
-      <x:c r="H10" s="3" t="str">
+      <x:c r="I10" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J10" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K10" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L10" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E6%98%9F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E5%BA%B7%E5%B9%B3%E8%B7%AF200%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I10" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J10" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K10" s="3" t="n">
+      <x:c r="M10" s="3" t="str">
+        <x:v>021-64689142</x:v>
+      </x:c>
+      <x:c r="N10" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O10" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L10" s="3" t="str">
+      <x:c r="P10" s="3" t="str">
         <x:v>天平、高安、康平、吴兴、宛平、余庆、广元、安亭、徐汇新村、张家浜肇谨、零陵、科汇、启明、沈马、王家堂、南赵巷、殷家角、汇翠、名园、德昌</x:v>
       </x:c>
-      <x:c r="M10" s="3" t="str">
+      <x:c r="Q10" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N10" s="3" t="str">
+      <x:c r="R10" s="3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="O10" s="3" t="str">
+      <x:c r="S10" s="3" t="str">
         <x:v>2024公办名单写康平路200号；2024招生简章/部分旧资料写华山路1815号，建议电话确认当前小班实际园区。</x:v>
       </x:c>
-      <x:c r="P10" s="3" t="str">
+      <x:c r="T10" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2082,40 +2213,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D11" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="str">
         <x:v>乐山幼儿园</x:v>
       </x:c>
-      <x:c r="E11" s="3" t="str">
+      <x:c r="F11" s="3" t="str">
         <x:v>徐家汇/交大</x:v>
       </x:c>
-      <x:c r="F11" s="3" t="str">
+      <x:c r="G11" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G11" s="3" t="str">
+      <x:c r="H11" s="3" t="str">
         <x:v>乐山路18号</x:v>
       </x:c>
-      <x:c r="H11" s="3" t="str">
+      <x:c r="I11" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J11" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K11" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L11" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%90%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B9%90%E5%B1%B1%E8%B7%AF18%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I11" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J11" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K11" s="3" t="n">
+      <x:c r="M11" s="3" t="str">
+        <x:v>64072867</x:v>
+      </x:c>
+      <x:c r="N11" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O11" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L11" s="3" t="str">
+      <x:c r="P11" s="3" t="str">
         <x:v>乐山一村、乐山二三村、乐山四五村、乐山六七村、乐山八九村、文定、汇站、交大、豪庭</x:v>
       </x:c>
-      <x:c r="M11" s="3" t="str">
+      <x:c r="Q11" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N11" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O11" s="3" t="str"/>
-      <x:c r="P11" s="3" t="str">
+      <x:c r="R11" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S11" s="3" t="str"/>
+      <x:c r="T11" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2130,40 +2273,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D12" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E12" s="3" t="str">
         <x:v>汇家幼儿园</x:v>
       </x:c>
-      <x:c r="E12" s="3" t="str">
+      <x:c r="F12" s="3" t="str">
         <x:v>徐家汇/虹桥路</x:v>
       </x:c>
-      <x:c r="F12" s="3" t="str">
+      <x:c r="G12" s="3" t="str">
         <x:v>北园</x:v>
       </x:c>
-      <x:c r="G12" s="3" t="str">
+      <x:c r="H12" s="3" t="str">
         <x:v>番禺路800弄24号</x:v>
       </x:c>
-      <x:c r="H12" s="3" t="str">
+      <x:c r="I12" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J12" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K12" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L12" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%AE%B6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E7%95%AA%E7%A6%BA%E8%B7%AF800%E5%BC%8424%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I12" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J12" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K12" s="3" t="n">
+      <x:c r="M12" s="3" t="str">
+        <x:v>62837361</x:v>
+      </x:c>
+      <x:c r="N12" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O12" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L12" s="3" t="str">
+      <x:c r="P12" s="3" t="str">
         <x:v>番禺、南丹、柿子湾、潘家宅、陈家宅、虹二、虹交、西塘、东塘</x:v>
       </x:c>
-      <x:c r="M12" s="3" t="str">
+      <x:c r="Q12" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N12" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O12" s="3" t="str"/>
-      <x:c r="P12" s="3" t="str">
+      <x:c r="R12" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S12" s="3" t="str"/>
+      <x:c r="T12" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2178,40 +2333,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D13" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E13" s="3" t="str">
         <x:v>汇家幼儿园</x:v>
       </x:c>
-      <x:c r="E13" s="3" t="str">
+      <x:c r="F13" s="3" t="str">
         <x:v>徐家汇/虹桥路</x:v>
       </x:c>
-      <x:c r="F13" s="3" t="str">
+      <x:c r="G13" s="3" t="str">
         <x:v>南园</x:v>
       </x:c>
-      <x:c r="G13" s="3" t="str">
+      <x:c r="H13" s="3" t="str">
         <x:v>番禺路1188号</x:v>
       </x:c>
-      <x:c r="H13" s="3" t="str">
+      <x:c r="I13" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J13" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K13" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L13" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%AE%B6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E7%95%AA%E7%A6%BA%E8%B7%AF1188%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I13" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J13" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K13" s="3" t="n">
+      <x:c r="M13" s="3" t="str">
+        <x:v>64860098</x:v>
+      </x:c>
+      <x:c r="N13" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O13" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L13" s="3" t="str">
+      <x:c r="P13" s="3" t="str">
         <x:v>番禺、南丹、柿子湾、潘家宅、陈家宅、虹二、虹交、西塘、东塘</x:v>
       </x:c>
-      <x:c r="M13" s="3" t="str">
+      <x:c r="Q13" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N13" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O13" s="3" t="str"/>
-      <x:c r="P13" s="3" t="str">
+      <x:c r="R13" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S13" s="3" t="str"/>
+      <x:c r="T13" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2226,40 +2393,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D14" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E14" s="3" t="str">
         <x:v>枫林幼儿园</x:v>
       </x:c>
-      <x:c r="E14" s="3" t="str">
+      <x:c r="F14" s="3" t="str">
         <x:v>枫林/斜土</x:v>
       </x:c>
-      <x:c r="F14" s="3" t="str">
+      <x:c r="G14" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G14" s="3" t="str">
+      <x:c r="H14" s="3" t="str">
         <x:v>小木桥路440弄30号</x:v>
       </x:c>
-      <x:c r="H14" s="3" t="str">
+      <x:c r="I14" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J14" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K14" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L14" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%AB%E6%9E%97%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%B0%8F%E6%9C%A8%E6%A1%A5%E8%B7%AF440%E5%BC%8430%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I14" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J14" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K14" s="3" t="n">
+      <x:c r="M14" s="3" t="str">
+        <x:v>64035845</x:v>
+      </x:c>
+      <x:c r="N14" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O14" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L14" s="3" t="str">
+      <x:c r="P14" s="3" t="str">
         <x:v>日新、日二、日五、日六第一、日六第二、大三、大四、康巨、茶陵、景泰、恒益、西木南、西木北、江南</x:v>
       </x:c>
-      <x:c r="M14" s="3" t="str">
+      <x:c r="Q14" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N14" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O14" s="3" t="str"/>
-      <x:c r="P14" s="3" t="str">
+      <x:c r="R14" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S14" s="3" t="str"/>
+      <x:c r="T14" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2274,42 +2453,54 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D15" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E15" s="3" t="str">
         <x:v>复旦大学附属徐汇实验幼儿园</x:v>
       </x:c>
-      <x:c r="E15" s="3" t="str">
+      <x:c r="F15" s="3" t="str">
         <x:v>枫林/斜土</x:v>
       </x:c>
-      <x:c r="F15" s="3" t="str">
+      <x:c r="G15" s="3" t="str">
         <x:v>托小班部</x:v>
       </x:c>
-      <x:c r="G15" s="3" t="str">
+      <x:c r="H15" s="3" t="str">
         <x:v>平江路17号</x:v>
       </x:c>
-      <x:c r="H15" s="3" t="str">
+      <x:c r="I15" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J15" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K15" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L15" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%A4%8D%E6%97%A6%E5%A4%A7%E5%AD%A6%E9%99%84%E5%B1%9E%E5%BE%90%E6%B1%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%89%98%E5%B0%8F%E7%8F%AD%E9%83%A8%20%E5%B9%B3%E6%B1%9F%E8%B7%AF17%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I15" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J15" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K15" s="3" t="n">
+      <x:c r="M15" s="3" t="str">
+        <x:v>64034223</x:v>
+      </x:c>
+      <x:c r="N15" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O15" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L15" s="3" t="str">
+      <x:c r="P15" s="3" t="str">
         <x:v>平江、肇一、上影、日七、大五、医清、四季园、肇清、医学院</x:v>
       </x:c>
-      <x:c r="M15" s="3" t="str">
+      <x:c r="Q15" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N15" s="3" t="str">
+      <x:c r="R15" s="3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="O15" s="3" t="str">
+      <x:c r="S15" s="3" t="str">
         <x:v>2024年7月由原平江路幼儿园与原复旦大学医学院幼儿园合并组建；2025/公开资料显示新小班启用平江路32号，需确认2026实际安排。</x:v>
       </x:c>
-      <x:c r="P15" s="3" t="str">
+      <x:c r="T15" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；复旦附属徐汇实验幼儿园公开资料/上哪学/021school；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2324,42 +2515,54 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D16" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E16" s="3" t="str">
         <x:v>复旦大学附属徐汇实验幼儿园</x:v>
       </x:c>
-      <x:c r="E16" s="3" t="str">
+      <x:c r="F16" s="3" t="str">
         <x:v>枫林/斜土</x:v>
       </x:c>
-      <x:c r="F16" s="3" t="str">
+      <x:c r="G16" s="3" t="str">
         <x:v>中大班部/新小班候选</x:v>
       </x:c>
-      <x:c r="G16" s="3" t="str">
+      <x:c r="H16" s="3" t="str">
         <x:v>平江路32号</x:v>
       </x:c>
-      <x:c r="H16" s="3" t="str">
+      <x:c r="I16" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J16" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K16" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L16" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%A4%8D%E6%97%A6%E5%A4%A7%E5%AD%A6%E9%99%84%E5%B1%9E%E5%BE%90%E6%B1%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%AD%E5%A4%A7%E7%8F%AD%E9%83%A8%2F%E6%96%B0%E5%B0%8F%E7%8F%AD%E5%80%99%E9%80%89%20%E5%B9%B3%E6%B1%9F%E8%B7%AF32%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I16" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J16" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K16" s="3" t="n">
+      <x:c r="M16" s="3" t="str">
+        <x:v>64034223</x:v>
+      </x:c>
+      <x:c r="N16" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O16" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L16" s="3" t="str">
+      <x:c r="P16" s="3" t="str">
         <x:v>平江、肇一、上影、日七、大五、医清、四季园、肇清、医学院</x:v>
       </x:c>
-      <x:c r="M16" s="3" t="str">
+      <x:c r="Q16" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N16" s="3" t="str">
+      <x:c r="R16" s="3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="O16" s="3" t="str">
+      <x:c r="S16" s="3" t="str">
         <x:v>公开资料显示办学地址为平江路32号、17号；原复旦医学院幼儿园东安路50弄10号为历史/合并相关地址。</x:v>
       </x:c>
-      <x:c r="P16" s="3" t="str">
+      <x:c r="T16" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；复旦附属徐汇实验幼儿园公开资料/上哪学/021school；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2374,40 +2577,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D17" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E17" s="3" t="str">
         <x:v>东安一村幼儿园</x:v>
       </x:c>
-      <x:c r="E17" s="3" t="str">
+      <x:c r="F17" s="3" t="str">
         <x:v>枫林/斜土</x:v>
       </x:c>
-      <x:c r="F17" s="3" t="str">
+      <x:c r="G17" s="3" t="str">
         <x:v>零陵园</x:v>
       </x:c>
-      <x:c r="G17" s="3" t="str">
+      <x:c r="H17" s="3" t="str">
         <x:v>零陵路250弄33号</x:v>
       </x:c>
-      <x:c r="H17" s="3" t="str">
+      <x:c r="I17" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J17" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K17" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L17" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%9C%E5%AE%89%E4%B8%80%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%9B%B6%E9%99%B5%E5%9B%AD%20%E9%9B%B6%E9%99%B5%E8%B7%AF250%E5%BC%8433%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I17" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J17" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K17" s="3" t="n">
+      <x:c r="M17" s="3" t="str">
+        <x:v>64041758</x:v>
+      </x:c>
+      <x:c r="N17" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O17" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L17" s="3" t="str">
+      <x:c r="P17" s="3" t="str">
         <x:v>东安一村北、东安一村南、安康、振兴、张东、爱华、汇园、东安二村、沈家里、东安四村、谨斜、东安苑、枫林新村、南康</x:v>
       </x:c>
-      <x:c r="M17" s="3" t="str">
+      <x:c r="Q17" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N17" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O17" s="3" t="str"/>
-      <x:c r="P17" s="3" t="str">
+      <x:c r="R17" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S17" s="3" t="str"/>
+      <x:c r="T17" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2422,42 +2637,54 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D18" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E18" s="3" t="str">
         <x:v>东安一村幼儿园</x:v>
       </x:c>
-      <x:c r="E18" s="3" t="str">
+      <x:c r="F18" s="3" t="str">
         <x:v>枫林/斜土</x:v>
       </x:c>
-      <x:c r="F18" s="3" t="str">
+      <x:c r="G18" s="3" t="str">
         <x:v>东安园</x:v>
       </x:c>
-      <x:c r="G18" s="3" t="str">
+      <x:c r="H18" s="3" t="str">
         <x:v>东安一村39号</x:v>
       </x:c>
-      <x:c r="H18" s="3" t="str">
+      <x:c r="I18" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J18" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K18" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L18" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%9C%E5%AE%89%E4%B8%80%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%9C%E5%AE%89%E5%9B%AD%20%E4%B8%9C%E5%AE%89%E4%B8%80%E6%9D%9139%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I18" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J18" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K18" s="3" t="n">
+      <x:c r="M18" s="3" t="str">
+        <x:v>64175625</x:v>
+      </x:c>
+      <x:c r="N18" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O18" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L18" s="3" t="str">
+      <x:c r="P18" s="3" t="str">
         <x:v>东安一村北、东安一村南、安康、振兴、张东、爱华、汇园、东安二村、沈家里、东安四村、谨斜、东安苑、枫林新村、南康</x:v>
       </x:c>
-      <x:c r="M18" s="3" t="str">
+      <x:c r="Q18" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N18" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O18" s="3" t="str">
+      <x:c r="R18" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S18" s="3" t="str">
         <x:v>公办名单列出东安一村39号及零陵路250弄33号。</x:v>
       </x:c>
-      <x:c r="P18" s="3" t="str">
+      <x:c r="T18" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2472,40 +2699,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D19" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E19" s="3" t="str">
         <x:v>龙山幼儿园</x:v>
       </x:c>
-      <x:c r="E19" s="3" t="str">
+      <x:c r="F19" s="3" t="str">
         <x:v>枫林/宛南</x:v>
       </x:c>
-      <x:c r="F19" s="3" t="str">
+      <x:c r="G19" s="3" t="str">
         <x:v>一分园</x:v>
       </x:c>
-      <x:c r="G19" s="3" t="str">
+      <x:c r="H19" s="3" t="str">
         <x:v>宛南四村16号</x:v>
       </x:c>
-      <x:c r="H19" s="3" t="str">
+      <x:c r="I19" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J19" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K19" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L19" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%80%E5%88%86%E5%9B%AD%20%E5%AE%9B%E5%8D%97%E5%9B%9B%E6%9D%9116%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I19" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J19" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K19" s="3" t="n">
+      <x:c r="M19" s="3" t="str">
+        <x:v>64383244</x:v>
+      </x:c>
+      <x:c r="N19" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O19" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L19" s="3" t="str">
+      <x:c r="P19" s="3" t="str">
         <x:v>天一二、天三、天四、宛南一二、宛三、宛四、宛五、宛六、庄家宅、黄家宅、华容、龙山一、龙山二、徐汇苑</x:v>
       </x:c>
-      <x:c r="M19" s="3" t="str">
+      <x:c r="Q19" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N19" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O19" s="3" t="str"/>
-      <x:c r="P19" s="3" t="str">
+      <x:c r="R19" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S19" s="3" t="str"/>
+      <x:c r="T19" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2520,40 +2759,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D20" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E20" s="3" t="str">
         <x:v>龙山幼儿园</x:v>
       </x:c>
-      <x:c r="E20" s="3" t="str">
+      <x:c r="F20" s="3" t="str">
         <x:v>枫林/宛南</x:v>
       </x:c>
-      <x:c r="F20" s="3" t="str">
+      <x:c r="G20" s="3" t="str">
         <x:v>二分园</x:v>
       </x:c>
-      <x:c r="G20" s="3" t="str">
+      <x:c r="H20" s="3" t="str">
         <x:v>中山南二路999弄5号</x:v>
       </x:c>
-      <x:c r="H20" s="3" t="str">
+      <x:c r="I20" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J20" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K20" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L20" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%BA%8C%E5%88%86%E5%9B%AD%20%E4%B8%AD%E5%B1%B1%E5%8D%97%E4%BA%8C%E8%B7%AF999%E5%BC%845%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I20" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J20" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K20" s="3" t="n">
+      <x:c r="M20" s="3" t="str">
+        <x:v>64869504</x:v>
+      </x:c>
+      <x:c r="N20" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O20" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L20" s="3" t="str">
+      <x:c r="P20" s="3" t="str">
         <x:v>天一二、天三、天四、宛南一二、宛三、宛四、宛五、宛六、庄家宅、黄家宅、华容、龙山一、龙山二、徐汇苑</x:v>
       </x:c>
-      <x:c r="M20" s="3" t="str">
+      <x:c r="Q20" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N20" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O20" s="3" t="str"/>
-      <x:c r="P20" s="3" t="str">
+      <x:c r="R20" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S20" s="3" t="str"/>
+      <x:c r="T20" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2568,40 +2819,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D21" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E21" s="3" t="str">
         <x:v>龙山幼儿园</x:v>
       </x:c>
-      <x:c r="E21" s="3" t="str">
+      <x:c r="F21" s="3" t="str">
         <x:v>枫林/宛南</x:v>
       </x:c>
-      <x:c r="F21" s="3" t="str">
+      <x:c r="G21" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G21" s="3" t="str">
+      <x:c r="H21" s="3" t="str">
         <x:v>天钥新村90号</x:v>
       </x:c>
-      <x:c r="H21" s="3" t="str">
+      <x:c r="I21" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J21" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K21" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L21" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%A9%E9%92%A5%E6%96%B0%E6%9D%9190%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I21" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J21" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K21" s="3" t="n">
+      <x:c r="M21" s="3" t="str">
+        <x:v>64383295</x:v>
+      </x:c>
+      <x:c r="N21" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O21" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L21" s="3" t="str">
+      <x:c r="P21" s="3" t="str">
         <x:v>天一二、天三、天四、宛南一二、宛三、宛四、宛五、宛六、庄家宅、黄家宅、华容、龙山一、龙山二、徐汇苑</x:v>
       </x:c>
-      <x:c r="M21" s="3" t="str">
+      <x:c r="Q21" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N21" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O21" s="3" t="str"/>
-      <x:c r="P21" s="3" t="str">
+      <x:c r="R21" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S21" s="3" t="str"/>
+      <x:c r="T21" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2616,40 +2879,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D22" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E22" s="3" t="str">
         <x:v>龙华幼儿园</x:v>
       </x:c>
-      <x:c r="E22" s="3" t="str">
+      <x:c r="F22" s="3" t="str">
         <x:v>龙华/西岸</x:v>
       </x:c>
-      <x:c r="F22" s="3" t="str">
+      <x:c r="G22" s="3" t="str">
         <x:v>丰谷园</x:v>
       </x:c>
-      <x:c r="G22" s="3" t="str">
+      <x:c r="H22" s="3" t="str">
         <x:v>丰谷路205弄34号</x:v>
       </x:c>
-      <x:c r="H22" s="3" t="str">
+      <x:c r="I22" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J22" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K22" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L22" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%B0%E8%B0%B7%E5%9B%AD%20%E4%B8%B0%E8%B0%B7%E8%B7%AF205%E5%BC%8434%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I22" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J22" s="3" t="str">
+      <x:c r="M22" s="3" t="str">
+        <x:v>64280780</x:v>
+      </x:c>
+      <x:c r="N22" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K22" s="3" t="n">
+      <x:c r="O22" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L22" s="3" t="str">
+      <x:c r="P22" s="3" t="str">
         <x:v>上缝、强生、东蔡、狮城、佳友、华富、宏润花园、漕溪四村单号、丰谷、云锦、机场、尚海湾、盛大、民苑、丰谷三、俞一、俞二、俞三、龙华新村、周家湾、汇龙、红馨、百汇园</x:v>
       </x:c>
-      <x:c r="M22" s="3" t="str">
+      <x:c r="Q22" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N22" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O22" s="3" t="str"/>
-      <x:c r="P22" s="3" t="str">
+      <x:c r="R22" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S22" s="3" t="str"/>
+      <x:c r="T22" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2664,40 +2939,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D23" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E23" s="3" t="str">
         <x:v>龙华幼儿园</x:v>
       </x:c>
-      <x:c r="E23" s="3" t="str">
+      <x:c r="F23" s="3" t="str">
         <x:v>龙华/西岸</x:v>
       </x:c>
-      <x:c r="F23" s="3" t="str">
+      <x:c r="G23" s="3" t="str">
         <x:v>龙恒园</x:v>
       </x:c>
-      <x:c r="G23" s="3" t="str">
+      <x:c r="H23" s="3" t="str">
         <x:v>龙华西路31弄15号</x:v>
       </x:c>
-      <x:c r="H23" s="3" t="str">
+      <x:c r="I23" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J23" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K23" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L23" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%BE%99%E6%81%92%E5%9B%AD%20%E9%BE%99%E5%8D%8E%E8%A5%BF%E8%B7%AF31%E5%BC%8415%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I23" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J23" s="3" t="str">
+      <x:c r="M23" s="3" t="str">
+        <x:v>64576761</x:v>
+      </x:c>
+      <x:c r="N23" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K23" s="3" t="n">
+      <x:c r="O23" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L23" s="3" t="str">
+      <x:c r="P23" s="3" t="str">
         <x:v>上缝、强生、东蔡、狮城、佳友、华富、宏润花园、漕溪四村单号、丰谷、云锦、机场、尚海湾、盛大、民苑、丰谷三、俞一、俞二、俞三、龙华新村、周家湾、汇龙、红馨、百汇园</x:v>
       </x:c>
-      <x:c r="M23" s="3" t="str">
+      <x:c r="Q23" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N23" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O23" s="3" t="str"/>
-      <x:c r="P23" s="3" t="str">
+      <x:c r="R23" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S23" s="3" t="str"/>
+      <x:c r="T23" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2712,40 +2999,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D24" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E24" s="3" t="str">
         <x:v>龙华幼儿园</x:v>
       </x:c>
-      <x:c r="E24" s="3" t="str">
+      <x:c r="F24" s="3" t="str">
         <x:v>龙华/西岸</x:v>
       </x:c>
-      <x:c r="F24" s="3" t="str">
+      <x:c r="G24" s="3" t="str">
         <x:v>龙华园</x:v>
       </x:c>
-      <x:c r="G24" s="3" t="str">
+      <x:c r="H24" s="3" t="str">
         <x:v>龙华西路285弄14号</x:v>
       </x:c>
-      <x:c r="H24" s="3" t="str">
+      <x:c r="I24" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J24" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K24" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L24" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%BE%99%E5%8D%8E%E5%9B%AD%20%E9%BE%99%E5%8D%8E%E8%A5%BF%E8%B7%AF285%E5%BC%8414%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I24" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J24" s="3" t="str">
+      <x:c r="M24" s="3" t="str">
+        <x:v>64571589</x:v>
+      </x:c>
+      <x:c r="N24" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K24" s="3" t="n">
+      <x:c r="O24" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L24" s="3" t="str">
+      <x:c r="P24" s="3" t="str">
         <x:v>上缝、强生、东蔡、狮城、佳友、华富、宏润花园、漕溪四村单号、丰谷、云锦、机场、尚海湾、盛大、民苑、丰谷三、俞一、俞二、俞三、龙华新村、周家湾、汇龙、红馨、百汇园</x:v>
       </x:c>
-      <x:c r="M24" s="3" t="str">
+      <x:c r="Q24" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N24" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O24" s="3" t="str"/>
-      <x:c r="P24" s="3" t="str">
+      <x:c r="R24" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S24" s="3" t="str"/>
+      <x:c r="T24" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2760,40 +3059,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D25" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E25" s="3" t="str">
         <x:v>汇霖幼儿园</x:v>
       </x:c>
-      <x:c r="E25" s="3" t="str">
+      <x:c r="F25" s="3" t="str">
         <x:v>田林/虹桥</x:v>
       </x:c>
-      <x:c r="F25" s="3" t="str">
+      <x:c r="G25" s="3" t="str">
         <x:v>吴中园</x:v>
       </x:c>
-      <x:c r="G25" s="3" t="str">
+      <x:c r="H25" s="3" t="str">
         <x:v>吴中东路500弄67号</x:v>
       </x:c>
-      <x:c r="H25" s="3" t="str">
+      <x:c r="I25" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J25" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K25" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L25" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E9%9C%96%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%90%B4%E4%B8%AD%E5%9B%AD%20%E5%90%B4%E4%B8%AD%E4%B8%9C%E8%B7%AF500%E5%BC%8467%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I25" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J25" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K25" s="3" t="n">
+      <x:c r="M25" s="3" t="str">
+        <x:v>62196848</x:v>
+      </x:c>
+      <x:c r="N25" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O25" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L25" s="3" t="str">
+      <x:c r="P25" s="3" t="str">
         <x:v>古宜、长春、吴中、桂林苑、虹南、虹星、怡桂苑、钦北、华悦家园、鑫耀</x:v>
       </x:c>
-      <x:c r="M25" s="3" t="str">
+      <x:c r="Q25" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N25" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O25" s="3" t="str"/>
-      <x:c r="P25" s="3" t="str">
+      <x:c r="R25" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S25" s="3" t="str"/>
+      <x:c r="T25" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2808,40 +3119,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D26" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E26" s="3" t="str">
         <x:v>汇霖幼儿园</x:v>
       </x:c>
-      <x:c r="E26" s="3" t="str">
+      <x:c r="F26" s="3" t="str">
         <x:v>田林/虹桥</x:v>
       </x:c>
-      <x:c r="F26" s="3" t="str">
+      <x:c r="G26" s="3" t="str">
         <x:v>钦州园</x:v>
       </x:c>
-      <x:c r="G26" s="3" t="str">
+      <x:c r="H26" s="3" t="str">
         <x:v>钦州北路898号</x:v>
       </x:c>
-      <x:c r="H26" s="3" t="str">
+      <x:c r="I26" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J26" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K26" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L26" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E9%9C%96%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%92%A6%E5%B7%9E%E5%9B%AD%20%E9%92%A6%E5%B7%9E%E5%8C%97%E8%B7%AF898%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I26" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J26" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K26" s="3" t="n">
+      <x:c r="M26" s="3" t="str">
+        <x:v>64668657</x:v>
+      </x:c>
+      <x:c r="N26" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O26" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L26" s="3" t="str">
+      <x:c r="P26" s="3" t="str">
         <x:v>古宜、长春、吴中、桂林苑、虹南、虹星、怡桂苑、钦北、华悦家园、鑫耀</x:v>
       </x:c>
-      <x:c r="M26" s="3" t="str">
+      <x:c r="Q26" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N26" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O26" s="3" t="str"/>
-      <x:c r="P26" s="3" t="str">
+      <x:c r="R26" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S26" s="3" t="str"/>
+      <x:c r="T26" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2856,40 +3179,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D27" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E27" s="3" t="str">
         <x:v>阳光幼儿园</x:v>
       </x:c>
-      <x:c r="E27" s="3" t="str">
+      <x:c r="F27" s="3" t="str">
         <x:v>龙华/滨江</x:v>
       </x:c>
-      <x:c r="F27" s="3" t="str">
+      <x:c r="G27" s="3" t="str">
         <x:v>中大班部</x:v>
       </x:c>
-      <x:c r="G27" s="3" t="str">
+      <x:c r="H27" s="3" t="str">
         <x:v>天钥桥南路1249弄11号</x:v>
       </x:c>
-      <x:c r="H27" s="3" t="str">
+      <x:c r="I27" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J27" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K27" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L27" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%98%B3%E5%85%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%AD%E5%A4%A7%E7%8F%AD%E9%83%A8%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E5%8D%97%E8%B7%AF1249%E5%BC%8411%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I27" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J27" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K27" s="3" t="n">
+      <x:c r="M27" s="3" t="str">
+        <x:v>54095768</x:v>
+      </x:c>
+      <x:c r="N27" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O27" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L27" s="3" t="str">
+      <x:c r="P27" s="3" t="str">
         <x:v>龙南三四、龙南五、龙南六、龙南七、滨江、樟树苑、东泉、张家园</x:v>
       </x:c>
-      <x:c r="M27" s="3" t="str">
+      <x:c r="Q27" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N27" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O27" s="3" t="str"/>
-      <x:c r="P27" s="3" t="str">
+      <x:c r="R27" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S27" s="3" t="str"/>
+      <x:c r="T27" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2904,40 +3239,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D28" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E28" s="3" t="str">
         <x:v>阳光幼儿园</x:v>
       </x:c>
-      <x:c r="E28" s="3" t="str">
+      <x:c r="F28" s="3" t="str">
         <x:v>龙华/滨江</x:v>
       </x:c>
-      <x:c r="F28" s="3" t="str">
+      <x:c r="G28" s="3" t="str">
         <x:v>小班部</x:v>
       </x:c>
-      <x:c r="G28" s="3" t="str">
+      <x:c r="H28" s="3" t="str">
         <x:v>龙水南路龙南三村7号</x:v>
       </x:c>
-      <x:c r="H28" s="3" t="str">
+      <x:c r="I28" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J28" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K28" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L28" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%98%B3%E5%85%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%B0%8F%E7%8F%AD%E9%83%A8%20%E9%BE%99%E6%B0%B4%E5%8D%97%E8%B7%AF%E9%BE%99%E5%8D%97%E4%B8%89%E6%9D%917%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I28" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J28" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K28" s="3" t="n">
+      <x:c r="M28" s="3" t="str">
+        <x:v>021-34604160</x:v>
+      </x:c>
+      <x:c r="N28" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O28" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L28" s="3" t="str">
+      <x:c r="P28" s="3" t="str">
         <x:v>龙南三四、龙南五、龙南六、龙南七、滨江、樟树苑、东泉、张家园</x:v>
       </x:c>
-      <x:c r="M28" s="3" t="str">
+      <x:c r="Q28" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N28" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O28" s="3" t="str"/>
-      <x:c r="P28" s="3" t="str">
+      <x:c r="R28" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S28" s="3" t="str"/>
+      <x:c r="T28" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2952,40 +3299,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D29" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E29" s="3" t="str">
         <x:v>漕溪新村幼儿园</x:v>
       </x:c>
-      <x:c r="E29" s="3" t="str">
+      <x:c r="F29" s="3" t="str">
         <x:v>漕溪/龙漕</x:v>
       </x:c>
-      <x:c r="F29" s="3" t="str">
+      <x:c r="G29" s="3" t="str">
         <x:v>中大班部</x:v>
       </x:c>
-      <x:c r="G29" s="3" t="str">
+      <x:c r="H29" s="3" t="str">
         <x:v>龙漕路139号</x:v>
       </x:c>
-      <x:c r="H29" s="3" t="str">
+      <x:c r="I29" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J29" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K29" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L29" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BC%95%E6%BA%AA%E6%96%B0%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%AD%E5%A4%A7%E7%8F%AD%E9%83%A8%20%E9%BE%99%E6%BC%95%E8%B7%AF139%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I29" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J29" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K29" s="3" t="n">
+      <x:c r="M29" s="3" t="str">
+        <x:v>64823976</x:v>
+      </x:c>
+      <x:c r="N29" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O29" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L29" s="3" t="str">
+      <x:c r="P29" s="3" t="str">
         <x:v>金谷园、南一村一、南一村二、漕溪四村双号、凯翔、龙漕、嘉萱苑、漕东</x:v>
       </x:c>
-      <x:c r="M29" s="3" t="str">
+      <x:c r="Q29" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N29" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O29" s="3" t="str"/>
-      <x:c r="P29" s="3" t="str">
+      <x:c r="R29" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S29" s="3" t="str"/>
+      <x:c r="T29" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3000,40 +3359,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D30" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E30" s="3" t="str">
         <x:v>漕溪新村幼儿园</x:v>
       </x:c>
-      <x:c r="E30" s="3" t="str">
+      <x:c r="F30" s="3" t="str">
         <x:v>漕溪/龙漕</x:v>
       </x:c>
-      <x:c r="F30" s="3" t="str">
+      <x:c r="G30" s="3" t="str">
         <x:v>小班部</x:v>
       </x:c>
-      <x:c r="G30" s="3" t="str">
+      <x:c r="H30" s="3" t="str">
         <x:v>漕东路193号</x:v>
       </x:c>
-      <x:c r="H30" s="3" t="str">
+      <x:c r="I30" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J30" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K30" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L30" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BC%95%E6%BA%AA%E6%96%B0%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%B0%8F%E7%8F%AD%E9%83%A8%20%E6%BC%95%E4%B8%9C%E8%B7%AF193%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I30" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J30" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K30" s="3" t="n">
+      <x:c r="M30" s="3" t="str">
+        <x:v>34616320</x:v>
+      </x:c>
+      <x:c r="N30" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O30" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L30" s="3" t="str">
+      <x:c r="P30" s="3" t="str">
         <x:v>金谷园、南一村一、南一村二、漕溪四村双号、凯翔、龙漕、嘉萱苑、漕东</x:v>
       </x:c>
-      <x:c r="M30" s="3" t="str">
+      <x:c r="Q30" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N30" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O30" s="3" t="str"/>
-      <x:c r="P30" s="3" t="str">
+      <x:c r="R30" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S30" s="3" t="str"/>
+      <x:c r="T30" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3048,40 +3419,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D31" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E31" s="3" t="str">
         <x:v>望德幼儿园</x:v>
       </x:c>
-      <x:c r="E31" s="3" t="str">
+      <x:c r="F31" s="3" t="str">
         <x:v>康健/南站</x:v>
       </x:c>
-      <x:c r="F31" s="3" t="str">
+      <x:c r="G31" s="3" t="str">
         <x:v>冠生园</x:v>
       </x:c>
-      <x:c r="G31" s="3" t="str">
+      <x:c r="H31" s="3" t="str">
         <x:v>冠生园路28号</x:v>
       </x:c>
-      <x:c r="H31" s="3" t="str">
+      <x:c r="I31" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J31" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K31" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L31" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%9B%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%86%A0%E7%94%9F%E5%9B%AD%20%E5%86%A0%E7%94%9F%E5%9B%AD%E8%B7%AF28%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I31" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J31" s="3" t="str">
+      <x:c r="M31" s="3" t="str">
+        <x:v>64751426</x:v>
+      </x:c>
+      <x:c r="N31" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K31" s="3" t="n">
+      <x:c r="O31" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="L31" s="3" t="str">
+      <x:c r="P31" s="3" t="str">
         <x:v>康健路、习勤、薛家宅、科苑、九弄、中海、梓树园、月河、宾阳、馨汇南苑、公园道</x:v>
       </x:c>
-      <x:c r="M31" s="3" t="str">
+      <x:c r="Q31" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N31" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O31" s="3" t="str"/>
-      <x:c r="P31" s="3" t="str">
+      <x:c r="R31" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S31" s="3" t="str"/>
+      <x:c r="T31" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3096,40 +3479,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D32" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E32" s="3" t="str">
         <x:v>望德幼儿园</x:v>
       </x:c>
-      <x:c r="E32" s="3" t="str">
+      <x:c r="F32" s="3" t="str">
         <x:v>康健/南站</x:v>
       </x:c>
-      <x:c r="F32" s="3" t="str">
+      <x:c r="G32" s="3" t="str">
         <x:v>南宁园</x:v>
       </x:c>
-      <x:c r="G32" s="3" t="str">
+      <x:c r="H32" s="3" t="str">
         <x:v>南宁路636号</x:v>
       </x:c>
-      <x:c r="H32" s="3" t="str">
+      <x:c r="I32" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J32" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K32" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L32" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%9B%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%AE%81%E5%9B%AD%20%E5%8D%97%E5%AE%81%E8%B7%AF636%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I32" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J32" s="3" t="str">
+      <x:c r="M32" s="3" t="str">
+        <x:v>64751426</x:v>
+      </x:c>
+      <x:c r="N32" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K32" s="3" t="n">
+      <x:c r="O32" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="L32" s="3" t="str">
+      <x:c r="P32" s="3" t="str">
         <x:v>康健路、习勤、薛家宅、科苑、九弄、中海、梓树园、月河、宾阳、馨汇南苑、公园道</x:v>
       </x:c>
-      <x:c r="M32" s="3" t="str">
+      <x:c r="Q32" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N32" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O32" s="3" t="str"/>
-      <x:c r="P32" s="3" t="str">
+      <x:c r="R32" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S32" s="3" t="str"/>
+      <x:c r="T32" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3144,40 +3539,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D33" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E33" s="3" t="str">
         <x:v>瑞德幼儿园</x:v>
       </x:c>
-      <x:c r="E33" s="3" t="str">
+      <x:c r="F33" s="3" t="str">
         <x:v>长桥/汇成</x:v>
       </x:c>
-      <x:c r="F33" s="3" t="str">
+      <x:c r="G33" s="3" t="str">
         <x:v>楼园园</x:v>
       </x:c>
-      <x:c r="G33" s="3" t="str">
+      <x:c r="H33" s="3" t="str">
         <x:v>老沪闵路706弄37号</x:v>
       </x:c>
-      <x:c r="H33" s="3" t="str">
+      <x:c r="I33" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J33" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K33" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L33" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%91%9E%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%A5%BC%E5%9B%AD%E5%9B%AD%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF706%E5%BC%8437%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I33" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J33" s="3" t="str">
+      <x:c r="M33" s="3" t="str">
+        <x:v>021-64234155</x:v>
+      </x:c>
+      <x:c r="N33" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K33" s="3" t="n">
+      <x:c r="O33" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L33" s="3" t="str">
+      <x:c r="P33" s="3" t="str">
         <x:v>汇成一村、汇成二村、汇成三村、汇成四村、华东二、楼园、金牛、挹翠苑、罗城、光华、汇澜苑、金塘</x:v>
       </x:c>
-      <x:c r="M33" s="3" t="str">
+      <x:c r="Q33" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N33" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O33" s="3" t="str"/>
-      <x:c r="P33" s="3" t="str">
+      <x:c r="R33" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S33" s="3" t="str"/>
+      <x:c r="T33" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3192,40 +3599,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D34" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E34" s="3" t="str">
         <x:v>瑞德幼儿园</x:v>
       </x:c>
-      <x:c r="E34" s="3" t="str">
+      <x:c r="F34" s="3" t="str">
         <x:v>长桥/汇成</x:v>
       </x:c>
-      <x:c r="F34" s="3" t="str">
+      <x:c r="G34" s="3" t="str">
         <x:v>金塘园</x:v>
       </x:c>
-      <x:c r="G34" s="3" t="str">
+      <x:c r="H34" s="3" t="str">
         <x:v>老沪闵路333弄70号</x:v>
       </x:c>
-      <x:c r="H34" s="3" t="str">
+      <x:c r="I34" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J34" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K34" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L34" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%91%9E%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%87%91%E5%A1%98%E5%9B%AD%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF333%E5%BC%8470%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I34" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J34" s="3" t="str">
+      <x:c r="M34" s="3" t="str">
+        <x:v>54963078</x:v>
+      </x:c>
+      <x:c r="N34" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K34" s="3" t="n">
+      <x:c r="O34" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L34" s="3" t="str">
+      <x:c r="P34" s="3" t="str">
         <x:v>汇成一村、汇成二村、汇成三村、汇成四村、华东二、楼园、金牛、挹翠苑、罗城、光华、汇澜苑、金塘</x:v>
       </x:c>
-      <x:c r="M34" s="3" t="str">
+      <x:c r="Q34" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N34" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O34" s="3" t="str"/>
-      <x:c r="P34" s="3" t="str">
+      <x:c r="R34" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S34" s="3" t="str"/>
+      <x:c r="T34" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3240,40 +3659,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D35" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E35" s="3" t="str">
         <x:v>益思幼儿园</x:v>
       </x:c>
-      <x:c r="E35" s="3" t="str">
+      <x:c r="F35" s="3" t="str">
         <x:v>田林/漕河泾</x:v>
       </x:c>
-      <x:c r="F35" s="3" t="str">
+      <x:c r="G35" s="3" t="str">
         <x:v>东园</x:v>
       </x:c>
-      <x:c r="G35" s="3" t="str">
+      <x:c r="H35" s="3" t="str">
         <x:v>田林九村6号</x:v>
       </x:c>
-      <x:c r="H35" s="3" t="str">
+      <x:c r="I35" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J35" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K35" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L35" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%9B%8A%E6%80%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%9C%E5%9B%AD%20%E7%94%B0%E6%9E%97%E4%B9%9D%E6%9D%916%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I35" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J35" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K35" s="3" t="n">
+      <x:c r="M35" s="3" t="str">
+        <x:v>64361935</x:v>
+      </x:c>
+      <x:c r="N35" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O35" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L35" s="3" t="str">
+      <x:c r="P35" s="3" t="str">
         <x:v>田林一二村、田林五六七村、田林八九十村、田林十三村、田林十一村、千鹤三、爱建园、万科华尔兹、新苑一二、新苑三四、新苑五六七、田林十四村第一、田林十四村第二</x:v>
       </x:c>
-      <x:c r="M35" s="3" t="str">
+      <x:c r="Q35" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N35" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O35" s="3" t="str"/>
-      <x:c r="P35" s="3" t="str">
+      <x:c r="R35" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S35" s="3" t="str"/>
+      <x:c r="T35" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3288,40 +3719,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D36" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E36" s="3" t="str">
         <x:v>益思幼儿园</x:v>
       </x:c>
-      <x:c r="E36" s="3" t="str">
+      <x:c r="F36" s="3" t="str">
         <x:v>田林/漕河泾</x:v>
       </x:c>
-      <x:c r="F36" s="3" t="str">
+      <x:c r="G36" s="3" t="str">
         <x:v>西园</x:v>
       </x:c>
-      <x:c r="G36" s="3" t="str">
+      <x:c r="H36" s="3" t="str">
         <x:v>宜山路701弄53号</x:v>
       </x:c>
-      <x:c r="H36" s="3" t="str">
+      <x:c r="I36" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J36" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K36" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L36" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%9B%8A%E6%80%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E8%A5%BF%E5%9B%AD%20%E5%AE%9C%E5%B1%B1%E8%B7%AF701%E5%BC%8453%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I36" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J36" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K36" s="3" t="n">
+      <x:c r="M36" s="3" t="str">
+        <x:v>64361935</x:v>
+      </x:c>
+      <x:c r="N36" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O36" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L36" s="3" t="str">
+      <x:c r="P36" s="3" t="str">
         <x:v>田林一二村、田林五六七村、田林八九十村、田林十三村、田林十一村、千鹤三、爱建园、万科华尔兹、新苑一二、新苑三四、新苑五六七、田林十四村第一、田林十四村第二</x:v>
       </x:c>
-      <x:c r="M36" s="3" t="str">
+      <x:c r="Q36" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N36" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O36" s="3" t="str"/>
-      <x:c r="P36" s="3" t="str">
+      <x:c r="R36" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S36" s="3" t="str"/>
+      <x:c r="T36" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3336,40 +3779,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D37" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E37" s="3" t="str">
         <x:v>樱花园幼儿园</x:v>
       </x:c>
-      <x:c r="E37" s="3" t="str">
+      <x:c r="F37" s="3" t="str">
         <x:v>康健/桂林</x:v>
       </x:c>
-      <x:c r="F37" s="3" t="str">
+      <x:c r="G37" s="3" t="str">
         <x:v>南园</x:v>
       </x:c>
-      <x:c r="G37" s="3" t="str">
+      <x:c r="H37" s="3" t="str">
         <x:v>百花街398号</x:v>
       </x:c>
-      <x:c r="H37" s="3" t="str">
+      <x:c r="I37" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J37" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K37" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L37" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A8%B1%E8%8A%B1%E5%9B%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E7%99%BE%E8%8A%B1%E8%A1%97398%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I37" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J37" s="3" t="str">
+      <x:c r="M37" s="3" t="str">
+        <x:v>021-54181491</x:v>
+      </x:c>
+      <x:c r="N37" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K37" s="3" t="n">
+      <x:c r="O37" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L37" s="3" t="str">
+      <x:c r="P37" s="3" t="str">
         <x:v>月季百藤、樱花园、茶花桂花、丁香迎春、玉兰园、寿益坊（海上华庭）、紫鹃园、紫薇园（牡丹园、玫瑰园）、金桂苑、紫荆党校</x:v>
       </x:c>
-      <x:c r="M37" s="3" t="str">
+      <x:c r="Q37" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N37" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O37" s="3" t="str"/>
-      <x:c r="P37" s="3" t="str">
+      <x:c r="R37" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S37" s="3" t="str"/>
+      <x:c r="T37" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3384,40 +3839,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D38" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E38" s="3" t="str">
         <x:v>樱花园幼儿园</x:v>
       </x:c>
-      <x:c r="E38" s="3" t="str">
+      <x:c r="F38" s="3" t="str">
         <x:v>康健/桂林</x:v>
       </x:c>
-      <x:c r="F38" s="3" t="str">
+      <x:c r="G38" s="3" t="str">
         <x:v>北园</x:v>
       </x:c>
-      <x:c r="G38" s="3" t="str">
+      <x:c r="H38" s="3" t="str">
         <x:v>虹漕南路杨家桥88号</x:v>
       </x:c>
-      <x:c r="H38" s="3" t="str">
+      <x:c r="I38" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J38" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K38" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L38" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A8%B1%E8%8A%B1%E5%9B%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E8%99%B9%E6%BC%95%E5%8D%97%E8%B7%AF%E6%9D%A8%E5%AE%B6%E6%A1%A588%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I38" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J38" s="3" t="str">
+      <x:c r="M38" s="3" t="str">
+        <x:v>54362050</x:v>
+      </x:c>
+      <x:c r="N38" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K38" s="3" t="n">
+      <x:c r="O38" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L38" s="3" t="str">
+      <x:c r="P38" s="3" t="str">
         <x:v>月季百藤、樱花园、茶花桂花、丁香迎春、玉兰园、寿益坊（海上华庭）、紫鹃园、紫薇园（牡丹园、玫瑰园）、金桂苑、紫荆党校</x:v>
       </x:c>
-      <x:c r="M38" s="3" t="str">
+      <x:c r="Q38" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N38" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O38" s="3" t="str"/>
-      <x:c r="P38" s="3" t="str">
+      <x:c r="R38" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S38" s="3" t="str"/>
+      <x:c r="T38" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3432,40 +3899,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D39" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E39" s="3" t="str">
         <x:v>长海幼儿园</x:v>
       </x:c>
-      <x:c r="E39" s="3" t="str">
+      <x:c r="F39" s="3" t="str">
         <x:v>康健/桂林</x:v>
       </x:c>
-      <x:c r="F39" s="3" t="str">
+      <x:c r="G39" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G39" s="3" t="str">
+      <x:c r="H39" s="3" t="str">
         <x:v>桂林西街15弄2号</x:v>
       </x:c>
-      <x:c r="H39" s="3" t="str">
+      <x:c r="I39" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J39" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K39" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L39" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E6%9E%97%E8%A5%BF%E8%A1%9715%E5%BC%842%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I39" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J39" s="3" t="str">
+      <x:c r="M39" s="3" t="str">
+        <x:v>54208285</x:v>
+      </x:c>
+      <x:c r="N39" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="K39" s="3" t="n">
+      <x:c r="O39" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L39" s="3" t="str">
+      <x:c r="P39" s="3" t="str">
         <x:v>长顺海、长虹坊、长青坊、长丰坊、长兴坊、师大新村、桂康</x:v>
       </x:c>
-      <x:c r="M39" s="3" t="str">
+      <x:c r="Q39" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N39" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O39" s="3" t="str"/>
-      <x:c r="P39" s="3" t="str">
+      <x:c r="R39" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S39" s="3" t="str"/>
+      <x:c r="T39" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3480,40 +3959,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D40" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E40" s="3" t="str">
         <x:v>康沁幼儿园</x:v>
       </x:c>
-      <x:c r="E40" s="3" t="str">
+      <x:c r="F40" s="3" t="str">
         <x:v>康健/桂林</x:v>
       </x:c>
-      <x:c r="F40" s="3" t="str">
+      <x:c r="G40" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G40" s="3" t="str">
+      <x:c r="H40" s="3" t="str">
         <x:v>桂林西街151弄20号甲</x:v>
       </x:c>
-      <x:c r="H40" s="3" t="str">
+      <x:c r="I40" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J40" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K40" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L40" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%BA%B7%E6%B2%81%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E6%9E%97%E8%A5%BF%E8%A1%97151%E5%BC%8420%E5%8F%B7%E7%94%B2</x:v>
       </x:c>
-      <x:c r="I40" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J40" s="3" t="str">
+      <x:c r="M40" s="3" t="str">
+        <x:v>54363105</x:v>
+      </x:c>
+      <x:c r="N40" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="K40" s="3" t="n">
+      <x:c r="O40" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L40" s="3" t="str">
+      <x:c r="P40" s="3" t="str">
         <x:v>寿昌山、寿祥坊、寿益坊（寿益坊、桂林西街101弄）、康乐、桂二、冠生园、康宁馨、康强海（康强坊）</x:v>
       </x:c>
-      <x:c r="M40" s="3" t="str">
+      <x:c r="Q40" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N40" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O40" s="3" t="str"/>
-      <x:c r="P40" s="3" t="str">
+      <x:c r="R40" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S40" s="3" t="str"/>
+      <x:c r="T40" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3528,40 +4019,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D41" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E41" s="3" t="str">
         <x:v>长桥第一幼儿园</x:v>
       </x:c>
-      <x:c r="E41" s="3" t="str">
+      <x:c r="F41" s="3" t="str">
         <x:v>长桥</x:v>
       </x:c>
-      <x:c r="F41" s="3" t="str">
+      <x:c r="G41" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G41" s="3" t="str">
+      <x:c r="H41" s="3" t="str">
         <x:v>长桥一村56号</x:v>
       </x:c>
-      <x:c r="H41" s="3" t="str">
+      <x:c r="I41" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J41" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K41" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L41" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%95%BF%E6%A1%A5%E4%B8%80%E6%9D%9156%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I41" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J41" s="3" t="str">
+      <x:c r="M41" s="3" t="str">
+        <x:v>64100149</x:v>
+      </x:c>
+      <x:c r="N41" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="K41" s="3" t="n">
+      <x:c r="O41" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L41" s="3" t="str">
+      <x:c r="P41" s="3" t="str">
         <x:v>长桥一村、长桥五村（书香逸居、长桥五村）、闵朱、舒城</x:v>
       </x:c>
-      <x:c r="M41" s="3" t="str">
+      <x:c r="Q41" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N41" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O41" s="3" t="str"/>
-      <x:c r="P41" s="3" t="str">
+      <x:c r="R41" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S41" s="3" t="str"/>
+      <x:c r="T41" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3576,40 +4079,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D42" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E42" s="3" t="str">
         <x:v>长桥第二幼儿园</x:v>
       </x:c>
-      <x:c r="E42" s="3" t="str">
+      <x:c r="F42" s="3" t="str">
         <x:v>长桥/凌云</x:v>
       </x:c>
-      <x:c r="F42" s="3" t="str">
+      <x:c r="G42" s="3" t="str">
         <x:v>凌云园</x:v>
       </x:c>
-      <x:c r="G42" s="3" t="str">
+      <x:c r="H42" s="3" t="str">
         <x:v>梅陇十一村97号</x:v>
       </x:c>
-      <x:c r="H42" s="3" t="str">
+      <x:c r="I42" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J42" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K42" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L42" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%BA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%87%8C%E4%BA%91%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%8D%81%E4%B8%80%E6%9D%9197%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I42" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J42" s="3" t="str">
+      <x:c r="M42" s="3" t="str">
+        <x:v>34318987</x:v>
+      </x:c>
+      <x:c r="N42" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K42" s="3" t="n">
+      <x:c r="O42" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L42" s="3" t="str">
+      <x:c r="P42" s="3" t="str">
         <x:v>长桥新村一、长桥新二村、长桥七村、兴荣苑、和平、龙州、梅陇十一第一、梅陇十一第二、陇南、闵秀</x:v>
       </x:c>
-      <x:c r="M42" s="3" t="str">
+      <x:c r="Q42" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N42" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O42" s="3" t="str"/>
-      <x:c r="P42" s="3" t="str">
+      <x:c r="R42" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S42" s="3" t="str"/>
+      <x:c r="T42" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3624,40 +4139,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D43" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E43" s="3" t="str">
         <x:v>长桥第二幼儿园</x:v>
       </x:c>
-      <x:c r="E43" s="3" t="str">
+      <x:c r="F43" s="3" t="str">
         <x:v>长桥/凌云</x:v>
       </x:c>
-      <x:c r="F43" s="3" t="str">
+      <x:c r="G43" s="3" t="str">
         <x:v>长桥园</x:v>
       </x:c>
-      <x:c r="G43" s="3" t="str">
+      <x:c r="H43" s="3" t="str">
         <x:v>长桥二村34号</x:v>
       </x:c>
-      <x:c r="H43" s="3" t="str">
+      <x:c r="I43" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J43" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K43" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L43" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%BA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E4%BA%8C%E6%9D%9134%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I43" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J43" s="3" t="str">
+      <x:c r="M43" s="3" t="str">
+        <x:v>64102557</x:v>
+      </x:c>
+      <x:c r="N43" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K43" s="3" t="n">
+      <x:c r="O43" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L43" s="3" t="str">
+      <x:c r="P43" s="3" t="str">
         <x:v>长桥新村一、长桥新二村、长桥七村、兴荣苑、和平、龙州、梅陇十一第一、梅陇十一第二、陇南、闵秀</x:v>
       </x:c>
-      <x:c r="M43" s="3" t="str">
+      <x:c r="Q43" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N43" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O43" s="3" t="str"/>
-      <x:c r="P43" s="3" t="str">
+      <x:c r="R43" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S43" s="3" t="str"/>
+      <x:c r="T43" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3672,40 +4199,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D44" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E44" s="3" t="str">
         <x:v>长桥第三幼儿园</x:v>
       </x:c>
-      <x:c r="E44" s="3" t="str">
+      <x:c r="F44" s="3" t="str">
         <x:v>长桥</x:v>
       </x:c>
-      <x:c r="F44" s="3" t="str">
+      <x:c r="G44" s="3" t="str">
         <x:v>长桥园</x:v>
       </x:c>
-      <x:c r="G44" s="3" t="str">
+      <x:c r="H44" s="3" t="str">
         <x:v>长桥三村124号</x:v>
       </x:c>
-      <x:c r="H44" s="3" t="str">
+      <x:c r="I44" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J44" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K44" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L44" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%B8%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E4%B8%89%E6%9D%91124%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I44" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J44" s="3" t="str">
+      <x:c r="M44" s="3" t="str">
+        <x:v>64102397</x:v>
+      </x:c>
+      <x:c r="N44" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K44" s="3" t="n">
+      <x:c r="O44" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L44" s="3" t="str">
+      <x:c r="P44" s="3" t="str">
         <x:v>长桥三村一、长桥三村二（长桥三村东区）、长桥八村、平福、长桥四村</x:v>
       </x:c>
-      <x:c r="M44" s="3" t="str">
+      <x:c r="Q44" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N44" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O44" s="3" t="str"/>
-      <x:c r="P44" s="3" t="str">
+      <x:c r="R44" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S44" s="3" t="str"/>
+      <x:c r="T44" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3720,40 +4259,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D45" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E45" s="3" t="str">
         <x:v>长桥第三幼儿园</x:v>
       </x:c>
-      <x:c r="E45" s="3" t="str">
+      <x:c r="F45" s="3" t="str">
         <x:v>长桥</x:v>
       </x:c>
-      <x:c r="F45" s="3" t="str">
+      <x:c r="G45" s="3" t="str">
         <x:v>平福园</x:v>
       </x:c>
-      <x:c r="G45" s="3" t="str">
+      <x:c r="H45" s="3" t="str">
         <x:v>上中路483弄32号</x:v>
       </x:c>
-      <x:c r="H45" s="3" t="str">
+      <x:c r="I45" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J45" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K45" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L45" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%B8%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%B9%B3%E7%A6%8F%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E8%B7%AF483%E5%BC%8432%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I45" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J45" s="3" t="str">
+      <x:c r="M45" s="3" t="str">
+        <x:v>64102397</x:v>
+      </x:c>
+      <x:c r="N45" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K45" s="3" t="n">
+      <x:c r="O45" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L45" s="3" t="str">
+      <x:c r="P45" s="3" t="str">
         <x:v>长桥三村一、长桥三村二（长桥三村东区）、长桥八村、平福、长桥四村</x:v>
       </x:c>
-      <x:c r="M45" s="3" t="str">
+      <x:c r="Q45" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N45" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O45" s="3" t="str"/>
-      <x:c r="P45" s="3" t="str">
+      <x:c r="R45" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S45" s="3" t="str"/>
+      <x:c r="T45" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3768,40 +4319,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D46" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E46" s="3" t="str">
         <x:v>园南幼儿园</x:v>
       </x:c>
-      <x:c r="E46" s="3" t="str">
+      <x:c r="F46" s="3" t="str">
         <x:v>长桥/园南</x:v>
       </x:c>
-      <x:c r="F46" s="3" t="str">
+      <x:c r="G46" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G46" s="3" t="str">
+      <x:c r="H46" s="3" t="str">
         <x:v>龙川北路园南一村27号</x:v>
       </x:c>
-      <x:c r="H46" s="3" t="str">
+      <x:c r="I46" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J46" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K46" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L46" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9B%AD%E5%8D%97%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%B7%9D%E5%8C%97%E8%B7%AF%E5%9B%AD%E5%8D%97%E4%B8%80%E6%9D%9127%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I46" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J46" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K46" s="3" t="n">
+      <x:c r="M46" s="3" t="str">
+        <x:v>64763190</x:v>
+      </x:c>
+      <x:c r="N46" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O46" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L46" s="3" t="str">
+      <x:c r="P46" s="3" t="str">
         <x:v>园南一村、园南二村、园南三村、汇成五村、华东一</x:v>
       </x:c>
-      <x:c r="M46" s="3" t="str">
+      <x:c r="Q46" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N46" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O46" s="3" t="str"/>
-      <x:c r="P46" s="3" t="str">
+      <x:c r="R46" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S46" s="3" t="str"/>
+      <x:c r="T46" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3816,40 +4379,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D47" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E47" s="3" t="str">
         <x:v>梅陇幼儿园</x:v>
       </x:c>
-      <x:c r="E47" s="3" t="str">
+      <x:c r="F47" s="3" t="str">
         <x:v>凌云/梅陇</x:v>
       </x:c>
-      <x:c r="F47" s="3" t="str">
+      <x:c r="G47" s="3" t="str">
         <x:v>嘉川园</x:v>
       </x:c>
-      <x:c r="G47" s="3" t="str">
+      <x:c r="H47" s="3" t="str">
         <x:v>梅陇四村56号甲</x:v>
       </x:c>
-      <x:c r="H47" s="3" t="str">
+      <x:c r="I47" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J47" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K47" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L47" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A2%85%E9%99%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%98%89%E5%B7%9D%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%9B%9B%E6%9D%9156%E5%8F%B7%E7%94%B2</x:v>
       </x:c>
-      <x:c r="I47" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J47" s="3" t="str">
+      <x:c r="M47" s="3" t="str">
+        <x:v>64100015</x:v>
+      </x:c>
+      <x:c r="N47" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K47" s="3" t="n">
+      <x:c r="O47" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L47" s="3" t="str">
+      <x:c r="P47" s="3" t="str">
         <x:v>梅三、梅六、梅苑一、梅苑二、凌云、梅四、理工一、理工二、华理苑、书香苑、家乐苑、阳光（阳光新景）</x:v>
       </x:c>
-      <x:c r="M47" s="3" t="str">
+      <x:c r="Q47" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N47" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O47" s="3" t="str"/>
-      <x:c r="P47" s="3" t="str">
+      <x:c r="R47" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S47" s="3" t="str"/>
+      <x:c r="T47" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3864,40 +4439,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D48" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E48" s="3" t="str">
         <x:v>梅陇幼儿园</x:v>
       </x:c>
-      <x:c r="E48" s="3" t="str">
+      <x:c r="F48" s="3" t="str">
         <x:v>凌云/梅陇</x:v>
       </x:c>
-      <x:c r="F48" s="3" t="str">
+      <x:c r="G48" s="3" t="str">
         <x:v>梅陇园</x:v>
       </x:c>
-      <x:c r="G48" s="3" t="str">
+      <x:c r="H48" s="3" t="str">
         <x:v>梅陇六村65号</x:v>
       </x:c>
-      <x:c r="H48" s="3" t="str">
+      <x:c r="I48" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J48" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K48" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L48" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A2%85%E9%99%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%85%AD%E6%9D%9165%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I48" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J48" s="3" t="str">
+      <x:c r="M48" s="3" t="str">
+        <x:v>64100015</x:v>
+      </x:c>
+      <x:c r="N48" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K48" s="3" t="n">
+      <x:c r="O48" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L48" s="3" t="str">
+      <x:c r="P48" s="3" t="str">
         <x:v>梅三、梅六、梅苑一、梅苑二、凌云、梅四、理工一、理工二、华理苑、书香苑、家乐苑、阳光（阳光新景）</x:v>
       </x:c>
-      <x:c r="M48" s="3" t="str">
+      <x:c r="Q48" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N48" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O48" s="3" t="str"/>
-      <x:c r="P48" s="3" t="str">
+      <x:c r="R48" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S48" s="3" t="str"/>
+      <x:c r="T48" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3912,40 +4499,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D49" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E49" s="3" t="str">
         <x:v>梅陇第二幼儿园</x:v>
       </x:c>
-      <x:c r="E49" s="3" t="str">
+      <x:c r="F49" s="3" t="str">
         <x:v>凌云/梅陇</x:v>
       </x:c>
-      <x:c r="F49" s="3" t="str">
+      <x:c r="G49" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G49" s="3" t="str">
+      <x:c r="H49" s="3" t="str">
         <x:v>梅陇五村54号</x:v>
       </x:c>
-      <x:c r="H49" s="3" t="str">
+      <x:c r="I49" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J49" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K49" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L49" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A2%85%E9%99%87%E7%AC%AC%E4%BA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E4%BA%94%E6%9D%9154%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I49" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J49" s="3" t="str">
+      <x:c r="M49" s="3" t="str">
+        <x:v>64775092</x:v>
+      </x:c>
+      <x:c r="N49" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="K49" s="3" t="n">
+      <x:c r="O49" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L49" s="3" t="str">
+      <x:c r="P49" s="3" t="str">
         <x:v>梅陇五村、梅陇七村、梅陇八村、梅陇十村、梅陇九村、阳光（阳光绿园）、长陇苑</x:v>
       </x:c>
-      <x:c r="M49" s="3" t="str">
+      <x:c r="Q49" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N49" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O49" s="3" t="str"/>
-      <x:c r="P49" s="3" t="str">
+      <x:c r="R49" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S49" s="3" t="str"/>
+      <x:c r="T49" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3960,40 +4559,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D50" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E50" s="3" t="str">
         <x:v>华建幼儿园</x:v>
       </x:c>
-      <x:c r="E50" s="3" t="str">
+      <x:c r="F50" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="F50" s="3" t="str">
+      <x:c r="G50" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G50" s="3" t="str">
+      <x:c r="H50" s="3" t="str">
         <x:v>老沪闵路1300号</x:v>
       </x:c>
-      <x:c r="H50" s="3" t="str">
+      <x:c r="I50" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J50" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K50" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L50" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%8D%8E%E5%BB%BA%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF1300%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I50" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J50" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K50" s="3" t="n">
+      <x:c r="M50" s="3" t="str">
+        <x:v>2164548743</x:v>
+      </x:c>
+      <x:c r="N50" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O50" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L50" s="3" t="str">
+      <x:c r="P50" s="3" t="str">
         <x:v>华建、建华村、北杨村</x:v>
       </x:c>
-      <x:c r="M50" s="3" t="str">
+      <x:c r="Q50" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N50" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O50" s="3" t="str"/>
-      <x:c r="P50" s="3" t="str">
+      <x:c r="R50" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S50" s="3" t="str"/>
+      <x:c r="T50" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4008,40 +4619,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D51" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E51" s="3" t="str">
         <x:v>位育幼儿园</x:v>
       </x:c>
-      <x:c r="E51" s="3" t="str">
+      <x:c r="F51" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="F51" s="3" t="str">
+      <x:c r="G51" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G51" s="3" t="str">
+      <x:c r="H51" s="3" t="str">
         <x:v>建华路102号</x:v>
       </x:c>
-      <x:c r="H51" s="3" t="str">
+      <x:c r="I51" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J51" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K51" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L51" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BD%8D%E8%82%B2%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%BB%BA%E5%8D%8E%E8%B7%AF102%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I51" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J51" s="3" t="str">
+      <x:c r="M51" s="3" t="str">
+        <x:v>64960505</x:v>
+      </x:c>
+      <x:c r="N51" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K51" s="3" t="n">
+      <x:c r="O51" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L51" s="3" t="str">
+      <x:c r="P51" s="3" t="str">
         <x:v>华泾四村、华泾五村、漓江山水、联合居委</x:v>
       </x:c>
-      <x:c r="M51" s="3" t="str">
+      <x:c r="Q51" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N51" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O51" s="3" t="str"/>
-      <x:c r="P51" s="3" t="str">
+      <x:c r="R51" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S51" s="3" t="str"/>
+      <x:c r="T51" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4056,40 +4679,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D52" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E52" s="3" t="str">
         <x:v>果果幼儿园</x:v>
       </x:c>
-      <x:c r="E52" s="3" t="str">
+      <x:c r="F52" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="F52" s="3" t="str">
+      <x:c r="G52" s="3" t="str">
         <x:v>华欣园</x:v>
       </x:c>
-      <x:c r="G52" s="3" t="str">
+      <x:c r="H52" s="3" t="str">
         <x:v>龙吴路2422号</x:v>
       </x:c>
-      <x:c r="H52" s="3" t="str">
+      <x:c r="I52" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J52" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K52" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L52" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%9C%E6%9E%9C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%8E%E6%AC%A3%E5%9B%AD%20%E9%BE%99%E5%90%B4%E8%B7%AF2422%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I52" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J52" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K52" s="3" t="n">
+      <x:c r="M52" s="3" t="str">
+        <x:v>54829893</x:v>
+      </x:c>
+      <x:c r="N52" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O52" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L52" s="3" t="str">
+      <x:c r="P52" s="3" t="str">
         <x:v>华欣家园、华发、馨宁、大桥、明丰新纪苑、名苑、华臻</x:v>
       </x:c>
-      <x:c r="M52" s="3" t="str">
+      <x:c r="Q52" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N52" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O52" s="3" t="str"/>
-      <x:c r="P52" s="3" t="str">
+      <x:c r="R52" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S52" s="3" t="str"/>
+      <x:c r="T52" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4104,40 +4739,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D53" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E53" s="3" t="str">
         <x:v>果果幼儿园</x:v>
       </x:c>
-      <x:c r="E53" s="3" t="str">
+      <x:c r="F53" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="F53" s="3" t="str">
+      <x:c r="G53" s="3" t="str">
         <x:v>华发园</x:v>
       </x:c>
-      <x:c r="G53" s="3" t="str">
+      <x:c r="H53" s="3" t="str">
         <x:v>华发路100弄22号</x:v>
       </x:c>
-      <x:c r="H53" s="3" t="str">
+      <x:c r="I53" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J53" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K53" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L53" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%9C%E6%9E%9C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%8E%E5%8F%91%E5%9B%AD%20%E5%8D%8E%E5%8F%91%E8%B7%AF100%E5%BC%8422%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I53" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J53" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K53" s="3" t="n">
+      <x:c r="M53" s="3" t="str">
+        <x:v>54829893</x:v>
+      </x:c>
+      <x:c r="N53" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O53" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L53" s="3" t="str">
+      <x:c r="P53" s="3" t="str">
         <x:v>华欣家园、华发、馨宁、大桥、明丰新纪苑、名苑、华臻</x:v>
       </x:c>
-      <x:c r="M53" s="3" t="str">
+      <x:c r="Q53" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N53" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O53" s="3" t="str"/>
-      <x:c r="P53" s="3" t="str">
+      <x:c r="R53" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S53" s="3" t="str"/>
+      <x:c r="T53" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4152,40 +4799,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D54" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E54" s="3" t="str">
         <x:v>星辰幼儿园</x:v>
       </x:c>
-      <x:c r="E54" s="3" t="str">
+      <x:c r="F54" s="3" t="str">
         <x:v>华泾/罗秀</x:v>
       </x:c>
-      <x:c r="F54" s="3" t="str">
+      <x:c r="G54" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G54" s="3" t="str">
+      <x:c r="H54" s="3" t="str">
         <x:v>罗秀路11号</x:v>
       </x:c>
-      <x:c r="H54" s="3" t="str">
+      <x:c r="I54" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J54" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K54" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L54" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%98%9F%E8%BE%B0%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%BD%97%E7%A7%80%E8%B7%AF11%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I54" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J54" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K54" s="3" t="n">
+      <x:c r="M54" s="3" t="str">
+        <x:v>54010448</x:v>
+      </x:c>
+      <x:c r="N54" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O54" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L54" s="3" t="str">
+      <x:c r="P54" s="3" t="str">
         <x:v>徐汇新城、罗秀三村、华滨家园、华沁家园、罗秀、罗秀二村</x:v>
       </x:c>
-      <x:c r="M54" s="3" t="str">
+      <x:c r="Q54" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N54" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O54" s="3" t="str"/>
-      <x:c r="P54" s="3" t="str">
+      <x:c r="R54" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S54" s="3" t="str"/>
+      <x:c r="T54" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4200,40 +4859,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D55" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E55" s="3" t="str">
         <x:v>徐汇实验幼儿园</x:v>
       </x:c>
-      <x:c r="E55" s="3" t="str">
+      <x:c r="F55" s="3" t="str">
         <x:v>华泾/罗秀</x:v>
       </x:c>
-      <x:c r="F55" s="3" t="str">
+      <x:c r="G55" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G55" s="3" t="str">
+      <x:c r="H55" s="3" t="str">
         <x:v>龙瑞路135号</x:v>
       </x:c>
-      <x:c r="H55" s="3" t="str">
+      <x:c r="I55" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J55" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K55" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L55" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%BE%90%E6%B1%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E7%91%9E%E8%B7%AF135%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I55" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J55" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K55" s="3" t="n">
+      <x:c r="M55" s="3" t="str">
+        <x:v>54045192</x:v>
+      </x:c>
+      <x:c r="N55" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O55" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L55" s="3" t="str">
+      <x:c r="P55" s="3" t="str">
         <x:v>中海瀛台、百龙、港口</x:v>
       </x:c>
-      <x:c r="M55" s="3" t="str">
+      <x:c r="Q55" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N55" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O55" s="3" t="str"/>
-      <x:c r="P55" s="3" t="str">
+      <x:c r="R55" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S55" s="3" t="str"/>
+      <x:c r="T55" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4248,40 +4919,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D56" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E56" s="3" t="str">
         <x:v>印象幼儿园</x:v>
       </x:c>
-      <x:c r="E56" s="3" t="str">
+      <x:c r="F56" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="F56" s="3" t="str">
+      <x:c r="G56" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G56" s="3" t="str">
+      <x:c r="H56" s="3" t="str">
         <x:v>望月路882号</x:v>
       </x:c>
-      <x:c r="H56" s="3" t="str">
+      <x:c r="I56" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J56" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K56" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L56" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%8D%B0%E8%B1%A1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%9C%9B%E6%9C%88%E8%B7%AF882%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I56" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J56" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K56" s="3" t="n">
+      <x:c r="M56" s="3" t="str">
+        <x:v>64960096</x:v>
+      </x:c>
+      <x:c r="N56" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O56" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L56" s="3" t="str">
+      <x:c r="P56" s="3" t="str">
         <x:v>印象、华阳、沙家浜</x:v>
       </x:c>
-      <x:c r="M56" s="3" t="str">
+      <x:c r="Q56" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N56" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O56" s="3" t="str"/>
-      <x:c r="P56" s="3" t="str">
+      <x:c r="R56" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S56" s="3" t="str"/>
+      <x:c r="T56" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4296,40 +4979,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D57" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E57" s="3" t="str">
         <x:v>科技逸夫幼儿园</x:v>
       </x:c>
-      <x:c r="E57" s="3" t="str">
+      <x:c r="F57" s="3" t="str">
         <x:v>南站/石龙</x:v>
       </x:c>
-      <x:c r="F57" s="3" t="str">
+      <x:c r="G57" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G57" s="3" t="str">
+      <x:c r="H57" s="3" t="str">
         <x:v>石龙路818弄8号</x:v>
       </x:c>
-      <x:c r="H57" s="3" t="str">
+      <x:c r="I57" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J57" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K57" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L57" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E9%80%B8%E5%A4%AB%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%9F%B3%E9%BE%99%E8%B7%AF818%E5%BC%848%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I57" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J57" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K57" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L57" s="3" t="str">
+      <x:c r="M57" s="3" t="str">
+        <x:v>64400295</x:v>
+      </x:c>
+      <x:c r="N57" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O57" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P57" s="3" t="str">
         <x:v>正南、东荡、南站居委（临）</x:v>
       </x:c>
-      <x:c r="M57" s="3" t="str">
+      <x:c r="Q57" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N57" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O57" s="3" t="str"/>
-      <x:c r="P57" s="3" t="str">
+      <x:c r="R57" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S57" s="3" t="str"/>
+      <x:c r="T57" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4344,40 +5039,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D58" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E58" s="3" t="str">
         <x:v>盛华幼儿园</x:v>
       </x:c>
-      <x:c r="E58" s="3" t="str">
+      <x:c r="F58" s="3" t="str">
         <x:v>华泾</x:v>
       </x:c>
-      <x:c r="F58" s="3" t="str">
+      <x:c r="G58" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G58" s="3" t="str">
+      <x:c r="H58" s="3" t="str">
         <x:v>望月路401号</x:v>
       </x:c>
-      <x:c r="H58" s="3" t="str">
+      <x:c r="I58" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J58" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K58" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L58" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%9B%9B%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%9C%9B%E6%9C%88%E8%B7%AF401%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I58" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J58" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K58" s="3" t="n">
+      <x:c r="M58" s="3" t="str">
+        <x:v>021-54852338</x:v>
+      </x:c>
+      <x:c r="N58" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O58" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L58" s="3" t="str">
+      <x:c r="P58" s="3" t="str">
         <x:v>盛华、华泾绿苑、光华绿苑</x:v>
       </x:c>
-      <x:c r="M58" s="3" t="str">
+      <x:c r="Q58" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N58" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O58" s="3" t="str"/>
-      <x:c r="P58" s="3" t="str">
+      <x:c r="R58" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S58" s="3" t="str"/>
+      <x:c r="T58" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4392,40 +5099,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D59" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E59" s="3" t="str">
         <x:v>艺树幼儿园</x:v>
       </x:c>
-      <x:c r="E59" s="3" t="str">
+      <x:c r="F59" s="3" t="str">
         <x:v>徐家汇/田林</x:v>
       </x:c>
-      <x:c r="F59" s="3" t="str">
+      <x:c r="G59" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G59" s="3" t="str">
+      <x:c r="H59" s="3" t="str">
         <x:v>古井路160号</x:v>
       </x:c>
-      <x:c r="H59" s="3" t="str">
+      <x:c r="I59" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J59" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K59" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L59" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%89%BA%E6%A0%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E4%BA%95%E8%B7%AF160%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I59" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J59" s="3" t="str">
+      <x:c r="M59" s="3" t="str">
+        <x:v>64388770</x:v>
+      </x:c>
+      <x:c r="N59" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K59" s="3" t="n">
+      <x:c r="O59" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L59" s="3" t="str">
+      <x:c r="P59" s="3" t="str">
         <x:v>锦馨苑、千鹤第六、小安桥、华鼎广场、千鹤五、尚汇豪庭、千鹤一、千鹤二；另向徐家汇街道、田林街道扩招</x:v>
       </x:c>
-      <x:c r="M59" s="3" t="str">
+      <x:c r="Q59" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="N59" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O59" s="3" t="str"/>
-      <x:c r="P59" s="3" t="str">
+      <x:c r="R59" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S59" s="3" t="str"/>
+      <x:c r="T59" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4440,40 +5159,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D60" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E60" s="3" t="str">
         <x:v>桂平幼儿园</x:v>
       </x:c>
-      <x:c r="E60" s="3" t="str">
+      <x:c r="F60" s="3" t="str">
         <x:v>漕河泾/虹梅</x:v>
       </x:c>
-      <x:c r="F60" s="3" t="str">
+      <x:c r="G60" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G60" s="3" t="str">
+      <x:c r="H60" s="3" t="str">
         <x:v>桂平路260弄14号</x:v>
       </x:c>
-      <x:c r="H60" s="3" t="str">
+      <x:c r="I60" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J60" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K60" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L60" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A1%82%E5%B9%B3%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E5%B9%B3%E8%B7%AF260%E5%BC%8414%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I60" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J60" s="3" t="str">
+      <x:c r="M60" s="3" t="str">
+        <x:v>64031921</x:v>
+      </x:c>
+      <x:c r="N60" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K60" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L60" s="3" t="str">
+      <x:c r="O60" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P60" s="3" t="str">
         <x:v>联莘、欣园</x:v>
       </x:c>
-      <x:c r="M60" s="3" t="str">
+      <x:c r="Q60" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="N60" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O60" s="3" t="str"/>
-      <x:c r="P60" s="3" t="str">
+      <x:c r="R60" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S60" s="3" t="str"/>
+      <x:c r="T60" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4488,40 +5219,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D61" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E61" s="3" t="str">
         <x:v>田林第六幼儿园</x:v>
       </x:c>
-      <x:c r="E61" s="3" t="str">
+      <x:c r="F61" s="3" t="str">
         <x:v>田林/虹梅</x:v>
       </x:c>
-      <x:c r="F61" s="3" t="str">
+      <x:c r="G61" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G61" s="3" t="str">
+      <x:c r="H61" s="3" t="str">
         <x:v>田林十二村40号</x:v>
       </x:c>
-      <x:c r="H61" s="3" t="str">
+      <x:c r="I61" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J61" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K61" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L61" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E7%AC%AC%E5%85%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%8D%81%E4%BA%8C%E6%9D%9140%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I61" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J61" s="3" t="str">
+      <x:c r="M61" s="3" t="str">
+        <x:v>64366380</x:v>
+      </x:c>
+      <x:c r="N61" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K61" s="3" t="n">
+      <x:c r="O61" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L61" s="3" t="str">
+      <x:c r="P61" s="3" t="str">
         <x:v>田林十二村、田林三四村、古一、古二、古三、古四、东兰、航天新苑、永兆、漕河泾开发园区（临）；另向田林街道、虹梅路街道扩招</x:v>
       </x:c>
-      <x:c r="M61" s="3" t="str">
+      <x:c r="Q61" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="N61" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O61" s="3" t="str"/>
-      <x:c r="P61" s="3" t="str">
+      <x:c r="R61" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S61" s="3" t="str"/>
+      <x:c r="T61" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4536,40 +5279,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D62" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E62" s="3" t="str">
         <x:v>田林第六幼儿园</x:v>
       </x:c>
-      <x:c r="E62" s="3" t="str">
+      <x:c r="F62" s="3" t="str">
         <x:v>田林/虹梅</x:v>
       </x:c>
-      <x:c r="F62" s="3" t="str">
+      <x:c r="G62" s="3" t="str">
         <x:v>贝贝分园</x:v>
       </x:c>
-      <x:c r="G62" s="3" t="str">
+      <x:c r="H62" s="3" t="str">
         <x:v>田林四村18号</x:v>
       </x:c>
-      <x:c r="H62" s="3" t="str">
+      <x:c r="I62" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J62" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K62" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L62" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E7%AC%AC%E5%85%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E8%B4%9D%E8%B4%9D%E5%88%86%E5%9B%AD%20%E7%94%B0%E6%9E%97%E5%9B%9B%E6%9D%9118%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I62" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J62" s="3" t="str">
+      <x:c r="M62" s="3" t="str">
+        <x:v>64367248</x:v>
+      </x:c>
+      <x:c r="N62" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K62" s="3" t="n">
+      <x:c r="O62" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L62" s="3" t="str">
+      <x:c r="P62" s="3" t="str">
         <x:v>田林十二村、田林三四村、古一、古二、古三、古四、东兰、航天新苑、永兆、漕河泾开发园区（临）；另向田林街道、虹梅路街道扩招</x:v>
       </x:c>
-      <x:c r="M62" s="3" t="str">
+      <x:c r="Q62" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="N62" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O62" s="3" t="str"/>
-      <x:c r="P62" s="3" t="str">
+      <x:c r="R62" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S62" s="3" t="str"/>
+      <x:c r="T62" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4584,40 +5339,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D63" s="3" t="str">
+        <x:v>一级</x:v>
+      </x:c>
+      <x:c r="E63" s="3" t="str">
         <x:v>田林第六幼儿园</x:v>
       </x:c>
-      <x:c r="E63" s="3" t="str">
+      <x:c r="F63" s="3" t="str">
         <x:v>田林/虹梅</x:v>
       </x:c>
-      <x:c r="F63" s="3" t="str">
+      <x:c r="G63" s="3" t="str">
         <x:v>东兰分园</x:v>
       </x:c>
-      <x:c r="G63" s="3" t="str">
+      <x:c r="H63" s="3" t="str">
         <x:v>古美路1107弄65号</x:v>
       </x:c>
-      <x:c r="H63" s="3" t="str">
+      <x:c r="I63" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J63" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K63" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L63" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E7%AC%AC%E5%85%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%9C%E5%85%B0%E5%88%86%E5%9B%AD%20%E5%8F%A4%E7%BE%8E%E8%B7%AF1107%E5%BC%8465%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I63" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J63" s="3" t="str">
+      <x:c r="M63" s="3" t="str">
+        <x:v>64707260</x:v>
+      </x:c>
+      <x:c r="N63" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K63" s="3" t="n">
+      <x:c r="O63" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L63" s="3" t="str">
+      <x:c r="P63" s="3" t="str">
         <x:v>田林十二村、田林三四村、古一、古二、古三、古四、东兰、航天新苑、永兆、漕河泾开发园区（临）；另向田林街道、虹梅路街道扩招</x:v>
       </x:c>
-      <x:c r="M63" s="3" t="str">
+      <x:c r="Q63" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="N63" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O63" s="3" t="str"/>
-      <x:c r="P63" s="3" t="str">
+      <x:c r="R63" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S63" s="3" t="str"/>
+      <x:c r="T63" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4632,40 +5399,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D64" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E64" s="3" t="str">
         <x:v>紫薇实验幼儿园</x:v>
       </x:c>
-      <x:c r="E64" s="3" t="str">
+      <x:c r="F64" s="3" t="str">
         <x:v>康健/漕河泾</x:v>
       </x:c>
-      <x:c r="F64" s="3" t="str">
+      <x:c r="G64" s="3" t="str">
         <x:v>桂平园</x:v>
       </x:c>
-      <x:c r="G64" s="3" t="str">
+      <x:c r="H64" s="3" t="str">
         <x:v>桂平路123弄23号</x:v>
       </x:c>
-      <x:c r="H64" s="3" t="str">
+      <x:c r="I64" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J64" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K64" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L64" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%B4%AB%E8%96%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%A1%82%E5%B9%B3%E5%9B%AD%20%E6%A1%82%E5%B9%B3%E8%B7%AF123%E5%BC%8423%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I64" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J64" s="3" t="str">
+      <x:c r="M64" s="3" t="str">
+        <x:v>54217515</x:v>
+      </x:c>
+      <x:c r="N64" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K64" s="3" t="n">
+      <x:c r="O64" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L64" s="3" t="str">
+      <x:c r="P64" s="3" t="str">
         <x:v>紫薇园（桂平路123弄）、康强海（海上名邸）；区域内自主招生</x:v>
       </x:c>
-      <x:c r="M64" s="3" t="str">
+      <x:c r="Q64" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N64" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O64" s="3" t="str"/>
-      <x:c r="P64" s="3" t="str">
+      <x:c r="R64" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S64" s="3" t="str"/>
+      <x:c r="T64" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4680,40 +5459,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D65" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E65" s="3" t="str">
         <x:v>紫薇实验幼儿园</x:v>
       </x:c>
-      <x:c r="E65" s="3" t="str">
+      <x:c r="F65" s="3" t="str">
         <x:v>康健/漕河泾</x:v>
       </x:c>
-      <x:c r="F65" s="3" t="str">
+      <x:c r="G65" s="3" t="str">
         <x:v>浦北园</x:v>
       </x:c>
-      <x:c r="G65" s="3" t="str">
+      <x:c r="H65" s="3" t="str">
         <x:v>浦北路173号</x:v>
       </x:c>
-      <x:c r="H65" s="3" t="str">
+      <x:c r="I65" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J65" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K65" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L65" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%B4%AB%E8%96%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%B5%A6%E5%8C%97%E5%9B%AD%20%E6%B5%A6%E5%8C%97%E8%B7%AF173%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I65" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J65" s="3" t="str">
+      <x:c r="M65" s="3" t="str">
+        <x:v>64830788</x:v>
+      </x:c>
+      <x:c r="N65" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K65" s="3" t="n">
+      <x:c r="O65" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L65" s="3" t="str">
+      <x:c r="P65" s="3" t="str">
         <x:v>紫薇园（桂平路123弄）、康强海（海上名邸）；区域内自主招生</x:v>
       </x:c>
-      <x:c r="M65" s="3" t="str">
+      <x:c r="Q65" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N65" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O65" s="3" t="str"/>
-      <x:c r="P65" s="3" t="str">
+      <x:c r="R65" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S65" s="3" t="str"/>
+      <x:c r="T65" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4728,40 +5519,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D66" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E66" s="3" t="str">
         <x:v>紫薇实验幼儿园</x:v>
       </x:c>
-      <x:c r="E66" s="3" t="str">
+      <x:c r="F66" s="3" t="str">
         <x:v>康健/漕河泾</x:v>
       </x:c>
-      <x:c r="F66" s="3" t="str">
+      <x:c r="G66" s="3" t="str">
         <x:v>全州园</x:v>
       </x:c>
-      <x:c r="G66" s="3" t="str">
+      <x:c r="H66" s="3" t="str">
         <x:v>宜州路26号</x:v>
       </x:c>
-      <x:c r="H66" s="3" t="str">
+      <x:c r="I66" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J66" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K66" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L66" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%B4%AB%E8%96%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%85%A8%E5%B7%9E%E5%9B%AD%20%E5%AE%9C%E5%B7%9E%E8%B7%AF26%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I66" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J66" s="3" t="str">
+      <x:c r="M66" s="3" t="str">
+        <x:v>54500996</x:v>
+      </x:c>
+      <x:c r="N66" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K66" s="3" t="n">
+      <x:c r="O66" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L66" s="3" t="str">
+      <x:c r="P66" s="3" t="str">
         <x:v>紫薇园（桂平路123弄）、康强海（海上名邸）；区域内自主招生</x:v>
       </x:c>
-      <x:c r="M66" s="3" t="str">
+      <x:c r="Q66" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N66" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O66" s="3" t="str"/>
-      <x:c r="P66" s="3" t="str">
+      <x:c r="R66" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S66" s="3" t="str"/>
+      <x:c r="T66" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4776,40 +5579,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D67" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E67" s="3" t="str">
         <x:v>上海幼儿园</x:v>
       </x:c>
-      <x:c r="E67" s="3" t="str">
+      <x:c r="F67" s="3" t="str">
         <x:v>长桥/凌云</x:v>
       </x:c>
-      <x:c r="F67" s="3" t="str">
+      <x:c r="G67" s="3" t="str">
         <x:v>凌云园</x:v>
       </x:c>
-      <x:c r="G67" s="3" t="str">
+      <x:c r="H67" s="3" t="str">
         <x:v>上中西路378号</x:v>
       </x:c>
-      <x:c r="H67" s="3" t="str">
+      <x:c r="I67" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J67" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K67" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L67" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%8A%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%87%8C%E4%BA%91%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E8%A5%BF%E8%B7%AF378%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I67" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J67" s="3" t="str">
+      <x:c r="M67" s="3" t="str">
+        <x:v>64106663 / 64100564 / 64250961</x:v>
+      </x:c>
+      <x:c r="N67" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K67" s="3" t="n">
+      <x:c r="O67" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L67" s="3" t="str">
+      <x:c r="P67" s="3" t="str">
         <x:v>体育花苑、长桥五村（上中路100弄）、长桥三村二（尚海悦庭）；另向凌云路街道、长桥街道、华泾镇扩招</x:v>
       </x:c>
-      <x:c r="M67" s="3" t="str">
+      <x:c r="Q67" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="N67" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O67" s="3" t="str"/>
-      <x:c r="P67" s="3" t="str">
+      <x:c r="R67" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S67" s="3" t="str"/>
+      <x:c r="T67" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4824,40 +5639,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D68" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E68" s="3" t="str">
         <x:v>上海幼儿园</x:v>
       </x:c>
-      <x:c r="E68" s="3" t="str">
+      <x:c r="F68" s="3" t="str">
         <x:v>长桥/凌云</x:v>
       </x:c>
-      <x:c r="F68" s="3" t="str">
+      <x:c r="G68" s="3" t="str">
         <x:v>冠军园</x:v>
       </x:c>
-      <x:c r="G68" s="3" t="str">
+      <x:c r="H68" s="3" t="str">
         <x:v>老沪闵路729弄41号乙</x:v>
       </x:c>
-      <x:c r="H68" s="3" t="str">
+      <x:c r="I68" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J68" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K68" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L68" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%8A%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%86%A0%E5%86%9B%E5%9B%AD%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF729%E5%BC%8441%E5%8F%B7%E4%B9%99</x:v>
       </x:c>
-      <x:c r="I68" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J68" s="3" t="str">
+      <x:c r="M68" s="3" t="str">
+        <x:v>64250961</x:v>
+      </x:c>
+      <x:c r="N68" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K68" s="3" t="n">
+      <x:c r="O68" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L68" s="3" t="str">
+      <x:c r="P68" s="3" t="str">
         <x:v>体育花苑、长桥五村（上中路100弄）、长桥三村二（尚海悦庭）；另向凌云路街道、长桥街道、华泾镇扩招</x:v>
       </x:c>
-      <x:c r="M68" s="3" t="str">
+      <x:c r="Q68" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="N68" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O68" s="3" t="str"/>
-      <x:c r="P68" s="3" t="str">
+      <x:c r="R68" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S68" s="3" t="str"/>
+      <x:c r="T68" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4872,40 +5699,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D69" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E69" s="3" t="str">
         <x:v>上海幼儿园</x:v>
       </x:c>
-      <x:c r="E69" s="3" t="str">
+      <x:c r="F69" s="3" t="str">
         <x:v>长桥/凌云</x:v>
       </x:c>
-      <x:c r="F69" s="3" t="str">
+      <x:c r="G69" s="3" t="str">
         <x:v>上中园</x:v>
       </x:c>
-      <x:c r="G69" s="3" t="str">
+      <x:c r="H69" s="3" t="str">
         <x:v>上中路402号</x:v>
       </x:c>
-      <x:c r="H69" s="3" t="str">
+      <x:c r="I69" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J69" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K69" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L69" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%8A%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E8%B7%AF402%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I69" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J69" s="3" t="str">
+      <x:c r="M69" s="3" t="str">
+        <x:v>64106663 / 64100564 / 64250961</x:v>
+      </x:c>
+      <x:c r="N69" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K69" s="3" t="n">
+      <x:c r="O69" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L69" s="3" t="str">
+      <x:c r="P69" s="3" t="str">
         <x:v>体育花苑、长桥五村（上中路100弄）、长桥三村二（尚海悦庭）；另向凌云路街道、长桥街道、华泾镇扩招</x:v>
       </x:c>
-      <x:c r="M69" s="3" t="str">
+      <x:c r="Q69" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="N69" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O69" s="3" t="str"/>
-      <x:c r="P69" s="3" t="str">
+      <x:c r="R69" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S69" s="3" t="str"/>
+      <x:c r="T69" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4920,40 +5759,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D70" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E70" s="3" t="str">
         <x:v>乌鲁木齐南路幼儿园</x:v>
       </x:c>
-      <x:c r="E70" s="3" t="str">
+      <x:c r="F70" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F70" s="3" t="str">
+      <x:c r="G70" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G70" s="3" t="str">
+      <x:c r="H70" s="3" t="str">
         <x:v>乌鲁木齐南路14号</x:v>
       </x:c>
-      <x:c r="H70" s="3" t="str">
+      <x:c r="I70" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J70" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K70" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L70" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF14%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I70" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J70" s="3" t="str">
+      <x:c r="M70" s="3" t="str">
+        <x:v>64319939</x:v>
+      </x:c>
+      <x:c r="N70" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K70" s="3" t="n">
+      <x:c r="O70" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L70" s="3" t="str">
+      <x:c r="P70" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M70" s="3" t="str">
+      <x:c r="Q70" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N70" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O70" s="3" t="str"/>
-      <x:c r="P70" s="3" t="str">
+      <x:c r="R70" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S70" s="3" t="str"/>
+      <x:c r="T70" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4968,40 +5819,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D71" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E71" s="3" t="str">
         <x:v>乌鲁木齐南路幼儿园</x:v>
       </x:c>
-      <x:c r="E71" s="3" t="str">
+      <x:c r="F71" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F71" s="3" t="str">
+      <x:c r="G71" s="3" t="str">
         <x:v>境内部</x:v>
       </x:c>
-      <x:c r="G71" s="3" t="str">
+      <x:c r="H71" s="3" t="str">
         <x:v>淮海路1788号</x:v>
       </x:c>
-      <x:c r="H71" s="3" t="str">
+      <x:c r="I71" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J71" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K71" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L71" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A2%83%E5%86%85%E9%83%A8%20%E6%B7%AE%E6%B5%B7%E8%B7%AF1788%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I71" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J71" s="3" t="str">
+      <x:c r="M71" s="3" t="str">
+        <x:v>64319939</x:v>
+      </x:c>
+      <x:c r="N71" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K71" s="3" t="n">
+      <x:c r="O71" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L71" s="3" t="str">
+      <x:c r="P71" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M71" s="3" t="str">
+      <x:c r="Q71" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N71" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O71" s="3" t="str"/>
-      <x:c r="P71" s="3" t="str">
+      <x:c r="R71" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S71" s="3" t="str"/>
+      <x:c r="T71" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5016,40 +5879,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D72" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E72" s="3" t="str">
         <x:v>乌鲁木齐南路幼儿园</x:v>
       </x:c>
-      <x:c r="E72" s="3" t="str">
+      <x:c r="F72" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F72" s="3" t="str">
+      <x:c r="G72" s="3" t="str">
         <x:v>境外部</x:v>
       </x:c>
-      <x:c r="G72" s="3" t="str">
+      <x:c r="H72" s="3" t="str">
         <x:v>淮海中路1480号</x:v>
       </x:c>
-      <x:c r="H72" s="3" t="str">
+      <x:c r="I72" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J72" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K72" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L72" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A2%83%E5%A4%96%E9%83%A8%20%E6%B7%AE%E6%B5%B7%E4%B8%AD%E8%B7%AF1480%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I72" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J72" s="3" t="str">
+      <x:c r="M72" s="3" t="str">
+        <x:v>64330160</x:v>
+      </x:c>
+      <x:c r="N72" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K72" s="3" t="n">
+      <x:c r="O72" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L72" s="3" t="str">
+      <x:c r="P72" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M72" s="3" t="str">
+      <x:c r="Q72" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N72" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O72" s="3" t="str"/>
-      <x:c r="P72" s="3" t="str">
+      <x:c r="R72" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S72" s="3" t="str"/>
+      <x:c r="T72" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5064,40 +5939,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D73" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E73" s="3" t="str">
         <x:v>科技幼儿园</x:v>
       </x:c>
-      <x:c r="E73" s="3" t="str">
+      <x:c r="F73" s="3" t="str">
         <x:v>徐家汇/田林</x:v>
       </x:c>
-      <x:c r="F73" s="3" t="str">
+      <x:c r="G73" s="3" t="str">
         <x:v>宜山园1部</x:v>
       </x:c>
-      <x:c r="G73" s="3" t="str">
+      <x:c r="H73" s="3" t="str">
         <x:v>宜山路655弄1号</x:v>
       </x:c>
-      <x:c r="H73" s="3" t="str">
+      <x:c r="I73" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J73" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K73" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L73" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%AE%9C%E5%B1%B1%E5%9B%AD1%E9%83%A8%20%E5%AE%9C%E5%B1%B1%E8%B7%AF655%E5%BC%841%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I73" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J73" s="3" t="str">
+      <x:c r="M73" s="3" t="str">
+        <x:v>64854450 / 64362975</x:v>
+      </x:c>
+      <x:c r="N73" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K73" s="3" t="n">
+      <x:c r="O73" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L73" s="3" t="str">
+      <x:c r="P73" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M73" s="3" t="str">
+      <x:c r="Q73" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N73" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O73" s="3" t="str"/>
-      <x:c r="P73" s="3" t="str">
+      <x:c r="R73" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S73" s="3" t="str"/>
+      <x:c r="T73" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5112,40 +5999,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D74" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E74" s="3" t="str">
         <x:v>科技幼儿园</x:v>
       </x:c>
-      <x:c r="E74" s="3" t="str">
+      <x:c r="F74" s="3" t="str">
         <x:v>徐家汇/田林</x:v>
       </x:c>
-      <x:c r="F74" s="3" t="str">
+      <x:c r="G74" s="3" t="str">
         <x:v>嘉陵园</x:v>
       </x:c>
-      <x:c r="G74" s="3" t="str">
+      <x:c r="H74" s="3" t="str">
         <x:v>嘉陵路28号</x:v>
       </x:c>
-      <x:c r="H74" s="3" t="str">
+      <x:c r="I74" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J74" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K74" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L74" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%98%89%E9%99%B5%E5%9B%AD%20%E5%98%89%E9%99%B5%E8%B7%AF28%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I74" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J74" s="3" t="str">
+      <x:c r="M74" s="3" t="str">
+        <x:v>54363003</x:v>
+      </x:c>
+      <x:c r="N74" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K74" s="3" t="n">
+      <x:c r="O74" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L74" s="3" t="str">
+      <x:c r="P74" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M74" s="3" t="str">
+      <x:c r="Q74" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N74" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O74" s="3" t="str"/>
-      <x:c r="P74" s="3" t="str">
+      <x:c r="R74" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S74" s="3" t="str"/>
+      <x:c r="T74" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5160,40 +6059,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D75" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E75" s="3" t="str">
         <x:v>科技幼儿园</x:v>
       </x:c>
-      <x:c r="E75" s="3" t="str">
+      <x:c r="F75" s="3" t="str">
         <x:v>徐家汇/田林</x:v>
       </x:c>
-      <x:c r="F75" s="3" t="str">
+      <x:c r="G75" s="3" t="str">
         <x:v>文定园</x:v>
       </x:c>
-      <x:c r="G75" s="3" t="str">
+      <x:c r="H75" s="3" t="str">
         <x:v>文定路476号</x:v>
       </x:c>
-      <x:c r="H75" s="3" t="str">
+      <x:c r="I75" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J75" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K75" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L75" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%96%87%E5%AE%9A%E5%9B%AD%20%E6%96%87%E5%AE%9A%E8%B7%AF476%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I75" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J75" s="3" t="str">
+      <x:c r="M75" s="3" t="str">
+        <x:v>64221181</x:v>
+      </x:c>
+      <x:c r="N75" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K75" s="3" t="n">
+      <x:c r="O75" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L75" s="3" t="str">
+      <x:c r="P75" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M75" s="3" t="str">
+      <x:c r="Q75" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N75" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O75" s="3" t="str"/>
-      <x:c r="P75" s="3" t="str">
+      <x:c r="R75" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S75" s="3" t="str"/>
+      <x:c r="T75" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5208,40 +6119,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D76" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E76" s="3" t="str">
         <x:v>科技幼儿园</x:v>
       </x:c>
-      <x:c r="E76" s="3" t="str">
+      <x:c r="F76" s="3" t="str">
         <x:v>徐家汇/田林</x:v>
       </x:c>
-      <x:c r="F76" s="3" t="str">
+      <x:c r="G76" s="3" t="str">
         <x:v>宜山园10部</x:v>
       </x:c>
-      <x:c r="G76" s="3" t="str">
+      <x:c r="H76" s="3" t="str">
         <x:v>宜山路655弄10号</x:v>
       </x:c>
-      <x:c r="H76" s="3" t="str">
+      <x:c r="I76" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J76" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K76" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L76" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%AE%9C%E5%B1%B1%E5%9B%AD10%E9%83%A8%20%E5%AE%9C%E5%B1%B1%E8%B7%AF655%E5%BC%8410%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I76" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J76" s="3" t="str">
+      <x:c r="M76" s="3" t="str">
+        <x:v>64854450 / 64362975</x:v>
+      </x:c>
+      <x:c r="N76" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K76" s="3" t="n">
+      <x:c r="O76" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L76" s="3" t="str">
+      <x:c r="P76" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M76" s="3" t="str">
+      <x:c r="Q76" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N76" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O76" s="3" t="str"/>
-      <x:c r="P76" s="3" t="str">
+      <x:c r="R76" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S76" s="3" t="str"/>
+      <x:c r="T76" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5256,40 +6179,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D77" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E77" s="3" t="str">
         <x:v>宛南实验幼儿园</x:v>
       </x:c>
-      <x:c r="E77" s="3" t="str">
+      <x:c r="F77" s="3" t="str">
         <x:v>龙华/滨江</x:v>
       </x:c>
-      <x:c r="F77" s="3" t="str">
+      <x:c r="G77" s="3" t="str">
         <x:v>瑞宁部</x:v>
       </x:c>
-      <x:c r="G77" s="3" t="str">
+      <x:c r="H77" s="3" t="str">
         <x:v>瑞宁路816号</x:v>
       </x:c>
-      <x:c r="H77" s="3" t="str">
+      <x:c r="I77" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J77" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K77" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L77" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%9B%E5%8D%97%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E7%91%9E%E5%AE%81%E9%83%A8%20%E7%91%9E%E5%AE%81%E8%B7%AF816%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I77" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J77" s="3" t="str">
+      <x:c r="M77" s="3" t="str">
+        <x:v>64363606</x:v>
+      </x:c>
+      <x:c r="N77" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K77" s="3" t="n">
+      <x:c r="O77" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L77" s="3" t="str">
+      <x:c r="P77" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M77" s="3" t="str">
+      <x:c r="Q77" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N77" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O77" s="3" t="str"/>
-      <x:c r="P77" s="3" t="str">
+      <x:c r="R77" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S77" s="3" t="str"/>
+      <x:c r="T77" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5304,40 +6239,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D78" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E78" s="3" t="str">
         <x:v>宛南实验幼儿园</x:v>
       </x:c>
-      <x:c r="E78" s="3" t="str">
+      <x:c r="F78" s="3" t="str">
         <x:v>龙华/滨江</x:v>
       </x:c>
-      <x:c r="F78" s="3" t="str">
+      <x:c r="G78" s="3" t="str">
         <x:v>滨江部</x:v>
       </x:c>
-      <x:c r="G78" s="3" t="str">
+      <x:c r="H78" s="3" t="str">
         <x:v>瑞宁路851号</x:v>
       </x:c>
-      <x:c r="H78" s="3" t="str">
+      <x:c r="I78" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J78" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K78" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L78" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%9B%E5%8D%97%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%BB%A8%E6%B1%9F%E9%83%A8%20%E7%91%9E%E5%AE%81%E8%B7%AF851%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I78" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J78" s="3" t="str">
+      <x:c r="M78" s="3" t="str">
+        <x:v>64161261</x:v>
+      </x:c>
+      <x:c r="N78" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K78" s="3" t="n">
+      <x:c r="O78" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L78" s="3" t="str">
+      <x:c r="P78" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M78" s="3" t="str">
+      <x:c r="Q78" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N78" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O78" s="3" t="str"/>
-      <x:c r="P78" s="3" t="str">
+      <x:c r="R78" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S78" s="3" t="str"/>
+      <x:c r="T78" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5352,40 +6299,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D79" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E79" s="3" t="str">
         <x:v>宛南实验幼儿园</x:v>
       </x:c>
-      <x:c r="E79" s="3" t="str">
+      <x:c r="F79" s="3" t="str">
         <x:v>龙华/滨江</x:v>
       </x:c>
-      <x:c r="F79" s="3" t="str">
+      <x:c r="G79" s="3" t="str">
         <x:v>大木桥部</x:v>
       </x:c>
-      <x:c r="G79" s="3" t="str">
+      <x:c r="H79" s="3" t="str">
         <x:v>大木桥路323号</x:v>
       </x:c>
-      <x:c r="H79" s="3" t="str">
+      <x:c r="I79" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J79" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K79" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L79" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%9B%E5%8D%97%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A4%A7%E6%9C%A8%E6%A1%A5%E9%83%A8%20%E5%A4%A7%E6%9C%A8%E6%A1%A5%E8%B7%AF323%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I79" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J79" s="3" t="str">
+      <x:c r="M79" s="3" t="str">
+        <x:v>64168714</x:v>
+      </x:c>
+      <x:c r="N79" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K79" s="3" t="n">
+      <x:c r="O79" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L79" s="3" t="str">
+      <x:c r="P79" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M79" s="3" t="str">
+      <x:c r="Q79" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N79" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O79" s="3" t="str"/>
-      <x:c r="P79" s="3" t="str">
+      <x:c r="R79" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S79" s="3" t="str"/>
+      <x:c r="T79" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5400,40 +6359,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D80" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E80" s="3" t="str">
         <x:v>机关建国幼儿园</x:v>
       </x:c>
-      <x:c r="E80" s="3" t="str">
+      <x:c r="F80" s="3" t="str">
         <x:v>衡复/湖南/滨江</x:v>
       </x:c>
-      <x:c r="F80" s="3" t="str">
+      <x:c r="G80" s="3" t="str">
         <x:v>建国园</x:v>
       </x:c>
-      <x:c r="G80" s="3" t="str">
+      <x:c r="H80" s="3" t="str">
         <x:v>建国西路570号</x:v>
       </x:c>
-      <x:c r="H80" s="3" t="str">
+      <x:c r="I80" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J80" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K80" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L80" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%BA%E5%85%B3%E5%BB%BA%E5%9B%BD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%BB%BA%E5%9B%BD%E5%9B%AD%20%E5%BB%BA%E5%9B%BD%E8%A5%BF%E8%B7%AF570%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I80" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J80" s="3" t="str">
+      <x:c r="M80" s="3" t="str">
+        <x:v>64372841</x:v>
+      </x:c>
+      <x:c r="N80" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K80" s="3" t="n">
+      <x:c r="O80" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L80" s="3" t="str">
+      <x:c r="P80" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M80" s="3" t="str">
+      <x:c r="Q80" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N80" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O80" s="3" t="str"/>
-      <x:c r="P80" s="3" t="str">
+      <x:c r="R80" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S80" s="3" t="str"/>
+      <x:c r="T80" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5448,40 +6419,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D81" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E81" s="3" t="str">
         <x:v>机关建国幼儿园</x:v>
       </x:c>
-      <x:c r="E81" s="3" t="str">
+      <x:c r="F81" s="3" t="str">
         <x:v>衡复/湖南/滨江</x:v>
       </x:c>
-      <x:c r="F81" s="3" t="str">
+      <x:c r="G81" s="3" t="str">
         <x:v>安亭园</x:v>
       </x:c>
-      <x:c r="G81" s="3" t="str">
+      <x:c r="H81" s="3" t="str">
         <x:v>安亭路112号</x:v>
       </x:c>
-      <x:c r="H81" s="3" t="str">
+      <x:c r="I81" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J81" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K81" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L81" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%BA%E5%85%B3%E5%BB%BA%E5%9B%BD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%AE%89%E4%BA%AD%E5%9B%AD%20%E5%AE%89%E4%BA%AD%E8%B7%AF112%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I81" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J81" s="3" t="str">
+      <x:c r="M81" s="3" t="str">
+        <x:v>64333332</x:v>
+      </x:c>
+      <x:c r="N81" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K81" s="3" t="n">
+      <x:c r="O81" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L81" s="3" t="str">
+      <x:c r="P81" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M81" s="3" t="str">
+      <x:c r="Q81" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N81" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O81" s="3" t="str"/>
-      <x:c r="P81" s="3" t="str">
+      <x:c r="R81" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S81" s="3" t="str"/>
+      <x:c r="T81" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5496,40 +6479,52 @@
         <x:v>公办</x:v>
       </x:c>
       <x:c r="D82" s="3" t="str">
+        <x:v>示范园</x:v>
+      </x:c>
+      <x:c r="E82" s="3" t="str">
         <x:v>机关建国幼儿园</x:v>
       </x:c>
-      <x:c r="E82" s="3" t="str">
+      <x:c r="F82" s="3" t="str">
         <x:v>衡复/湖南/滨江</x:v>
       </x:c>
-      <x:c r="F82" s="3" t="str">
+      <x:c r="G82" s="3" t="str">
         <x:v>滨江园</x:v>
       </x:c>
-      <x:c r="G82" s="3" t="str">
+      <x:c r="H82" s="3" t="str">
         <x:v>云锦路183弄30号</x:v>
       </x:c>
-      <x:c r="H82" s="3" t="str">
+      <x:c r="I82" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J82" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K82" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L82" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%BA%E5%85%B3%E5%BB%BA%E5%9B%BD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%BB%A8%E6%B1%9F%E5%9B%AD%20%E4%BA%91%E9%94%A6%E8%B7%AF183%E5%BC%8430%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I82" s="3" t="str">
-        <x:v>待电话确认</x:v>
-      </x:c>
-      <x:c r="J82" s="3" t="str">
+      <x:c r="M82" s="3" t="str">
+        <x:v>54252106</x:v>
+      </x:c>
+      <x:c r="N82" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K82" s="3" t="n">
+      <x:c r="O82" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L82" s="3" t="str">
+      <x:c r="P82" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="M82" s="3" t="str">
+      <x:c r="Q82" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="N82" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O82" s="3" t="str"/>
-      <x:c r="P82" s="3" t="str">
+      <x:c r="R82" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S82" s="3" t="str"/>
+      <x:c r="T82" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5541,46 +6536,58 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C83" s="3" t="str">
-        <x:v>二级</x:v>
+        <x:v>民办（类型待核验）</x:v>
       </x:c>
       <x:c r="D83" s="3" t="str">
-        <x:v>维亚幼儿园</x:v>
+        <x:v>一级</x:v>
       </x:c>
       <x:c r="E83" s="3" t="str">
-        <x:v>衡复/湖南</x:v>
+        <x:v>杜鹃园幼稚园</x:v>
       </x:c>
       <x:c r="F83" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="G83" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G83" s="3" t="str">
-        <x:v>华亭路71弄1号</x:v>
-      </x:c>
       <x:c r="H83" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%BB%B4%E4%BA%9A%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8D%8E%E4%BA%AD%E8%B7%AF71%E5%BC%841%E5%8F%B7</x:v>
+        <x:v>桂林西街9弄57号</x:v>
       </x:c>
       <x:c r="I83" s="3" t="str">
-        <x:v>54036901</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J83" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K83" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L83" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9D%9C%E9%B9%83%E5%9B%AD%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E6%9E%97%E8%A5%BF%E8%A1%979%E5%BC%8457%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M83" s="3" t="str">
+        <x:v>021-54202188</x:v>
+      </x:c>
+      <x:c r="N83" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K83" s="3" t="str">
+      <x:c r="O83" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L83" s="3" t="str">
+      <x:c r="P83" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M83" s="3" t="str">
+      <x:c r="Q83" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N83" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O83" s="3" t="str">
+      <x:c r="R83" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S83" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P83" s="3" t="str">
-        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      <x:c r="T83" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -5591,46 +6598,58 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C84" s="3" t="str">
-        <x:v>二级</x:v>
+        <x:v>民办（类型待核验）</x:v>
       </x:c>
       <x:c r="D84" s="3" t="str">
-        <x:v>四季方馨幼儿园</x:v>
+        <x:v>一级</x:v>
       </x:c>
       <x:c r="E84" s="3" t="str">
-        <x:v>衡复/湖南</x:v>
+        <x:v>胡姬港湾幼儿园</x:v>
       </x:c>
       <x:c r="F84" s="3" t="str">
+        <x:v>龙华/滨江</x:v>
+      </x:c>
+      <x:c r="G84" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G84" s="3" t="str">
-        <x:v>五原路112号</x:v>
-      </x:c>
       <x:c r="H84" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9B%9B%E5%AD%A3%E6%96%B9%E9%A6%A8%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%BA%94%E5%8E%9F%E8%B7%AF112%E5%8F%B7</x:v>
+        <x:v>丰谷路205弄35号</x:v>
       </x:c>
       <x:c r="I84" s="3" t="str">
-        <x:v>021-54036603</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J84" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K84" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L84" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%83%A1%E5%A7%AC%E6%B8%AF%E6%B9%BE%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B8%B0%E8%B0%B7%E8%B7%AF205%E5%BC%8435%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M84" s="3" t="str">
+        <x:v>64560614</x:v>
+      </x:c>
+      <x:c r="N84" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K84" s="3" t="str">
+      <x:c r="O84" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L84" s="3" t="str">
+      <x:c r="P84" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M84" s="3" t="str">
+      <x:c r="Q84" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N84" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O84" s="3" t="str">
+      <x:c r="R84" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S84" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P84" s="3" t="str">
-        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      <x:c r="T84" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -5641,46 +6660,58 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C85" s="3" t="str">
-        <x:v>二级</x:v>
+        <x:v>普惠民办</x:v>
       </x:c>
       <x:c r="D85" s="3" t="str">
-        <x:v>滨江幼儿园</x:v>
+        <x:v>一级</x:v>
       </x:c>
       <x:c r="E85" s="3" t="str">
-        <x:v>龙华/滨江</x:v>
+        <x:v>汇城苑幼稚园</x:v>
       </x:c>
       <x:c r="F85" s="3" t="str">
+        <x:v>长桥/梅陇</x:v>
+      </x:c>
+      <x:c r="G85" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G85" s="3" t="str">
-        <x:v>云锦路80弄10号</x:v>
-      </x:c>
       <x:c r="H85" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BB%A8%E6%B1%9F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%BA%91%E9%94%A6%E8%B7%AF80%E5%BC%8410%E5%8F%B7</x:v>
+        <x:v>百色路汇城五村75号</x:v>
       </x:c>
       <x:c r="I85" s="3" t="str">
-        <x:v>64380700</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J85" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K85" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L85" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%9F%8E%E8%8B%91%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%99%BE%E8%89%B2%E8%B7%AF%E6%B1%87%E5%9F%8E%E4%BA%94%E6%9D%9175%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M85" s="3" t="str">
+        <x:v>64235119</x:v>
+      </x:c>
+      <x:c r="N85" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K85" s="3" t="str">
+      <x:c r="O85" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L85" s="3" t="str">
+      <x:c r="P85" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M85" s="3" t="str">
+      <x:c r="Q85" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N85" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O85" s="3" t="str">
+      <x:c r="R85" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S85" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P85" s="3" t="str">
-        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      <x:c r="T85" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -5691,45 +6722,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C86" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D86" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D86" s="3" t="str">
-        <x:v>汇宝幼儿园</x:v>
-      </x:c>
       <x:c r="E86" s="3" t="str">
-        <x:v>徐家汇/枫林</x:v>
+        <x:v>维亚幼儿园</x:v>
       </x:c>
       <x:c r="F86" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="G86" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G86" s="3" t="str">
-        <x:v>宛平南路592号</x:v>
-      </x:c>
       <x:c r="H86" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9B%E5%B9%B3%E5%8D%97%E8%B7%AF592%E5%8F%B7</x:v>
+        <x:v>华亭路71弄1号</x:v>
       </x:c>
       <x:c r="I86" s="3" t="str">
-        <x:v>64690445</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J86" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K86" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L86" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%BB%B4%E4%BA%9A%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8D%8E%E4%BA%AD%E8%B7%AF71%E5%BC%841%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M86" s="3" t="str">
+        <x:v>54036901</x:v>
+      </x:c>
+      <x:c r="N86" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K86" s="3" t="str">
+      <x:c r="O86" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L86" s="3" t="str">
+      <x:c r="P86" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M86" s="3" t="str">
+      <x:c r="Q86" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N86" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O86" s="3" t="str">
+      <x:c r="R86" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S86" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P86" s="3" t="str">
+      <x:c r="T86" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -5741,45 +6784,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C87" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D87" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D87" s="3" t="str">
-        <x:v>蒙世学堂幼儿园</x:v>
-      </x:c>
       <x:c r="E87" s="3" t="str">
-        <x:v>徐家汇/枫林</x:v>
+        <x:v>四季方馨幼儿园</x:v>
       </x:c>
       <x:c r="F87" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="G87" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G87" s="3" t="str">
-        <x:v>斜土路2421号</x:v>
-      </x:c>
       <x:c r="H87" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%92%99%E4%B8%96%E5%AD%A6%E5%A0%82%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%96%9C%E5%9C%9F%E8%B7%AF2421%E5%8F%B7</x:v>
+        <x:v>五原路112号</x:v>
       </x:c>
       <x:c r="I87" s="3" t="str">
-        <x:v>021-64686261*8103</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J87" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K87" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L87" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9B%9B%E5%AD%A3%E6%96%B9%E9%A6%A8%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%BA%94%E5%8E%9F%E8%B7%AF112%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M87" s="3" t="str">
+        <x:v>021-54036603</x:v>
+      </x:c>
+      <x:c r="N87" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K87" s="3" t="str">
+      <x:c r="O87" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L87" s="3" t="str">
+      <x:c r="P87" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M87" s="3" t="str">
+      <x:c r="Q87" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N87" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O87" s="3" t="str">
+      <x:c r="R87" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S87" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P87" s="3" t="str">
+      <x:c r="T87" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -5791,45 +6846,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C88" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D88" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D88" s="3" t="str">
-        <x:v>樱花园幼稚园</x:v>
-      </x:c>
       <x:c r="E88" s="3" t="str">
-        <x:v>田林/康健</x:v>
+        <x:v>滨江幼儿园</x:v>
       </x:c>
       <x:c r="F88" s="3" t="str">
+        <x:v>龙华/滨江</x:v>
+      </x:c>
+      <x:c r="G88" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G88" s="3" t="str">
-        <x:v>百花街380号</x:v>
-      </x:c>
       <x:c r="H88" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A8%B1%E8%8A%B1%E5%9B%AD%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%99%BE%E8%8A%B1%E8%A1%97380%E5%8F%B7</x:v>
+        <x:v>云锦路80弄10号</x:v>
       </x:c>
       <x:c r="I88" s="3" t="str">
-        <x:v>54185106</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J88" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K88" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L88" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BB%A8%E6%B1%9F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%BA%91%E9%94%A6%E8%B7%AF80%E5%BC%8410%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M88" s="3" t="str">
+        <x:v>64380700</x:v>
+      </x:c>
+      <x:c r="N88" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K88" s="3" t="str">
+      <x:c r="O88" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L88" s="3" t="str">
+      <x:c r="P88" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M88" s="3" t="str">
+      <x:c r="Q88" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N88" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O88" s="3" t="str">
+      <x:c r="R88" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S88" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P88" s="3" t="str">
+      <x:c r="T88" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -5841,45 +6908,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C89" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D89" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D89" s="3" t="str">
-        <x:v>新宜幼稚园</x:v>
-      </x:c>
       <x:c r="E89" s="3" t="str">
-        <x:v>田林/康健</x:v>
+        <x:v>汇宝幼儿园</x:v>
       </x:c>
       <x:c r="F89" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="G89" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G89" s="3" t="str">
-        <x:v>古宜路170弄7号</x:v>
-      </x:c>
       <x:c r="H89" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%96%B0%E5%AE%9C%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E5%AE%9C%E8%B7%AF170%E5%BC%847%E5%8F%B7</x:v>
+        <x:v>宛平南路592号</x:v>
       </x:c>
       <x:c r="I89" s="3" t="str">
-        <x:v>64684874</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J89" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K89" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L89" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9B%E5%B9%B3%E5%8D%97%E8%B7%AF592%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M89" s="3" t="str">
+        <x:v>64690445</x:v>
+      </x:c>
+      <x:c r="N89" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K89" s="3" t="str">
+      <x:c r="O89" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L89" s="3" t="str">
+      <x:c r="P89" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M89" s="3" t="str">
+      <x:c r="Q89" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N89" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O89" s="3" t="str">
+      <x:c r="R89" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S89" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P89" s="3" t="str">
+      <x:c r="T89" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -5891,45 +6970,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C90" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D90" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D90" s="3" t="str">
-        <x:v>蓓蕾幼稚园</x:v>
-      </x:c>
       <x:c r="E90" s="3" t="str">
+        <x:v>蒙世学堂幼儿园</x:v>
+      </x:c>
+      <x:c r="F90" s="3" t="str">
         <x:v>徐家汇/枫林</x:v>
       </x:c>
-      <x:c r="F90" s="3" t="str">
+      <x:c r="G90" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G90" s="3" t="str">
-        <x:v>蒲江塘路50号玉兰花苑6幢</x:v>
-      </x:c>
       <x:c r="H90" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%93%93%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%92%B2%E6%B1%9F%E5%A1%98%E8%B7%AF50%E5%8F%B7%E7%8E%89%E5%85%B0%E8%8A%B1%E8%8B%916%E5%B9%A2</x:v>
+        <x:v>斜土路2421号</x:v>
       </x:c>
       <x:c r="I90" s="3" t="str">
-        <x:v>64647491</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J90" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K90" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L90" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%92%99%E4%B8%96%E5%AD%A6%E5%A0%82%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%96%9C%E5%9C%9F%E8%B7%AF2421%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M90" s="3" t="str">
+        <x:v>021-64686261*8103</x:v>
+      </x:c>
+      <x:c r="N90" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K90" s="3" t="str">
+      <x:c r="O90" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L90" s="3" t="str">
+      <x:c r="P90" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M90" s="3" t="str">
+      <x:c r="Q90" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N90" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O90" s="3" t="str">
+      <x:c r="R90" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S90" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P90" s="3" t="str">
+      <x:c r="T90" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -5941,45 +7032,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C91" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D91" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D91" s="3" t="str">
-        <x:v>蓓蕾幼稚园</x:v>
-      </x:c>
       <x:c r="E91" s="3" t="str">
-        <x:v>徐家汇/枫林</x:v>
+        <x:v>樱花园幼稚园</x:v>
       </x:c>
       <x:c r="F91" s="3" t="str">
-        <x:v>分园</x:v>
+        <x:v>田林/康健</x:v>
       </x:c>
       <x:c r="G91" s="3" t="str">
-        <x:v>天钥桥路380弄11号</x:v>
+        <x:v>本部</x:v>
       </x:c>
       <x:c r="H91" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%93%93%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E8%B7%AF380%E5%BC%8411%E5%8F%B7</x:v>
+        <x:v>百花街380号</x:v>
       </x:c>
       <x:c r="I91" s="3" t="str">
-        <x:v>64647491</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J91" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K91" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L91" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A8%B1%E8%8A%B1%E5%9B%AD%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%99%BE%E8%8A%B1%E8%A1%97380%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M91" s="3" t="str">
+        <x:v>54185106</x:v>
+      </x:c>
+      <x:c r="N91" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K91" s="3" t="str">
+      <x:c r="O91" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L91" s="3" t="str">
+      <x:c r="P91" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M91" s="3" t="str">
+      <x:c r="Q91" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N91" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O91" s="3" t="str">
+      <x:c r="R91" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S91" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P91" s="3" t="str">
+      <x:c r="T91" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -5991,45 +7094,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C92" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D92" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D92" s="3" t="str">
-        <x:v>淇莲幼儿园</x:v>
-      </x:c>
       <x:c r="E92" s="3" t="str">
+        <x:v>新宜幼稚园</x:v>
+      </x:c>
+      <x:c r="F92" s="3" t="str">
         <x:v>田林/康健</x:v>
       </x:c>
-      <x:c r="F92" s="3" t="str">
+      <x:c r="G92" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G92" s="3" t="str">
-        <x:v>浦北路50号</x:v>
-      </x:c>
       <x:c r="H92" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B7%87%E8%8E%B2%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B5%A6%E5%8C%97%E8%B7%AF50%E5%8F%B7</x:v>
+        <x:v>古宜路170弄7号</x:v>
       </x:c>
       <x:c r="I92" s="3" t="str">
-        <x:v>54669909</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J92" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K92" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L92" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%96%B0%E5%AE%9C%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E5%AE%9C%E8%B7%AF170%E5%BC%847%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M92" s="3" t="str">
+        <x:v>64684874</x:v>
+      </x:c>
+      <x:c r="N92" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K92" s="3" t="str">
+      <x:c r="O92" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L92" s="3" t="str">
+      <x:c r="P92" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M92" s="3" t="str">
+      <x:c r="Q92" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N92" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O92" s="3" t="str">
+      <x:c r="R92" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S92" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P92" s="3" t="str">
+      <x:c r="T92" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6041,45 +7156,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C93" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D93" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D93" s="3" t="str">
-        <x:v>田林街道中心幼儿园</x:v>
-      </x:c>
       <x:c r="E93" s="3" t="str">
-        <x:v>田林/康健</x:v>
+        <x:v>蓓蕾幼稚园</x:v>
       </x:c>
       <x:c r="F93" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="G93" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G93" s="3" t="str">
-        <x:v>田林六村10号</x:v>
-      </x:c>
       <x:c r="H93" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E8%A1%97%E9%81%93%E4%B8%AD%E5%BF%83%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%85%AD%E6%9D%9110%E5%8F%B7</x:v>
+        <x:v>蒲江塘路50号玉兰花苑6幢</x:v>
       </x:c>
       <x:c r="I93" s="3" t="str">
-        <x:v>64705223</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J93" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K93" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L93" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%93%93%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%92%B2%E6%B1%9F%E5%A1%98%E8%B7%AF50%E5%8F%B7%E7%8E%89%E5%85%B0%E8%8A%B1%E8%8B%916%E5%B9%A2</x:v>
+      </x:c>
+      <x:c r="M93" s="3" t="str">
+        <x:v>64647491</x:v>
+      </x:c>
+      <x:c r="N93" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K93" s="3" t="str">
+      <x:c r="O93" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L93" s="3" t="str">
+      <x:c r="P93" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M93" s="3" t="str">
+      <x:c r="Q93" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N93" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O93" s="3" t="str">
+      <x:c r="R93" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S93" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P93" s="3" t="str">
+      <x:c r="T93" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6091,45 +7218,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C94" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D94" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D94" s="3" t="str">
-        <x:v>胡姬港湾新汇幼儿园</x:v>
-      </x:c>
       <x:c r="E94" s="3" t="str">
-        <x:v>田林/康健</x:v>
+        <x:v>蓓蕾幼稚园</x:v>
       </x:c>
       <x:c r="F94" s="3" t="str">
-        <x:v>本部</x:v>
+        <x:v>徐家汇/枫林</x:v>
       </x:c>
       <x:c r="G94" s="3" t="str">
-        <x:v>浦北路21弄42号</x:v>
+        <x:v>分园</x:v>
       </x:c>
       <x:c r="H94" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%83%A1%E5%A7%AC%E6%B8%AF%E6%B9%BE%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B5%A6%E5%8C%97%E8%B7%AF21%E5%BC%8442%E5%8F%B7</x:v>
+        <x:v>天钥桥路380弄11号</x:v>
       </x:c>
       <x:c r="I94" s="3" t="str">
-        <x:v>54669810</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J94" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K94" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L94" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%93%93%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E8%B7%AF380%E5%BC%8411%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M94" s="3" t="str">
+        <x:v>64647491</x:v>
+      </x:c>
+      <x:c r="N94" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K94" s="3" t="str">
+      <x:c r="O94" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L94" s="3" t="str">
+      <x:c r="P94" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M94" s="3" t="str">
+      <x:c r="Q94" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N94" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O94" s="3" t="str">
+      <x:c r="R94" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S94" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P94" s="3" t="str">
+      <x:c r="T94" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6141,45 +7280,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C95" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D95" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D95" s="3" t="str">
-        <x:v>小神童幼儿园</x:v>
-      </x:c>
       <x:c r="E95" s="3" t="str">
-        <x:v>华泾/龙吴</x:v>
+        <x:v>淇莲幼儿园</x:v>
       </x:c>
       <x:c r="F95" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="G95" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G95" s="3" t="str">
-        <x:v>龙吴路988弄25号</x:v>
-      </x:c>
       <x:c r="H95" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%B0%8F%E7%A5%9E%E7%AB%A5%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%90%B4%E8%B7%AF988%E5%BC%8425%E5%8F%B7</x:v>
+        <x:v>浦北路50号</x:v>
       </x:c>
       <x:c r="I95" s="3" t="str">
-        <x:v>021-54360296</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J95" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K95" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L95" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B7%87%E8%8E%B2%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B5%A6%E5%8C%97%E8%B7%AF50%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M95" s="3" t="str">
+        <x:v>54669909</x:v>
+      </x:c>
+      <x:c r="N95" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K95" s="3" t="str">
+      <x:c r="O95" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L95" s="3" t="str">
+      <x:c r="P95" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M95" s="3" t="str">
+      <x:c r="Q95" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N95" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O95" s="3" t="str">
+      <x:c r="R95" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S95" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P95" s="3" t="str">
+      <x:c r="T95" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6191,45 +7342,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C96" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D96" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D96" s="3" t="str">
-        <x:v>安琪曈幼稚园</x:v>
-      </x:c>
       <x:c r="E96" s="3" t="str">
-        <x:v>衡复/湖南</x:v>
+        <x:v>田林街道中心幼儿园</x:v>
       </x:c>
       <x:c r="F96" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="G96" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G96" s="3" t="str">
-        <x:v>衡山路9弄2号</x:v>
-      </x:c>
       <x:c r="H96" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%89%E7%90%AA%E6%9B%88%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%A1%A1%E5%B1%B1%E8%B7%AF9%E5%BC%842%E5%8F%B7</x:v>
+        <x:v>田林六村10号</x:v>
       </x:c>
       <x:c r="I96" s="3" t="str">
-        <x:v>64665309</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J96" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K96" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L96" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E8%A1%97%E9%81%93%E4%B8%AD%E5%BF%83%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%85%AD%E6%9D%9110%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M96" s="3" t="str">
+        <x:v>64705223</x:v>
+      </x:c>
+      <x:c r="N96" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K96" s="3" t="str">
+      <x:c r="O96" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L96" s="3" t="str">
+      <x:c r="P96" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M96" s="3" t="str">
+      <x:c r="Q96" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N96" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O96" s="3" t="str">
+      <x:c r="R96" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S96" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P96" s="3" t="str">
+      <x:c r="T96" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6241,45 +7404,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C97" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D97" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D97" s="3" t="str">
-        <x:v>鲁浦幼儿园</x:v>
-      </x:c>
       <x:c r="E97" s="3" t="str">
-        <x:v>龙华/滨江</x:v>
+        <x:v>胡姬港湾新汇幼儿园</x:v>
       </x:c>
       <x:c r="F97" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="G97" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G97" s="3" t="str">
-        <x:v>宛南一村23号</x:v>
-      </x:c>
       <x:c r="H97" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%B2%81%E6%B5%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9B%E5%8D%97%E4%B8%80%E6%9D%9123%E5%8F%B7</x:v>
+        <x:v>浦北路21弄42号</x:v>
       </x:c>
       <x:c r="I97" s="3" t="str">
-        <x:v>64384206</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J97" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K97" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L97" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%83%A1%E5%A7%AC%E6%B8%AF%E6%B9%BE%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B5%A6%E5%8C%97%E8%B7%AF21%E5%BC%8442%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M97" s="3" t="str">
+        <x:v>54669810</x:v>
+      </x:c>
+      <x:c r="N97" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K97" s="3" t="str">
+      <x:c r="O97" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L97" s="3" t="str">
+      <x:c r="P97" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M97" s="3" t="str">
+      <x:c r="Q97" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N97" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O97" s="3" t="str">
+      <x:c r="R97" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S97" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P97" s="3" t="str">
+      <x:c r="T97" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6291,45 +7466,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C98" s="3" t="str">
+        <x:v>普惠民办</x:v>
+      </x:c>
+      <x:c r="D98" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D98" s="3" t="str">
-        <x:v>鲁浦幼儿园</x:v>
-      </x:c>
       <x:c r="E98" s="3" t="str">
-        <x:v>龙华/滨江</x:v>
+        <x:v>小神童幼儿园</x:v>
       </x:c>
       <x:c r="F98" s="3" t="str">
-        <x:v>分园</x:v>
+        <x:v>华泾/龙吴</x:v>
       </x:c>
       <x:c r="G98" s="3" t="str">
-        <x:v>宛南五村1号</x:v>
+        <x:v>本部</x:v>
       </x:c>
       <x:c r="H98" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%B2%81%E6%B5%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E5%AE%9B%E5%8D%97%E4%BA%94%E6%9D%911%E5%8F%B7</x:v>
+        <x:v>龙吴路988弄25号</x:v>
       </x:c>
       <x:c r="I98" s="3" t="str">
-        <x:v>64384206</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J98" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K98" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L98" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%B0%8F%E7%A5%9E%E7%AB%A5%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%90%B4%E8%B7%AF988%E5%BC%8425%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M98" s="3" t="str">
+        <x:v>021-54360296</x:v>
+      </x:c>
+      <x:c r="N98" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K98" s="3" t="str">
+      <x:c r="O98" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L98" s="3" t="str">
+      <x:c r="P98" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M98" s="3" t="str">
+      <x:c r="Q98" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N98" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O98" s="3" t="str">
+      <x:c r="R98" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S98" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P98" s="3" t="str">
+      <x:c r="T98" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6341,45 +7528,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C99" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D99" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D99" s="3" t="str">
-        <x:v>康文云锦幼儿园</x:v>
-      </x:c>
       <x:c r="E99" s="3" t="str">
-        <x:v>龙华/滨江</x:v>
+        <x:v>安琪曈幼稚园</x:v>
       </x:c>
       <x:c r="F99" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="G99" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G99" s="3" t="str">
-        <x:v>龙兰路398号</x:v>
-      </x:c>
       <x:c r="H99" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%BA%B7%E6%96%87%E4%BA%91%E9%94%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%85%B0%E8%B7%AF398%E5%8F%B7</x:v>
+        <x:v>衡山路9弄2号</x:v>
       </x:c>
       <x:c r="I99" s="3" t="str">
-        <x:v>64282682</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J99" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K99" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L99" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%89%E7%90%AA%E6%9B%88%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%A1%A1%E5%B1%B1%E8%B7%AF9%E5%BC%842%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M99" s="3" t="str">
+        <x:v>64665309</x:v>
+      </x:c>
+      <x:c r="N99" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K99" s="3" t="str">
+      <x:c r="O99" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L99" s="3" t="str">
+      <x:c r="P99" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M99" s="3" t="str">
+      <x:c r="Q99" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N99" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O99" s="3" t="str">
+      <x:c r="R99" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S99" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P99" s="3" t="str">
+      <x:c r="T99" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6391,45 +7590,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C100" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D100" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D100" s="3" t="str">
-        <x:v>爱文幼儿园</x:v>
-      </x:c>
       <x:c r="E100" s="3" t="str">
-        <x:v>徐家汇/虹桥</x:v>
+        <x:v>鲁浦幼儿园</x:v>
       </x:c>
       <x:c r="F100" s="3" t="str">
+        <x:v>龙华/滨江</x:v>
+      </x:c>
+      <x:c r="G100" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G100" s="3" t="str">
-        <x:v>古羊路160号1幢</x:v>
-      </x:c>
       <x:c r="H100" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E6%96%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E7%BE%8A%E8%B7%AF160%E5%8F%B71%E5%B9%A2</x:v>
+        <x:v>宛南一村23号</x:v>
       </x:c>
       <x:c r="I100" s="3" t="str">
-        <x:v>021-62090135</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J100" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K100" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L100" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%B2%81%E6%B5%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9B%E5%8D%97%E4%B8%80%E6%9D%9123%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M100" s="3" t="str">
+        <x:v>64384206</x:v>
+      </x:c>
+      <x:c r="N100" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K100" s="3" t="str">
+      <x:c r="O100" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L100" s="3" t="str">
+      <x:c r="P100" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M100" s="3" t="str">
+      <x:c r="Q100" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N100" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O100" s="3" t="str">
+      <x:c r="R100" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S100" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P100" s="3" t="str">
+      <x:c r="T100" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6441,45 +7652,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C101" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D101" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D101" s="3" t="str">
-        <x:v>童稻幼儿园</x:v>
-      </x:c>
       <x:c r="E101" s="3" t="str">
-        <x:v>徐家汇/虹桥</x:v>
+        <x:v>鲁浦幼儿园</x:v>
       </x:c>
       <x:c r="F101" s="3" t="str">
-        <x:v>本部</x:v>
+        <x:v>龙华/滨江</x:v>
       </x:c>
       <x:c r="G101" s="3" t="str">
-        <x:v>淮海西路365弄2号楼、3号楼</x:v>
+        <x:v>分园</x:v>
       </x:c>
       <x:c r="H101" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%AB%A5%E7%A8%BB%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B7%AE%E6%B5%B7%E8%A5%BF%E8%B7%AF365%E5%BC%842%E5%8F%B7%E6%A5%BC%E3%80%813%E5%8F%B7%E6%A5%BC</x:v>
+        <x:v>宛南五村1号</x:v>
       </x:c>
       <x:c r="I101" s="3" t="str">
-        <x:v>52668270</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J101" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K101" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L101" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%B2%81%E6%B5%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E5%AE%9B%E5%8D%97%E4%BA%94%E6%9D%911%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M101" s="3" t="str">
+        <x:v>64384206</x:v>
+      </x:c>
+      <x:c r="N101" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K101" s="3" t="str">
+      <x:c r="O101" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L101" s="3" t="str">
+      <x:c r="P101" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M101" s="3" t="str">
+      <x:c r="Q101" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N101" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O101" s="3" t="str">
+      <x:c r="R101" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S101" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P101" s="3" t="str">
+      <x:c r="T101" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6491,45 +7714,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C102" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D102" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D102" s="3" t="str">
-        <x:v>嘉宝幼儿园</x:v>
-      </x:c>
       <x:c r="E102" s="3" t="str">
-        <x:v>徐家汇/枫林</x:v>
+        <x:v>康文云锦幼儿园</x:v>
       </x:c>
       <x:c r="F102" s="3" t="str">
+        <x:v>龙华/滨江</x:v>
+      </x:c>
+      <x:c r="G102" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G102" s="3" t="str">
-        <x:v>吴兴路75号</x:v>
-      </x:c>
       <x:c r="H102" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%98%89%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%90%B4%E5%85%B4%E8%B7%AF75%E5%8F%B7</x:v>
+        <x:v>龙兰路398号</x:v>
       </x:c>
       <x:c r="I102" s="3" t="str">
-        <x:v>64373773</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J102" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K102" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L102" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%BA%B7%E6%96%87%E4%BA%91%E9%94%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%85%B0%E8%B7%AF398%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M102" s="3" t="str">
+        <x:v>64282682</x:v>
+      </x:c>
+      <x:c r="N102" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K102" s="3" t="str">
+      <x:c r="O102" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L102" s="3" t="str">
+      <x:c r="P102" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M102" s="3" t="str">
+      <x:c r="Q102" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N102" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O102" s="3" t="str">
+      <x:c r="R102" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S102" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P102" s="3" t="str">
+      <x:c r="T102" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6541,45 +7776,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C103" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D103" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D103" s="3" t="str">
-        <x:v>金贝贝幼儿园</x:v>
-      </x:c>
       <x:c r="E103" s="3" t="str">
-        <x:v>华泾/龙吴</x:v>
+        <x:v>爱文幼儿园</x:v>
       </x:c>
       <x:c r="F103" s="3" t="str">
+        <x:v>徐家汇/虹桥</x:v>
+      </x:c>
+      <x:c r="G103" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G103" s="3" t="str">
-        <x:v>龙吟路300号</x:v>
-      </x:c>
       <x:c r="H103" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%87%91%E8%B4%9D%E8%B4%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%90%9F%E8%B7%AF300%E5%8F%B7</x:v>
+        <x:v>古羊路160号1幢</x:v>
       </x:c>
       <x:c r="I103" s="3" t="str">
-        <x:v>54820000</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J103" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K103" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L103" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E6%96%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E7%BE%8A%E8%B7%AF160%E5%8F%B71%E5%B9%A2</x:v>
+      </x:c>
+      <x:c r="M103" s="3" t="str">
+        <x:v>021-62090135</x:v>
+      </x:c>
+      <x:c r="N103" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K103" s="3" t="str">
+      <x:c r="O103" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L103" s="3" t="str">
+      <x:c r="P103" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M103" s="3" t="str">
+      <x:c r="Q103" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N103" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O103" s="3" t="str">
+      <x:c r="R103" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S103" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P103" s="3" t="str">
+      <x:c r="T103" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6591,45 +7838,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C104" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D104" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D104" s="3" t="str">
-        <x:v>世纪昂立幼儿园</x:v>
-      </x:c>
       <x:c r="E104" s="3" t="str">
-        <x:v>徐家汇/枫林</x:v>
+        <x:v>童稻幼儿园</x:v>
       </x:c>
       <x:c r="F104" s="3" t="str">
+        <x:v>徐家汇/虹桥</x:v>
+      </x:c>
+      <x:c r="G104" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G104" s="3" t="str">
-        <x:v>龙山新村115号（近零陵路）</x:v>
-      </x:c>
       <x:c r="H104" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%96%E7%BA%AA%E6%98%82%E7%AB%8B%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%B1%B1%E6%96%B0%E6%9D%91115%E5%8F%B7%EF%BC%88%E8%BF%91%E9%9B%B6%E9%99%B5%E8%B7%AF%EF%BC%89</x:v>
+        <x:v>淮海西路365弄2号楼、3号楼</x:v>
       </x:c>
       <x:c r="I104" s="3" t="str">
-        <x:v>54890979 / 64382277</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J104" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K104" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L104" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%AB%A5%E7%A8%BB%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B7%AE%E6%B5%B7%E8%A5%BF%E8%B7%AF365%E5%BC%842%E5%8F%B7%E6%A5%BC%E3%80%813%E5%8F%B7%E6%A5%BC</x:v>
+      </x:c>
+      <x:c r="M104" s="3" t="str">
+        <x:v>52668270</x:v>
+      </x:c>
+      <x:c r="N104" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K104" s="3" t="str">
+      <x:c r="O104" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L104" s="3" t="str">
+      <x:c r="P104" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M104" s="3" t="str">
+      <x:c r="Q104" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N104" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O104" s="3" t="str">
+      <x:c r="R104" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S104" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P104" s="3" t="str">
+      <x:c r="T104" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6641,45 +7900,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C105" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D105" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D105" s="3" t="str">
-        <x:v>爱菊幼儿园</x:v>
-      </x:c>
       <x:c r="E105" s="3" t="str">
-        <x:v>衡复/湖南</x:v>
+        <x:v>嘉宝幼儿园</x:v>
       </x:c>
       <x:c r="F105" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="G105" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G105" s="3" t="str">
-        <x:v>复兴西路70号</x:v>
-      </x:c>
       <x:c r="H105" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E8%8F%8A%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%8D%E5%85%B4%E8%A5%BF%E8%B7%AF70%E5%8F%B7</x:v>
+        <x:v>吴兴路75号</x:v>
       </x:c>
       <x:c r="I105" s="3" t="str">
-        <x:v>64043162</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J105" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K105" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L105" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%98%89%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%90%B4%E5%85%B4%E8%B7%AF75%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M105" s="3" t="str">
+        <x:v>64373773</x:v>
+      </x:c>
+      <x:c r="N105" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K105" s="3" t="str">
+      <x:c r="O105" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L105" s="3" t="str">
+      <x:c r="P105" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M105" s="3" t="str">
+      <x:c r="Q105" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N105" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O105" s="3" t="str">
+      <x:c r="R105" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S105" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P105" s="3" t="str">
+      <x:c r="T105" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6691,45 +7962,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C106" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D106" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D106" s="3" t="str">
-        <x:v>培蕾幼稚园</x:v>
-      </x:c>
       <x:c r="E106" s="3" t="str">
-        <x:v>长桥/梅陇</x:v>
+        <x:v>金贝贝幼儿园</x:v>
       </x:c>
       <x:c r="F106" s="3" t="str">
+        <x:v>华泾/龙吴</x:v>
+      </x:c>
+      <x:c r="G106" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G106" s="3" t="str">
-        <x:v>梅陇三村49号</x:v>
-      </x:c>
       <x:c r="H106" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9F%B9%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E4%B8%89%E6%9D%9149%E5%8F%B7</x:v>
+        <x:v>龙吟路300号</x:v>
       </x:c>
       <x:c r="I106" s="3" t="str">
-        <x:v>64768480</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J106" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K106" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L106" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%87%91%E8%B4%9D%E8%B4%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%90%9F%E8%B7%AF300%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M106" s="3" t="str">
+        <x:v>54820000</x:v>
+      </x:c>
+      <x:c r="N106" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K106" s="3" t="str">
+      <x:c r="O106" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L106" s="3" t="str">
+      <x:c r="P106" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M106" s="3" t="str">
+      <x:c r="Q106" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N106" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O106" s="3" t="str">
+      <x:c r="R106" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S106" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P106" s="3" t="str">
+      <x:c r="T106" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6741,45 +8024,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C107" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D107" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D107" s="3" t="str">
-        <x:v>培蕾幼稚园</x:v>
-      </x:c>
       <x:c r="E107" s="3" t="str">
-        <x:v>长桥/梅陇</x:v>
+        <x:v>世纪昂立幼儿园</x:v>
       </x:c>
       <x:c r="F107" s="3" t="str">
-        <x:v>分园</x:v>
+        <x:v>徐家汇/枫林</x:v>
       </x:c>
       <x:c r="G107" s="3" t="str">
-        <x:v>梅陇六村41号</x:v>
+        <x:v>本部</x:v>
       </x:c>
       <x:c r="H107" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9F%B9%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%85%AD%E6%9D%9141%E5%8F%B7</x:v>
+        <x:v>龙山新村115号（近零陵路）</x:v>
       </x:c>
       <x:c r="I107" s="3" t="str">
-        <x:v>64767077</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J107" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K107" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L107" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%96%E7%BA%AA%E6%98%82%E7%AB%8B%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%B1%B1%E6%96%B0%E6%9D%91115%E5%8F%B7%EF%BC%88%E8%BF%91%E9%9B%B6%E9%99%B5%E8%B7%AF%EF%BC%89</x:v>
+      </x:c>
+      <x:c r="M107" s="3" t="str">
+        <x:v>54890979 / 64382277</x:v>
+      </x:c>
+      <x:c r="N107" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K107" s="3" t="str">
+      <x:c r="O107" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L107" s="3" t="str">
+      <x:c r="P107" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M107" s="3" t="str">
+      <x:c r="Q107" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N107" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O107" s="3" t="str">
+      <x:c r="R107" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S107" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P107" s="3" t="str">
+      <x:c r="T107" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6791,45 +8086,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C108" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D108" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D108" s="3" t="str">
-        <x:v>枫叶交响幼儿园</x:v>
-      </x:c>
       <x:c r="E108" s="3" t="str">
+        <x:v>爱菊幼儿园</x:v>
+      </x:c>
+      <x:c r="F108" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F108" s="3" t="str">
+      <x:c r="G108" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G108" s="3" t="str">
-        <x:v>太原路87号</x:v>
-      </x:c>
       <x:c r="H108" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%AB%E5%8F%B6%E4%BA%A4%E5%93%8D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%AA%E5%8E%9F%E8%B7%AF87%E5%8F%B7</x:v>
+        <x:v>复兴西路70号</x:v>
       </x:c>
       <x:c r="I108" s="3" t="str">
-        <x:v>64730053</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J108" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K108" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L108" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E8%8F%8A%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%8D%E5%85%B4%E8%A5%BF%E8%B7%AF70%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M108" s="3" t="str">
+        <x:v>64043162</x:v>
+      </x:c>
+      <x:c r="N108" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K108" s="3" t="str">
+      <x:c r="O108" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L108" s="3" t="str">
+      <x:c r="P108" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M108" s="3" t="str">
+      <x:c r="Q108" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N108" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O108" s="3" t="str">
+      <x:c r="R108" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S108" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P108" s="3" t="str">
+      <x:c r="T108" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6841,45 +8148,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C109" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D109" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D109" s="3" t="str">
-        <x:v>泰宁田林幼儿园</x:v>
-      </x:c>
       <x:c r="E109" s="3" t="str">
-        <x:v>田林/康健</x:v>
+        <x:v>培蕾幼稚园</x:v>
       </x:c>
       <x:c r="F109" s="3" t="str">
+        <x:v>长桥/梅陇</x:v>
+      </x:c>
+      <x:c r="G109" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G109" s="3" t="str">
-        <x:v>田林十一村36号</x:v>
-      </x:c>
       <x:c r="H109" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B3%B0%E5%AE%81%E7%94%B0%E6%9E%97%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%8D%81%E4%B8%80%E6%9D%9136%E5%8F%B7</x:v>
+        <x:v>梅陇三村49号</x:v>
       </x:c>
       <x:c r="I109" s="3" t="str">
-        <x:v>64755118-804</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J109" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K109" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L109" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9F%B9%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E4%B8%89%E6%9D%9149%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M109" s="3" t="str">
+        <x:v>64768480</x:v>
+      </x:c>
+      <x:c r="N109" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K109" s="3" t="str">
+      <x:c r="O109" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L109" s="3" t="str">
+      <x:c r="P109" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M109" s="3" t="str">
+      <x:c r="Q109" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N109" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O109" s="3" t="str">
+      <x:c r="R109" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S109" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P109" s="3" t="str">
+      <x:c r="T109" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6891,45 +8210,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C110" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D110" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D110" s="3" t="str">
-        <x:v>田林东方幼儿园</x:v>
-      </x:c>
       <x:c r="E110" s="3" t="str">
-        <x:v>田林/康健</x:v>
+        <x:v>培蕾幼稚园</x:v>
       </x:c>
       <x:c r="F110" s="3" t="str">
-        <x:v>本部</x:v>
+        <x:v>长桥/梅陇</x:v>
       </x:c>
       <x:c r="G110" s="3" t="str">
-        <x:v>宜山路田林十四村27号</x:v>
+        <x:v>分园</x:v>
       </x:c>
       <x:c r="H110" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E4%B8%9C%E6%96%B9%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9C%E5%B1%B1%E8%B7%AF%E7%94%B0%E6%9E%97%E5%8D%81%E5%9B%9B%E6%9D%9127%E5%8F%B7</x:v>
+        <x:v>梅陇六村41号</x:v>
       </x:c>
       <x:c r="I110" s="3" t="str">
-        <x:v>021-64085912</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J110" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K110" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L110" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9F%B9%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%85%AD%E6%9D%9141%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M110" s="3" t="str">
+        <x:v>64767077</x:v>
+      </x:c>
+      <x:c r="N110" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K110" s="3" t="str">
+      <x:c r="O110" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L110" s="3" t="str">
+      <x:c r="P110" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M110" s="3" t="str">
+      <x:c r="Q110" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N110" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O110" s="3" t="str">
+      <x:c r="R110" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S110" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P110" s="3" t="str">
+      <x:c r="T110" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6941,45 +8272,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C111" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D111" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D111" s="3" t="str">
-        <x:v>澳宝幼儿园</x:v>
-      </x:c>
       <x:c r="E111" s="3" t="str">
+        <x:v>枫叶交响幼儿园</x:v>
+      </x:c>
+      <x:c r="F111" s="3" t="str">
         <x:v>衡复/湖南</x:v>
       </x:c>
-      <x:c r="F111" s="3" t="str">
+      <x:c r="G111" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G111" s="3" t="str">
-        <x:v>永嘉路356弄31号</x:v>
-      </x:c>
       <x:c r="H111" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BE%B3%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B0%B8%E5%98%89%E8%B7%AF356%E5%BC%8431%E5%8F%B7</x:v>
+        <x:v>太原路87号</x:v>
       </x:c>
       <x:c r="I111" s="3" t="str">
-        <x:v>64720200</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J111" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K111" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L111" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%AB%E5%8F%B6%E4%BA%A4%E5%93%8D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%AA%E5%8E%9F%E8%B7%AF87%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M111" s="3" t="str">
+        <x:v>64730053</x:v>
+      </x:c>
+      <x:c r="N111" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K111" s="3" t="str">
+      <x:c r="O111" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L111" s="3" t="str">
+      <x:c r="P111" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M111" s="3" t="str">
+      <x:c r="Q111" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N111" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O111" s="3" t="str">
+      <x:c r="R111" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S111" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P111" s="3" t="str">
+      <x:c r="T111" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6991,45 +8334,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C112" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D112" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D112" s="3" t="str">
-        <x:v>吉的堡小蜻蜓幼儿园</x:v>
-      </x:c>
       <x:c r="E112" s="3" t="str">
+        <x:v>泰宁田林幼儿园</x:v>
+      </x:c>
+      <x:c r="F112" s="3" t="str">
         <x:v>田林/康健</x:v>
       </x:c>
-      <x:c r="F112" s="3" t="str">
+      <x:c r="G112" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G112" s="3" t="str">
-        <x:v>虹梅路1035弄30号</x:v>
-      </x:c>
       <x:c r="H112" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E5%B0%8F%E8%9C%BB%E8%9C%93%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%99%B9%E6%A2%85%E8%B7%AF1035%E5%BC%8430%E5%8F%B7</x:v>
+        <x:v>田林十一村36号</x:v>
       </x:c>
       <x:c r="I112" s="3" t="str">
-        <x:v>64368108</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J112" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K112" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L112" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B3%B0%E5%AE%81%E7%94%B0%E6%9E%97%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%8D%81%E4%B8%80%E6%9D%9136%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M112" s="3" t="str">
+        <x:v>64755118-804</x:v>
+      </x:c>
+      <x:c r="N112" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K112" s="3" t="str">
+      <x:c r="O112" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L112" s="3" t="str">
+      <x:c r="P112" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M112" s="3" t="str">
+      <x:c r="Q112" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N112" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O112" s="3" t="str">
+      <x:c r="R112" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S112" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P112" s="3" t="str">
+      <x:c r="T112" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7041,45 +8396,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C113" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D113" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D113" s="3" t="str">
-        <x:v>东泉大地幼儿园</x:v>
-      </x:c>
       <x:c r="E113" s="3" t="str">
-        <x:v>龙华/滨江</x:v>
+        <x:v>田林东方幼儿园</x:v>
       </x:c>
       <x:c r="F113" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="G113" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G113" s="3" t="str">
-        <x:v>东泉路65弄9号</x:v>
-      </x:c>
       <x:c r="H113" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%9C%E6%B3%89%E5%A4%A7%E5%9C%B0%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B8%9C%E6%B3%89%E8%B7%AF65%E5%BC%849%E5%8F%B7</x:v>
+        <x:v>宜山路田林十四村27号</x:v>
       </x:c>
       <x:c r="I113" s="3" t="str">
-        <x:v>54084130</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J113" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K113" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L113" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E4%B8%9C%E6%96%B9%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9C%E5%B1%B1%E8%B7%AF%E7%94%B0%E6%9E%97%E5%8D%81%E5%9B%9B%E6%9D%9127%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M113" s="3" t="str">
+        <x:v>021-64085912</x:v>
+      </x:c>
+      <x:c r="N113" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K113" s="3" t="str">
+      <x:c r="O113" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L113" s="3" t="str">
+      <x:c r="P113" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M113" s="3" t="str">
+      <x:c r="Q113" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N113" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O113" s="3" t="str">
+      <x:c r="R113" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S113" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P113" s="3" t="str">
+      <x:c r="T113" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7091,45 +8458,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C114" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D114" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D114" s="3" t="str">
-        <x:v>吉的堡新徐汇幼儿园</x:v>
-      </x:c>
       <x:c r="E114" s="3" t="str">
-        <x:v>徐家汇/枫林</x:v>
+        <x:v>澳宝幼儿园</x:v>
       </x:c>
       <x:c r="F114" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="G114" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G114" s="3" t="str">
-        <x:v>小木桥路101弄20号</x:v>
-      </x:c>
       <x:c r="H114" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E6%96%B0%E5%BE%90%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%B0%8F%E6%9C%A8%E6%A1%A5%E8%B7%AF101%E5%BC%8420%E5%8F%B7</x:v>
+        <x:v>永嘉路356弄31号</x:v>
       </x:c>
       <x:c r="I114" s="3" t="str">
-        <x:v>021-54245100</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J114" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K114" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L114" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BE%B3%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B0%B8%E5%98%89%E8%B7%AF356%E5%BC%8431%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M114" s="3" t="str">
+        <x:v>64720200</x:v>
+      </x:c>
+      <x:c r="N114" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K114" s="3" t="str">
+      <x:c r="O114" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L114" s="3" t="str">
+      <x:c r="P114" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M114" s="3" t="str">
+      <x:c r="Q114" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N114" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O114" s="3" t="str">
+      <x:c r="R114" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S114" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P114" s="3" t="str">
+      <x:c r="T114" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7141,45 +8520,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C115" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D115" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D115" s="3" t="str">
-        <x:v>爱悠小红花幼儿园</x:v>
-      </x:c>
       <x:c r="E115" s="3" t="str">
-        <x:v>长桥/梅陇</x:v>
+        <x:v>吉的堡小蜻蜓幼儿园</x:v>
       </x:c>
       <x:c r="F115" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="G115" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G115" s="3" t="str">
-        <x:v>梅陇路130号1幢、2幢</x:v>
-      </x:c>
       <x:c r="H115" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E6%82%A0%E5%B0%8F%E7%BA%A2%E8%8A%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E8%B7%AF130%E5%8F%B71%E5%B9%A2%E3%80%812%E5%B9%A2</x:v>
+        <x:v>虹梅路1035弄30号</x:v>
       </x:c>
       <x:c r="I115" s="3" t="str">
-        <x:v>021-54333289</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J115" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K115" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L115" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E5%B0%8F%E8%9C%BB%E8%9C%93%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%99%B9%E6%A2%85%E8%B7%AF1035%E5%BC%8430%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M115" s="3" t="str">
+        <x:v>64368108</x:v>
+      </x:c>
+      <x:c r="N115" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K115" s="3" t="str">
+      <x:c r="O115" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L115" s="3" t="str">
+      <x:c r="P115" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M115" s="3" t="str">
+      <x:c r="Q115" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N115" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O115" s="3" t="str">
+      <x:c r="R115" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S115" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P115" s="3" t="str">
+      <x:c r="T115" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7191,45 +8582,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C116" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D116" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D116" s="3" t="str">
-        <x:v>中山幼儿园</x:v>
-      </x:c>
       <x:c r="E116" s="3" t="str">
-        <x:v>衡复/湖南</x:v>
+        <x:v>东泉大地幼儿园</x:v>
       </x:c>
       <x:c r="F116" s="3" t="str">
+        <x:v>龙华/滨江</x:v>
+      </x:c>
+      <x:c r="G116" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G116" s="3" t="str">
-        <x:v>桃江路42号</x:v>
-      </x:c>
       <x:c r="H116" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%AD%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%83%E6%B1%9F%E8%B7%AF42%E5%8F%B7</x:v>
+        <x:v>东泉路65弄9号</x:v>
       </x:c>
       <x:c r="I116" s="3" t="str">
-        <x:v>021-33565515</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J116" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K116" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L116" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%9C%E6%B3%89%E5%A4%A7%E5%9C%B0%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B8%9C%E6%B3%89%E8%B7%AF65%E5%BC%849%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M116" s="3" t="str">
+        <x:v>54084130</x:v>
+      </x:c>
+      <x:c r="N116" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K116" s="3" t="str">
+      <x:c r="O116" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L116" s="3" t="str">
+      <x:c r="P116" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M116" s="3" t="str">
+      <x:c r="Q116" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N116" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O116" s="3" t="str">
+      <x:c r="R116" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S116" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P116" s="3" t="str">
+      <x:c r="T116" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7241,45 +8644,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C117" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D117" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D117" s="3" t="str">
-        <x:v>创意幼儿园</x:v>
-      </x:c>
       <x:c r="E117" s="3" t="str">
-        <x:v>田林/康健</x:v>
+        <x:v>吉的堡新徐汇幼儿园</x:v>
       </x:c>
       <x:c r="F117" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="G117" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G117" s="3" t="str">
-        <x:v>柳州路田林十村6号</x:v>
-      </x:c>
       <x:c r="H117" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%88%9B%E6%84%8F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%9F%B3%E5%B7%9E%E8%B7%AF%E7%94%B0%E6%9E%97%E5%8D%81%E6%9D%916%E5%8F%B7</x:v>
+        <x:v>小木桥路101弄20号</x:v>
       </x:c>
       <x:c r="I117" s="3" t="str">
-        <x:v>64828813 / 64820881</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J117" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K117" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L117" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E6%96%B0%E5%BE%90%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%B0%8F%E6%9C%A8%E6%A1%A5%E8%B7%AF101%E5%BC%8420%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M117" s="3" t="str">
+        <x:v>021-54245100</x:v>
+      </x:c>
+      <x:c r="N117" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K117" s="3" t="str">
+      <x:c r="O117" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L117" s="3" t="str">
+      <x:c r="P117" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M117" s="3" t="str">
+      <x:c r="Q117" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N117" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O117" s="3" t="str">
+      <x:c r="R117" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S117" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P117" s="3" t="str">
+      <x:c r="T117" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7291,45 +8706,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C118" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D118" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D118" s="3" t="str">
-        <x:v>牛牛幼稚园</x:v>
-      </x:c>
       <x:c r="E118" s="3" t="str">
+        <x:v>爱悠小红花幼儿园</x:v>
+      </x:c>
+      <x:c r="F118" s="3" t="str">
         <x:v>长桥/梅陇</x:v>
       </x:c>
-      <x:c r="F118" s="3" t="str">
+      <x:c r="G118" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G118" s="3" t="str">
-        <x:v>罗城路700弄95号</x:v>
-      </x:c>
       <x:c r="H118" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%89%9B%E7%89%9B%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%BD%97%E5%9F%8E%E8%B7%AF700%E5%BC%8495%E5%8F%B7</x:v>
+        <x:v>梅陇路130号1幢、2幢</x:v>
       </x:c>
       <x:c r="I118" s="3" t="str">
-        <x:v>54115988</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J118" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K118" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L118" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E6%82%A0%E5%B0%8F%E7%BA%A2%E8%8A%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E8%B7%AF130%E5%8F%B71%E5%B9%A2%E3%80%812%E5%B9%A2</x:v>
+      </x:c>
+      <x:c r="M118" s="3" t="str">
+        <x:v>021-54333289</x:v>
+      </x:c>
+      <x:c r="N118" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K118" s="3" t="str">
+      <x:c r="O118" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L118" s="3" t="str">
+      <x:c r="P118" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M118" s="3" t="str">
+      <x:c r="Q118" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N118" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O118" s="3" t="str">
+      <x:c r="R118" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S118" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P118" s="3" t="str">
+      <x:c r="T118" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7341,45 +8768,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C119" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D119" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D119" s="3" t="str">
-        <x:v>领幼幼儿园</x:v>
-      </x:c>
       <x:c r="E119" s="3" t="str">
-        <x:v>徐家汇/枫林</x:v>
+        <x:v>中山幼儿园</x:v>
       </x:c>
       <x:c r="F119" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="G119" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G119" s="3" t="str">
-        <x:v>天钥桥路1057弄3号</x:v>
-      </x:c>
       <x:c r="H119" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%A2%86%E5%B9%BC%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E8%B7%AF1057%E5%BC%843%E5%8F%B7</x:v>
+        <x:v>桃江路42号</x:v>
       </x:c>
       <x:c r="I119" s="3" t="str">
-        <x:v>64458520</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J119" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K119" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L119" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%AD%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%83%E6%B1%9F%E8%B7%AF42%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M119" s="3" t="str">
+        <x:v>021-33565515</x:v>
+      </x:c>
+      <x:c r="N119" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K119" s="3" t="str">
+      <x:c r="O119" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L119" s="3" t="str">
+      <x:c r="P119" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M119" s="3" t="str">
+      <x:c r="Q119" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N119" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O119" s="3" t="str">
+      <x:c r="R119" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S119" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P119" s="3" t="str">
+      <x:c r="T119" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7391,45 +8830,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C120" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D120" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D120" s="3" t="str">
-        <x:v>漕河泾新汇幼儿园</x:v>
-      </x:c>
       <x:c r="E120" s="3" t="str">
-        <x:v>漕溪/龙漕</x:v>
+        <x:v>创意幼儿园</x:v>
       </x:c>
       <x:c r="F120" s="3" t="str">
+        <x:v>田林/康健</x:v>
+      </x:c>
+      <x:c r="G120" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G120" s="3" t="str">
-        <x:v>漕泾一村30号</x:v>
-      </x:c>
       <x:c r="H120" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BC%95%E6%B2%B3%E6%B3%BE%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%BC%95%E6%B3%BE%E4%B8%80%E6%9D%9130%E5%8F%B7</x:v>
+        <x:v>柳州路田林十村6号</x:v>
       </x:c>
       <x:c r="I120" s="3" t="str">
-        <x:v>64364348</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J120" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K120" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L120" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%88%9B%E6%84%8F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%9F%B3%E5%B7%9E%E8%B7%AF%E7%94%B0%E6%9E%97%E5%8D%81%E6%9D%916%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M120" s="3" t="str">
+        <x:v>64828813 / 64820881</x:v>
+      </x:c>
+      <x:c r="N120" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K120" s="3" t="str">
+      <x:c r="O120" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L120" s="3" t="str">
+      <x:c r="P120" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M120" s="3" t="str">
+      <x:c r="Q120" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N120" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O120" s="3" t="str">
+      <x:c r="R120" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S120" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P120" s="3" t="str">
+      <x:c r="T120" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7441,45 +8892,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C121" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D121" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D121" s="3" t="str">
-        <x:v>凯琴数码幼儿园</x:v>
-      </x:c>
       <x:c r="E121" s="3" t="str">
-        <x:v>华泾/龙吴</x:v>
+        <x:v>牛牛幼稚园</x:v>
       </x:c>
       <x:c r="F121" s="3" t="str">
+        <x:v>长桥/梅陇</x:v>
+      </x:c>
+      <x:c r="G121" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G121" s="3" t="str">
-        <x:v>华泾路995号</x:v>
-      </x:c>
       <x:c r="H121" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%87%AF%E7%90%B4%E6%95%B0%E7%A0%81%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8D%8E%E6%B3%BE%E8%B7%AF995%E5%8F%B7</x:v>
+        <x:v>罗城路700弄95号</x:v>
       </x:c>
       <x:c r="I121" s="3" t="str">
-        <x:v>54822626</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J121" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K121" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L121" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%89%9B%E7%89%9B%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%BD%97%E5%9F%8E%E8%B7%AF700%E5%BC%8495%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M121" s="3" t="str">
+        <x:v>54115988</x:v>
+      </x:c>
+      <x:c r="N121" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K121" s="3" t="str">
+      <x:c r="O121" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L121" s="3" t="str">
+      <x:c r="P121" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M121" s="3" t="str">
+      <x:c r="Q121" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N121" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O121" s="3" t="str">
+      <x:c r="R121" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S121" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P121" s="3" t="str">
+      <x:c r="T121" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7491,45 +8954,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C122" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D122" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D122" s="3" t="str">
-        <x:v>陇龙幼稚园</x:v>
-      </x:c>
       <x:c r="E122" s="3" t="str">
-        <x:v>长桥/梅陇</x:v>
+        <x:v>领幼幼儿园</x:v>
       </x:c>
       <x:c r="F122" s="3" t="str">
+        <x:v>徐家汇/枫林</x:v>
+      </x:c>
+      <x:c r="G122" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G122" s="3" t="str">
-        <x:v>梅陇十一村96号</x:v>
-      </x:c>
       <x:c r="H122" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%99%87%E9%BE%99%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E5%8D%81%E4%B8%80%E6%9D%9196%E5%8F%B7</x:v>
+        <x:v>天钥桥路1057弄3号</x:v>
       </x:c>
       <x:c r="I122" s="3" t="str">
-        <x:v>64549910</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J122" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K122" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L122" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%A2%86%E5%B9%BC%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E8%B7%AF1057%E5%BC%843%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M122" s="3" t="str">
+        <x:v>64458520</x:v>
+      </x:c>
+      <x:c r="N122" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K122" s="3" t="str">
+      <x:c r="O122" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L122" s="3" t="str">
+      <x:c r="P122" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M122" s="3" t="str">
+      <x:c r="Q122" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N122" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O122" s="3" t="str">
+      <x:c r="R122" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S122" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P122" s="3" t="str">
+      <x:c r="T122" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7541,45 +9016,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C123" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D123" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D123" s="3" t="str">
-        <x:v>世蒙幼儿园</x:v>
-      </x:c>
       <x:c r="E123" s="3" t="str">
-        <x:v>衡复/湖南</x:v>
+        <x:v>漕河泾新汇幼儿园</x:v>
       </x:c>
       <x:c r="F123" s="3" t="str">
+        <x:v>漕溪/龙漕</x:v>
+      </x:c>
+      <x:c r="G123" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G123" s="3" t="str">
-        <x:v>东湖路21号</x:v>
-      </x:c>
       <x:c r="H123" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%96%E8%92%99%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B8%9C%E6%B9%96%E8%B7%AF21%E5%8F%B7</x:v>
+        <x:v>漕泾一村30号</x:v>
       </x:c>
       <x:c r="I123" s="3" t="str">
-        <x:v>021-54038979</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J123" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K123" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L123" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BC%95%E6%B2%B3%E6%B3%BE%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%BC%95%E6%B3%BE%E4%B8%80%E6%9D%9130%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M123" s="3" t="str">
+        <x:v>64364348</x:v>
+      </x:c>
+      <x:c r="N123" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K123" s="3" t="str">
+      <x:c r="O123" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L123" s="3" t="str">
+      <x:c r="P123" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M123" s="3" t="str">
+      <x:c r="Q123" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N123" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O123" s="3" t="str">
+      <x:c r="R123" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S123" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P123" s="3" t="str">
+      <x:c r="T123" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7591,45 +9078,57 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C124" s="3" t="str">
+        <x:v>普惠民办</x:v>
+      </x:c>
+      <x:c r="D124" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D124" s="3" t="str">
-        <x:v>蒂伊幼稚园</x:v>
-      </x:c>
       <x:c r="E124" s="3" t="str">
-        <x:v>衡复/湖南</x:v>
+        <x:v>凯琴数码幼儿园</x:v>
       </x:c>
       <x:c r="F124" s="3" t="str">
+        <x:v>华泾/龙吴</x:v>
+      </x:c>
+      <x:c r="G124" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G124" s="3" t="str">
-        <x:v>永嘉路383号</x:v>
-      </x:c>
       <x:c r="H124" s="3" t="str">
-        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%92%82%E4%BC%8A%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B0%B8%E5%98%89%E8%B7%AF383%E5%8F%B7</x:v>
+        <x:v>华泾路995号</x:v>
       </x:c>
       <x:c r="I124" s="3" t="str">
-        <x:v>64749388</x:v>
+        <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="J124" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K124" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L124" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%87%AF%E7%90%B4%E6%95%B0%E7%A0%81%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8D%8E%E6%B3%BE%E8%B7%AF995%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M124" s="3" t="str">
+        <x:v>54822626</x:v>
+      </x:c>
+      <x:c r="N124" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K124" s="3" t="str">
+      <x:c r="O124" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L124" s="3" t="str">
+      <x:c r="P124" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M124" s="3" t="str">
+      <x:c r="Q124" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N124" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O124" s="3" t="str">
+      <x:c r="R124" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S124" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P124" s="3" t="str">
+      <x:c r="T124" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7641,45 +9140,243 @@
         <x:v>民办</x:v>
       </x:c>
       <x:c r="C125" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D125" s="3" t="str">
         <x:v>二级</x:v>
       </x:c>
-      <x:c r="D125" s="3" t="str">
+      <x:c r="E125" s="3" t="str">
+        <x:v>陇龙幼稚园</x:v>
+      </x:c>
+      <x:c r="F125" s="3" t="str">
+        <x:v>长桥/梅陇</x:v>
+      </x:c>
+      <x:c r="G125" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="H125" s="3" t="str">
+        <x:v>梅陇十一村96号</x:v>
+      </x:c>
+      <x:c r="I125" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J125" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K125" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L125" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%99%87%E9%BE%99%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E5%8D%81%E4%B8%80%E6%9D%9196%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M125" s="3" t="str">
+        <x:v>64549910</x:v>
+      </x:c>
+      <x:c r="N125" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="O125" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="P125" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="Q125" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="R125" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S125" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="T125" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="3" t="str">
+        <x:v>M44</x:v>
+      </x:c>
+      <x:c r="B126" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C126" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D126" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E126" s="3" t="str">
+        <x:v>世蒙幼儿园</x:v>
+      </x:c>
+      <x:c r="F126" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="G126" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="H126" s="3" t="str">
+        <x:v>东湖路21号</x:v>
+      </x:c>
+      <x:c r="I126" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J126" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K126" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L126" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%96%E8%92%99%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B8%9C%E6%B9%96%E8%B7%AF21%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M126" s="3" t="str">
+        <x:v>021-54038979</x:v>
+      </x:c>
+      <x:c r="N126" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="O126" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="P126" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="Q126" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="R126" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S126" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="T126" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="3" t="str">
+        <x:v>M45</x:v>
+      </x:c>
+      <x:c r="B127" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C127" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D127" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E127" s="3" t="str">
+        <x:v>蒂伊幼稚园</x:v>
+      </x:c>
+      <x:c r="F127" s="3" t="str">
+        <x:v>衡复/湖南</x:v>
+      </x:c>
+      <x:c r="G127" s="3" t="str">
+        <x:v>本部</x:v>
+      </x:c>
+      <x:c r="H127" s="3" t="str">
+        <x:v>永嘉路383号</x:v>
+      </x:c>
+      <x:c r="I127" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J127" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K127" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L127" s="3" t="str">
+        <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%92%82%E4%BC%8A%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B0%B8%E5%98%89%E8%B7%AF383%E5%8F%B7</x:v>
+      </x:c>
+      <x:c r="M127" s="3" t="str">
+        <x:v>64749388</x:v>
+      </x:c>
+      <x:c r="N127" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="O127" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="P127" s="3" t="str">
+        <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
+      </x:c>
+      <x:c r="Q127" s="3" t="str">
+        <x:v>民办招生</x:v>
+      </x:c>
+      <x:c r="R127" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S127" s="3" t="str">
+        <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
+      </x:c>
+      <x:c r="T127" s="3" t="str">
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="3" t="str">
+        <x:v>M46</x:v>
+      </x:c>
+      <x:c r="B128" s="3" t="str">
+        <x:v>民办</x:v>
+      </x:c>
+      <x:c r="C128" s="3" t="str">
+        <x:v>民办（类型待核验）</x:v>
+      </x:c>
+      <x:c r="D128" s="3" t="str">
+        <x:v>二级</x:v>
+      </x:c>
+      <x:c r="E128" s="3" t="str">
         <x:v>吉的堡新汇幼儿园</x:v>
       </x:c>
-      <x:c r="E125" s="3" t="str">
+      <x:c r="F128" s="3" t="str">
         <x:v>田林/康健</x:v>
       </x:c>
-      <x:c r="F125" s="3" t="str">
+      <x:c r="G128" s="3" t="str">
         <x:v>本部</x:v>
       </x:c>
-      <x:c r="G125" s="3" t="str">
+      <x:c r="H128" s="3" t="str">
         <x:v>康健小区虹漕南路百花街18号、6号</x:v>
       </x:c>
-      <x:c r="H125" s="3" t="str">
+      <x:c r="I128" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="J128" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="K128" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="L128" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%BA%B7%E5%81%A5%E5%B0%8F%E5%8C%BA%E8%99%B9%E6%BC%95%E5%8D%97%E8%B7%AF%E7%99%BE%E8%8A%B1%E8%A1%9718%E5%8F%B7%E3%80%816%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="I125" s="3" t="str">
+      <x:c r="M128" s="3" t="str">
         <x:v>54183331</x:v>
       </x:c>
-      <x:c r="J125" s="3" t="str">
+      <x:c r="N128" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="K125" s="3" t="str">
+      <x:c r="O128" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
-      <x:c r="L125" s="3" t="str">
+      <x:c r="P128" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="M125" s="3" t="str">
+      <x:c r="Q128" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="N125" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="O125" s="3" t="str">
+      <x:c r="R128" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="S128" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="P125" s="3" t="str">
+      <x:c r="T128" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8339,41 +10036,49 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="str">
-        <x:v>高德检索口径</x:v>
+        <x:v>高德MCP接入口径</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
-        <x:v>表格中的高德链接使用“上海市徐汇区 + 幼儿园名 + 园区名 + 地址”生成，用于逐点打开核验。</x:v>
+        <x:v>目标办公点：西岸网易研发中心；上海市徐汇区西岸网易研发中心。待配置AMAP_MAPS_API_KEY后，用关键词搜索/详情搜索/距离测量补齐高德POI、经纬度和距离。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="str">
-        <x:v>A级</x:v>
+        <x:v>高德检索口径</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
-        <x:v>园部地址在公办园地址清单中明确列出，且无明显冲突。</x:v>
+        <x:v>表格中的高德链接使用“上海市徐汇区 + 幼儿园名 + 园区名 + 地址”生成，用于逐点打开核验。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="str">
-        <x:v>B级</x:v>
+        <x:v>A级</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
-        <x:v>公开资料有变更、合并或地址冲突，位置大体可定位，但实际入读园区需电话确认。</x:v>
+        <x:v>园部地址在公办园地址清单中明确列出，且无明显冲突。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="str">
-        <x:v>C级</x:v>
+        <x:v>B级</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
-        <x:v>仅有第三方或地图信息，缺少官方交叉验证。本表目前未使用C级作为主确认。</x:v>
+        <x:v>公开资料有变更、合并或地址冲突，位置大体可定位，但实际入读园区需电话确认。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="3" t="str">
+        <x:v>C级</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="str">
+        <x:v>仅有第三方或地图信息，缺少官方交叉验证。本表目前未使用C级作为主确认。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="3" t="str">
         <x:v>电话确认重点</x:v>
       </x:c>
-      <x:c r="B10" s="3" t="str">
+      <x:c r="B11" s="3" t="str">
         <x:v>汇星幼儿园北园；复旦大学附属徐汇实验幼儿园；区域内自主招生、扩招园、民办/私立园。</x:v>
       </x:c>
     </x:row>

--- a/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
+++ b/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="Rc804914f18b54af6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="R609c636306114181"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R08cc0d7c87cb41ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="Re02d65294e944d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="Ra4a66fcb8bde4813"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R0327cee29f8c41f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="Rb502e0a547f24228"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R668be1861abf42ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R105f884346764fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R17a3f3a0e49c4d3f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -295,10 +295,10 @@
         <x:v>高德增强字段</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
-        <x:v>待接入</x:v>
+        <x:v>已接入</x:v>
       </x:c>
       <x:c r="C6" s="3" t="str">
-        <x:v>高德MCP需要AMAP_MAPS_API_KEY；接入后补POI名称、经纬度和到西岸网易距离。</x:v>
+        <x:v>已批量补POI名称、经纬度和到网易上海西岸研发中心的高德直线距离；低置信匹配保留为待核验。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1578,18 +1578,19 @@
     <x:col min="6" max="6" width="14.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="17.790000915527344" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="17.790000915527344" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="19.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="19.020000457763672" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="14.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="43.560001373291016" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="14.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="10.180000305175781" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="43.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.180000305175781" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="63.189998626708984" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="10.430000305175781" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="10.180000305175781" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="63.189998626708984" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="10.430000305175781" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="43.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="10.430000305175781" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="43.560001373291016" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="43.560001373291016" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1621,39 +1622,41 @@
         <x:v>高德POI名称</x:v>
       </x:c>
       <x:c r="J1" s="2" t="str">
+        <x:v>高德POI地址</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="str">
         <x:v>高德经纬度</x:v>
       </x:c>
-      <x:c r="K1" s="2" t="str">
+      <x:c r="L1" s="2" t="str">
         <x:v>距西岸网易研发中心</x:v>
       </x:c>
-      <x:c r="L1" s="2" t="str">
+      <x:c r="M1" s="2" t="str">
         <x:v>高德搜索链接</x:v>
       </x:c>
-      <x:c r="M1" s="2" t="str">
+      <x:c r="N1" s="2" t="str">
         <x:v>联系电话</x:v>
       </x:c>
-      <x:c r="N1" s="2" t="str">
+      <x:c r="O1" s="2" t="str">
         <x:v>托班计划</x:v>
       </x:c>
-      <x:c r="O1" s="2" t="str">
+      <x:c r="P1" s="2" t="str">
         <x:v>小班计划</x:v>
       </x:c>
-      <x:c r="P1" s="2" t="str">
+      <x:c r="Q1" s="2" t="str">
         <x:v>对口居委/招生范围</x:v>
       </x:c>
-      <x:c r="Q1" s="2" t="str">
+      <x:c r="R1" s="2" t="str">
         <x:v>招生类型</x:v>
       </x:c>
-      <x:c r="R1" s="2" t="str">
+      <x:c r="S1" s="2" t="str">
         <x:v>置信度</x:v>
       </x:c>
-      <x:c r="S1" s="2" t="str">
+      <x:c r="T1" s="2" t="str">
         <x:v>备注</x:v>
       </x:c>
-      <x:c r="T1" s="2" t="str">
+      <x:c r="U1" s="2" t="str">
         <x:v>主要来源</x:v>
       </x:c>
-      <x:c r="U1" s="2"/>
       <x:c r="V1" s="2"/>
       <x:c r="W1" s="2"/>
       <x:c r="X1" s="2"/>
@@ -1686,37 +1689,40 @@
         <x:v>复兴中路1260弄2号</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区襄阳南路第一幼儿园(复中园)</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>复兴中路1260弄2号(陕西南路地铁站7号口步行260米)</x:v>
       </x:c>
       <x:c r="K2" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.457896,31.212846</x:v>
       </x:c>
       <x:c r="L2" s="3" t="str">
+        <x:v>高德直线约 6.29 km</x:v>
+      </x:c>
+      <x:c r="M2" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A4%8D%E4%B8%AD%E5%9B%AD%20%E5%A4%8D%E5%85%B4%E4%B8%AD%E8%B7%AF1260%E5%BC%842%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M2" s="3" t="str">
+      <x:c r="N2" s="3" t="str">
         <x:v>021-64335881</x:v>
       </x:c>
-      <x:c r="N2" s="3" t="str">
+      <x:c r="O2" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O2" s="3" t="n">
+      <x:c r="P2" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P2" s="3" t="str">
+      <x:c r="Q2" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="Q2" s="3" t="str">
+      <x:c r="R2" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R2" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S2" s="3" t="str"/>
-      <x:c r="T2" s="3" t="str">
+      <x:c r="S2" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T2" s="3" t="str"/>
+      <x:c r="U2" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1746,37 +1752,40 @@
         <x:v>襄阳南路317号</x:v>
       </x:c>
       <x:c r="I3" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区襄阳南路第一幼儿园(南园)</x:v>
       </x:c>
       <x:c r="J3" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>襄阳南路317号</x:v>
       </x:c>
       <x:c r="K3" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.458251,31.208448</x:v>
       </x:c>
       <x:c r="L3" s="3" t="str">
+        <x:v>高德直线约 5.80 km</x:v>
+      </x:c>
+      <x:c r="M3" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF317%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M3" s="3" t="str">
+      <x:c r="N3" s="3" t="str">
         <x:v>021-64335881</x:v>
       </x:c>
-      <x:c r="N3" s="3" t="str">
+      <x:c r="O3" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O3" s="3" t="n">
+      <x:c r="P3" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P3" s="3" t="str">
+      <x:c r="Q3" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="Q3" s="3" t="str">
+      <x:c r="R3" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R3" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S3" s="3" t="str"/>
-      <x:c r="T3" s="3" t="str">
+      <x:c r="S3" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T3" s="3" t="str"/>
+      <x:c r="U3" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1806,37 +1815,40 @@
         <x:v>陕西南路540号</x:v>
       </x:c>
       <x:c r="I4" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区襄阳南路第一幼儿园(陕南园)</x:v>
       </x:c>
       <x:c r="J4" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>中国民主促进会旧址西门旁</x:v>
       </x:c>
       <x:c r="K4" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.461578,31.208853</x:v>
       </x:c>
       <x:c r="L4" s="3" t="str">
+        <x:v>高德直线约 5.85 km</x:v>
+      </x:c>
+      <x:c r="M4" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%99%95%E5%8D%97%E5%9B%AD%20%E9%99%95%E8%A5%BF%E5%8D%97%E8%B7%AF540%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M4" s="3" t="str">
+      <x:c r="N4" s="3" t="str">
         <x:v>021-64335881</x:v>
       </x:c>
-      <x:c r="N4" s="3" t="str">
+      <x:c r="O4" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O4" s="3" t="n">
+      <x:c r="P4" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P4" s="3" t="str">
+      <x:c r="Q4" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="Q4" s="3" t="str">
+      <x:c r="R4" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R4" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S4" s="3" t="str"/>
-      <x:c r="T4" s="3" t="str">
+      <x:c r="S4" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T4" s="3" t="str"/>
+      <x:c r="U4" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1866,37 +1878,40 @@
         <x:v>襄阳南路207号</x:v>
       </x:c>
       <x:c r="I5" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区襄阳南路第一幼儿园(北园)</x:v>
       </x:c>
       <x:c r="J5" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>襄阳南路207号(陕西南路地铁站7号口步行360米)</x:v>
       </x:c>
       <x:c r="K5" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.457816,31.211726</x:v>
       </x:c>
       <x:c r="L5" s="3" t="str">
+        <x:v>高德直线约 6.16 km</x:v>
+      </x:c>
+      <x:c r="M5" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E8%A5%84%E9%98%B3%E5%8D%97%E8%B7%AF207%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M5" s="3" t="str">
+      <x:c r="N5" s="3" t="str">
         <x:v>64335881</x:v>
       </x:c>
-      <x:c r="N5" s="3" t="str">
+      <x:c r="O5" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O5" s="3" t="n">
+      <x:c r="P5" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P5" s="3" t="str">
+      <x:c r="Q5" s="3" t="str">
         <x:v>慎成里、肇嘉浜、陕西、建新、息村、桃源村、嘉善、永康、张家弄、复中</x:v>
       </x:c>
-      <x:c r="Q5" s="3" t="str">
+      <x:c r="R5" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R5" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S5" s="3" t="str"/>
-      <x:c r="T5" s="3" t="str">
+      <x:c r="S5" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T5" s="3" t="str"/>
+      <x:c r="U5" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1926,37 +1941,40 @@
         <x:v>永嘉路420号</x:v>
       </x:c>
       <x:c r="I6" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区五原路幼儿园(永嘉园)</x:v>
       </x:c>
       <x:c r="J6" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>永嘉路420号</x:v>
       </x:c>
       <x:c r="K6" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.453931,31.207165</x:v>
       </x:c>
       <x:c r="L6" s="3" t="str">
+        <x:v>高德直线约 5.67 km</x:v>
+      </x:c>
+      <x:c r="M6" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BA%94%E5%8E%9F%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%B0%B8%E5%98%89%E5%9B%AD%20%E6%B0%B8%E5%98%89%E8%B7%AF420%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M6" s="3" t="str">
+      <x:c r="N6" s="3" t="str">
         <x:v>64759122</x:v>
       </x:c>
-      <x:c r="N6" s="3" t="str">
+      <x:c r="O6" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O6" s="3" t="n">
+      <x:c r="P6" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P6" s="3" t="str">
+      <x:c r="Q6" s="3" t="str">
         <x:v>上海新村、东湖、金波、延庆、陕新、新乐、复襄、淮海、安福、春华、淮中、建岳、太原、永太、永嘉新村、复永、兴武、华康、武康</x:v>
       </x:c>
-      <x:c r="Q6" s="3" t="str">
+      <x:c r="R6" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R6" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S6" s="3" t="str"/>
-      <x:c r="T6" s="3" t="str">
+      <x:c r="S6" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T6" s="3" t="str"/>
+      <x:c r="U6" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -1986,37 +2004,40 @@
         <x:v>五原路400号</x:v>
       </x:c>
       <x:c r="I7" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区五原路幼儿园(武康园)</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>五原路400号</x:v>
       </x:c>
       <x:c r="K7" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.441380,31.211969</x:v>
       </x:c>
       <x:c r="L7" s="3" t="str">
+        <x:v>高德直线约 6.41 km</x:v>
+      </x:c>
+      <x:c r="M7" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BA%94%E5%8E%9F%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%AD%A6%E5%BA%B7%E5%9B%AD%20%E4%BA%94%E5%8E%9F%E8%B7%AF400%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M7" s="3" t="str">
+      <x:c r="N7" s="3" t="str">
         <x:v>54035366</x:v>
       </x:c>
-      <x:c r="N7" s="3" t="str">
+      <x:c r="O7" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O7" s="3" t="n">
+      <x:c r="P7" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P7" s="3" t="str">
+      <x:c r="Q7" s="3" t="str">
         <x:v>上海新村、东湖、金波、延庆、陕新、新乐、复襄、淮海、安福、春华、淮中、建岳、太原、永太、永嘉新村、复永、兴武、华康、武康</x:v>
       </x:c>
-      <x:c r="Q7" s="3" t="str">
+      <x:c r="R7" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R7" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S7" s="3" t="str"/>
-      <x:c r="T7" s="3" t="str">
+      <x:c r="S7" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T7" s="3" t="str"/>
+      <x:c r="U7" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2046,37 +2067,40 @@
         <x:v>武康路280弄24号</x:v>
       </x:c>
       <x:c r="I8" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区五原路幼儿园(永嘉园)</x:v>
       </x:c>
       <x:c r="J8" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>永嘉路420号</x:v>
       </x:c>
       <x:c r="K8" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.453931,31.207165</x:v>
       </x:c>
       <x:c r="L8" s="3" t="str">
+        <x:v>高德直线约 5.67 km</x:v>
+      </x:c>
+      <x:c r="M8" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BA%94%E5%8E%9F%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%85%B4%E5%9B%BD%E5%9B%AD%20%E6%AD%A6%E5%BA%B7%E8%B7%AF280%E5%BC%8424%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M8" s="3" t="str">
+      <x:c r="N8" s="3" t="str">
         <x:v>64360627</x:v>
       </x:c>
-      <x:c r="N8" s="3" t="str">
+      <x:c r="O8" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O8" s="3" t="n">
+      <x:c r="P8" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P8" s="3" t="str">
+      <x:c r="Q8" s="3" t="str">
         <x:v>上海新村、东湖、金波、延庆、陕新、新乐、复襄、淮海、安福、春华、淮中、建岳、太原、永太、永嘉新村、复永、兴武、华康、武康</x:v>
       </x:c>
-      <x:c r="Q8" s="3" t="str">
+      <x:c r="R8" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S8" s="3" t="str"/>
-      <x:c r="T8" s="3" t="str">
+      <x:c r="S8" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T8" s="3" t="str"/>
+      <x:c r="U8" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2106,37 +2130,40 @@
         <x:v>宛平南路19弄3号</x:v>
       </x:c>
       <x:c r="I9" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区汇星幼儿园(南园)</x:v>
       </x:c>
       <x:c r="J9" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>宛平南路19弄3号</x:v>
       </x:c>
       <x:c r="K9" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.445600,31.196414</x:v>
       </x:c>
       <x:c r="L9" s="3" t="str">
+        <x:v>高德直线约 4.64 km</x:v>
+      </x:c>
+      <x:c r="M9" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E6%98%9F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E5%AE%9B%E5%B9%B3%E5%8D%97%E8%B7%AF19%E5%BC%843%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M9" s="3" t="str">
+      <x:c r="N9" s="3" t="str">
         <x:v>021-64689142</x:v>
       </x:c>
-      <x:c r="N9" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O9" s="3" t="n">
+      <x:c r="O9" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P9" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P9" s="3" t="str">
+      <x:c r="Q9" s="3" t="str">
         <x:v>天平、高安、康平、吴兴、宛平、余庆、广元、安亭、徐汇新村、张家浜肇谨、零陵、科汇、启明、沈马、王家堂、南赵巷、殷家角、汇翠、名园、德昌</x:v>
       </x:c>
-      <x:c r="Q9" s="3" t="str">
+      <x:c r="R9" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R9" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S9" s="3" t="str"/>
-      <x:c r="T9" s="3" t="str">
+      <x:c r="S9" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T9" s="3" t="str"/>
+      <x:c r="U9" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2166,39 +2193,42 @@
         <x:v>康平路200号</x:v>
       </x:c>
       <x:c r="I10" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区汇星幼儿园(北园)</x:v>
       </x:c>
       <x:c r="J10" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>康平路200号(交通大学地铁站1号口步行240米)</x:v>
       </x:c>
       <x:c r="K10" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.436909,31.200199</x:v>
       </x:c>
       <x:c r="L10" s="3" t="str">
+        <x:v>高德直线约 5.31 km</x:v>
+      </x:c>
+      <x:c r="M10" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E6%98%9F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E5%BA%B7%E5%B9%B3%E8%B7%AF200%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M10" s="3" t="str">
+      <x:c r="N10" s="3" t="str">
         <x:v>021-64689142</x:v>
       </x:c>
-      <x:c r="N10" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="3" t="n">
+      <x:c r="O10" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P10" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P10" s="3" t="str">
+      <x:c r="Q10" s="3" t="str">
         <x:v>天平、高安、康平、吴兴、宛平、余庆、广元、安亭、徐汇新村、张家浜肇谨、零陵、科汇、启明、沈马、王家堂、南赵巷、殷家角、汇翠、名园、德昌</x:v>
       </x:c>
-      <x:c r="Q10" s="3" t="str">
+      <x:c r="R10" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R10" s="3" t="str">
+      <x:c r="S10" s="3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="S10" s="3" t="str">
+      <x:c r="T10" s="3" t="str">
         <x:v>2024公办名单写康平路200号；2024招生简章/部分旧资料写华山路1815号，建议电话确认当前小班实际园区。</x:v>
       </x:c>
-      <x:c r="T10" s="3" t="str">
+      <x:c r="U10" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2228,37 +2258,40 @@
         <x:v>乐山路18号</x:v>
       </x:c>
       <x:c r="I11" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区乐山幼儿园</x:v>
       </x:c>
       <x:c r="J11" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>乐山路18号</x:v>
       </x:c>
       <x:c r="K11" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.431613,31.196337</x:v>
       </x:c>
       <x:c r="L11" s="3" t="str">
+        <x:v>高德直线约 5.16 km</x:v>
+      </x:c>
+      <x:c r="M11" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%90%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B9%90%E5%B1%B1%E8%B7%AF18%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M11" s="3" t="str">
+      <x:c r="N11" s="3" t="str">
         <x:v>64072867</x:v>
       </x:c>
-      <x:c r="N11" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O11" s="3" t="n">
+      <x:c r="O11" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P11" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P11" s="3" t="str">
+      <x:c r="Q11" s="3" t="str">
         <x:v>乐山一村、乐山二三村、乐山四五村、乐山六七村、乐山八九村、文定、汇站、交大、豪庭</x:v>
       </x:c>
-      <x:c r="Q11" s="3" t="str">
+      <x:c r="R11" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R11" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S11" s="3" t="str"/>
-      <x:c r="T11" s="3" t="str">
+      <x:c r="S11" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T11" s="3" t="str"/>
+      <x:c r="U11" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2288,37 +2321,40 @@
         <x:v>番禺路800弄24号</x:v>
       </x:c>
       <x:c r="I12" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区汇家幼儿园(北园)</x:v>
       </x:c>
       <x:c r="J12" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>番禺路800弄24号</x:v>
       </x:c>
       <x:c r="K12" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.427837,31.197598</x:v>
       </x:c>
       <x:c r="L12" s="3" t="str">
+        <x:v>高德直线约 5.46 km</x:v>
+      </x:c>
+      <x:c r="M12" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%AE%B6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E7%95%AA%E7%A6%BA%E8%B7%AF800%E5%BC%8424%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M12" s="3" t="str">
+      <x:c r="N12" s="3" t="str">
         <x:v>62837361</x:v>
       </x:c>
-      <x:c r="N12" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="3" t="n">
+      <x:c r="O12" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P12" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P12" s="3" t="str">
+      <x:c r="Q12" s="3" t="str">
         <x:v>番禺、南丹、柿子湾、潘家宅、陈家宅、虹二、虹交、西塘、东塘</x:v>
       </x:c>
-      <x:c r="Q12" s="3" t="str">
+      <x:c r="R12" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R12" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S12" s="3" t="str"/>
-      <x:c r="T12" s="3" t="str">
+      <x:c r="S12" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T12" s="3" t="str"/>
+      <x:c r="U12" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2348,37 +2384,40 @@
         <x:v>番禺路1188号</x:v>
       </x:c>
       <x:c r="I13" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区汇家幼儿园(南园)</x:v>
       </x:c>
       <x:c r="J13" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>番禺路1188号(宜山路地铁站5号口步行460米)</x:v>
       </x:c>
       <x:c r="K13" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.425446,31.191704</x:v>
       </x:c>
       <x:c r="L13" s="3" t="str">
+        <x:v>高德直线约 5.07 km</x:v>
+      </x:c>
+      <x:c r="M13" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%AE%B6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E7%95%AA%E7%A6%BA%E8%B7%AF1188%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M13" s="3" t="str">
+      <x:c r="N13" s="3" t="str">
         <x:v>64860098</x:v>
       </x:c>
-      <x:c r="N13" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="3" t="n">
+      <x:c r="O13" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P13" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P13" s="3" t="str">
+      <x:c r="Q13" s="3" t="str">
         <x:v>番禺、南丹、柿子湾、潘家宅、陈家宅、虹二、虹交、西塘、东塘</x:v>
       </x:c>
-      <x:c r="Q13" s="3" t="str">
+      <x:c r="R13" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R13" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S13" s="3" t="str"/>
-      <x:c r="T13" s="3" t="str">
+      <x:c r="S13" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T13" s="3" t="str"/>
+      <x:c r="U13" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2408,37 +2447,40 @@
         <x:v>小木桥路440弄30号</x:v>
       </x:c>
       <x:c r="I14" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区枫林幼儿园</x:v>
       </x:c>
       <x:c r="J14" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>小木桥路440弄30号</x:v>
       </x:c>
       <x:c r="K14" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.458998,31.194273</x:v>
       </x:c>
       <x:c r="L14" s="3" t="str">
+        <x:v>高德直线约 4.22 km</x:v>
+      </x:c>
+      <x:c r="M14" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%AB%E6%9E%97%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%B0%8F%E6%9C%A8%E6%A1%A5%E8%B7%AF440%E5%BC%8430%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M14" s="3" t="str">
+      <x:c r="N14" s="3" t="str">
         <x:v>64035845</x:v>
       </x:c>
-      <x:c r="N14" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O14" s="3" t="n">
+      <x:c r="O14" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P14" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P14" s="3" t="str">
+      <x:c r="Q14" s="3" t="str">
         <x:v>日新、日二、日五、日六第一、日六第二、大三、大四、康巨、茶陵、景泰、恒益、西木南、西木北、江南</x:v>
       </x:c>
-      <x:c r="Q14" s="3" t="str">
+      <x:c r="R14" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R14" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S14" s="3" t="str"/>
-      <x:c r="T14" s="3" t="str">
+      <x:c r="S14" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T14" s="3" t="str"/>
+      <x:c r="U14" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2468,39 +2510,42 @@
         <x:v>平江路17号</x:v>
       </x:c>
       <x:c r="I15" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>复旦大学附属徐汇实验幼儿园(中大班部)</x:v>
       </x:c>
       <x:c r="J15" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>平江路32号</x:v>
       </x:c>
       <x:c r="K15" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.456478,31.200659</x:v>
       </x:c>
       <x:c r="L15" s="3" t="str">
+        <x:v>高德直线约 4.94 km</x:v>
+      </x:c>
+      <x:c r="M15" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%A4%8D%E6%97%A6%E5%A4%A7%E5%AD%A6%E9%99%84%E5%B1%9E%E5%BE%90%E6%B1%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%89%98%E5%B0%8F%E7%8F%AD%E9%83%A8%20%E5%B9%B3%E6%B1%9F%E8%B7%AF17%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M15" s="3" t="str">
+      <x:c r="N15" s="3" t="str">
         <x:v>64034223</x:v>
       </x:c>
-      <x:c r="N15" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="3" t="n">
+      <x:c r="O15" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P15" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P15" s="3" t="str">
+      <x:c r="Q15" s="3" t="str">
         <x:v>平江、肇一、上影、日七、大五、医清、四季园、肇清、医学院</x:v>
       </x:c>
-      <x:c r="Q15" s="3" t="str">
+      <x:c r="R15" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R15" s="3" t="str">
+      <x:c r="S15" s="3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="S15" s="3" t="str">
+      <x:c r="T15" s="3" t="str">
         <x:v>2024年7月由原平江路幼儿园与原复旦大学医学院幼儿园合并组建；2025/公开资料显示新小班启用平江路32号，需确认2026实际安排。</x:v>
       </x:c>
-      <x:c r="T15" s="3" t="str">
+      <x:c r="U15" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；复旦附属徐汇实验幼儿园公开资料/上哪学/021school；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2530,39 +2575,42 @@
         <x:v>平江路32号</x:v>
       </x:c>
       <x:c r="I16" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>复旦大学附属徐汇实验幼儿园(中大班部)</x:v>
       </x:c>
       <x:c r="J16" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>平江路32号</x:v>
       </x:c>
       <x:c r="K16" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.456478,31.200659</x:v>
       </x:c>
       <x:c r="L16" s="3" t="str">
+        <x:v>高德直线约 4.94 km</x:v>
+      </x:c>
+      <x:c r="M16" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%A4%8D%E6%97%A6%E5%A4%A7%E5%AD%A6%E9%99%84%E5%B1%9E%E5%BE%90%E6%B1%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%AD%E5%A4%A7%E7%8F%AD%E9%83%A8%2F%E6%96%B0%E5%B0%8F%E7%8F%AD%E5%80%99%E9%80%89%20%E5%B9%B3%E6%B1%9F%E8%B7%AF32%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M16" s="3" t="str">
+      <x:c r="N16" s="3" t="str">
         <x:v>64034223</x:v>
       </x:c>
-      <x:c r="N16" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="3" t="n">
+      <x:c r="O16" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P16" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P16" s="3" t="str">
+      <x:c r="Q16" s="3" t="str">
         <x:v>平江、肇一、上影、日七、大五、医清、四季园、肇清、医学院</x:v>
       </x:c>
-      <x:c r="Q16" s="3" t="str">
+      <x:c r="R16" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R16" s="3" t="str">
+      <x:c r="S16" s="3" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="S16" s="3" t="str">
+      <x:c r="T16" s="3" t="str">
         <x:v>公开资料显示办学地址为平江路32号、17号；原复旦医学院幼儿园东安路50弄10号为历史/合并相关地址。</x:v>
       </x:c>
-      <x:c r="T16" s="3" t="str">
+      <x:c r="U16" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；复旦附属徐汇实验幼儿园公开资料/上哪学/021school；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2592,37 +2640,40 @@
         <x:v>零陵路250弄33号</x:v>
       </x:c>
       <x:c r="I17" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区东安一村幼儿园(零陵园)</x:v>
       </x:c>
       <x:c r="J17" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>零陵路250弄33号(大木桥路地铁站3号口步行470米)</x:v>
       </x:c>
       <x:c r="K17" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.460111,31.191485</x:v>
       </x:c>
       <x:c r="L17" s="3" t="str">
+        <x:v>高德直线约 3.91 km</x:v>
+      </x:c>
+      <x:c r="M17" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%9C%E5%AE%89%E4%B8%80%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%9B%B6%E9%99%B5%E5%9B%AD%20%E9%9B%B6%E9%99%B5%E8%B7%AF250%E5%BC%8433%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M17" s="3" t="str">
+      <x:c r="N17" s="3" t="str">
         <x:v>64041758</x:v>
       </x:c>
-      <x:c r="N17" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O17" s="3" t="n">
+      <x:c r="O17" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P17" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P17" s="3" t="str">
+      <x:c r="Q17" s="3" t="str">
         <x:v>东安一村北、东安一村南、安康、振兴、张东、爱华、汇园、东安二村、沈家里、东安四村、谨斜、东安苑、枫林新村、南康</x:v>
       </x:c>
-      <x:c r="Q17" s="3" t="str">
+      <x:c r="R17" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R17" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S17" s="3" t="str"/>
-      <x:c r="T17" s="3" t="str">
+      <x:c r="S17" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T17" s="3" t="str"/>
+      <x:c r="U17" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2652,39 +2703,42 @@
         <x:v>东安一村39号</x:v>
       </x:c>
       <x:c r="I18" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区东安一村幼儿园(零陵园)</x:v>
       </x:c>
       <x:c r="J18" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>零陵路250弄33号(大木桥路地铁站3号口步行470米)</x:v>
       </x:c>
       <x:c r="K18" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.460111,31.191485</x:v>
       </x:c>
       <x:c r="L18" s="3" t="str">
+        <x:v>高德直线约 3.91 km</x:v>
+      </x:c>
+      <x:c r="M18" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%9C%E5%AE%89%E4%B8%80%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%9C%E5%AE%89%E5%9B%AD%20%E4%B8%9C%E5%AE%89%E4%B8%80%E6%9D%9139%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M18" s="3" t="str">
+      <x:c r="N18" s="3" t="str">
         <x:v>64175625</x:v>
       </x:c>
-      <x:c r="N18" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O18" s="3" t="n">
+      <x:c r="O18" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P18" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P18" s="3" t="str">
+      <x:c r="Q18" s="3" t="str">
         <x:v>东安一村北、东安一村南、安康、振兴、张东、爱华、汇园、东安二村、沈家里、东安四村、谨斜、东安苑、枫林新村、南康</x:v>
       </x:c>
-      <x:c r="Q18" s="3" t="str">
+      <x:c r="R18" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R18" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S18" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T18" s="3" t="str">
         <x:v>公办名单列出东安一村39号及零陵路250弄33号。</x:v>
       </x:c>
-      <x:c r="T18" s="3" t="str">
+      <x:c r="U18" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2714,37 +2768,40 @@
         <x:v>宛南四村16号</x:v>
       </x:c>
       <x:c r="I19" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区龙山幼儿园一分园</x:v>
       </x:c>
       <x:c r="J19" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>宛南四村16号</x:v>
       </x:c>
       <x:c r="K19" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.450444,31.181580</x:v>
       </x:c>
       <x:c r="L19" s="3" t="str">
+        <x:v>高德直线约 2.92 km</x:v>
+      </x:c>
+      <x:c r="M19" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%80%E5%88%86%E5%9B%AD%20%E5%AE%9B%E5%8D%97%E5%9B%9B%E6%9D%9116%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M19" s="3" t="str">
+      <x:c r="N19" s="3" t="str">
         <x:v>64383244</x:v>
       </x:c>
-      <x:c r="N19" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="3" t="n">
+      <x:c r="O19" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P19" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P19" s="3" t="str">
+      <x:c r="Q19" s="3" t="str">
         <x:v>天一二、天三、天四、宛南一二、宛三、宛四、宛五、宛六、庄家宅、黄家宅、华容、龙山一、龙山二、徐汇苑</x:v>
       </x:c>
-      <x:c r="Q19" s="3" t="str">
+      <x:c r="R19" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R19" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S19" s="3" t="str"/>
-      <x:c r="T19" s="3" t="str">
+      <x:c r="S19" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T19" s="3" t="str"/>
+      <x:c r="U19" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2774,37 +2831,40 @@
         <x:v>中山南二路999弄5号</x:v>
       </x:c>
       <x:c r="I20" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区龙山幼儿园二分园</x:v>
       </x:c>
       <x:c r="J20" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>中山南二路999弄5号</x:v>
       </x:c>
       <x:c r="K20" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.447293,31.181380</x:v>
       </x:c>
       <x:c r="L20" s="3" t="str">
+        <x:v>高德直线约 3.00 km</x:v>
+      </x:c>
+      <x:c r="M20" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%BA%8C%E5%88%86%E5%9B%AD%20%E4%B8%AD%E5%B1%B1%E5%8D%97%E4%BA%8C%E8%B7%AF999%E5%BC%845%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M20" s="3" t="str">
+      <x:c r="N20" s="3" t="str">
         <x:v>64869504</x:v>
       </x:c>
-      <x:c r="N20" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="3" t="n">
+      <x:c r="O20" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P20" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P20" s="3" t="str">
+      <x:c r="Q20" s="3" t="str">
         <x:v>天一二、天三、天四、宛南一二、宛三、宛四、宛五、宛六、庄家宅、黄家宅、华容、龙山一、龙山二、徐汇苑</x:v>
       </x:c>
-      <x:c r="Q20" s="3" t="str">
+      <x:c r="R20" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R20" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S20" s="3" t="str"/>
-      <x:c r="T20" s="3" t="str">
+      <x:c r="S20" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T20" s="3" t="str"/>
+      <x:c r="U20" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2834,37 +2894,40 @@
         <x:v>天钥新村90号</x:v>
       </x:c>
       <x:c r="I21" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>龙山幼儿园(总园)</x:v>
       </x:c>
       <x:c r="J21" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>天钥新村90</x:v>
       </x:c>
       <x:c r="K21" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.447837,31.185665</x:v>
       </x:c>
       <x:c r="L21" s="3" t="str">
+        <x:v>高德直线约 3.43 km</x:v>
+      </x:c>
+      <x:c r="M21" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%A9%E9%92%A5%E6%96%B0%E6%9D%9190%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M21" s="3" t="str">
+      <x:c r="N21" s="3" t="str">
         <x:v>64383295</x:v>
       </x:c>
-      <x:c r="N21" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O21" s="3" t="n">
+      <x:c r="O21" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P21" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P21" s="3" t="str">
+      <x:c r="Q21" s="3" t="str">
         <x:v>天一二、天三、天四、宛南一二、宛三、宛四、宛五、宛六、庄家宅、黄家宅、华容、龙山一、龙山二、徐汇苑</x:v>
       </x:c>
-      <x:c r="Q21" s="3" t="str">
+      <x:c r="R21" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R21" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S21" s="3" t="str"/>
-      <x:c r="T21" s="3" t="str">
+      <x:c r="S21" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T21" s="3" t="str"/>
+      <x:c r="U21" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2903,28 +2966,31 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L22" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M22" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%B0%E8%B0%B7%E5%9B%AD%20%E4%B8%B0%E8%B0%B7%E8%B7%AF205%E5%BC%8434%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M22" s="3" t="str">
+      <x:c r="N22" s="3" t="str">
         <x:v>64280780</x:v>
       </x:c>
-      <x:c r="N22" s="3" t="str">
+      <x:c r="O22" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O22" s="3" t="n">
+      <x:c r="P22" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P22" s="3" t="str">
+      <x:c r="Q22" s="3" t="str">
         <x:v>上缝、强生、东蔡、狮城、佳友、华富、宏润花园、漕溪四村单号、丰谷、云锦、机场、尚海湾、盛大、民苑、丰谷三、俞一、俞二、俞三、龙华新村、周家湾、汇龙、红馨、百汇园</x:v>
       </x:c>
-      <x:c r="Q22" s="3" t="str">
+      <x:c r="R22" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R22" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S22" s="3" t="str"/>
-      <x:c r="T22" s="3" t="str">
+      <x:c r="S22" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T22" s="3" t="str"/>
+      <x:c r="U22" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -2954,37 +3020,40 @@
         <x:v>龙华西路31弄15号</x:v>
       </x:c>
       <x:c r="I23" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区龙华幼儿园(龙恒园)</x:v>
       </x:c>
       <x:c r="J23" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>龙华西路31弄15号</x:v>
       </x:c>
       <x:c r="K23" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.452231,31.169864</x:v>
       </x:c>
       <x:c r="L23" s="3" t="str">
+        <x:v>高德直线约 1.63 km</x:v>
+      </x:c>
+      <x:c r="M23" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%BE%99%E6%81%92%E5%9B%AD%20%E9%BE%99%E5%8D%8E%E8%A5%BF%E8%B7%AF31%E5%BC%8415%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M23" s="3" t="str">
+      <x:c r="N23" s="3" t="str">
         <x:v>64576761</x:v>
       </x:c>
-      <x:c r="N23" s="3" t="str">
+      <x:c r="O23" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O23" s="3" t="n">
+      <x:c r="P23" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P23" s="3" t="str">
+      <x:c r="Q23" s="3" t="str">
         <x:v>上缝、强生、东蔡、狮城、佳友、华富、宏润花园、漕溪四村单号、丰谷、云锦、机场、尚海湾、盛大、民苑、丰谷三、俞一、俞二、俞三、龙华新村、周家湾、汇龙、红馨、百汇园</x:v>
       </x:c>
-      <x:c r="Q23" s="3" t="str">
+      <x:c r="R23" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R23" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S23" s="3" t="str"/>
-      <x:c r="T23" s="3" t="str">
+      <x:c r="S23" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T23" s="3" t="str"/>
+      <x:c r="U23" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3014,37 +3083,40 @@
         <x:v>龙华西路285弄14号</x:v>
       </x:c>
       <x:c r="I24" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区龙华幼儿园(龙华园)</x:v>
       </x:c>
       <x:c r="J24" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>龙华西路285弄14号</x:v>
       </x:c>
       <x:c r="K24" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.446108,31.172523</x:v>
       </x:c>
       <x:c r="L24" s="3" t="str">
+        <x:v>高德直线约 2.18 km</x:v>
+      </x:c>
+      <x:c r="M24" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%BE%99%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%BE%99%E5%8D%8E%E5%9B%AD%20%E9%BE%99%E5%8D%8E%E8%A5%BF%E8%B7%AF285%E5%BC%8414%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M24" s="3" t="str">
+      <x:c r="N24" s="3" t="str">
         <x:v>64571589</x:v>
       </x:c>
-      <x:c r="N24" s="3" t="str">
+      <x:c r="O24" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O24" s="3" t="n">
+      <x:c r="P24" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P24" s="3" t="str">
+      <x:c r="Q24" s="3" t="str">
         <x:v>上缝、强生、东蔡、狮城、佳友、华富、宏润花园、漕溪四村单号、丰谷、云锦、机场、尚海湾、盛大、民苑、丰谷三、俞一、俞二、俞三、龙华新村、周家湾、汇龙、红馨、百汇园</x:v>
       </x:c>
-      <x:c r="Q24" s="3" t="str">
+      <x:c r="R24" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R24" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S24" s="3" t="str"/>
-      <x:c r="T24" s="3" t="str">
+      <x:c r="S24" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T24" s="3" t="str"/>
+      <x:c r="U24" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3074,37 +3146,40 @@
         <x:v>吴中东路500弄67号</x:v>
       </x:c>
       <x:c r="I25" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区汇霖幼儿园(吴中园)</x:v>
       </x:c>
       <x:c r="J25" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>吴中东路500弄67号</x:v>
       </x:c>
       <x:c r="K25" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.422704,31.191453</x:v>
       </x:c>
       <x:c r="L25" s="3" t="str">
+        <x:v>高德直线约 5.21 km</x:v>
+      </x:c>
+      <x:c r="M25" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E9%9C%96%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%90%B4%E4%B8%AD%E5%9B%AD%20%E5%90%B4%E4%B8%AD%E4%B8%9C%E8%B7%AF500%E5%BC%8467%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M25" s="3" t="str">
+      <x:c r="N25" s="3" t="str">
         <x:v>62196848</x:v>
       </x:c>
-      <x:c r="N25" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O25" s="3" t="n">
+      <x:c r="O25" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P25" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P25" s="3" t="str">
+      <x:c r="Q25" s="3" t="str">
         <x:v>古宜、长春、吴中、桂林苑、虹南、虹星、怡桂苑、钦北、华悦家园、鑫耀</x:v>
       </x:c>
-      <x:c r="Q25" s="3" t="str">
+      <x:c r="R25" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R25" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S25" s="3" t="str"/>
-      <x:c r="T25" s="3" t="str">
+      <x:c r="S25" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T25" s="3" t="str"/>
+      <x:c r="U25" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3134,37 +3209,40 @@
         <x:v>钦州北路898号</x:v>
       </x:c>
       <x:c r="I26" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区汇霖幼儿园(钦州园区)</x:v>
       </x:c>
       <x:c r="J26" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>钦州北路898号(桂林路地铁站12号口步行350米)</x:v>
       </x:c>
       <x:c r="K26" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.412308,31.180895</x:v>
       </x:c>
       <x:c r="L26" s="3" t="str">
+        <x:v>高德直线约 5.22 km</x:v>
+      </x:c>
+      <x:c r="M26" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E9%9C%96%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%92%A6%E5%B7%9E%E5%9B%AD%20%E9%92%A6%E5%B7%9E%E5%8C%97%E8%B7%AF898%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M26" s="3" t="str">
+      <x:c r="N26" s="3" t="str">
         <x:v>64668657</x:v>
       </x:c>
-      <x:c r="N26" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O26" s="3" t="n">
+      <x:c r="O26" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P26" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P26" s="3" t="str">
+      <x:c r="Q26" s="3" t="str">
         <x:v>古宜、长春、吴中、桂林苑、虹南、虹星、怡桂苑、钦北、华悦家园、鑫耀</x:v>
       </x:c>
-      <x:c r="Q26" s="3" t="str">
+      <x:c r="R26" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R26" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S26" s="3" t="str"/>
-      <x:c r="T26" s="3" t="str">
+      <x:c r="S26" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T26" s="3" t="str"/>
+      <x:c r="U26" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3194,37 +3272,40 @@
         <x:v>天钥桥南路1249弄11号</x:v>
       </x:c>
       <x:c r="I27" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区阳光幼儿园(中大班部)</x:v>
       </x:c>
       <x:c r="J27" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>天钥桥南路1249弄11号</x:v>
       </x:c>
       <x:c r="K27" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.457330,31.151725</x:v>
       </x:c>
       <x:c r="L27" s="3" t="str">
+        <x:v>高德直线约 0.54 km</x:v>
+      </x:c>
+      <x:c r="M27" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%98%B3%E5%85%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%AD%E5%A4%A7%E7%8F%AD%E9%83%A8%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E5%8D%97%E8%B7%AF1249%E5%BC%8411%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M27" s="3" t="str">
+      <x:c r="N27" s="3" t="str">
         <x:v>54095768</x:v>
       </x:c>
-      <x:c r="N27" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O27" s="3" t="n">
+      <x:c r="O27" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P27" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P27" s="3" t="str">
+      <x:c r="Q27" s="3" t="str">
         <x:v>龙南三四、龙南五、龙南六、龙南七、滨江、樟树苑、东泉、张家园</x:v>
       </x:c>
-      <x:c r="Q27" s="3" t="str">
+      <x:c r="R27" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R27" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S27" s="3" t="str"/>
-      <x:c r="T27" s="3" t="str">
+      <x:c r="S27" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T27" s="3" t="str"/>
+      <x:c r="U27" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3254,37 +3335,40 @@
         <x:v>龙水南路龙南三村7号</x:v>
       </x:c>
       <x:c r="I28" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区阳光幼儿园(小班部)</x:v>
       </x:c>
       <x:c r="J28" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>龙南三村7号</x:v>
       </x:c>
       <x:c r="K28" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.458110,31.155090</x:v>
       </x:c>
       <x:c r="L28" s="3" t="str">
+        <x:v>高德直线约 0.17 km</x:v>
+      </x:c>
+      <x:c r="M28" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%98%B3%E5%85%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%B0%8F%E7%8F%AD%E9%83%A8%20%E9%BE%99%E6%B0%B4%E5%8D%97%E8%B7%AF%E9%BE%99%E5%8D%97%E4%B8%89%E6%9D%917%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M28" s="3" t="str">
+      <x:c r="N28" s="3" t="str">
         <x:v>021-34604160</x:v>
       </x:c>
-      <x:c r="N28" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O28" s="3" t="n">
+      <x:c r="O28" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P28" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P28" s="3" t="str">
+      <x:c r="Q28" s="3" t="str">
         <x:v>龙南三四、龙南五、龙南六、龙南七、滨江、樟树苑、东泉、张家园</x:v>
       </x:c>
-      <x:c r="Q28" s="3" t="str">
+      <x:c r="R28" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R28" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S28" s="3" t="str"/>
-      <x:c r="T28" s="3" t="str">
+      <x:c r="S28" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T28" s="3" t="str"/>
+      <x:c r="U28" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3314,37 +3398,40 @@
         <x:v>龙漕路139号</x:v>
       </x:c>
       <x:c r="I29" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区漕溪新村幼儿园(中大班部)</x:v>
       </x:c>
       <x:c r="J29" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>龙漕路139号(龙漕路地铁站5号口步行280米)</x:v>
       </x:c>
       <x:c r="K29" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.439944,31.169669</x:v>
       </x:c>
       <x:c r="L29" s="3" t="str">
+        <x:v>高德直线约 2.34 km</x:v>
+      </x:c>
+      <x:c r="M29" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BC%95%E6%BA%AA%E6%96%B0%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%AD%E5%A4%A7%E7%8F%AD%E9%83%A8%20%E9%BE%99%E6%BC%95%E8%B7%AF139%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M29" s="3" t="str">
+      <x:c r="N29" s="3" t="str">
         <x:v>64823976</x:v>
       </x:c>
-      <x:c r="N29" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O29" s="3" t="n">
+      <x:c r="O29" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P29" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P29" s="3" t="str">
+      <x:c r="Q29" s="3" t="str">
         <x:v>金谷园、南一村一、南一村二、漕溪四村双号、凯翔、龙漕、嘉萱苑、漕东</x:v>
       </x:c>
-      <x:c r="Q29" s="3" t="str">
+      <x:c r="R29" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R29" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S29" s="3" t="str"/>
-      <x:c r="T29" s="3" t="str">
+      <x:c r="S29" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T29" s="3" t="str"/>
+      <x:c r="U29" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3374,37 +3461,40 @@
         <x:v>漕东路193号</x:v>
       </x:c>
       <x:c r="I30" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区漕溪新村幼儿园(小班部)</x:v>
       </x:c>
       <x:c r="J30" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>漕东路193号(漕溪路地铁站2号口步行480米)</x:v>
       </x:c>
       <x:c r="K30" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.438802,31.173226</x:v>
       </x:c>
       <x:c r="L30" s="3" t="str">
+        <x:v>高德直线约 2.69 km</x:v>
+      </x:c>
+      <x:c r="M30" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BC%95%E6%BA%AA%E6%96%B0%E6%9D%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%B0%8F%E7%8F%AD%E9%83%A8%20%E6%BC%95%E4%B8%9C%E8%B7%AF193%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M30" s="3" t="str">
+      <x:c r="N30" s="3" t="str">
         <x:v>34616320</x:v>
       </x:c>
-      <x:c r="N30" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O30" s="3" t="n">
+      <x:c r="O30" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P30" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P30" s="3" t="str">
+      <x:c r="Q30" s="3" t="str">
         <x:v>金谷园、南一村一、南一村二、漕溪四村双号、凯翔、龙漕、嘉萱苑、漕东</x:v>
       </x:c>
-      <x:c r="Q30" s="3" t="str">
+      <x:c r="R30" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R30" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S30" s="3" t="str"/>
-      <x:c r="T30" s="3" t="str">
+      <x:c r="S30" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T30" s="3" t="str"/>
+      <x:c r="U30" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3434,37 +3524,40 @@
         <x:v>冠生园路28号</x:v>
       </x:c>
       <x:c r="I31" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区望德幼儿园(冠生园)</x:v>
       </x:c>
       <x:c r="J31" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>冠生园路28号</x:v>
       </x:c>
       <x:c r="K31" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.432425,31.163607</x:v>
       </x:c>
       <x:c r="L31" s="3" t="str">
+        <x:v>高德直线约 2.66 km</x:v>
+      </x:c>
+      <x:c r="M31" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%9B%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%86%A0%E7%94%9F%E5%9B%AD%20%E5%86%A0%E7%94%9F%E5%9B%AD%E8%B7%AF28%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M31" s="3" t="str">
+      <x:c r="N31" s="3" t="str">
         <x:v>64751426</x:v>
       </x:c>
-      <x:c r="N31" s="3" t="str">
+      <x:c r="O31" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="O31" s="3" t="n">
+      <x:c r="P31" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P31" s="3" t="str">
+      <x:c r="Q31" s="3" t="str">
         <x:v>康健路、习勤、薛家宅、科苑、九弄、中海、梓树园、月河、宾阳、馨汇南苑、公园道</x:v>
       </x:c>
-      <x:c r="Q31" s="3" t="str">
+      <x:c r="R31" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R31" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S31" s="3" t="str"/>
-      <x:c r="T31" s="3" t="str">
+      <x:c r="S31" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T31" s="3" t="str"/>
+      <x:c r="U31" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3503,28 +3596,31 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L32" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M32" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%9B%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%AE%81%E5%9B%AD%20%E5%8D%97%E5%AE%81%E8%B7%AF636%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M32" s="3" t="str">
+      <x:c r="N32" s="3" t="str">
         <x:v>64751426</x:v>
       </x:c>
-      <x:c r="N32" s="3" t="str">
+      <x:c r="O32" s="3" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="O32" s="3" t="n">
+      <x:c r="P32" s="3" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="P32" s="3" t="str">
+      <x:c r="Q32" s="3" t="str">
         <x:v>康健路、习勤、薛家宅、科苑、九弄、中海、梓树园、月河、宾阳、馨汇南苑、公园道</x:v>
       </x:c>
-      <x:c r="Q32" s="3" t="str">
+      <x:c r="R32" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R32" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S32" s="3" t="str"/>
-      <x:c r="T32" s="3" t="str">
+      <x:c r="S32" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T32" s="3" t="str"/>
+      <x:c r="U32" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3554,37 +3650,40 @@
         <x:v>老沪闵路706弄37号</x:v>
       </x:c>
       <x:c r="I33" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区瑞德幼儿园(金塘部)</x:v>
       </x:c>
       <x:c r="J33" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>老沪闵路333弄70号</x:v>
       </x:c>
       <x:c r="K33" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.424046,31.147289</x:v>
       </x:c>
       <x:c r="L33" s="3" t="str">
+        <x:v>高德直线约 3.48 km</x:v>
+      </x:c>
+      <x:c r="M33" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%91%9E%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%A5%BC%E5%9B%AD%E5%9B%AD%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF706%E5%BC%8437%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M33" s="3" t="str">
+      <x:c r="N33" s="3" t="str">
         <x:v>021-64234155</x:v>
       </x:c>
-      <x:c r="N33" s="3" t="str">
+      <x:c r="O33" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O33" s="3" t="n">
+      <x:c r="P33" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P33" s="3" t="str">
+      <x:c r="Q33" s="3" t="str">
         <x:v>汇成一村、汇成二村、汇成三村、汇成四村、华东二、楼园、金牛、挹翠苑、罗城、光华、汇澜苑、金塘</x:v>
       </x:c>
-      <x:c r="Q33" s="3" t="str">
+      <x:c r="R33" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R33" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S33" s="3" t="str"/>
-      <x:c r="T33" s="3" t="str">
+      <x:c r="S33" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T33" s="3" t="str"/>
+      <x:c r="U33" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3614,37 +3713,40 @@
         <x:v>老沪闵路333弄70号</x:v>
       </x:c>
       <x:c r="I34" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区瑞德幼儿园(金塘部)</x:v>
       </x:c>
       <x:c r="J34" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>老沪闵路333弄70号</x:v>
       </x:c>
       <x:c r="K34" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.424046,31.147289</x:v>
       </x:c>
       <x:c r="L34" s="3" t="str">
+        <x:v>高德直线约 3.48 km</x:v>
+      </x:c>
+      <x:c r="M34" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%91%9E%E5%BE%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%87%91%E5%A1%98%E5%9B%AD%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF333%E5%BC%8470%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M34" s="3" t="str">
+      <x:c r="N34" s="3" t="str">
         <x:v>54963078</x:v>
       </x:c>
-      <x:c r="N34" s="3" t="str">
+      <x:c r="O34" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O34" s="3" t="n">
+      <x:c r="P34" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P34" s="3" t="str">
+      <x:c r="Q34" s="3" t="str">
         <x:v>汇成一村、汇成二村、汇成三村、汇成四村、华东二、楼园、金牛、挹翠苑、罗城、光华、汇澜苑、金塘</x:v>
       </x:c>
-      <x:c r="Q34" s="3" t="str">
+      <x:c r="R34" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R34" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S34" s="3" t="str"/>
-      <x:c r="T34" s="3" t="str">
+      <x:c r="S34" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T34" s="3" t="str"/>
+      <x:c r="U34" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3674,37 +3776,40 @@
         <x:v>田林九村6号</x:v>
       </x:c>
       <x:c r="I35" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区益思幼儿园(东园)</x:v>
       </x:c>
       <x:c r="J35" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>田林九村6号</x:v>
       </x:c>
       <x:c r="K35" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.421545,31.172257</x:v>
       </x:c>
       <x:c r="L35" s="3" t="str">
+        <x:v>高德直线约 3.98 km</x:v>
+      </x:c>
+      <x:c r="M35" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%9B%8A%E6%80%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%9C%E5%9B%AD%20%E7%94%B0%E6%9E%97%E4%B9%9D%E6%9D%916%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M35" s="3" t="str">
+      <x:c r="N35" s="3" t="str">
         <x:v>64361935</x:v>
       </x:c>
-      <x:c r="N35" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O35" s="3" t="n">
+      <x:c r="O35" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P35" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P35" s="3" t="str">
+      <x:c r="Q35" s="3" t="str">
         <x:v>田林一二村、田林五六七村、田林八九十村、田林十三村、田林十一村、千鹤三、爱建园、万科华尔兹、新苑一二、新苑三四、新苑五六七、田林十四村第一、田林十四村第二</x:v>
       </x:c>
-      <x:c r="Q35" s="3" t="str">
+      <x:c r="R35" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R35" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S35" s="3" t="str"/>
-      <x:c r="T35" s="3" t="str">
+      <x:c r="S35" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T35" s="3" t="str"/>
+      <x:c r="U35" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3734,37 +3839,40 @@
         <x:v>宜山路701弄53号</x:v>
       </x:c>
       <x:c r="I36" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区益思幼儿园(西园)</x:v>
       </x:c>
       <x:c r="J36" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>宜山路701弄53号(桂林路地铁站4号口步行430米)</x:v>
       </x:c>
       <x:c r="K36" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.418573,31.173443</x:v>
       </x:c>
       <x:c r="L36" s="3" t="str">
+        <x:v>高德直线约 4.29 km</x:v>
+      </x:c>
+      <x:c r="M36" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%9B%8A%E6%80%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E8%A5%BF%E5%9B%AD%20%E5%AE%9C%E5%B1%B1%E8%B7%AF701%E5%BC%8453%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M36" s="3" t="str">
+      <x:c r="N36" s="3" t="str">
         <x:v>64361935</x:v>
       </x:c>
-      <x:c r="N36" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O36" s="3" t="n">
+      <x:c r="O36" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P36" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P36" s="3" t="str">
+      <x:c r="Q36" s="3" t="str">
         <x:v>田林一二村、田林五六七村、田林八九十村、田林十三村、田林十一村、千鹤三、爱建园、万科华尔兹、新苑一二、新苑三四、新苑五六七、田林十四村第一、田林十四村第二</x:v>
       </x:c>
-      <x:c r="Q36" s="3" t="str">
+      <x:c r="R36" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R36" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S36" s="3" t="str"/>
-      <x:c r="T36" s="3" t="str">
+      <x:c r="S36" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T36" s="3" t="str"/>
+      <x:c r="U36" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3803,28 +3911,31 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L37" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M37" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A8%B1%E8%8A%B1%E5%9B%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%97%E5%9B%AD%20%E7%99%BE%E8%8A%B1%E8%A1%97398%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M37" s="3" t="str">
+      <x:c r="N37" s="3" t="str">
         <x:v>021-54181491</x:v>
       </x:c>
-      <x:c r="N37" s="3" t="str">
+      <x:c r="O37" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O37" s="3" t="n">
+      <x:c r="P37" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P37" s="3" t="str">
+      <x:c r="Q37" s="3" t="str">
         <x:v>月季百藤、樱花园、茶花桂花、丁香迎春、玉兰园、寿益坊（海上华庭）、紫鹃园、紫薇园（牡丹园、玫瑰园）、金桂苑、紫荆党校</x:v>
       </x:c>
-      <x:c r="Q37" s="3" t="str">
+      <x:c r="R37" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R37" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S37" s="3" t="str"/>
-      <x:c r="T37" s="3" t="str">
+      <x:c r="S37" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T37" s="3" t="str"/>
+      <x:c r="U37" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3854,37 +3965,40 @@
         <x:v>虹漕南路杨家桥88号</x:v>
       </x:c>
       <x:c r="I38" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区樱花园幼儿园(北园)</x:v>
       </x:c>
       <x:c r="J38" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>虹漕南路杨家桥88号</x:v>
       </x:c>
       <x:c r="K38" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.411201,31.162605</x:v>
       </x:c>
       <x:c r="L38" s="3" t="str">
+        <x:v>高德直线约 4.61 km</x:v>
+      </x:c>
+      <x:c r="M38" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A8%B1%E8%8A%B1%E5%9B%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8C%97%E5%9B%AD%20%E8%99%B9%E6%BC%95%E5%8D%97%E8%B7%AF%E6%9D%A8%E5%AE%B6%E6%A1%A588%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M38" s="3" t="str">
+      <x:c r="N38" s="3" t="str">
         <x:v>54362050</x:v>
       </x:c>
-      <x:c r="N38" s="3" t="str">
+      <x:c r="O38" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O38" s="3" t="n">
+      <x:c r="P38" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P38" s="3" t="str">
+      <x:c r="Q38" s="3" t="str">
         <x:v>月季百藤、樱花园、茶花桂花、丁香迎春、玉兰园、寿益坊（海上华庭）、紫鹃园、紫薇园（牡丹园、玫瑰园）、金桂苑、紫荆党校</x:v>
       </x:c>
-      <x:c r="Q38" s="3" t="str">
+      <x:c r="R38" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R38" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S38" s="3" t="str"/>
-      <x:c r="T38" s="3" t="str">
+      <x:c r="S38" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T38" s="3" t="str"/>
+      <x:c r="U38" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3914,37 +4028,40 @@
         <x:v>桂林西街15弄2号</x:v>
       </x:c>
       <x:c r="I39" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区长海幼儿园</x:v>
       </x:c>
       <x:c r="J39" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>桂林西街15弄2号</x:v>
       </x:c>
       <x:c r="K39" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.415823,31.155405</x:v>
       </x:c>
       <x:c r="L39" s="3" t="str">
+        <x:v>高德直线约 4.11 km</x:v>
+      </x:c>
+      <x:c r="M39" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E6%9E%97%E8%A5%BF%E8%A1%9715%E5%BC%842%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M39" s="3" t="str">
+      <x:c r="N39" s="3" t="str">
         <x:v>54208285</x:v>
       </x:c>
-      <x:c r="N39" s="3" t="str">
+      <x:c r="O39" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="O39" s="3" t="n">
+      <x:c r="P39" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P39" s="3" t="str">
+      <x:c r="Q39" s="3" t="str">
         <x:v>长顺海、长虹坊、长青坊、长丰坊、长兴坊、师大新村、桂康</x:v>
       </x:c>
-      <x:c r="Q39" s="3" t="str">
+      <x:c r="R39" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R39" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S39" s="3" t="str"/>
-      <x:c r="T39" s="3" t="str">
+      <x:c r="S39" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T39" s="3" t="str"/>
+      <x:c r="U39" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -3974,37 +4091,40 @@
         <x:v>桂林西街151弄20号甲</x:v>
       </x:c>
       <x:c r="I40" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区康沁幼儿园</x:v>
       </x:c>
       <x:c r="J40" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>桂林西街151弄20号甲</x:v>
       </x:c>
       <x:c r="K40" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.421715,31.151763</x:v>
       </x:c>
       <x:c r="L40" s="3" t="str">
+        <x:v>高德直线约 3.59 km</x:v>
+      </x:c>
+      <x:c r="M40" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%BA%B7%E6%B2%81%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E6%9E%97%E8%A5%BF%E8%A1%97151%E5%BC%8420%E5%8F%B7%E7%94%B2</x:v>
       </x:c>
-      <x:c r="M40" s="3" t="str">
+      <x:c r="N40" s="3" t="str">
         <x:v>54363105</x:v>
       </x:c>
-      <x:c r="N40" s="3" t="str">
+      <x:c r="O40" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="O40" s="3" t="n">
+      <x:c r="P40" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P40" s="3" t="str">
+      <x:c r="Q40" s="3" t="str">
         <x:v>寿昌山、寿祥坊、寿益坊（寿益坊、桂林西街101弄）、康乐、桂二、冠生园、康宁馨、康强海（康强坊）</x:v>
       </x:c>
-      <x:c r="Q40" s="3" t="str">
+      <x:c r="R40" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R40" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S40" s="3" t="str"/>
-      <x:c r="T40" s="3" t="str">
+      <x:c r="S40" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T40" s="3" t="str"/>
+      <x:c r="U40" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4034,37 +4154,40 @@
         <x:v>长桥一村56号</x:v>
       </x:c>
       <x:c r="I41" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区长桥第一幼儿园</x:v>
       </x:c>
       <x:c r="J41" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>长桥一村56号</x:v>
       </x:c>
       <x:c r="K41" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.437856,31.136245</x:v>
       </x:c>
       <x:c r="L41" s="3" t="str">
+        <x:v>高德直线约 3.01 km</x:v>
+      </x:c>
+      <x:c r="M41" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%B8%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%95%BF%E6%A1%A5%E4%B8%80%E6%9D%9156%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M41" s="3" t="str">
+      <x:c r="N41" s="3" t="str">
         <x:v>64100149</x:v>
       </x:c>
-      <x:c r="N41" s="3" t="str">
+      <x:c r="O41" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="O41" s="3" t="n">
+      <x:c r="P41" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P41" s="3" t="str">
+      <x:c r="Q41" s="3" t="str">
         <x:v>长桥一村、长桥五村（书香逸居、长桥五村）、闵朱、舒城</x:v>
       </x:c>
-      <x:c r="Q41" s="3" t="str">
+      <x:c r="R41" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R41" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S41" s="3" t="str"/>
-      <x:c r="T41" s="3" t="str">
+      <x:c r="S41" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T41" s="3" t="str"/>
+      <x:c r="U41" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4094,37 +4217,40 @@
         <x:v>梅陇十一村97号</x:v>
       </x:c>
       <x:c r="I42" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区长桥第二幼儿园(凌云园)</x:v>
       </x:c>
       <x:c r="J42" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>梅陇十一村97号</x:v>
       </x:c>
       <x:c r="K42" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.427022,31.131789</x:v>
       </x:c>
       <x:c r="L42" s="3" t="str">
+        <x:v>高德直线约 4.09 km</x:v>
+      </x:c>
+      <x:c r="M42" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%BA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%87%8C%E4%BA%91%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%8D%81%E4%B8%80%E6%9D%9197%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M42" s="3" t="str">
+      <x:c r="N42" s="3" t="str">
         <x:v>34318987</x:v>
       </x:c>
-      <x:c r="N42" s="3" t="str">
+      <x:c r="O42" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O42" s="3" t="n">
+      <x:c r="P42" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P42" s="3" t="str">
+      <x:c r="Q42" s="3" t="str">
         <x:v>长桥新村一、长桥新二村、长桥七村、兴荣苑、和平、龙州、梅陇十一第一、梅陇十一第二、陇南、闵秀</x:v>
       </x:c>
-      <x:c r="Q42" s="3" t="str">
+      <x:c r="R42" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R42" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S42" s="3" t="str"/>
-      <x:c r="T42" s="3" t="str">
+      <x:c r="S42" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T42" s="3" t="str"/>
+      <x:c r="U42" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4154,37 +4280,40 @@
         <x:v>长桥二村34号</x:v>
       </x:c>
       <x:c r="I43" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区长桥第二幼儿园(长桥园)</x:v>
       </x:c>
       <x:c r="J43" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>长桥二村34号</x:v>
       </x:c>
       <x:c r="K43" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.441523,31.137059</x:v>
       </x:c>
       <x:c r="L43" s="3" t="str">
+        <x:v>高德直线约 2.72 km</x:v>
+      </x:c>
+      <x:c r="M43" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%BA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E4%BA%8C%E6%9D%9134%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M43" s="3" t="str">
+      <x:c r="N43" s="3" t="str">
         <x:v>64102557</x:v>
       </x:c>
-      <x:c r="N43" s="3" t="str">
+      <x:c r="O43" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O43" s="3" t="n">
+      <x:c r="P43" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P43" s="3" t="str">
+      <x:c r="Q43" s="3" t="str">
         <x:v>长桥新村一、长桥新二村、长桥七村、兴荣苑、和平、龙州、梅陇十一第一、梅陇十一第二、陇南、闵秀</x:v>
       </x:c>
-      <x:c r="Q43" s="3" t="str">
+      <x:c r="R43" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R43" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S43" s="3" t="str"/>
-      <x:c r="T43" s="3" t="str">
+      <x:c r="S43" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T43" s="3" t="str"/>
+      <x:c r="U43" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4214,37 +4343,40 @@
         <x:v>长桥三村124号</x:v>
       </x:c>
       <x:c r="I44" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区长桥第三幼儿园(长桥园)</x:v>
       </x:c>
       <x:c r="J44" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>长桥三村124号</x:v>
       </x:c>
       <x:c r="K44" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.441011,31.134607</x:v>
       </x:c>
       <x:c r="L44" s="3" t="str">
+        <x:v>高德直线约 2.97 km</x:v>
+      </x:c>
+      <x:c r="M44" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%B8%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E5%9B%AD%20%E9%95%BF%E6%A1%A5%E4%B8%89%E6%9D%91124%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M44" s="3" t="str">
+      <x:c r="N44" s="3" t="str">
         <x:v>64102397</x:v>
       </x:c>
-      <x:c r="N44" s="3" t="str">
+      <x:c r="O44" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O44" s="3" t="n">
+      <x:c r="P44" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P44" s="3" t="str">
+      <x:c r="Q44" s="3" t="str">
         <x:v>长桥三村一、长桥三村二（长桥三村东区）、长桥八村、平福、长桥四村</x:v>
       </x:c>
-      <x:c r="Q44" s="3" t="str">
+      <x:c r="R44" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R44" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S44" s="3" t="str"/>
-      <x:c r="T44" s="3" t="str">
+      <x:c r="S44" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T44" s="3" t="str"/>
+      <x:c r="U44" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4274,37 +4406,40 @@
         <x:v>上中路483弄32号</x:v>
       </x:c>
       <x:c r="I45" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区长桥第三幼儿园(平福园)</x:v>
       </x:c>
       <x:c r="J45" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上中路483弄32号</x:v>
       </x:c>
       <x:c r="K45" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.448286,31.140012</x:v>
       </x:c>
       <x:c r="L45" s="3" t="str">
+        <x:v>高德直线约 2.09 km</x:v>
+      </x:c>
+      <x:c r="M45" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%95%BF%E6%A1%A5%E7%AC%AC%E4%B8%89%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%B9%B3%E7%A6%8F%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E8%B7%AF483%E5%BC%8432%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M45" s="3" t="str">
+      <x:c r="N45" s="3" t="str">
         <x:v>64102397</x:v>
       </x:c>
-      <x:c r="N45" s="3" t="str">
+      <x:c r="O45" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O45" s="3" t="n">
+      <x:c r="P45" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P45" s="3" t="str">
+      <x:c r="Q45" s="3" t="str">
         <x:v>长桥三村一、长桥三村二（长桥三村东区）、长桥八村、平福、长桥四村</x:v>
       </x:c>
-      <x:c r="Q45" s="3" t="str">
+      <x:c r="R45" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R45" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S45" s="3" t="str"/>
-      <x:c r="T45" s="3" t="str">
+      <x:c r="S45" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T45" s="3" t="str"/>
+      <x:c r="U45" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4334,37 +4469,40 @@
         <x:v>龙川北路园南一村27号</x:v>
       </x:c>
       <x:c r="I46" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区园南幼儿园</x:v>
       </x:c>
       <x:c r="J46" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>园南一村27号</x:v>
       </x:c>
       <x:c r="K46" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.440190,31.141129</x:v>
       </x:c>
       <x:c r="L46" s="3" t="str">
+        <x:v>高德直线约 2.47 km</x:v>
+      </x:c>
+      <x:c r="M46" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9B%AD%E5%8D%97%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%B7%9D%E5%8C%97%E8%B7%AF%E5%9B%AD%E5%8D%97%E4%B8%80%E6%9D%9127%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M46" s="3" t="str">
+      <x:c r="N46" s="3" t="str">
         <x:v>64763190</x:v>
       </x:c>
-      <x:c r="N46" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O46" s="3" t="n">
+      <x:c r="O46" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P46" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P46" s="3" t="str">
+      <x:c r="Q46" s="3" t="str">
         <x:v>园南一村、园南二村、园南三村、汇成五村、华东一</x:v>
       </x:c>
-      <x:c r="Q46" s="3" t="str">
+      <x:c r="R46" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R46" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S46" s="3" t="str"/>
-      <x:c r="T46" s="3" t="str">
+      <x:c r="S46" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T46" s="3" t="str"/>
+      <x:c r="U46" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4394,37 +4532,40 @@
         <x:v>梅陇四村56号甲</x:v>
       </x:c>
       <x:c r="I47" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区梅陇幼儿园(嘉川园)</x:v>
       </x:c>
       <x:c r="J47" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>梅陇四村56号甲</x:v>
       </x:c>
       <x:c r="K47" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.421073,31.137521</x:v>
       </x:c>
       <x:c r="L47" s="3" t="str">
+        <x:v>高德直线约 4.18 km</x:v>
+      </x:c>
+      <x:c r="M47" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A2%85%E9%99%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%98%89%E5%B7%9D%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%9B%9B%E6%9D%9156%E5%8F%B7%E7%94%B2</x:v>
       </x:c>
-      <x:c r="M47" s="3" t="str">
+      <x:c r="N47" s="3" t="str">
         <x:v>64100015</x:v>
       </x:c>
-      <x:c r="N47" s="3" t="str">
+      <x:c r="O47" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O47" s="3" t="n">
+      <x:c r="P47" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P47" s="3" t="str">
+      <x:c r="Q47" s="3" t="str">
         <x:v>梅三、梅六、梅苑一、梅苑二、凌云、梅四、理工一、理工二、华理苑、书香苑、家乐苑、阳光（阳光新景）</x:v>
       </x:c>
-      <x:c r="Q47" s="3" t="str">
+      <x:c r="R47" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R47" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S47" s="3" t="str"/>
-      <x:c r="T47" s="3" t="str">
+      <x:c r="S47" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T47" s="3" t="str"/>
+      <x:c r="U47" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4454,37 +4595,40 @@
         <x:v>梅陇六村65号</x:v>
       </x:c>
       <x:c r="I48" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区梅陇幼儿园(梅陇园)</x:v>
       </x:c>
       <x:c r="J48" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>梅陇六村65号</x:v>
       </x:c>
       <x:c r="K48" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.419034,31.133842</x:v>
       </x:c>
       <x:c r="L48" s="3" t="str">
+        <x:v>高德直线约 4.56 km</x:v>
+      </x:c>
+      <x:c r="M48" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A2%85%E9%99%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%85%AD%E6%9D%9165%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M48" s="3" t="str">
+      <x:c r="N48" s="3" t="str">
         <x:v>64100015</x:v>
       </x:c>
-      <x:c r="N48" s="3" t="str">
+      <x:c r="O48" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O48" s="3" t="n">
+      <x:c r="P48" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P48" s="3" t="str">
+      <x:c r="Q48" s="3" t="str">
         <x:v>梅三、梅六、梅苑一、梅苑二、凌云、梅四、理工一、理工二、华理苑、书香苑、家乐苑、阳光（阳光新景）</x:v>
       </x:c>
-      <x:c r="Q48" s="3" t="str">
+      <x:c r="R48" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R48" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S48" s="3" t="str"/>
-      <x:c r="T48" s="3" t="str">
+      <x:c r="S48" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T48" s="3" t="str"/>
+      <x:c r="U48" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4514,37 +4658,40 @@
         <x:v>梅陇五村54号</x:v>
       </x:c>
       <x:c r="I49" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区梅陇第二幼儿园</x:v>
       </x:c>
       <x:c r="J49" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>梅陇五村54号</x:v>
       </x:c>
       <x:c r="K49" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.421629,31.135390</x:v>
       </x:c>
       <x:c r="L49" s="3" t="str">
+        <x:v>高德直线约 4.26 km</x:v>
+      </x:c>
+      <x:c r="M49" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A2%85%E9%99%87%E7%AC%AC%E4%BA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E4%BA%94%E6%9D%9154%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M49" s="3" t="str">
+      <x:c r="N49" s="3" t="str">
         <x:v>64775092</x:v>
       </x:c>
-      <x:c r="N49" s="3" t="str">
+      <x:c r="O49" s="3" t="str">
         <x:v>混龄式招生</x:v>
       </x:c>
-      <x:c r="O49" s="3" t="n">
+      <x:c r="P49" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P49" s="3" t="str">
+      <x:c r="Q49" s="3" t="str">
         <x:v>梅陇五村、梅陇七村、梅陇八村、梅陇十村、梅陇九村、阳光（阳光绿园）、长陇苑</x:v>
       </x:c>
-      <x:c r="Q49" s="3" t="str">
+      <x:c r="R49" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R49" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S49" s="3" t="str"/>
-      <x:c r="T49" s="3" t="str">
+      <x:c r="S49" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T49" s="3" t="str"/>
+      <x:c r="U49" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4574,37 +4721,40 @@
         <x:v>老沪闵路1300号</x:v>
       </x:c>
       <x:c r="I50" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区华建幼儿园</x:v>
       </x:c>
       <x:c r="J50" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>老沪闵路1300号</x:v>
       </x:c>
       <x:c r="K50" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.439517,31.119198</x:v>
       </x:c>
       <x:c r="L50" s="3" t="str">
+        <x:v>高德直线约 4.54 km</x:v>
+      </x:c>
+      <x:c r="M50" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%8D%8E%E5%BB%BA%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF1300%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M50" s="3" t="str">
+      <x:c r="N50" s="3" t="str">
         <x:v>2164548743</x:v>
       </x:c>
-      <x:c r="N50" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O50" s="3" t="n">
+      <x:c r="O50" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P50" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P50" s="3" t="str">
+      <x:c r="Q50" s="3" t="str">
         <x:v>华建、建华村、北杨村</x:v>
       </x:c>
-      <x:c r="Q50" s="3" t="str">
+      <x:c r="R50" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R50" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S50" s="3" t="str"/>
-      <x:c r="T50" s="3" t="str">
+      <x:c r="S50" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T50" s="3" t="str"/>
+      <x:c r="U50" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4634,37 +4784,40 @@
         <x:v>建华路102号</x:v>
       </x:c>
       <x:c r="I51" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区位育幼儿园</x:v>
       </x:c>
       <x:c r="J51" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>建华路102号</x:v>
       </x:c>
       <x:c r="K51" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.445555,31.121767</x:v>
       </x:c>
       <x:c r="L51" s="3" t="str">
+        <x:v>高德直线约 4.06 km</x:v>
+      </x:c>
+      <x:c r="M51" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%BD%8D%E8%82%B2%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%BB%BA%E5%8D%8E%E8%B7%AF102%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M51" s="3" t="str">
+      <x:c r="N51" s="3" t="str">
         <x:v>64960505</x:v>
       </x:c>
-      <x:c r="N51" s="3" t="str">
+      <x:c r="O51" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O51" s="3" t="n">
+      <x:c r="P51" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P51" s="3" t="str">
+      <x:c r="Q51" s="3" t="str">
         <x:v>华泾四村、华泾五村、漓江山水、联合居委</x:v>
       </x:c>
-      <x:c r="Q51" s="3" t="str">
+      <x:c r="R51" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R51" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S51" s="3" t="str"/>
-      <x:c r="T51" s="3" t="str">
+      <x:c r="S51" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T51" s="3" t="str"/>
+      <x:c r="U51" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4694,37 +4847,40 @@
         <x:v>龙吴路2422号</x:v>
       </x:c>
       <x:c r="I52" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区果果幼儿园(华欣园)</x:v>
       </x:c>
       <x:c r="J52" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>龙吴路2422号</x:v>
       </x:c>
       <x:c r="K52" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.457615,31.118824</x:v>
       </x:c>
       <x:c r="L52" s="3" t="str">
+        <x:v>高德直线约 4.18 km</x:v>
+      </x:c>
+      <x:c r="M52" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%9C%E6%9E%9C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%8E%E6%AC%A3%E5%9B%AD%20%E9%BE%99%E5%90%B4%E8%B7%AF2422%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M52" s="3" t="str">
+      <x:c r="N52" s="3" t="str">
         <x:v>54829893</x:v>
       </x:c>
-      <x:c r="N52" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O52" s="3" t="n">
+      <x:c r="O52" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P52" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P52" s="3" t="str">
+      <x:c r="Q52" s="3" t="str">
         <x:v>华欣家园、华发、馨宁、大桥、明丰新纪苑、名苑、华臻</x:v>
       </x:c>
-      <x:c r="Q52" s="3" t="str">
+      <x:c r="R52" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R52" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S52" s="3" t="str"/>
-      <x:c r="T52" s="3" t="str">
+      <x:c r="S52" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T52" s="3" t="str"/>
+      <x:c r="U52" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4754,37 +4910,40 @@
         <x:v>华发路100弄22号</x:v>
       </x:c>
       <x:c r="I53" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区果果幼儿园(华发园)</x:v>
       </x:c>
       <x:c r="J53" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>华发路100弄22号</x:v>
       </x:c>
       <x:c r="K53" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.452820,31.127984</x:v>
       </x:c>
       <x:c r="L53" s="3" t="str">
+        <x:v>高德直线约 3.21 km</x:v>
+      </x:c>
+      <x:c r="M53" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%9C%E6%9E%9C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%8D%8E%E5%8F%91%E5%9B%AD%20%E5%8D%8E%E5%8F%91%E8%B7%AF100%E5%BC%8422%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M53" s="3" t="str">
+      <x:c r="N53" s="3" t="str">
         <x:v>54829893</x:v>
       </x:c>
-      <x:c r="N53" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O53" s="3" t="n">
+      <x:c r="O53" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P53" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P53" s="3" t="str">
+      <x:c r="Q53" s="3" t="str">
         <x:v>华欣家园、华发、馨宁、大桥、明丰新纪苑、名苑、华臻</x:v>
       </x:c>
-      <x:c r="Q53" s="3" t="str">
+      <x:c r="R53" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R53" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S53" s="3" t="str"/>
-      <x:c r="T53" s="3" t="str">
+      <x:c r="S53" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T53" s="3" t="str"/>
+      <x:c r="U53" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4814,37 +4973,40 @@
         <x:v>罗秀路11号</x:v>
       </x:c>
       <x:c r="I54" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区星辰幼儿园</x:v>
       </x:c>
       <x:c r="J54" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>罗秀路11号</x:v>
       </x:c>
       <x:c r="K54" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.452281,31.134424</x:v>
       </x:c>
       <x:c r="L54" s="3" t="str">
+        <x:v>高德直线约 2.52 km</x:v>
+      </x:c>
+      <x:c r="M54" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%98%9F%E8%BE%B0%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%BD%97%E7%A7%80%E8%B7%AF11%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M54" s="3" t="str">
+      <x:c r="N54" s="3" t="str">
         <x:v>54010448</x:v>
       </x:c>
-      <x:c r="N54" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O54" s="3" t="n">
+      <x:c r="O54" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P54" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P54" s="3" t="str">
+      <x:c r="Q54" s="3" t="str">
         <x:v>徐汇新城、罗秀三村、华滨家园、华沁家园、罗秀、罗秀二村</x:v>
       </x:c>
-      <x:c r="Q54" s="3" t="str">
+      <x:c r="R54" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R54" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S54" s="3" t="str"/>
-      <x:c r="T54" s="3" t="str">
+      <x:c r="S54" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T54" s="3" t="str"/>
+      <x:c r="U54" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4874,37 +5036,40 @@
         <x:v>龙瑞路135号</x:v>
       </x:c>
       <x:c r="I55" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区徐汇实验幼儿园</x:v>
       </x:c>
       <x:c r="J55" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>龙瑞路135号</x:v>
       </x:c>
       <x:c r="K55" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.452624,31.138923</x:v>
       </x:c>
       <x:c r="L55" s="3" t="str">
+        <x:v>高德直线约 2.03 km</x:v>
+      </x:c>
+      <x:c r="M55" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%BE%90%E6%B1%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E7%91%9E%E8%B7%AF135%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M55" s="3" t="str">
+      <x:c r="N55" s="3" t="str">
         <x:v>54045192</x:v>
       </x:c>
-      <x:c r="N55" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O55" s="3" t="n">
+      <x:c r="O55" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P55" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P55" s="3" t="str">
+      <x:c r="Q55" s="3" t="str">
         <x:v>中海瀛台、百龙、港口</x:v>
       </x:c>
-      <x:c r="Q55" s="3" t="str">
+      <x:c r="R55" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R55" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S55" s="3" t="str"/>
-      <x:c r="T55" s="3" t="str">
+      <x:c r="S55" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T55" s="3" t="str"/>
+      <x:c r="U55" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4934,37 +5099,40 @@
         <x:v>望月路882号</x:v>
       </x:c>
       <x:c r="I56" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区印象幼儿园</x:v>
       </x:c>
       <x:c r="J56" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>望月路882号</x:v>
       </x:c>
       <x:c r="K56" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.461128,31.116608</x:v>
       </x:c>
       <x:c r="L56" s="3" t="str">
+        <x:v>高德直线约 4.43 km</x:v>
+      </x:c>
+      <x:c r="M56" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%8D%B0%E8%B1%A1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%9C%9B%E6%9C%88%E8%B7%AF882%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M56" s="3" t="str">
+      <x:c r="N56" s="3" t="str">
         <x:v>64960096</x:v>
       </x:c>
-      <x:c r="N56" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O56" s="3" t="n">
+      <x:c r="O56" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P56" s="3" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="P56" s="3" t="str">
+      <x:c r="Q56" s="3" t="str">
         <x:v>印象、华阳、沙家浜</x:v>
       </x:c>
-      <x:c r="Q56" s="3" t="str">
+      <x:c r="R56" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R56" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S56" s="3" t="str"/>
-      <x:c r="T56" s="3" t="str">
+      <x:c r="S56" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T56" s="3" t="str"/>
+      <x:c r="U56" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -4994,37 +5162,40 @@
         <x:v>石龙路818弄8号</x:v>
       </x:c>
       <x:c r="I57" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区科技逸夫幼儿园</x:v>
       </x:c>
       <x:c r="J57" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>石龙路818弄8号</x:v>
       </x:c>
       <x:c r="K57" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.430659,31.150107</x:v>
       </x:c>
       <x:c r="L57" s="3" t="str">
+        <x:v>高德直线约 2.79 km</x:v>
+      </x:c>
+      <x:c r="M57" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E9%80%B8%E5%A4%AB%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%9F%B3%E9%BE%99%E8%B7%AF818%E5%BC%848%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M57" s="3" t="str">
+      <x:c r="N57" s="3" t="str">
         <x:v>64400295</x:v>
       </x:c>
-      <x:c r="N57" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O57" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P57" s="3" t="str">
+      <x:c r="O57" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P57" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q57" s="3" t="str">
         <x:v>正南、东荡、南站居委（临）</x:v>
       </x:c>
-      <x:c r="Q57" s="3" t="str">
+      <x:c r="R57" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R57" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S57" s="3" t="str"/>
-      <x:c r="T57" s="3" t="str">
+      <x:c r="S57" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T57" s="3" t="str"/>
+      <x:c r="U57" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5054,37 +5225,40 @@
         <x:v>望月路401号</x:v>
       </x:c>
       <x:c r="I58" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区盛华幼儿园</x:v>
       </x:c>
       <x:c r="J58" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>望月路401号</x:v>
       </x:c>
       <x:c r="K58" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.457146,31.107316</x:v>
       </x:c>
       <x:c r="L58" s="3" t="str">
+        <x:v>高德直线约 5.46 km</x:v>
+      </x:c>
+      <x:c r="M58" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%9B%9B%E5%8D%8E%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%9C%9B%E6%9C%88%E8%B7%AF401%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M58" s="3" t="str">
+      <x:c r="N58" s="3" t="str">
         <x:v>021-54852338</x:v>
       </x:c>
-      <x:c r="N58" s="3" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O58" s="3" t="n">
+      <x:c r="O58" s="3" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P58" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P58" s="3" t="str">
+      <x:c r="Q58" s="3" t="str">
         <x:v>盛华、华泾绿苑、光华绿苑</x:v>
       </x:c>
-      <x:c r="Q58" s="3" t="str">
+      <x:c r="R58" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R58" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S58" s="3" t="str"/>
-      <x:c r="T58" s="3" t="str">
+      <x:c r="S58" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T58" s="3" t="str"/>
+      <x:c r="U58" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5114,37 +5288,40 @@
         <x:v>古井路160号</x:v>
       </x:c>
       <x:c r="I59" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区艺树幼儿园</x:v>
       </x:c>
       <x:c r="J59" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>古井路160号</x:v>
       </x:c>
       <x:c r="K59" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.417163,31.189960</x:v>
       </x:c>
       <x:c r="L59" s="3" t="str">
+        <x:v>高德直线约 5.46 km</x:v>
+      </x:c>
+      <x:c r="M59" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%89%BA%E6%A0%91%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E4%BA%95%E8%B7%AF160%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M59" s="3" t="str">
+      <x:c r="N59" s="3" t="str">
         <x:v>64388770</x:v>
       </x:c>
-      <x:c r="N59" s="3" t="str">
+      <x:c r="O59" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O59" s="3" t="n">
+      <x:c r="P59" s="3" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="P59" s="3" t="str">
+      <x:c r="Q59" s="3" t="str">
         <x:v>锦馨苑、千鹤第六、小安桥、华鼎广场、千鹤五、尚汇豪庭、千鹤一、千鹤二；另向徐家汇街道、田林街道扩招</x:v>
       </x:c>
-      <x:c r="Q59" s="3" t="str">
+      <x:c r="R59" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="R59" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S59" s="3" t="str"/>
-      <x:c r="T59" s="3" t="str">
+      <x:c r="S59" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T59" s="3" t="str"/>
+      <x:c r="U59" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5174,37 +5351,40 @@
         <x:v>桂平路260弄14号</x:v>
       </x:c>
       <x:c r="I60" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区桂平幼儿园</x:v>
       </x:c>
       <x:c r="J60" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>桂平路260弄14号</x:v>
       </x:c>
       <x:c r="K60" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.408648,31.158721</x:v>
       </x:c>
       <x:c r="L60" s="3" t="str">
+        <x:v>高德直线约 4.80 km</x:v>
+      </x:c>
+      <x:c r="M60" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A1%82%E5%B9%B3%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E5%B9%B3%E8%B7%AF260%E5%BC%8414%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M60" s="3" t="str">
+      <x:c r="N60" s="3" t="str">
         <x:v>64031921</x:v>
       </x:c>
-      <x:c r="N60" s="3" t="str">
+      <x:c r="O60" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O60" s="3" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="P60" s="3" t="str">
+      <x:c r="P60" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q60" s="3" t="str">
         <x:v>联莘、欣园</x:v>
       </x:c>
-      <x:c r="Q60" s="3" t="str">
+      <x:c r="R60" s="3" t="str">
         <x:v>固定对口</x:v>
       </x:c>
-      <x:c r="R60" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S60" s="3" t="str"/>
-      <x:c r="T60" s="3" t="str">
+      <x:c r="S60" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T60" s="3" t="str"/>
+      <x:c r="U60" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5234,37 +5414,40 @@
         <x:v>田林十二村40号</x:v>
       </x:c>
       <x:c r="I61" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区田林第六幼儿园</x:v>
       </x:c>
       <x:c r="J61" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>田林十二村40号</x:v>
       </x:c>
       <x:c r="K61" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.428787,31.171843</x:v>
       </x:c>
       <x:c r="L61" s="3" t="str">
+        <x:v>高德直线约 3.35 km</x:v>
+      </x:c>
+      <x:c r="M61" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E7%AC%AC%E5%85%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%8D%81%E4%BA%8C%E6%9D%9140%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M61" s="3" t="str">
+      <x:c r="N61" s="3" t="str">
         <x:v>64366380</x:v>
       </x:c>
-      <x:c r="N61" s="3" t="str">
+      <x:c r="O61" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O61" s="3" t="n">
+      <x:c r="P61" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P61" s="3" t="str">
+      <x:c r="Q61" s="3" t="str">
         <x:v>田林十二村、田林三四村、古一、古二、古三、古四、东兰、航天新苑、永兆、漕河泾开发园区（临）；另向田林街道、虹梅路街道扩招</x:v>
       </x:c>
-      <x:c r="Q61" s="3" t="str">
+      <x:c r="R61" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="R61" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S61" s="3" t="str"/>
-      <x:c r="T61" s="3" t="str">
+      <x:c r="S61" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T61" s="3" t="str"/>
+      <x:c r="U61" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5294,37 +5477,40 @@
         <x:v>田林四村18号</x:v>
       </x:c>
       <x:c r="I62" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区田林第六幼儿园(贝贝分园)</x:v>
       </x:c>
       <x:c r="J62" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>田林四村18号</x:v>
       </x:c>
       <x:c r="K62" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.422992,31.170556</x:v>
       </x:c>
       <x:c r="L62" s="3" t="str">
+        <x:v>高德直线约 3.78 km</x:v>
+      </x:c>
+      <x:c r="M62" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E7%AC%AC%E5%85%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E8%B4%9D%E8%B4%9D%E5%88%86%E5%9B%AD%20%E7%94%B0%E6%9E%97%E5%9B%9B%E6%9D%9118%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M62" s="3" t="str">
+      <x:c r="N62" s="3" t="str">
         <x:v>64367248</x:v>
       </x:c>
-      <x:c r="N62" s="3" t="str">
+      <x:c r="O62" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O62" s="3" t="n">
+      <x:c r="P62" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P62" s="3" t="str">
+      <x:c r="Q62" s="3" t="str">
         <x:v>田林十二村、田林三四村、古一、古二、古三、古四、东兰、航天新苑、永兆、漕河泾开发园区（临）；另向田林街道、虹梅路街道扩招</x:v>
       </x:c>
-      <x:c r="Q62" s="3" t="str">
+      <x:c r="R62" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="R62" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S62" s="3" t="str"/>
-      <x:c r="T62" s="3" t="str">
+      <x:c r="S62" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T62" s="3" t="str"/>
+      <x:c r="U62" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5354,37 +5540,40 @@
         <x:v>古美路1107弄65号</x:v>
       </x:c>
       <x:c r="I63" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区田林第六幼儿园(东兰分园)</x:v>
       </x:c>
       <x:c r="J63" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>古美路1107弄65号</x:v>
       </x:c>
       <x:c r="K63" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.398709,31.154511</x:v>
       </x:c>
       <x:c r="L63" s="3" t="str">
+        <x:v>高德直线约 5.75 km</x:v>
+      </x:c>
+      <x:c r="M63" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E7%AC%AC%E5%85%AD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%9C%E5%85%B0%E5%88%86%E5%9B%AD%20%E5%8F%A4%E7%BE%8E%E8%B7%AF1107%E5%BC%8465%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M63" s="3" t="str">
+      <x:c r="N63" s="3" t="str">
         <x:v>64707260</x:v>
       </x:c>
-      <x:c r="N63" s="3" t="str">
+      <x:c r="O63" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O63" s="3" t="n">
+      <x:c r="P63" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P63" s="3" t="str">
+      <x:c r="Q63" s="3" t="str">
         <x:v>田林十二村、田林三四村、古一、古二、古三、古四、东兰、航天新苑、永兆、漕河泾开发园区（临）；另向田林街道、虹梅路街道扩招</x:v>
       </x:c>
-      <x:c r="Q63" s="3" t="str">
+      <x:c r="R63" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="R63" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S63" s="3" t="str"/>
-      <x:c r="T63" s="3" t="str">
+      <x:c r="S63" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T63" s="3" t="str"/>
+      <x:c r="U63" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5414,37 +5603,40 @@
         <x:v>桂平路123弄23号</x:v>
       </x:c>
       <x:c r="I64" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区紫薇实验幼儿园(桂平园)</x:v>
       </x:c>
       <x:c r="J64" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>桂平路123弄23号</x:v>
       </x:c>
       <x:c r="K64" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.410334,31.152247</x:v>
       </x:c>
       <x:c r="L64" s="3" t="str">
+        <x:v>高德直线约 4.66 km</x:v>
+      </x:c>
+      <x:c r="M64" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%B4%AB%E8%96%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%A1%82%E5%B9%B3%E5%9B%AD%20%E6%A1%82%E5%B9%B3%E8%B7%AF123%E5%BC%8423%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M64" s="3" t="str">
+      <x:c r="N64" s="3" t="str">
         <x:v>54217515</x:v>
       </x:c>
-      <x:c r="N64" s="3" t="str">
+      <x:c r="O64" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="O64" s="3" t="n">
+      <x:c r="P64" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P64" s="3" t="str">
+      <x:c r="Q64" s="3" t="str">
         <x:v>紫薇园（桂平路123弄）、康强海（海上名邸）；区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q64" s="3" t="str">
+      <x:c r="R64" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R64" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S64" s="3" t="str"/>
-      <x:c r="T64" s="3" t="str">
+      <x:c r="S64" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T64" s="3" t="str"/>
+      <x:c r="U64" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5474,37 +5666,40 @@
         <x:v>浦北路173号</x:v>
       </x:c>
       <x:c r="I65" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区紫薇实验幼儿园(浦北园)</x:v>
       </x:c>
       <x:c r="J65" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>浦北路173号</x:v>
       </x:c>
       <x:c r="K65" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.425264,31.156355</x:v>
       </x:c>
       <x:c r="L65" s="3" t="str">
+        <x:v>高德直线约 3.21 km</x:v>
+      </x:c>
+      <x:c r="M65" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%B4%AB%E8%96%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%B5%A6%E5%8C%97%E5%9B%AD%20%E6%B5%A6%E5%8C%97%E8%B7%AF173%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M65" s="3" t="str">
+      <x:c r="N65" s="3" t="str">
         <x:v>64830788</x:v>
       </x:c>
-      <x:c r="N65" s="3" t="str">
+      <x:c r="O65" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="O65" s="3" t="n">
+      <x:c r="P65" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P65" s="3" t="str">
+      <x:c r="Q65" s="3" t="str">
         <x:v>紫薇园（桂平路123弄）、康强海（海上名邸）；区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q65" s="3" t="str">
+      <x:c r="R65" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R65" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S65" s="3" t="str"/>
-      <x:c r="T65" s="3" t="str">
+      <x:c r="S65" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T65" s="3" t="str"/>
+      <x:c r="U65" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5534,37 +5729,40 @@
         <x:v>宜州路26号</x:v>
       </x:c>
       <x:c r="I66" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区紫薇实验幼儿园(全州园)</x:v>
       </x:c>
       <x:c r="J66" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>宜州路26号</x:v>
       </x:c>
       <x:c r="K66" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.408875,31.167055</x:v>
       </x:c>
       <x:c r="L66" s="3" t="str">
+        <x:v>高德直线约 4.92 km</x:v>
+      </x:c>
+      <x:c r="M66" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%B4%AB%E8%96%87%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%85%A8%E5%B7%9E%E5%9B%AD%20%E5%AE%9C%E5%B7%9E%E8%B7%AF26%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M66" s="3" t="str">
+      <x:c r="N66" s="3" t="str">
         <x:v>54500996</x:v>
       </x:c>
-      <x:c r="N66" s="3" t="str">
+      <x:c r="O66" s="3" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="O66" s="3" t="n">
+      <x:c r="P66" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P66" s="3" t="str">
+      <x:c r="Q66" s="3" t="str">
         <x:v>紫薇园（桂平路123弄）、康强海（海上名邸）；区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q66" s="3" t="str">
+      <x:c r="R66" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R66" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S66" s="3" t="str"/>
-      <x:c r="T66" s="3" t="str">
+      <x:c r="S66" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T66" s="3" t="str"/>
+      <x:c r="U66" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5594,37 +5792,40 @@
         <x:v>上中西路378号</x:v>
       </x:c>
       <x:c r="I67" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区上海幼儿园(凌云园)</x:v>
       </x:c>
       <x:c r="J67" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上中西路378号</x:v>
       </x:c>
       <x:c r="K67" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.423721,31.134831</x:v>
       </x:c>
       <x:c r="L67" s="3" t="str">
+        <x:v>高德直线约 4.13 km</x:v>
+      </x:c>
+      <x:c r="M67" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%8A%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%87%8C%E4%BA%91%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E8%A5%BF%E8%B7%AF378%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M67" s="3" t="str">
+      <x:c r="N67" s="3" t="str">
         <x:v>64106663 / 64100564 / 64250961</x:v>
       </x:c>
-      <x:c r="N67" s="3" t="str">
+      <x:c r="O67" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O67" s="3" t="n">
+      <x:c r="P67" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P67" s="3" t="str">
+      <x:c r="Q67" s="3" t="str">
         <x:v>体育花苑、长桥五村（上中路100弄）、长桥三村二（尚海悦庭）；另向凌云路街道、长桥街道、华泾镇扩招</x:v>
       </x:c>
-      <x:c r="Q67" s="3" t="str">
+      <x:c r="R67" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="R67" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S67" s="3" t="str"/>
-      <x:c r="T67" s="3" t="str">
+      <x:c r="S67" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T67" s="3" t="str"/>
+      <x:c r="U67" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5654,37 +5855,40 @@
         <x:v>老沪闵路729弄41号乙</x:v>
       </x:c>
       <x:c r="I68" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区上海幼儿园(冠军园)</x:v>
       </x:c>
       <x:c r="J68" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>老沪闵路728弄41号乙</x:v>
       </x:c>
       <x:c r="K68" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.430246,31.143076</x:v>
       </x:c>
       <x:c r="L68" s="3" t="str">
+        <x:v>高德直线约 3.11 km</x:v>
+      </x:c>
+      <x:c r="M68" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%8A%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%86%A0%E5%86%9B%E5%9B%AD%20%E8%80%81%E6%B2%AA%E9%97%B5%E8%B7%AF729%E5%BC%8441%E5%8F%B7%E4%B9%99</x:v>
       </x:c>
-      <x:c r="M68" s="3" t="str">
+      <x:c r="N68" s="3" t="str">
         <x:v>64250961</x:v>
       </x:c>
-      <x:c r="N68" s="3" t="str">
+      <x:c r="O68" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O68" s="3" t="n">
+      <x:c r="P68" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P68" s="3" t="str">
+      <x:c r="Q68" s="3" t="str">
         <x:v>体育花苑、长桥五村（上中路100弄）、长桥三村二（尚海悦庭）；另向凌云路街道、长桥街道、华泾镇扩招</x:v>
       </x:c>
-      <x:c r="Q68" s="3" t="str">
+      <x:c r="R68" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="R68" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S68" s="3" t="str"/>
-      <x:c r="T68" s="3" t="str">
+      <x:c r="S68" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T68" s="3" t="str"/>
+      <x:c r="U68" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5714,37 +5918,40 @@
         <x:v>上中路402号</x:v>
       </x:c>
       <x:c r="I69" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区上海幼儿园(上中园)</x:v>
       </x:c>
       <x:c r="J69" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上中路402号</x:v>
       </x:c>
       <x:c r="K69" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.439692,31.138699</x:v>
       </x:c>
       <x:c r="L69" s="3" t="str">
+        <x:v>高德直线约 2.69 km</x:v>
+      </x:c>
+      <x:c r="M69" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%8A%E6%B5%B7%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E5%9B%AD%20%E4%B8%8A%E4%B8%AD%E8%B7%AF402%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M69" s="3" t="str">
+      <x:c r="N69" s="3" t="str">
         <x:v>64106663 / 64100564 / 64250961</x:v>
       </x:c>
-      <x:c r="N69" s="3" t="str">
+      <x:c r="O69" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O69" s="3" t="n">
+      <x:c r="P69" s="3" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="P69" s="3" t="str">
+      <x:c r="Q69" s="3" t="str">
         <x:v>体育花苑、长桥五村（上中路100弄）、长桥三村二（尚海悦庭）；另向凌云路街道、长桥街道、华泾镇扩招</x:v>
       </x:c>
-      <x:c r="Q69" s="3" t="str">
+      <x:c r="R69" s="3" t="str">
         <x:v>扩招</x:v>
       </x:c>
-      <x:c r="R69" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S69" s="3" t="str"/>
-      <x:c r="T69" s="3" t="str">
+      <x:c r="S69" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T69" s="3" t="str"/>
+      <x:c r="U69" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5774,37 +5981,40 @@
         <x:v>乌鲁木齐南路14号</x:v>
       </x:c>
       <x:c r="I70" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区乌鲁木齐南路幼儿园</x:v>
       </x:c>
       <x:c r="J70" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>乌鲁木齐南路14号(衡山路地铁站3号口步行440米)</x:v>
       </x:c>
       <x:c r="K70" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.447657,31.207598</x:v>
       </x:c>
       <x:c r="L70" s="3" t="str">
+        <x:v>高德直线约 5.80 km</x:v>
+      </x:c>
+      <x:c r="M70" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF14%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M70" s="3" t="str">
+      <x:c r="N70" s="3" t="str">
         <x:v>64319939</x:v>
       </x:c>
-      <x:c r="N70" s="3" t="str">
+      <x:c r="O70" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O70" s="3" t="n">
+      <x:c r="P70" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P70" s="3" t="str">
+      <x:c r="Q70" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q70" s="3" t="str">
+      <x:c r="R70" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R70" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S70" s="3" t="str"/>
-      <x:c r="T70" s="3" t="str">
+      <x:c r="S70" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T70" s="3" t="str"/>
+      <x:c r="U70" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5834,37 +6044,40 @@
         <x:v>淮海路1788号</x:v>
       </x:c>
       <x:c r="I71" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区乌鲁木齐南路幼儿园(境内部)</x:v>
       </x:c>
       <x:c r="J71" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>淮海中路1788号</x:v>
       </x:c>
       <x:c r="K71" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.439514,31.205251</x:v>
       </x:c>
       <x:c r="L71" s="3" t="str">
+        <x:v>高德直线约 5.75 km</x:v>
+      </x:c>
+      <x:c r="M71" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A2%83%E5%86%85%E9%83%A8%20%E6%B7%AE%E6%B5%B7%E8%B7%AF1788%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M71" s="3" t="str">
+      <x:c r="N71" s="3" t="str">
         <x:v>64319939</x:v>
       </x:c>
-      <x:c r="N71" s="3" t="str">
+      <x:c r="O71" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O71" s="3" t="n">
+      <x:c r="P71" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P71" s="3" t="str">
+      <x:c r="Q71" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q71" s="3" t="str">
+      <x:c r="R71" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R71" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S71" s="3" t="str"/>
-      <x:c r="T71" s="3" t="str">
+      <x:c r="S71" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T71" s="3" t="str"/>
+      <x:c r="U71" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5903,28 +6116,31 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L72" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M72" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B9%8C%E9%B2%81%E6%9C%A8%E9%BD%90%E5%8D%97%E8%B7%AF%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A2%83%E5%A4%96%E9%83%A8%20%E6%B7%AE%E6%B5%B7%E4%B8%AD%E8%B7%AF1480%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M72" s="3" t="str">
+      <x:c r="N72" s="3" t="str">
         <x:v>64330160</x:v>
       </x:c>
-      <x:c r="N72" s="3" t="str">
+      <x:c r="O72" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O72" s="3" t="n">
+      <x:c r="P72" s="3" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="P72" s="3" t="str">
+      <x:c r="Q72" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q72" s="3" t="str">
+      <x:c r="R72" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R72" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S72" s="3" t="str"/>
-      <x:c r="T72" s="3" t="str">
+      <x:c r="S72" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T72" s="3" t="str"/>
+      <x:c r="U72" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -5954,37 +6170,40 @@
         <x:v>宜山路655弄1号</x:v>
       </x:c>
       <x:c r="I73" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区科技幼儿园(宜山园1部)</x:v>
       </x:c>
       <x:c r="J73" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>宜山路655弄1号</x:v>
       </x:c>
       <x:c r="K73" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.425330,31.177847</x:v>
       </x:c>
       <x:c r="L73" s="3" t="str">
+        <x:v>高德直线约 4.00 km</x:v>
+      </x:c>
+      <x:c r="M73" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%AE%9C%E5%B1%B1%E5%9B%AD1%E9%83%A8%20%E5%AE%9C%E5%B1%B1%E8%B7%AF655%E5%BC%841%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M73" s="3" t="str">
+      <x:c r="N73" s="3" t="str">
         <x:v>64854450 / 64362975</x:v>
       </x:c>
-      <x:c r="N73" s="3" t="str">
+      <x:c r="O73" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O73" s="3" t="n">
+      <x:c r="P73" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="P73" s="3" t="str">
+      <x:c r="Q73" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q73" s="3" t="str">
+      <x:c r="R73" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R73" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S73" s="3" t="str"/>
-      <x:c r="T73" s="3" t="str">
+      <x:c r="S73" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T73" s="3" t="str"/>
+      <x:c r="U73" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6014,37 +6233,40 @@
         <x:v>嘉陵路28号</x:v>
       </x:c>
       <x:c r="I74" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区科技幼儿园(嘉陵园)</x:v>
       </x:c>
       <x:c r="J74" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>嘉陵路28号</x:v>
       </x:c>
       <x:c r="K74" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.428986,31.149286</x:v>
       </x:c>
       <x:c r="L74" s="3" t="str">
+        <x:v>高德直线约 2.97 km</x:v>
+      </x:c>
+      <x:c r="M74" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%98%89%E9%99%B5%E5%9B%AD%20%E5%98%89%E9%99%B5%E8%B7%AF28%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M74" s="3" t="str">
+      <x:c r="N74" s="3" t="str">
         <x:v>54363003</x:v>
       </x:c>
-      <x:c r="N74" s="3" t="str">
+      <x:c r="O74" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O74" s="3" t="n">
+      <x:c r="P74" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="P74" s="3" t="str">
+      <x:c r="Q74" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q74" s="3" t="str">
+      <x:c r="R74" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R74" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S74" s="3" t="str"/>
-      <x:c r="T74" s="3" t="str">
+      <x:c r="S74" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T74" s="3" t="str"/>
+      <x:c r="U74" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6074,37 +6296,40 @@
         <x:v>文定路476号</x:v>
       </x:c>
       <x:c r="I75" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区科技幼儿园(文定园)</x:v>
       </x:c>
       <x:c r="J75" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>文定路476号</x:v>
       </x:c>
       <x:c r="K75" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.427762,31.180155</x:v>
       </x:c>
       <x:c r="L75" s="3" t="str">
+        <x:v>高德直线约 3.98 km</x:v>
+      </x:c>
+      <x:c r="M75" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%96%87%E5%AE%9A%E5%9B%AD%20%E6%96%87%E5%AE%9A%E8%B7%AF476%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M75" s="3" t="str">
+      <x:c r="N75" s="3" t="str">
         <x:v>64221181</x:v>
       </x:c>
-      <x:c r="N75" s="3" t="str">
+      <x:c r="O75" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O75" s="3" t="n">
+      <x:c r="P75" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="P75" s="3" t="str">
+      <x:c r="Q75" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q75" s="3" t="str">
+      <x:c r="R75" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R75" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S75" s="3" t="str"/>
-      <x:c r="T75" s="3" t="str">
+      <x:c r="S75" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T75" s="3" t="str"/>
+      <x:c r="U75" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6134,37 +6359,40 @@
         <x:v>宜山路655弄10号</x:v>
       </x:c>
       <x:c r="I76" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>徐汇区科技幼儿园宜山园</x:v>
       </x:c>
       <x:c r="J76" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>宜山路655弄10号</x:v>
       </x:c>
       <x:c r="K76" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.426582,31.175483</x:v>
       </x:c>
       <x:c r="L76" s="3" t="str">
+        <x:v>高德直线约 3.75 km</x:v>
+      </x:c>
+      <x:c r="M76" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%A7%91%E6%8A%80%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%AE%9C%E5%B1%B1%E5%9B%AD10%E9%83%A8%20%E5%AE%9C%E5%B1%B1%E8%B7%AF655%E5%BC%8410%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M76" s="3" t="str">
+      <x:c r="N76" s="3" t="str">
         <x:v>64854450 / 64362975</x:v>
       </x:c>
-      <x:c r="N76" s="3" t="str">
+      <x:c r="O76" s="3" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="O76" s="3" t="n">
+      <x:c r="P76" s="3" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="P76" s="3" t="str">
+      <x:c r="Q76" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q76" s="3" t="str">
+      <x:c r="R76" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R76" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S76" s="3" t="str"/>
-      <x:c r="T76" s="3" t="str">
+      <x:c r="S76" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T76" s="3" t="str"/>
+      <x:c r="U76" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6194,37 +6422,40 @@
         <x:v>瑞宁路816号</x:v>
       </x:c>
       <x:c r="I77" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区宛南实验幼儿园(瑞宁园)</x:v>
       </x:c>
       <x:c r="J77" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>瑞宁路816号(龙华中路地铁站5号口步行410米)</x:v>
       </x:c>
       <x:c r="K77" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.458813,31.181853</x:v>
       </x:c>
       <x:c r="L77" s="3" t="str">
+        <x:v>高德直线约 2.84 km</x:v>
+      </x:c>
+      <x:c r="M77" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%9B%E5%8D%97%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E7%91%9E%E5%AE%81%E9%83%A8%20%E7%91%9E%E5%AE%81%E8%B7%AF816%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M77" s="3" t="str">
+      <x:c r="N77" s="3" t="str">
         <x:v>64363606</x:v>
       </x:c>
-      <x:c r="N77" s="3" t="str">
+      <x:c r="O77" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="O77" s="3" t="n">
+      <x:c r="P77" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P77" s="3" t="str">
+      <x:c r="Q77" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q77" s="3" t="str">
+      <x:c r="R77" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R77" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S77" s="3" t="str"/>
-      <x:c r="T77" s="3" t="str">
+      <x:c r="S77" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T77" s="3" t="str"/>
+      <x:c r="U77" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6254,37 +6485,40 @@
         <x:v>瑞宁路851号</x:v>
       </x:c>
       <x:c r="I78" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区宛南实验幼儿园(滨江部)</x:v>
       </x:c>
       <x:c r="J78" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>瑞宁路851号</x:v>
       </x:c>
       <x:c r="K78" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.460808,31.181252</x:v>
       </x:c>
       <x:c r="L78" s="3" t="str">
+        <x:v>高德直线约 2.77 km</x:v>
+      </x:c>
+      <x:c r="M78" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%9B%E5%8D%97%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%BB%A8%E6%B1%9F%E9%83%A8%20%E7%91%9E%E5%AE%81%E8%B7%AF851%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M78" s="3" t="str">
+      <x:c r="N78" s="3" t="str">
         <x:v>64161261</x:v>
       </x:c>
-      <x:c r="N78" s="3" t="str">
+      <x:c r="O78" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="O78" s="3" t="n">
+      <x:c r="P78" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P78" s="3" t="str">
+      <x:c r="Q78" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q78" s="3" t="str">
+      <x:c r="R78" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R78" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S78" s="3" t="str"/>
-      <x:c r="T78" s="3" t="str">
+      <x:c r="S78" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T78" s="3" t="str"/>
+      <x:c r="U78" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6314,37 +6548,40 @@
         <x:v>大木桥路323号</x:v>
       </x:c>
       <x:c r="I79" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区宛南实验幼儿园(大木桥部)</x:v>
       </x:c>
       <x:c r="J79" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>大木桥路323号(大木桥路地铁站4号口步行340米)</x:v>
       </x:c>
       <x:c r="K79" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.462978,31.197281</x:v>
       </x:c>
       <x:c r="L79" s="3" t="str">
+        <x:v>高德直线约 4.57 km</x:v>
+      </x:c>
+      <x:c r="M79" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%9B%E5%8D%97%E5%AE%9E%E9%AA%8C%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%A4%A7%E6%9C%A8%E6%A1%A5%E9%83%A8%20%E5%A4%A7%E6%9C%A8%E6%A1%A5%E8%B7%AF323%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M79" s="3" t="str">
+      <x:c r="N79" s="3" t="str">
         <x:v>64168714</x:v>
       </x:c>
-      <x:c r="N79" s="3" t="str">
+      <x:c r="O79" s="3" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="O79" s="3" t="n">
+      <x:c r="P79" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P79" s="3" t="str">
+      <x:c r="Q79" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q79" s="3" t="str">
+      <x:c r="R79" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R79" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S79" s="3" t="str"/>
-      <x:c r="T79" s="3" t="str">
+      <x:c r="S79" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T79" s="3" t="str"/>
+      <x:c r="U79" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6374,37 +6611,40 @@
         <x:v>建国西路570号</x:v>
       </x:c>
       <x:c r="I80" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区机关建国幼儿园(建国园)</x:v>
       </x:c>
       <x:c r="J80" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>建国西路570号(肇嘉浜路地铁站2号口步行420米)</x:v>
       </x:c>
       <x:c r="K80" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.450074,31.202785</x:v>
       </x:c>
       <x:c r="L80" s="3" t="str">
+        <x:v>高德直线约 5.24 km</x:v>
+      </x:c>
+      <x:c r="M80" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%BA%E5%85%B3%E5%BB%BA%E5%9B%BD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%BB%BA%E5%9B%BD%E5%9B%AD%20%E5%BB%BA%E5%9B%BD%E8%A5%BF%E8%B7%AF570%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M80" s="3" t="str">
+      <x:c r="N80" s="3" t="str">
         <x:v>64372841</x:v>
       </x:c>
-      <x:c r="N80" s="3" t="str">
+      <x:c r="O80" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O80" s="3" t="n">
+      <x:c r="P80" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P80" s="3" t="str">
+      <x:c r="Q80" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q80" s="3" t="str">
+      <x:c r="R80" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R80" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S80" s="3" t="str"/>
-      <x:c r="T80" s="3" t="str">
+      <x:c r="S80" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T80" s="3" t="str"/>
+      <x:c r="U80" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6434,37 +6674,40 @@
         <x:v>安亭路112号</x:v>
       </x:c>
       <x:c r="I81" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区机关建国幼儿园(安亭园)</x:v>
       </x:c>
       <x:c r="J81" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>安亭路112号(衡山路地铁站1号口步行320米)</x:v>
       </x:c>
       <x:c r="K81" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.447497,31.202392</x:v>
       </x:c>
       <x:c r="L81" s="3" t="str">
+        <x:v>高德直线约 5.24 km</x:v>
+      </x:c>
+      <x:c r="M81" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%BA%E5%85%B3%E5%BB%BA%E5%9B%BD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%AE%89%E4%BA%AD%E5%9B%AD%20%E5%AE%89%E4%BA%AD%E8%B7%AF112%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M81" s="3" t="str">
+      <x:c r="N81" s="3" t="str">
         <x:v>64333332</x:v>
       </x:c>
-      <x:c r="N81" s="3" t="str">
+      <x:c r="O81" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O81" s="3" t="n">
+      <x:c r="P81" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P81" s="3" t="str">
+      <x:c r="Q81" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q81" s="3" t="str">
+      <x:c r="R81" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R81" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S81" s="3" t="str"/>
-      <x:c r="T81" s="3" t="str">
+      <x:c r="S81" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T81" s="3" t="str"/>
+      <x:c r="U81" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6494,37 +6737,40 @@
         <x:v>云锦路183弄30号</x:v>
       </x:c>
       <x:c r="I82" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区机关建国幼儿园(滨江园)</x:v>
       </x:c>
       <x:c r="J82" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>云锦路183弄30号</x:v>
       </x:c>
       <x:c r="K82" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.459526,31.173173</x:v>
       </x:c>
       <x:c r="L82" s="3" t="str">
+        <x:v>高德直线约 1.87 km</x:v>
+      </x:c>
+      <x:c r="M82" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9C%BA%E5%85%B3%E5%BB%BA%E5%9B%BD%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%BB%A8%E6%B1%9F%E5%9B%AD%20%E4%BA%91%E9%94%A6%E8%B7%AF183%E5%BC%8430%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M82" s="3" t="str">
+      <x:c r="N82" s="3" t="str">
         <x:v>54252106</x:v>
       </x:c>
-      <x:c r="N82" s="3" t="str">
+      <x:c r="O82" s="3" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="O82" s="3" t="n">
+      <x:c r="P82" s="3" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="P82" s="3" t="str">
+      <x:c r="Q82" s="3" t="str">
         <x:v>区域内自主招生</x:v>
       </x:c>
-      <x:c r="Q82" s="3" t="str">
+      <x:c r="R82" s="3" t="str">
         <x:v>区域自主</x:v>
       </x:c>
-      <x:c r="R82" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
-      <x:c r="S82" s="3" t="str"/>
-      <x:c r="T82" s="3" t="str">
+      <x:c r="S82" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T82" s="3" t="str"/>
+      <x:c r="U82" s="3" t="str">
         <x:v>上海本地宝《2026徐汇区幼儿园招生对口地段及招生计划班级数》，2026-04-15：https://m.sh.bendibao.com/edu/305291.html；上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6554,39 +6800,42 @@
         <x:v>桂林西街9弄57号</x:v>
       </x:c>
       <x:c r="I83" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区杜鹃园幼稚园</x:v>
       </x:c>
       <x:c r="J83" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>桂林西街9弄57号</x:v>
       </x:c>
       <x:c r="K83" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.418245,31.156567</x:v>
       </x:c>
       <x:c r="L83" s="3" t="str">
+        <x:v>高德直线约 3.88 km</x:v>
+      </x:c>
+      <x:c r="M83" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9D%9C%E9%B9%83%E5%9B%AD%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%82%E6%9E%97%E8%A5%BF%E8%A1%979%E5%BC%8457%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M83" s="3" t="str">
+      <x:c r="N83" s="3" t="str">
         <x:v>021-54202188</x:v>
-      </x:c>
-      <x:c r="N83" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O83" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P83" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q83" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q83" s="3" t="str">
+      <x:c r="R83" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R83" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S83" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T83" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T83" s="3" t="str">
+      <x:c r="U83" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6616,39 +6865,42 @@
         <x:v>丰谷路205弄35号</x:v>
       </x:c>
       <x:c r="I84" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办胡姬港湾幼儿园</x:v>
       </x:c>
       <x:c r="J84" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>云锦路80弄10号(龙华地铁站5号口步行3分钟)</x:v>
       </x:c>
       <x:c r="K84" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.456122,31.173426</x:v>
       </x:c>
       <x:c r="L84" s="3" t="str">
+        <x:v>高德直线约 1.92 km</x:v>
+      </x:c>
+      <x:c r="M84" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%83%A1%E5%A7%AC%E6%B8%AF%E6%B9%BE%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B8%B0%E8%B0%B7%E8%B7%AF205%E5%BC%8435%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M84" s="3" t="str">
+      <x:c r="N84" s="3" t="str">
         <x:v>64560614</x:v>
-      </x:c>
-      <x:c r="N84" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O84" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P84" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q84" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q84" s="3" t="str">
+      <x:c r="R84" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R84" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S84" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T84" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T84" s="3" t="str">
+      <x:c r="U84" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6678,39 +6930,42 @@
         <x:v>百色路汇城五村75号</x:v>
       </x:c>
       <x:c r="I85" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区汇城苑幼稚园</x:v>
       </x:c>
       <x:c r="J85" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>百色路汇成五村75号</x:v>
       </x:c>
       <x:c r="K85" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.435948,31.142137</x:v>
       </x:c>
       <x:c r="L85" s="3" t="str">
+        <x:v>高德直线约 2.71 km</x:v>
+      </x:c>
+      <x:c r="M85" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%9F%8E%E8%8B%91%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%99%BE%E8%89%B2%E8%B7%AF%E6%B1%87%E5%9F%8E%E4%BA%94%E6%9D%9175%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M85" s="3" t="str">
+      <x:c r="N85" s="3" t="str">
         <x:v>64235119</x:v>
-      </x:c>
-      <x:c r="N85" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O85" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P85" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q85" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q85" s="3" t="str">
+      <x:c r="R85" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R85" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S85" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T85" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T85" s="3" t="str">
+      <x:c r="U85" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
@@ -6749,30 +7004,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L86" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M86" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%BB%B4%E4%BA%9A%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8D%8E%E4%BA%AD%E8%B7%AF71%E5%BC%841%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M86" s="3" t="str">
+      <x:c r="N86" s="3" t="str">
         <x:v>54036901</x:v>
-      </x:c>
-      <x:c r="N86" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O86" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P86" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q86" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q86" s="3" t="str">
+      <x:c r="R86" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R86" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S86" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T86" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T86" s="3" t="str">
+      <x:c r="U86" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6802,39 +7060,42 @@
         <x:v>五原路112号</x:v>
       </x:c>
       <x:c r="I87" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办四季方馨幼儿园</x:v>
       </x:c>
       <x:c r="J87" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>五原路112号(常熟路地铁站8号口步行260米)</x:v>
       </x:c>
       <x:c r="K87" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.446789,31.213302</x:v>
       </x:c>
       <x:c r="L87" s="3" t="str">
+        <x:v>高德直线约 6.44 km</x:v>
+      </x:c>
+      <x:c r="M87" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9B%9B%E5%AD%A3%E6%96%B9%E9%A6%A8%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%BA%94%E5%8E%9F%E8%B7%AF112%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M87" s="3" t="str">
+      <x:c r="N87" s="3" t="str">
         <x:v>021-54036603</x:v>
-      </x:c>
-      <x:c r="N87" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O87" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P87" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q87" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q87" s="3" t="str">
+      <x:c r="R87" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R87" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S87" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T87" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T87" s="3" t="str">
+      <x:c r="U87" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6873,30 +7134,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L88" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M88" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BB%A8%E6%B1%9F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%BA%91%E9%94%A6%E8%B7%AF80%E5%BC%8410%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M88" s="3" t="str">
+      <x:c r="N88" s="3" t="str">
         <x:v>64380700</x:v>
-      </x:c>
-      <x:c r="N88" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O88" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P88" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q88" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q88" s="3" t="str">
+      <x:c r="R88" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R88" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S88" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T88" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T88" s="3" t="str">
+      <x:c r="U88" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6926,39 +7190,42 @@
         <x:v>宛平南路592号</x:v>
       </x:c>
       <x:c r="I89" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海汇宝幼儿园</x:v>
       </x:c>
       <x:c r="J89" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>零陵路与宛平南路交叉口西40米</x:v>
       </x:c>
       <x:c r="K89" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.448494,31.188588</x:v>
       </x:c>
       <x:c r="L89" s="3" t="str">
+        <x:v>高德直线约 3.72 km</x:v>
+      </x:c>
+      <x:c r="M89" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B1%87%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9B%E5%B9%B3%E5%8D%97%E8%B7%AF592%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M89" s="3" t="str">
+      <x:c r="N89" s="3" t="str">
         <x:v>64690445</x:v>
-      </x:c>
-      <x:c r="N89" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O89" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P89" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q89" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q89" s="3" t="str">
+      <x:c r="R89" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R89" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S89" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T89" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T89" s="3" t="str">
+      <x:c r="U89" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -6997,30 +7264,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L90" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M90" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%92%99%E4%B8%96%E5%AD%A6%E5%A0%82%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%96%9C%E5%9C%9F%E8%B7%AF2421%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M90" s="3" t="str">
+      <x:c r="N90" s="3" t="str">
         <x:v>021-64686261*8103</x:v>
-      </x:c>
-      <x:c r="N90" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O90" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P90" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q90" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q90" s="3" t="str">
+      <x:c r="R90" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R90" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S90" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T90" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T90" s="3" t="str">
+      <x:c r="U90" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7059,30 +7329,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L91" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M91" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%A8%B1%E8%8A%B1%E5%9B%AD%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%99%BE%E8%8A%B1%E8%A1%97380%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M91" s="3" t="str">
+      <x:c r="N91" s="3" t="str">
         <x:v>54185106</x:v>
-      </x:c>
-      <x:c r="N91" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O91" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P91" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q91" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q91" s="3" t="str">
+      <x:c r="R91" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R91" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S91" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T91" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T91" s="3" t="str">
+      <x:c r="U91" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7121,30 +7394,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L92" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M92" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%96%B0%E5%AE%9C%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E5%AE%9C%E8%B7%AF170%E5%BC%847%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M92" s="3" t="str">
+      <x:c r="N92" s="3" t="str">
         <x:v>64684874</x:v>
-      </x:c>
-      <x:c r="N92" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O92" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P92" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q92" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q92" s="3" t="str">
+      <x:c r="R92" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R92" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S92" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T92" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T92" s="3" t="str">
+      <x:c r="U92" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7183,30 +7459,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L93" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M93" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%93%93%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%92%B2%E6%B1%9F%E5%A1%98%E8%B7%AF50%E5%8F%B7%E7%8E%89%E5%85%B0%E8%8A%B1%E8%8B%916%E5%B9%A2</x:v>
       </x:c>
-      <x:c r="M93" s="3" t="str">
+      <x:c r="N93" s="3" t="str">
         <x:v>64647491</x:v>
-      </x:c>
-      <x:c r="N93" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O93" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P93" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q93" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q93" s="3" t="str">
+      <x:c r="R93" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R93" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S93" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T93" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T93" s="3" t="str">
+      <x:c r="U93" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7236,39 +7515,42 @@
         <x:v>天钥桥路380弄11号</x:v>
       </x:c>
       <x:c r="I94" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区蓓蕾幼稚园</x:v>
       </x:c>
       <x:c r="J94" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>蒲汇塘路50号6幢(上海体育馆地铁站8号口步行400米)</x:v>
       </x:c>
       <x:c r="K94" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.434989,31.185300</x:v>
       </x:c>
       <x:c r="L94" s="3" t="str">
+        <x:v>高德直线约 3.95 km</x:v>
+      </x:c>
+      <x:c r="M94" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%93%93%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E8%B7%AF380%E5%BC%8411%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M94" s="3" t="str">
+      <x:c r="N94" s="3" t="str">
         <x:v>64647491</x:v>
-      </x:c>
-      <x:c r="N94" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O94" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P94" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q94" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q94" s="3" t="str">
+      <x:c r="R94" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R94" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S94" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T94" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T94" s="3" t="str">
+      <x:c r="U94" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7298,39 +7580,42 @@
         <x:v>浦北路50号</x:v>
       </x:c>
       <x:c r="I95" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海淇莲幼儿园</x:v>
       </x:c>
       <x:c r="J95" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>浦北路50号</x:v>
       </x:c>
       <x:c r="K95" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.425938,31.158260</x:v>
       </x:c>
       <x:c r="L95" s="3" t="str">
+        <x:v>高德直线约 3.16 km</x:v>
+      </x:c>
+      <x:c r="M95" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B7%87%E8%8E%B2%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B5%A6%E5%8C%97%E8%B7%AF50%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M95" s="3" t="str">
+      <x:c r="N95" s="3" t="str">
         <x:v>54669909</x:v>
-      </x:c>
-      <x:c r="N95" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O95" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P95" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q95" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q95" s="3" t="str">
+      <x:c r="R95" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R95" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S95" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T95" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T95" s="3" t="str">
+      <x:c r="U95" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7369,30 +7654,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L96" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M96" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E8%A1%97%E9%81%93%E4%B8%AD%E5%BF%83%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%85%AD%E6%9D%9110%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M96" s="3" t="str">
+      <x:c r="N96" s="3" t="str">
         <x:v>64705223</x:v>
-      </x:c>
-      <x:c r="N96" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O96" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P96" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q96" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q96" s="3" t="str">
+      <x:c r="R96" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R96" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S96" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T96" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T96" s="3" t="str">
+      <x:c r="U96" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7422,39 +7710,42 @@
         <x:v>浦北路21弄42号</x:v>
       </x:c>
       <x:c r="I97" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办胡姬港湾新汇幼儿园</x:v>
       </x:c>
       <x:c r="J97" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>浦北路21弄42号</x:v>
       </x:c>
       <x:c r="K97" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.426513,31.156689</x:v>
       </x:c>
       <x:c r="L97" s="3" t="str">
+        <x:v>高德直线约 3.09 km</x:v>
+      </x:c>
+      <x:c r="M97" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%83%A1%E5%A7%AC%E6%B8%AF%E6%B9%BE%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B5%A6%E5%8C%97%E8%B7%AF21%E5%BC%8442%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M97" s="3" t="str">
+      <x:c r="N97" s="3" t="str">
         <x:v>54669810</x:v>
-      </x:c>
-      <x:c r="N97" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O97" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P97" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q97" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q97" s="3" t="str">
+      <x:c r="R97" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R97" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S97" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T97" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T97" s="3" t="str">
+      <x:c r="U97" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7493,30 +7784,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L98" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M98" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%B0%8F%E7%A5%9E%E7%AB%A5%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%90%B4%E8%B7%AF988%E5%BC%8425%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M98" s="3" t="str">
+      <x:c r="N98" s="3" t="str">
         <x:v>021-54360296</x:v>
-      </x:c>
-      <x:c r="N98" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O98" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P98" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q98" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q98" s="3" t="str">
+      <x:c r="R98" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R98" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S98" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T98" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T98" s="3" t="str">
+      <x:c r="U98" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7555,30 +7849,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L99" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M99" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%AE%89%E7%90%AA%E6%9B%88%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%A1%A1%E5%B1%B1%E8%B7%AF9%E5%BC%842%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M99" s="3" t="str">
+      <x:c r="N99" s="3" t="str">
         <x:v>64665309</x:v>
-      </x:c>
-      <x:c r="N99" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O99" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P99" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q99" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q99" s="3" t="str">
+      <x:c r="R99" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R99" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S99" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T99" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T99" s="3" t="str">
+      <x:c r="U99" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7608,39 +7905,42 @@
         <x:v>宛南一村23号</x:v>
       </x:c>
       <x:c r="I100" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区鲁浦幼儿园</x:v>
       </x:c>
       <x:c r="J100" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>宛南一村23号</x:v>
       </x:c>
       <x:c r="K100" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.449968,31.183733</x:v>
       </x:c>
       <x:c r="L100" s="3" t="str">
+        <x:v>高德直线约 3.17 km</x:v>
+      </x:c>
+      <x:c r="M100" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%B2%81%E6%B5%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9B%E5%8D%97%E4%B8%80%E6%9D%9123%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M100" s="3" t="str">
+      <x:c r="N100" s="3" t="str">
         <x:v>64384206</x:v>
-      </x:c>
-      <x:c r="N100" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O100" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P100" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q100" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q100" s="3" t="str">
+      <x:c r="R100" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R100" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S100" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T100" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T100" s="3" t="str">
+      <x:c r="U100" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7679,30 +7979,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L101" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M101" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%B2%81%E6%B5%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E5%AE%9B%E5%8D%97%E4%BA%94%E6%9D%911%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M101" s="3" t="str">
+      <x:c r="N101" s="3" t="str">
         <x:v>64384206</x:v>
-      </x:c>
-      <x:c r="N101" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O101" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P101" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q101" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q101" s="3" t="str">
+      <x:c r="R101" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R101" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S101" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T101" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T101" s="3" t="str">
+      <x:c r="U101" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7741,30 +8044,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L102" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M102" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%BA%B7%E6%96%87%E4%BA%91%E9%94%A6%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%85%B0%E8%B7%AF398%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M102" s="3" t="str">
+      <x:c r="N102" s="3" t="str">
         <x:v>64282682</x:v>
-      </x:c>
-      <x:c r="N102" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O102" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P102" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q102" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q102" s="3" t="str">
+      <x:c r="R102" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R102" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S102" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T102" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T102" s="3" t="str">
+      <x:c r="U102" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7794,39 +8100,42 @@
         <x:v>古羊路160号1幢</x:v>
       </x:c>
       <x:c r="I103" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海爱文幼儿园</x:v>
       </x:c>
       <x:c r="J103" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>古羊路160号</x:v>
       </x:c>
       <x:c r="K103" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.415415,31.191313</x:v>
       </x:c>
       <x:c r="L103" s="3" t="str">
+        <x:v>高德直线约 5.69 km</x:v>
+      </x:c>
+      <x:c r="M103" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E6%96%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8F%A4%E7%BE%8A%E8%B7%AF160%E5%8F%B71%E5%B9%A2</x:v>
       </x:c>
-      <x:c r="M103" s="3" t="str">
+      <x:c r="N103" s="3" t="str">
         <x:v>021-62090135</x:v>
-      </x:c>
-      <x:c r="N103" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O103" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P103" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q103" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q103" s="3" t="str">
+      <x:c r="R103" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R103" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S103" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T103" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T103" s="3" t="str">
+      <x:c r="U103" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7856,39 +8165,42 @@
         <x:v>淮海西路365弄2号楼、3号楼</x:v>
       </x:c>
       <x:c r="I104" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办童稻幼儿园</x:v>
       </x:c>
       <x:c r="J104" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>淮海西路365弄2号楼、3号楼</x:v>
       </x:c>
       <x:c r="K104" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.423919,31.197101</x:v>
       </x:c>
       <x:c r="L104" s="3" t="str">
+        <x:v>高德直线约 5.63 km</x:v>
+      </x:c>
+      <x:c r="M104" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%AB%A5%E7%A8%BB%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B7%AE%E6%B5%B7%E8%A5%BF%E8%B7%AF365%E5%BC%842%E5%8F%B7%E6%A5%BC%E3%80%813%E5%8F%B7%E6%A5%BC</x:v>
       </x:c>
-      <x:c r="M104" s="3" t="str">
+      <x:c r="N104" s="3" t="str">
         <x:v>52668270</x:v>
-      </x:c>
-      <x:c r="N104" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O104" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P104" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q104" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q104" s="3" t="str">
+      <x:c r="R104" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R104" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S104" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T104" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T104" s="3" t="str">
+      <x:c r="U104" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7918,39 +8230,42 @@
         <x:v>吴兴路75号</x:v>
       </x:c>
       <x:c r="I105" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办嘉宝幼儿园</x:v>
       </x:c>
       <x:c r="J105" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>吴兴路75号(衡山路地铁站2号口步行480米)</x:v>
       </x:c>
       <x:c r="K105" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.443884,31.203510</x:v>
       </x:c>
       <x:c r="L105" s="3" t="str">
+        <x:v>高德直线约 5.44 km</x:v>
+      </x:c>
+      <x:c r="M105" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%98%89%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%90%B4%E5%85%B4%E8%B7%AF75%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M105" s="3" t="str">
+      <x:c r="N105" s="3" t="str">
         <x:v>64373773</x:v>
-      </x:c>
-      <x:c r="N105" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O105" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P105" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q105" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q105" s="3" t="str">
+      <x:c r="R105" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R105" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S105" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T105" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T105" s="3" t="str">
+      <x:c r="U105" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -7980,39 +8295,42 @@
         <x:v>龙吟路300号</x:v>
       </x:c>
       <x:c r="I106" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办金贝贝幼儿园</x:v>
       </x:c>
       <x:c r="J106" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>龙吟路300号</x:v>
       </x:c>
       <x:c r="K106" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.452622,31.114943</x:v>
       </x:c>
       <x:c r="L106" s="3" t="str">
+        <x:v>高德直线约 4.65 km</x:v>
+      </x:c>
+      <x:c r="M106" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%87%91%E8%B4%9D%E8%B4%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%90%9F%E8%B7%AF300%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M106" s="3" t="str">
+      <x:c r="N106" s="3" t="str">
         <x:v>54820000</x:v>
-      </x:c>
-      <x:c r="N106" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O106" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P106" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q106" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q106" s="3" t="str">
+      <x:c r="R106" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R106" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S106" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T106" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T106" s="3" t="str">
+      <x:c r="U106" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8051,30 +8369,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L107" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M107" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%96%E7%BA%AA%E6%98%82%E7%AB%8B%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E9%BE%99%E5%B1%B1%E6%96%B0%E6%9D%91115%E5%8F%B7%EF%BC%88%E8%BF%91%E9%9B%B6%E9%99%B5%E8%B7%AF%EF%BC%89</x:v>
       </x:c>
-      <x:c r="M107" s="3" t="str">
+      <x:c r="N107" s="3" t="str">
         <x:v>54890979 / 64382277</x:v>
-      </x:c>
-      <x:c r="N107" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O107" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P107" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q107" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q107" s="3" t="str">
+      <x:c r="R107" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R107" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S107" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T107" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T107" s="3" t="str">
+      <x:c r="U107" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8104,39 +8425,42 @@
         <x:v>复兴西路70号</x:v>
       </x:c>
       <x:c r="I108" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办爱菊幼儿园</x:v>
       </x:c>
       <x:c r="J108" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>复兴西路70号</x:v>
       </x:c>
       <x:c r="K108" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.443406,31.210887</x:v>
       </x:c>
       <x:c r="L108" s="3" t="str">
+        <x:v>高德直线约 6.25 km</x:v>
+      </x:c>
+      <x:c r="M108" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E8%8F%8A%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%8D%E5%85%B4%E8%A5%BF%E8%B7%AF70%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M108" s="3" t="str">
+      <x:c r="N108" s="3" t="str">
         <x:v>64043162</x:v>
-      </x:c>
-      <x:c r="N108" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O108" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P108" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q108" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q108" s="3" t="str">
+      <x:c r="R108" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R108" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S108" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T108" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T108" s="3" t="str">
+      <x:c r="U108" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8166,39 +8490,42 @@
         <x:v>梅陇三村49号</x:v>
       </x:c>
       <x:c r="I109" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海市徐汇区培蕾幼稚园</x:v>
       </x:c>
       <x:c r="J109" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>梅陇三村49号</x:v>
       </x:c>
       <x:c r="K109" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.417425,31.135875</x:v>
       </x:c>
       <x:c r="L109" s="3" t="str">
+        <x:v>高德直线约 4.57 km</x:v>
+      </x:c>
+      <x:c r="M109" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9F%B9%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E4%B8%89%E6%9D%9149%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M109" s="3" t="str">
+      <x:c r="N109" s="3" t="str">
         <x:v>64768480</x:v>
-      </x:c>
-      <x:c r="N109" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O109" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P109" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q109" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q109" s="3" t="str">
+      <x:c r="R109" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R109" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S109" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T109" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T109" s="3" t="str">
+      <x:c r="U109" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8237,30 +8564,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L110" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M110" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%9F%B9%E8%95%BE%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E5%88%86%E5%9B%AD%20%E6%A2%85%E9%99%87%E5%85%AD%E6%9D%9141%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M110" s="3" t="str">
+      <x:c r="N110" s="3" t="str">
         <x:v>64767077</x:v>
-      </x:c>
-      <x:c r="N110" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O110" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P110" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q110" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q110" s="3" t="str">
+      <x:c r="R110" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R110" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S110" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T110" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T110" s="3" t="str">
+      <x:c r="U110" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8290,39 +8620,42 @@
         <x:v>太原路87号</x:v>
       </x:c>
       <x:c r="I111" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海枫叶交响幼儿园</x:v>
       </x:c>
       <x:c r="J111" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>太原路87号</x:v>
       </x:c>
       <x:c r="K111" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.454991,31.207756</x:v>
       </x:c>
       <x:c r="L111" s="3" t="str">
+        <x:v>高德直线约 5.73 km</x:v>
+      </x:c>
+      <x:c r="M111" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%9E%AB%E5%8F%B6%E4%BA%A4%E5%93%8D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%AA%E5%8E%9F%E8%B7%AF87%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M111" s="3" t="str">
+      <x:c r="N111" s="3" t="str">
         <x:v>64730053</x:v>
-      </x:c>
-      <x:c r="N111" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O111" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P111" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q111" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q111" s="3" t="str">
+      <x:c r="R111" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R111" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S111" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T111" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T111" s="3" t="str">
+      <x:c r="U111" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8352,39 +8685,42 @@
         <x:v>田林十一村36号</x:v>
       </x:c>
       <x:c r="I112" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办泰宁田林幼儿园</x:v>
       </x:c>
       <x:c r="J112" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>田林十一村36号</x:v>
       </x:c>
       <x:c r="K112" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.426535,31.171256</x:v>
       </x:c>
       <x:c r="L112" s="3" t="str">
+        <x:v>高德直线约 3.51 km</x:v>
+      </x:c>
+      <x:c r="M112" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%B3%B0%E5%AE%81%E7%94%B0%E6%9E%97%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%94%B0%E6%9E%97%E5%8D%81%E4%B8%80%E6%9D%9136%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M112" s="3" t="str">
+      <x:c r="N112" s="3" t="str">
         <x:v>64755118-804</x:v>
-      </x:c>
-      <x:c r="N112" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O112" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P112" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q112" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q112" s="3" t="str">
+      <x:c r="R112" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R112" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S112" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T112" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T112" s="3" t="str">
+      <x:c r="U112" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8414,39 +8750,42 @@
         <x:v>宜山路田林十四村27号</x:v>
       </x:c>
       <x:c r="I113" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办田林东方幼儿园</x:v>
       </x:c>
       <x:c r="J113" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>田林十四村27号</x:v>
       </x:c>
       <x:c r="K113" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.423893,31.176131</x:v>
       </x:c>
       <x:c r="L113" s="3" t="str">
+        <x:v>高德直线约 4.00 km</x:v>
+      </x:c>
+      <x:c r="M113" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%94%B0%E6%9E%97%E4%B8%9C%E6%96%B9%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%AE%9C%E5%B1%B1%E8%B7%AF%E7%94%B0%E6%9E%97%E5%8D%81%E5%9B%9B%E6%9D%9127%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M113" s="3" t="str">
+      <x:c r="N113" s="3" t="str">
         <x:v>021-64085912</x:v>
-      </x:c>
-      <x:c r="N113" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O113" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P113" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q113" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q113" s="3" t="str">
+      <x:c r="R113" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R113" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S113" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T113" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T113" s="3" t="str">
+      <x:c r="U113" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8476,39 +8815,42 @@
         <x:v>永嘉路356弄31号</x:v>
       </x:c>
       <x:c r="I114" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办澳宝幼儿园</x:v>
       </x:c>
       <x:c r="J114" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>永嘉路356弄31号</x:v>
       </x:c>
       <x:c r="K114" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.456483,31.209345</x:v>
       </x:c>
       <x:c r="L114" s="3" t="str">
+        <x:v>高德直线约 5.90 km</x:v>
+      </x:c>
+      <x:c r="M114" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BE%B3%E5%AE%9D%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B0%B8%E5%98%89%E8%B7%AF356%E5%BC%8431%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M114" s="3" t="str">
+      <x:c r="N114" s="3" t="str">
         <x:v>64720200</x:v>
-      </x:c>
-      <x:c r="N114" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O114" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P114" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q114" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q114" s="3" t="str">
+      <x:c r="R114" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R114" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S114" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T114" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T114" s="3" t="str">
+      <x:c r="U114" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8547,30 +8889,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L115" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M115" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E5%B0%8F%E8%9C%BB%E8%9C%93%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E8%99%B9%E6%A2%85%E8%B7%AF1035%E5%BC%8430%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M115" s="3" t="str">
+      <x:c r="N115" s="3" t="str">
         <x:v>64368108</x:v>
-      </x:c>
-      <x:c r="N115" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O115" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P115" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q115" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q115" s="3" t="str">
+      <x:c r="R115" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R115" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S115" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T115" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T115" s="3" t="str">
+      <x:c r="U115" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8609,30 +8954,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L116" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M116" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%9C%E6%B3%89%E5%A4%A7%E5%9C%B0%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B8%9C%E6%B3%89%E8%B7%AF65%E5%BC%849%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M116" s="3" t="str">
+      <x:c r="N116" s="3" t="str">
         <x:v>54084130</x:v>
-      </x:c>
-      <x:c r="N116" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O116" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P116" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q116" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q116" s="3" t="str">
+      <x:c r="R116" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R116" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S116" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T116" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T116" s="3" t="str">
+      <x:c r="U116" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8662,39 +9010,42 @@
         <x:v>小木桥路101弄20号</x:v>
       </x:c>
       <x:c r="I117" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办吉的堡新徐汇幼儿园</x:v>
       </x:c>
       <x:c r="J117" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>小木桥路101弄20号</x:v>
       </x:c>
       <x:c r="K117" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.457939,31.199425</x:v>
       </x:c>
       <x:c r="L117" s="3" t="str">
+        <x:v>高德直线约 4.79 km</x:v>
+      </x:c>
+      <x:c r="M117" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E6%96%B0%E5%BE%90%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%B0%8F%E6%9C%A8%E6%A1%A5%E8%B7%AF101%E5%BC%8420%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M117" s="3" t="str">
+      <x:c r="N117" s="3" t="str">
         <x:v>021-54245100</x:v>
-      </x:c>
-      <x:c r="N117" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O117" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P117" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q117" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q117" s="3" t="str">
+      <x:c r="R117" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R117" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S117" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T117" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T117" s="3" t="str">
+      <x:c r="U117" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8733,30 +9084,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L118" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M118" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%88%B1%E6%82%A0%E5%B0%8F%E7%BA%A2%E8%8A%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E8%B7%AF130%E5%8F%B71%E5%B9%A2%E3%80%812%E5%B9%A2</x:v>
       </x:c>
-      <x:c r="M118" s="3" t="str">
+      <x:c r="N118" s="3" t="str">
         <x:v>021-54333289</x:v>
-      </x:c>
-      <x:c r="N118" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O118" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P118" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q118" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q118" s="3" t="str">
+      <x:c r="R118" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R118" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S118" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T118" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T118" s="3" t="str">
+      <x:c r="U118" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8786,39 +9140,42 @@
         <x:v>桃江路42号</x:v>
       </x:c>
       <x:c r="I119" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海中山幼儿园</x:v>
       </x:c>
       <x:c r="J119" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>桃江路42号(上海图书馆地铁站2号口步行450米)</x:v>
       </x:c>
       <x:c r="K119" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.448321,31.209534</x:v>
       </x:c>
       <x:c r="L119" s="3" t="str">
+        <x:v>高德直线约 6.00 km</x:v>
+      </x:c>
+      <x:c r="M119" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%AD%E5%B1%B1%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A1%83%E6%B1%9F%E8%B7%AF42%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M119" s="3" t="str">
+      <x:c r="N119" s="3" t="str">
         <x:v>021-33565515</x:v>
-      </x:c>
-      <x:c r="N119" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O119" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P119" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q119" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q119" s="3" t="str">
+      <x:c r="R119" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R119" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S119" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T119" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T119" s="3" t="str">
+      <x:c r="U119" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8857,30 +9214,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L120" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M120" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%88%9B%E6%84%8F%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%9F%B3%E5%B7%9E%E8%B7%AF%E7%94%B0%E6%9E%97%E5%8D%81%E6%9D%916%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M120" s="3" t="str">
+      <x:c r="N120" s="3" t="str">
         <x:v>64828813 / 64820881</x:v>
-      </x:c>
-      <x:c r="N120" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O120" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P120" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q120" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q120" s="3" t="str">
+      <x:c r="R120" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R120" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S120" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T120" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T120" s="3" t="str">
+      <x:c r="U120" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8910,39 +9270,42 @@
         <x:v>罗城路700弄95号</x:v>
       </x:c>
       <x:c r="I121" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>徐汇区牛牛幼稚园(南门)</x:v>
       </x:c>
       <x:c r="J121" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>罗城路700弄95号</x:v>
       </x:c>
       <x:c r="K121" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.433333,31.149958</x:v>
       </x:c>
       <x:c r="L121" s="3" t="str">
+        <x:v>高德直线约 2.55 km</x:v>
+      </x:c>
+      <x:c r="M121" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E7%89%9B%E7%89%9B%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E7%BD%97%E5%9F%8E%E8%B7%AF700%E5%BC%8495%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M121" s="3" t="str">
+      <x:c r="N121" s="3" t="str">
         <x:v>54115988</x:v>
-      </x:c>
-      <x:c r="N121" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O121" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P121" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q121" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q121" s="3" t="str">
+      <x:c r="R121" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R121" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S121" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T121" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T121" s="3" t="str">
+      <x:c r="U121" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -8981,30 +9344,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L122" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M122" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%A2%86%E5%B9%BC%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%A4%A9%E9%92%A5%E6%A1%A5%E8%B7%AF1057%E5%BC%843%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M122" s="3" t="str">
+      <x:c r="N122" s="3" t="str">
         <x:v>64458520</x:v>
-      </x:c>
-      <x:c r="N122" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O122" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P122" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q122" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q122" s="3" t="str">
+      <x:c r="R122" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R122" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S122" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T122" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T122" s="3" t="str">
+      <x:c r="U122" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -9043,30 +9409,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L123" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M123" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E6%BC%95%E6%B2%B3%E6%B3%BE%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%BC%95%E6%B3%BE%E4%B8%80%E6%9D%9130%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M123" s="3" t="str">
+      <x:c r="N123" s="3" t="str">
         <x:v>64364348</x:v>
-      </x:c>
-      <x:c r="N123" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O123" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P123" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q123" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q123" s="3" t="str">
+      <x:c r="R123" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R123" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S123" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T123" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T123" s="3" t="str">
+      <x:c r="U123" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -9096,39 +9465,42 @@
         <x:v>华泾路995号</x:v>
       </x:c>
       <x:c r="I124" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办凯琴数码幼儿园</x:v>
       </x:c>
       <x:c r="J124" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>华泾路995号</x:v>
       </x:c>
       <x:c r="K124" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.445751,31.117771</x:v>
       </x:c>
       <x:c r="L124" s="3" t="str">
+        <x:v>高德直线约 4.48 km</x:v>
+      </x:c>
+      <x:c r="M124" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%87%AF%E7%90%B4%E6%95%B0%E7%A0%81%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%8D%8E%E6%B3%BE%E8%B7%AF995%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M124" s="3" t="str">
+      <x:c r="N124" s="3" t="str">
         <x:v>54822626</x:v>
-      </x:c>
-      <x:c r="N124" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O124" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P124" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q124" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q124" s="3" t="str">
+      <x:c r="R124" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R124" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S124" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T124" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T124" s="3" t="str">
+      <x:c r="U124" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -9167,30 +9539,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L125" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M125" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E9%99%87%E9%BE%99%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%A2%85%E9%99%87%E5%8D%81%E4%B8%80%E6%9D%9196%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M125" s="3" t="str">
+      <x:c r="N125" s="3" t="str">
         <x:v>64549910</x:v>
-      </x:c>
-      <x:c r="N125" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O125" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P125" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q125" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q125" s="3" t="str">
+      <x:c r="R125" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R125" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S125" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T125" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T125" s="3" t="str">
+      <x:c r="U125" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -9229,30 +9604,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L126" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M126" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E4%B8%96%E8%92%99%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E4%B8%9C%E6%B9%96%E8%B7%AF21%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M126" s="3" t="str">
+      <x:c r="N126" s="3" t="str">
         <x:v>021-54038979</x:v>
-      </x:c>
-      <x:c r="N126" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O126" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P126" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q126" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q126" s="3" t="str">
+      <x:c r="R126" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R126" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S126" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T126" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T126" s="3" t="str">
+      <x:c r="U126" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -9291,30 +9669,33 @@
         <x:v>待高德MCP查询</x:v>
       </x:c>
       <x:c r="L127" s="3" t="str">
+        <x:v>待高德MCP查询</x:v>
+      </x:c>
+      <x:c r="M127" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E8%92%82%E4%BC%8A%E5%B9%BC%E7%A8%9A%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E6%B0%B8%E5%98%89%E8%B7%AF383%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M127" s="3" t="str">
+      <x:c r="N127" s="3" t="str">
         <x:v>64749388</x:v>
-      </x:c>
-      <x:c r="N127" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O127" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P127" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q127" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q127" s="3" t="str">
+      <x:c r="R127" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R127" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S127" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T127" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T127" s="3" t="str">
+      <x:c r="U127" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -9344,39 +9725,42 @@
         <x:v>康健小区虹漕南路百花街18号、6号</x:v>
       </x:c>
       <x:c r="I128" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>上海徐汇区民办吉的堡新汇幼儿园</x:v>
       </x:c>
       <x:c r="J128" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>百花街18号</x:v>
       </x:c>
       <x:c r="K128" s="3" t="str">
-        <x:v>待高德MCP查询</x:v>
+        <x:v>121.412573,31.153868</x:v>
       </x:c>
       <x:c r="L128" s="3" t="str">
+        <x:v>高德直线约 4.43 km</x:v>
+      </x:c>
+      <x:c r="M128" s="3" t="str">
         <x:v>https://ditu.amap.com/search?query=%E4%B8%8A%E6%B5%B7%E5%B8%82%E5%BE%90%E6%B1%87%E5%8C%BA%20%E5%90%89%E7%9A%84%E5%A0%A1%E6%96%B0%E6%B1%87%E5%B9%BC%E5%84%BF%E5%9B%AD%20%E6%9C%AC%E9%83%A8%20%E5%BA%B7%E5%81%A5%E5%B0%8F%E5%8C%BA%E8%99%B9%E6%BC%95%E5%8D%97%E8%B7%AF%E7%99%BE%E8%8A%B1%E8%A1%9718%E5%8F%B7%E3%80%816%E5%8F%B7</x:v>
       </x:c>
-      <x:c r="M128" s="3" t="str">
+      <x:c r="N128" s="3" t="str">
         <x:v>54183331</x:v>
-      </x:c>
-      <x:c r="N128" s="3" t="str">
-        <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="O128" s="3" t="str">
         <x:v>待电话确认</x:v>
       </x:c>
       <x:c r="P128" s="3" t="str">
+        <x:v>待电话确认</x:v>
+      </x:c>
+      <x:c r="Q128" s="3" t="str">
         <x:v>民办招生范围、托班、小班名额、收费和材料要求需电话确认。</x:v>
       </x:c>
-      <x:c r="Q128" s="3" t="str">
+      <x:c r="R128" s="3" t="str">
         <x:v>民办招生</x:v>
       </x:c>
-      <x:c r="R128" s="3" t="str">
-        <x:v>A</x:v>
-      </x:c>
       <x:c r="S128" s="3" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="T128" s="3" t="str">
         <x:v>民办/私立招生条件、收费、名额每年可能变化，报名前必须电话核验。</x:v>
       </x:c>
-      <x:c r="T128" s="3" t="str">
+      <x:c r="U128" s="3" t="str">
         <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
@@ -10039,7 +10423,7 @@
         <x:v>高德MCP接入口径</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
-        <x:v>目标办公点：西岸网易研发中心；上海市徐汇区西岸网易研发中心。待配置AMAP_MAPS_API_KEY后，用关键词搜索/详情搜索/距离测量补齐高德POI、经纬度和距离。</x:v>
+        <x:v>目标办公点：西岸网易研发中心；高德匹配为“网易上海西岸研发中心”。用关键词搜索和距离测量补齐高德POI、经纬度和距离。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">

--- a/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
+++ b/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R0327cee29f8c41f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="Rb502e0a547f24228"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R668be1861abf42ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R105f884346764fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R17a3f3a0e49c4d3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R7287790bb28248c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="R3da8c0f6ebbb4ca1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R9fa1440029174752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="Rfb603b6bf225419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R5c45b33935aa4b0a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -295,7 +295,7 @@
         <x:v>高德增强字段</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
-        <x:v>已接入</x:v>
+        <x:v>101/127</x:v>
       </x:c>
       <x:c r="C6" s="3" t="str">
         <x:v>已批量补POI名称、经纬度和到网易上海西岸研发中心的高德直线距离；低置信匹配保留为待核验。</x:v>

--- a/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
+++ b/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R7287790bb28248c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="R3da8c0f6ebbb4ca1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="R9fa1440029174752"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="Rfb603b6bf225419c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R5c45b33935aa4b0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="Rfb7f32c519f44300"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="Rc1d19fd76cf44df3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="Rc2be6762bca146c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R96fe5e3c6ee44778"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="Rfc2794de94224cc6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10404,65 +10404,129 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="3" t="str">
-        <x:v>公办园部地址主来源</x:v>
+        <x:v>2026招生工作方案</x:v>
       </x:c>
       <x:c r="B4" s="3" t="str">
-        <x:v>上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
+        <x:v>https://sh.bendibao.com/news/2026415/305294.shtm；用于判断户籍优先、外省市户籍排序、录取批次、报名验证和统筹规则。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="str">
-        <x:v>民办/私立地址与电话来源</x:v>
+        <x:v>2026报名材料</x:v>
       </x:c>
       <x:c r="B5" s="3" t="str">
-        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
+        <x:v>https://m.sh.bendibao.com/edu/305384.html；用于核对非沪籍幼儿、父母居住证、租赁合同、居住登记和地址一致性要求。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="str">
-        <x:v>高德MCP接入口径</x:v>
+        <x:v>上海居住证办理条件</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
-        <x:v>目标办公点：西岸网易研发中心；高德匹配为“网易上海西岸研发中心”。用关键词搜索和距离测量补齐高德POI、经纬度和距离。</x:v>
+        <x:v>https://m.sh.bendibao.com/zffw/285087.html；用于确认居住登记、合法稳定住所、租赁合同/备案等材料链要求。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="3" t="str">
-        <x:v>高德检索口径</x:v>
+        <x:v>公办园部地址主来源</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
-        <x:v>表格中的高德链接使用“上海市徐汇区 + 幼儿园名 + 园区名 + 地址”生成，用于逐点打开核验。</x:v>
+        <x:v>上海本地宝《上海市徐汇区公办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://m.sh.bendibao.com/edu/284155.html</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="3" t="str">
-        <x:v>A级</x:v>
+        <x:v>民办/私立地址与电话来源</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
-        <x:v>园部地址在公办园地址清单中明确列出，且无明显冲突。</x:v>
+        <x:v>上海本地宝《上海市徐汇区民办幼儿园名单一览》，内容来源标注为上海学前教育网，2024-03-25：https://sh.bendibao.com/edu/2024325/284155_2.shtm</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="str">
-        <x:v>B级</x:v>
+        <x:v>高德MCP接入口径</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
-        <x:v>公开资料有变更、合并或地址冲突，位置大体可定位，但实际入读园区需电话确认。</x:v>
+        <x:v>目标办公点：西岸网易研发中心；高德匹配为“网易上海西岸研发中心”。用关键词搜索和距离测量补齐高德POI、经纬度和距离。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="3" t="str">
-        <x:v>C级</x:v>
+        <x:v>高德增强落地数据</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
-        <x:v>仅有第三方或地图信息，缺少官方交叉验证。本表目前未使用C级作为主确认。</x:v>
+        <x:v>data/amap_enrichment.json；用于补充POI名称、POI地址、经纬度、距公司直线距离。低置信匹配不写入推荐结论。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="3" t="str">
+        <x:v>高德检索口径</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="str">
+        <x:v>表格中的高德链接使用“上海市徐汇区 + 幼儿园名 + 园区名 + 地址”生成，用于逐点打开核验。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="3" t="str">
+        <x:v>贝壳租房参数</x:v>
+      </x:c>
+      <x:c r="B12" s="3" t="str">
+        <x:v>data/beike_rental_filter_schema.json；用于生成徐汇及二级商圈结构化租房链接，固定token：rt200600000001brp0erp10000l2l3ra4ra5ie1。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="3" t="str">
+        <x:v>贝壳租房口径</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="str">
+        <x:v>https://sh.zu.ke.com/；房源价格和库存实时变化，本页只保存查询条件和入口，不固化具体房源。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="3" t="str">
+        <x:v>办公点参考</x:v>
+      </x:c>
+      <x:c r="B14" s="3" t="str">
+        <x:v>https://www.chooffice.com/1357.html；用于确认西岸网易研发中心靠近龙耀路、徐汇滨江一带。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="3" t="str">
+        <x:v>第三方园所资料</x:v>
+      </x:c>
+      <x:c r="B15" s="3" t="str">
+        <x:v>上哪学、021school、园所公开页面等；用于交叉核对部分民办园电话、收费、托幼一体和地址差异，最终以园所电话确认为准。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="3" t="str">
+        <x:v>A级</x:v>
+      </x:c>
+      <x:c r="B16" s="3" t="str">
+        <x:v>园部地址在公办园地址清单中明确列出，且无明显冲突。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="3" t="str">
+        <x:v>B级</x:v>
+      </x:c>
+      <x:c r="B17" s="3" t="str">
+        <x:v>公开资料有变更、合并或地址冲突，位置大体可定位，但实际入读园区需电话确认。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="3" t="str">
+        <x:v>C级</x:v>
+      </x:c>
+      <x:c r="B18" s="3" t="str">
+        <x:v>仅有第三方或地图信息，缺少官方交叉验证。本表目前未使用C级作为主确认。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="3" t="str">
         <x:v>电话确认重点</x:v>
       </x:c>
-      <x:c r="B11" s="3" t="str">
+      <x:c r="B19" s="3" t="str">
         <x:v>汇星幼儿园北园；复旦大学附属徐汇实验幼儿园；区域内自主招生、扩招园、民办/私立园。</x:v>
       </x:c>
     </x:row>

--- a/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
+++ b/outputs/徐汇区幼儿园园区位置与择园参考.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="Rfb7f32c519f44300"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="Rc1d19fd76cf44df3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="Rc2be6762bca146c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="R96fe5e3c6ee44778"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="Rfc2794de94224cc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="摘要" sheetId="1" r:id="R7cc67c46c7f24172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="招生主体" sheetId="2" r:id="R3953e62910ab425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="园区点位" sheetId="3" r:id="Rc6167b0f7de54ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="片区统计" sheetId="4" r:id="Rc45ae9785eca477f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与核验规则" sheetId="5" r:id="R4d1ebac9885c4e9f"/>
   </x:sheets>
 </x:workbook>
 </file>
